--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1514">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">6.39007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39808225631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2299222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26996088027954</t>
+    <t xml:space="preserve">6.3980827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2699613571167</t>
   </si>
   <si>
     <t xml:space="preserve">6.0937933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92563390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548099517822</t>
+    <t xml:space="preserve">6.12582397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9256329536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548147201538</t>
   </si>
   <si>
     <t xml:space="preserve">5.9456524848938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946594238281</t>
+    <t xml:space="preserve">5.74946546554565</t>
   </si>
   <si>
     <t xml:space="preserve">5.72143983840942</t>
@@ -89,82 +89,82 @@
     <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9977011680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559579849243</t>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559532165527</t>
   </si>
   <si>
     <t xml:space="preserve">5.91762590408325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94164848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00570917129517</t>
+    <t xml:space="preserve">5.94164896011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00570964813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.84956073760986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77749300003052</t>
+    <t xml:space="preserve">5.77749252319336</t>
   </si>
   <si>
     <t xml:space="preserve">6.17386960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14984655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20590019226074</t>
+    <t xml:space="preserve">6.14984607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20589971542358</t>
   </si>
   <si>
     <t xml:space="preserve">6.29398393630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990419387817</t>
+    <t xml:space="preserve">6.22191476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1978931427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990371704102</t>
   </si>
   <si>
     <t xml:space="preserve">6.406090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409826278687</t>
+    <t xml:space="preserve">6.45813989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409778594971</t>
   </si>
   <si>
     <t xml:space="preserve">6.48616647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50218152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388866424561</t>
+    <t xml:space="preserve">6.50218105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388914108276</t>
   </si>
   <si>
     <t xml:space="preserve">6.14183950424194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15385007858276</t>
+    <t xml:space="preserve">6.15385055541992</t>
   </si>
   <si>
     <t xml:space="preserve">6.10980844497681</t>
@@ -173,40 +173,40 @@
     <t xml:space="preserve">6.1138129234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98969411849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01772022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375576019287</t>
+    <t xml:space="preserve">5.98969459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965600967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375480651855</t>
   </si>
   <si>
     <t xml:space="preserve">6.15785455703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09779691696167</t>
+    <t xml:space="preserve">6.09779644012451</t>
   </si>
   <si>
     <t xml:space="preserve">6.18187665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390771865845</t>
   </si>
   <si>
     <t xml:space="preserve">6.03373575210571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1018009185791</t>
+    <t xml:space="preserve">6.10180044174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.01371717453003</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">6.07377433776855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06977033615112</t>
+    <t xml:space="preserve">6.06977081298828</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342565536499</t>
@@ -236,52 +236,52 @@
     <t xml:space="preserve">6.07336568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16030550003052</t>
+    <t xml:space="preserve">6.16030502319336</t>
   </si>
   <si>
     <t xml:space="preserve">6.20998525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09406614303589</t>
+    <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
     <t xml:space="preserve">6.16858530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18928527832031</t>
+    <t xml:space="preserve">6.18928575515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.20170497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890554428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864526748657</t>
+    <t xml:space="preserve">6.11890602111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864431381226</t>
   </si>
   <si>
     <t xml:space="preserve">6.19756507873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1271858215332</t>
+    <t xml:space="preserve">6.12718534469604</t>
   </si>
   <si>
     <t xml:space="preserve">6.13960599899292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11062574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438638687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534521102905</t>
+    <t xml:space="preserve">6.11062622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534616470337</t>
   </si>
   <si>
     <t xml:space="preserve">5.90776634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81254625320435</t>
+    <t xml:space="preserve">5.8125467300415</t>
   </si>
   <si>
     <t xml:space="preserve">5.99470567703247</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">5.96158599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85394668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770589828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222553253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190576553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636638641357</t>
+    <t xml:space="preserve">5.85394716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8622260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636590957642</t>
   </si>
   <si>
     <t xml:space="preserve">6.12304592132568</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">6.10234594345093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26794528961182</t>
+    <t xml:space="preserve">6.26794481277466</t>
   </si>
   <si>
     <t xml:space="preserve">6.156165599823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0319652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820556640625</t>
+    <t xml:space="preserve">6.03196620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820508956909</t>
   </si>
   <si>
     <t xml:space="preserve">6.17686557769775</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">6.25138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13132524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202522277832</t>
+    <t xml:space="preserve">6.13132572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">6.14374542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07750558853149</t>
+    <t xml:space="preserve">6.07750606536865</t>
   </si>
   <si>
     <t xml:space="preserve">6.14788579940796</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">6.10648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98642539978027</t>
+    <t xml:space="preserve">5.98642635345459</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">5.95330619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03610515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744609832764</t>
+    <t xml:space="preserve">6.03610563278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744705200195</t>
   </si>
   <si>
     <t xml:space="preserve">6.00298595428467</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">5.88706636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93260669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84980630874634</t>
+    <t xml:space="preserve">5.93260622024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8249659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8498067855835</t>
   </si>
   <si>
     <t xml:space="preserve">5.85808610916138</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">5.87878608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9201865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06094598770142</t>
+    <t xml:space="preserve">5.92018604278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06094646453857</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
@@ -425,46 +425,46 @@
     <t xml:space="preserve">6.45010471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53290414810181</t>
+    <t xml:space="preserve">6.53290510177612</t>
   </si>
   <si>
     <t xml:space="preserve">6.5494647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45424461364746</t>
+    <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
     <t xml:space="preserve">6.29278516769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45838499069214</t>
+    <t xml:space="preserve">6.4583854675293</t>
   </si>
   <si>
     <t xml:space="preserve">6.38386535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40042495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2348256111145</t>
+    <t xml:space="preserve">6.40042543411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23482513427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.33832550048828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37972497940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40870475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3755841255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34246492385864</t>
+    <t xml:space="preserve">6.37972545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40870571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37558507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806474685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34246397018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.49150466918945</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">6.3714451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30520534515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214515686035</t>
+    <t xml:space="preserve">6.30520486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214468002319</t>
   </si>
   <si>
     <t xml:space="preserve">6.18514537811279</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">5.97400617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01126670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01954507827759</t>
+    <t xml:space="preserve">6.01126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0195460319519</t>
   </si>
   <si>
     <t xml:space="preserve">6.02782583236694</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">6.36730527877808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28450536727905</t>
+    <t xml:space="preserve">6.28450489044189</t>
   </si>
   <si>
     <t xml:space="preserve">6.41284513473511</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.17272520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69850492477417</t>
+    <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194389343262</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03798389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384351730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01314449310303</t>
+    <t xml:space="preserve">6.72334337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990488052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03798341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01314401626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.07938432693481</t>
@@ -551,52 +551,52 @@
     <t xml:space="preserve">7.02142333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05454301834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772218704224</t>
+    <t xml:space="preserve">7.05454397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830318450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772266387939</t>
   </si>
   <si>
     <t xml:space="preserve">7.60102224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688186645508</t>
+    <t xml:space="preserve">7.63414239883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688234329224</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682189941406</t>
+    <t xml:space="preserve">7.30294227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682237625122</t>
   </si>
   <si>
     <t xml:space="preserve">7.48924255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43542194366455</t>
+    <t xml:space="preserve">7.43542146682739</t>
   </si>
   <si>
     <t xml:space="preserve">7.27810287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17046308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94276523590088</t>
+    <t xml:space="preserve">7.17046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94276428222656</t>
   </si>
   <si>
     <t xml:space="preserve">7.07110357284546</t>
@@ -605,91 +605,91 @@
     <t xml:space="preserve">7.05868339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04212379455566</t>
+    <t xml:space="preserve">7.04212331771851</t>
   </si>
   <si>
     <t xml:space="preserve">7.00486421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83512401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95518398284912</t>
+    <t xml:space="preserve">6.83512353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518350601196</t>
   </si>
   <si>
     <t xml:space="preserve">7.01728439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88894319534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378355026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994205474854</t>
+    <t xml:space="preserve">6.88894414901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26982307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306221008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994110107422</t>
   </si>
   <si>
     <t xml:space="preserve">7.64242172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674152374268</t>
+    <t xml:space="preserve">7.69210290908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324068069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674247741699</t>
   </si>
   <si>
     <t xml:space="preserve">8.03158092498779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07297992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356092453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2592830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19304180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48698139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49525928497314</t>
+    <t xml:space="preserve">8.07298183441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356187820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25514030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48698043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36278057098389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39590072631836</t>
+    <t xml:space="preserve">8.39589977264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.43729972839355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62773990631104</t>
+    <t xml:space="preserve">8.62773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">8.63601970672607</t>
@@ -698,37 +698,37 @@
     <t xml:space="preserve">8.59462070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52838039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966041564941</t>
+    <t xml:space="preserve">8.52837944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966136932373</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76662111282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120023727417</t>
+    <t xml:space="preserve">7.76662158966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96120119094849</t>
   </si>
   <si>
     <t xml:space="preserve">8.17648029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51182079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60290050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.776780128479</t>
+    <t xml:space="preserve">8.51181983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6028995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77677917480469</t>
   </si>
   <si>
     <t xml:space="preserve">8.85957908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37293720245361</t>
+    <t xml:space="preserve">9.37293815612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.4474573135376</t>
@@ -737,88 +737,91 @@
     <t xml:space="preserve">10.0850162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.15953540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556943893433</t>
+    <t xml:space="preserve">10.1595363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894550323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556953430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.2920150756836</t>
   </si>
   <si>
+    <t xml:space="preserve">10.3499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5790319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4602603912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.053050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1803045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.078501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7062864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6638679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6129665374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772300720215</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.3499755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5790328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4602613449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615320205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0530500411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.171820640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1803045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0785007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839082717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6638679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6129674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7232532501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6469020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6299333572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384172439575</t>
+    <t xml:space="preserve">10.7232522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6469011306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6299343109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384181976318</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584585189819</t>
+    <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2736234664917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075571060181</t>
+    <t xml:space="preserve">10.3075590133667</t>
   </si>
   <si>
     <t xml:space="preserve">10.0445671081543</t>
@@ -830,13 +833,13 @@
     <t xml:space="preserve">9.83247661590576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78157424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61190319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374824523926</t>
+    <t xml:space="preserve">9.78157520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61190414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374919891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.1028881072998</t>
@@ -851,7 +854,7 @@
     <t xml:space="preserve">9.19620800018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23862552642822</t>
+    <t xml:space="preserve">9.23862648010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.23014259338379</t>
@@ -860,40 +863,40 @@
     <t xml:space="preserve">9.33194637298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317386627197</t>
+    <t xml:space="preserve">9.21317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.37436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825531005859</t>
+    <t xml:space="preserve">9.68825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360832214355</t>
+    <t xml:space="preserve">10.0360841751099</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034580230713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84944248199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2312049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2821073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2905893325806</t>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2312059402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2821063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566576004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
     <t xml:space="preserve">10.366943359375</t>
@@ -902,85 +905,85 @@
     <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0191173553467</t>
+    <t xml:space="preserve">10.0191164016724</t>
   </si>
   <si>
     <t xml:space="preserve">9.96821403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89186191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85792827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74764060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51010036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.89186096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8579273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74763965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51009941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522212982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35739612579346</t>
+    <t xml:space="preserve">9.35739707946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66280555725098</t>
+    <t xml:space="preserve">9.66280460357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.50161743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39132976531982</t>
+    <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
     <t xml:space="preserve">9.28104305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38284683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071506500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645343780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313449859619</t>
+    <t xml:space="preserve">9.38284778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51858329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27256107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313259124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.84096050262451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67977237701416</t>
+    <t xml:space="preserve">9.67977142333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.64583778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63735389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75612354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399272918701</t>
+    <t xml:space="preserve">9.63735294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75612449645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399368286133</t>
   </si>
   <si>
     <t xml:space="preserve">9.77309226989746</t>
@@ -989,7 +992,7 @@
     <t xml:space="preserve">9.79854297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69673824310303</t>
+    <t xml:space="preserve">9.69673919677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.67128849029541</t>
@@ -998,55 +1001,55 @@
     <t xml:space="preserve">9.62887096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79005813598633</t>
+    <t xml:space="preserve">9.79005908966064</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13682270050049</t>
+    <t xml:space="preserve">9.47616577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1368236541748</t>
   </si>
   <si>
     <t xml:space="preserve">9.00108432769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7211275100708</t>
+    <t xml:space="preserve">8.72112655639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32663917541504</t>
+    <t xml:space="preserve">8.07637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182571411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12303352355957</t>
+    <t xml:space="preserve">8.12303447723389</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33088111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34360694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19514560699463</t>
+    <t xml:space="preserve">8.33088207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34360790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37330055236816</t>
+    <t xml:space="preserve">8.37329959869385</t>
   </si>
   <si>
     <t xml:space="preserve">8.31391525268555</t>
@@ -1055,85 +1058,85 @@
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819942474365</t>
+    <t xml:space="preserve">8.09334182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819847106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610750198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065774917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580110549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881364822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02123165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16121006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14848518371582</t>
+    <t xml:space="preserve">7.82610940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094446182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881412506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01274681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16120910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1484842300415</t>
   </si>
   <si>
     <t xml:space="preserve">8.05092430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08061599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22483825683594</t>
+    <t xml:space="preserve">8.08061504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2248363494873</t>
   </si>
   <si>
     <t xml:space="preserve">8.28846454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42420101165771</t>
+    <t xml:space="preserve">8.42420291900635</t>
   </si>
   <si>
     <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7380952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55145454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48358535766602</t>
+    <t xml:space="preserve">8.51752185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5514554977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48358631134033</t>
   </si>
   <si>
     <t xml:space="preserve">8.50055408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325927734375</t>
+    <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.58538913726807</t>
@@ -1142,10 +1145,10 @@
     <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45813465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723419189453</t>
+    <t xml:space="preserve">8.4581356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723514556885</t>
   </si>
   <si>
     <t xml:space="preserve">8.3817834854126</t>
@@ -1157,19 +1160,19 @@
     <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99153900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518545150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12727642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32239818572998</t>
+    <t xml:space="preserve">7.99153804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12727546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97457027435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.90776538848877</t>
@@ -1178,19 +1181,19 @@
     <t xml:space="preserve">8.75506019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77202892303467</t>
+    <t xml:space="preserve">8.82292938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77202796936035</t>
   </si>
   <si>
     <t xml:space="preserve">8.61932373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60235691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83989715576172</t>
+    <t xml:space="preserve">8.60235595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8398962020874</t>
   </si>
   <si>
     <t xml:space="preserve">8.94169998168945</t>
@@ -1208,64 +1211,64 @@
     <t xml:space="preserve">9.11137104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04350280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09440422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26407718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41678142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6723518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.621452331543</t>
+    <t xml:space="preserve">9.0435037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09440517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26407623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41678237915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142381668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705480575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6723508834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6214504241943</t>
   </si>
   <si>
     <t xml:space="preserve">10.9607944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4358739852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.543098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8729000091553</t>
+    <t xml:space="preserve">11.4358730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8729009628296</t>
   </si>
   <si>
     <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4148426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3049068450928</t>
+    <t xml:space="preserve">11.4148416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3049077987671</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
+    <t xml:space="preserve">10.9567832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834915161133</t>
   </si>
   <si>
     <t xml:space="preserve">10.4987230300903</t>
@@ -1274,43 +1277,43 @@
     <t xml:space="preserve">10.7002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6086568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.645302772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4804000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">10.6086578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6453018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589838027954</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0773096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2238864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2605323791504</t>
+    <t xml:space="preserve">10.0773086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2238874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2605314254761</t>
   </si>
   <si>
     <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4071111679077</t>
+    <t xml:space="preserve">10.4071102142334</t>
   </si>
   <si>
     <t xml:space="preserve">10.3154993057251</t>
@@ -1322,55 +1325,55 @@
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2055644989014</t>
+    <t xml:space="preserve">10.20556640625</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80247116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71086120605469</t>
+    <t xml:space="preserve">9.78415107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80247211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65589332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61924839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74750518798828</t>
+    <t xml:space="preserve">9.67421531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65589237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7475061416626</t>
   </si>
   <si>
     <t xml:space="preserve">9.69253826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56428050994873</t>
+    <t xml:space="preserve">9.56428146362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.30776786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2528018951416</t>
+    <t xml:space="preserve">9.25279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">9.36273574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32609081268311</t>
+    <t xml:space="preserve">9.32609176635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.27112293243408</t>
@@ -1388,34 +1391,34 @@
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293132781982</t>
+    <t xml:space="preserve">9.03293228149414</t>
   </si>
   <si>
     <t xml:space="preserve">8.95964241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97796535491943</t>
+    <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.94132137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51990699768066</t>
+    <t xml:space="preserve">8.51990509033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.28171539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92299842834473</t>
+    <t xml:space="preserve">8.92299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.7031307220459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65732383728027</t>
+    <t xml:space="preserve">8.63900184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65732288360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.62983989715576</t>
@@ -1424,25 +1427,25 @@
     <t xml:space="preserve">8.35500431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44661617279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39937973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3810567855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00544834136963</t>
+    <t xml:space="preserve">8.44661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39938068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19783496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00544929504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454414367676</t>
+    <t xml:space="preserve">9.12454319000244</t>
   </si>
   <si>
     <t xml:space="preserve">9.04209327697754</t>
@@ -1451,13 +1454,13 @@
     <t xml:space="preserve">8.96880435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99628639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88635349273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86803245544434</t>
+    <t xml:space="preserve">8.99628829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86803150177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.7855806350708</t>
@@ -1466,10 +1469,10 @@
     <t xml:space="preserve">8.83138561248779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84054756164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7764196395874</t>
+    <t xml:space="preserve">8.84054660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.71229076385498</t>
@@ -1478,85 +1481,82 @@
     <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60235786437988</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3091983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24506950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74120426177979</t>
+    <t xml:space="preserve">8.30919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2450704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7412052154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.70455980300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68623876571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55798149108887</t>
+    <t xml:space="preserve">7.68623828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55798101425171</t>
   </si>
   <si>
     <t xml:space="preserve">7.59462547302246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4938530921936</t>
+    <t xml:space="preserve">7.49385261535645</t>
   </si>
   <si>
     <t xml:space="preserve">7.39307975769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40224123001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10908317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16405010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30146789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31978940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4205641746521</t>
+    <t xml:space="preserve">7.40224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10908222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16404962539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30146741867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31978988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.7686882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720863342285</t>
+    <t xml:space="preserve">7.80533456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720911026001</t>
   </si>
   <si>
     <t xml:space="preserve">7.58546447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727382659912</t>
+    <t xml:space="preserve">7.56714296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727430343628</t>
   </si>
   <si>
     <t xml:space="preserve">7.5121750831604</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14572763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15488910675049</t>
+    <t xml:space="preserve">7.14572811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15488862991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.06327724456787</t>
@@ -1583,31 +1583,31 @@
     <t xml:space="preserve">7.53965854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53049802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29230642318726</t>
+    <t xml:space="preserve">7.5304970741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811235427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29230690002441</t>
   </si>
   <si>
     <t xml:space="preserve">7.2831449508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31062841415405</t>
+    <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
     <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2739839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643434524536</t>
+    <t xml:space="preserve">7.27398443222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643482208252</t>
   </si>
   <si>
     <t xml:space="preserve">7.67707586288452</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">7.72288179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946153640747</t>
+    <t xml:space="preserve">7.86946201324463</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37332725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3916482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49242210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40081024169922</t>
+    <t xml:space="preserve">8.37332630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39164924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49242305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40081119537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.34584331512451</t>
@@ -1643,31 +1643,31 @@
     <t xml:space="preserve">9.02377128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73977375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10622119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05125522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66648483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85887050628662</t>
+    <t xml:space="preserve">9.13370609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73977470397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10622215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05125427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7947416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66648387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">9.01461029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91383647918701</t>
+    <t xml:space="preserve">8.91383743286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467548370361</t>
@@ -1676,28 +1676,28 @@
     <t xml:space="preserve">8.84970855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8039026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81306266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58403301239014</t>
+    <t xml:space="preserve">8.80390357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81306457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58403396606445</t>
   </si>
   <si>
     <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25423049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12597560882568</t>
+    <t xml:space="preserve">8.25423145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.26339244842529</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">8.50158309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42829418182373</t>
+    <t xml:space="preserve">8.42829322814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.46493816375732</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">8.51074504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822708129883</t>
+    <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.62067890167236</t>
@@ -1745,28 +1745,28 @@
     <t xml:space="preserve">8.70226860046387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40219211578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89883375167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06339263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98595333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29571151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435325622559</t>
+    <t xml:space="preserve">8.40219116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923187255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89883327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06339359283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98595285415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.05371189117432</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12147331237793</t>
+    <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627258300781</t>
+    <t xml:space="preserve">7.97627305984497</t>
   </si>
   <si>
     <t xml:space="preserve">7.96659278869629</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">8.16987133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24731159210205</t>
+    <t xml:space="preserve">8.24731254577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.25699043273926</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">8.14083194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92787313461304</t>
+    <t xml:space="preserve">7.92787218093872</t>
   </si>
   <si>
     <t xml:space="preserve">8.07307243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0827522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
+    <t xml:space="preserve">8.08275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.11179161071777</t>
@@ -1838,40 +1838,40 @@
     <t xml:space="preserve">8.16019153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99563312530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0053129196167</t>
+    <t xml:space="preserve">7.99563360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979389190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91819381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95691394805908</t>
+    <t xml:space="preserve">7.8697943687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947463989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91819334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95691299438477</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33442974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28603076934814</t>
+    <t xml:space="preserve">8.33443069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">8.227952003479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45058917999268</t>
+    <t xml:space="preserve">8.45059013366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.5280294418335</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">9.51538372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38954448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48634433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45730495452881</t>
+    <t xml:space="preserve">9.3895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4863452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45730400085449</t>
   </si>
   <si>
     <t xml:space="preserve">9.44762516021729</t>
@@ -1907,43 +1907,43 @@
     <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0284204483032</t>
+    <t xml:space="preserve">9.52506351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0284214019775</t>
   </si>
   <si>
     <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477819442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95098209381104</t>
+    <t xml:space="preserve">10.0477809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0671396255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98970127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95098114013672</t>
   </si>
   <si>
     <t xml:space="preserve">9.60250377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67994213104248</t>
+    <t xml:space="preserve">9.6799430847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71866226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50570297241211</t>
+    <t xml:space="preserve">9.69930362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71866321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.58314323425293</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">9.46698379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87354278564453</t>
+    <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
     <t xml:space="preserve">9.40890407562256</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">9.33146476745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77674293518066</t>
+    <t xml:space="preserve">9.77674198150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.64122295379639</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">9.11850643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08946800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16690731048584</t>
+    <t xml:space="preserve">9.09914588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0894660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19594573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.0797872543335</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">9.10882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9442663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85714721679688</t>
+    <t xml:space="preserve">8.94426727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85714817047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.72162818908691</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93458652496338</t>
+    <t xml:space="preserve">8.9345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266719818115</t>
@@ -2030,67 +2030,67 @@
     <t xml:space="preserve">9.15722560882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05074596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97330665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84075498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60843515396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53099536895752</t>
+    <t xml:space="preserve">9.05074691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97330760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84075403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79235410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60843563079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
     <t xml:space="preserve">7.61811494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34707641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236169815063</t>
+    <t xml:space="preserve">7.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236074447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.44684171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14004898071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47884750366211</t>
+    <t xml:space="preserve">5.14004993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47884798049927</t>
   </si>
   <si>
     <t xml:space="preserve">4.53989362716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64637327194214</t>
+    <t xml:space="preserve">4.64637279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.48181343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52053308486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83997106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13037014007568</t>
+    <t xml:space="preserve">4.5205340385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8399715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13036966323853</t>
   </si>
   <si>
     <t xml:space="preserve">5.51756715774536</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">6.04028415679932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00156450271606</t>
+    <t xml:space="preserve">6.00156497955322</t>
   </si>
   <si>
     <t xml:space="preserve">5.98220443725586</t>
@@ -2114,22 +2114,22 @@
     <t xml:space="preserve">5.96284437179565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99188470840454</t>
+    <t xml:space="preserve">5.9918851852417</t>
   </si>
   <si>
     <t xml:space="preserve">6.15644407272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38876247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46620178222656</t>
+    <t xml:space="preserve">6.38876295089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420263290405</t>
+    <t xml:space="preserve">6.22420358657837</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
@@ -2138,34 +2138,34 @@
     <t xml:space="preserve">6.5339617729187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54364204406738</t>
+    <t xml:space="preserve">6.54364156723022</t>
   </si>
   <si>
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619466781616</t>
+    <t xml:space="preserve">7.67619514465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491479873657</t>
+    <t xml:space="preserve">7.58907508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71491432189941</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3954758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43419551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19219779968262</t>
+    <t xml:space="preserve">7.39547634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43419647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.40515661239624</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">7.44387626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49227619171143</t>
+    <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
     <t xml:space="preserve">7.4632363319397</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">7.32771730422974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56003570556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59875535964966</t>
+    <t xml:space="preserve">7.56003522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5987548828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.65683460235596</t>
@@ -2204,46 +2204,46 @@
     <t xml:space="preserve">7.50195598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30835676193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23091793060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52131605148315</t>
+    <t xml:space="preserve">7.3180365562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30835723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23091745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.521315574646</t>
   </si>
   <si>
     <t xml:space="preserve">7.5406756401062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51163625717163</t>
+    <t xml:space="preserve">7.51163578033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.38579607009888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3373966217041</t>
+    <t xml:space="preserve">7.33739709854126</t>
   </si>
   <si>
     <t xml:space="preserve">7.35675621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45355653762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.45355606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
+    <t xml:space="preserve">7.41483592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867744445801</t>
   </si>
   <si>
     <t xml:space="preserve">7.2599573135376</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">7.47291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68587446212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88915348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74395418167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73427391052246</t>
+    <t xml:space="preserve">7.68587493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7439546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73427438735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.36643695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26963710784912</t>
+    <t xml:space="preserve">7.26963806152344</t>
   </si>
   <si>
     <t xml:space="preserve">7.21155738830566</t>
@@ -2282,19 +2282,19 @@
     <t xml:space="preserve">7.12443828582764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22123765945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70523452758789</t>
+    <t xml:space="preserve">7.22123718261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70523500442505</t>
   </si>
   <si>
     <t xml:space="preserve">7.72459411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48259592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6665153503418</t>
+    <t xml:space="preserve">7.4825963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66651487350464</t>
   </si>
   <si>
     <t xml:space="preserve">7.42451620101929</t>
@@ -2303,37 +2303,37 @@
     <t xml:space="preserve">7.14379835128784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04699802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11475849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17283773422241</t>
+    <t xml:space="preserve">7.04699850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11475801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17283725738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.25027704238892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24059724807739</t>
+    <t xml:space="preserve">7.24059772491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.20187759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18251800537109</t>
+    <t xml:space="preserve">7.18251752853394</t>
   </si>
   <si>
     <t xml:space="preserve">7.13411808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15347814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62779521942139</t>
+    <t xml:space="preserve">7.15347766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62779474258423</t>
   </si>
   <si>
     <t xml:space="preserve">7.02763891220093</t>
@@ -2345,28 +2345,28 @@
     <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96955919265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89211940765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97923898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06635856628418</t>
+    <t xml:space="preserve">6.96955871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89211893081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97923851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06635904312134</t>
   </si>
   <si>
     <t xml:space="preserve">7.0566782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8727593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94051885604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90179920196533</t>
+    <t xml:space="preserve">6.87275981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94051933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90179967880249</t>
   </si>
   <si>
     <t xml:space="preserve">6.82435989379883</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77596044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76628017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564023971558</t>
+    <t xml:space="preserve">6.77595996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76627969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83404016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78563976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.8146800994873</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">6.7953200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75660037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7372407913208</t>
+    <t xml:space="preserve">6.75659990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73724031448364</t>
   </si>
   <si>
     <t xml:space="preserve">6.63076114654541</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067213058472</t>
+    <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174600601196</t>
+    <t xml:space="preserve">7.17201471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174648284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">7.49315023422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395635604858</t>
+    <t xml:space="preserve">7.59046411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5223445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395587921143</t>
   </si>
   <si>
     <t xml:space="preserve">7.70724010467529</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0089111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0964937210083</t>
+    <t xml:space="preserve">8.00891208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09649467468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96998643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89213514328003</t>
+    <t xml:space="preserve">7.9699854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89213562011719</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019540786743</t>
+    <t xml:space="preserve">7.60019493103027</t>
   </si>
   <si>
     <t xml:space="preserve">7.57100105285645</t>
@@ -2507,46 +2507,46 @@
     <t xml:space="preserve">7.73643398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69750833511353</t>
+    <t xml:space="preserve">7.69750881195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64885234832764</t>
+    <t xml:space="preserve">7.82401609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64885187149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992670059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912057876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6293888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56126928329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8434796333313</t>
+    <t xml:space="preserve">7.60992622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912010192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62938928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56126976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84347915649414</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79482269287109</t>
+    <t xml:space="preserve">7.79482221603394</t>
   </si>
   <si>
     <t xml:space="preserve">8.01864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079303741455</t>
+    <t xml:space="preserve">7.94079256057739</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112243652344</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07703304290771</t>
+    <t xml:space="preserve">8.0770320892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977890014648</t>
+    <t xml:space="preserve">8.33977794647217</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74849605560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67064380645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68037605285645</t>
+    <t xml:space="preserve">8.74849510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68037700653076</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">9.04043674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75822830200195</t>
+    <t xml:space="preserve">8.75822734832764</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789794921875</t>
+    <t xml:space="preserve">8.40789890289307</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46628665924072</t>
+    <t xml:space="preserve">8.46628570556641</t>
   </si>
   <si>
     <t xml:space="preserve">8.4565544128418</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23273372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17434597015381</t>
+    <t xml:space="preserve">8.15488243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23273468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17434501647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.14515113830566</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22300148010254</t>
+    <t xml:space="preserve">8.22300243377686</t>
   </si>
   <si>
     <t xml:space="preserve">8.33004760742188</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58306121826172</t>
+    <t xml:space="preserve">8.58306217193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2678,37 +2678,37 @@
     <t xml:space="preserve">8.60252571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83607864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70957088470459</t>
+    <t xml:space="preserve">8.83607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">8.84581089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01124286651611</t>
+    <t xml:space="preserve">9.0112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75082588195801</t>
+    <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3541707992554</t>
+    <t xml:space="preserve">10.3152446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3541717529297</t>
   </si>
   <si>
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028846740723</t>
+    <t xml:space="preserve">9.77028942108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14748191833496</t>
+    <t xml:space="preserve">8.90419769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14748096466064</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05989933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08909320831299</t>
+    <t xml:space="preserve">9.05990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909511566162</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2753,43 +2753,43 @@
     <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93339252471924</t>
+    <t xml:space="preserve">8.93339157104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613838195801</t>
+    <t xml:space="preserve">9.19613742828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62431907653809</t>
+    <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
     <t xml:space="preserve">9.57566165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53673648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82867813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86760330200195</t>
+    <t xml:space="preserve">9.5367374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8286771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86760234832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61458683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59512424468994</t>
+    <t xml:space="preserve">9.67297554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61458778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">9.45888519287109</t>
@@ -2804,31 +2804,31 @@
     <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21560096740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20587062835693</t>
+    <t xml:space="preserve">9.21560192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20586967468262</t>
   </si>
   <si>
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49547958374023</t>
+    <t xml:space="preserve">8.98204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56359958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49548053741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795768737793</t>
+    <t xml:space="preserve">8.76795864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41762924194336</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">8.37870311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71930122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601795196533</t>
+    <t xml:space="preserve">8.7193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39816570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601890563965</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04783821105957</t>
+    <t xml:space="preserve">8.04783916473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500286102295</t>
+    <t xml:space="preserve">8.87500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921459197998</t>
+    <t xml:space="preserve">9.80921363830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51727390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47834777832031</t>
+    <t xml:space="preserve">9.98437976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51727294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47834873199463</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4491548538208</t>
+    <t xml:space="preserve">9.44915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136425018311</t>
+    <t xml:space="preserve">9.73136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038423538208</t>
+    <t xml:space="preserve">10.0038414001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595430374146</t>
@@ -2927,40 +2927,40 @@
     <t xml:space="preserve">10.02330493927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622291564941</t>
+    <t xml:space="preserve">10.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622301101685</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652847290039</t>
+    <t xml:space="preserve">9.90652942657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33237838745117</t>
+    <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.25452613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40049648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48807907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6340503692627</t>
+    <t xml:space="preserve">9.40049743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48808002471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63404941558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347072601318</t>
+    <t xml:space="preserve">10.3347091674805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440841674805</t>
+    <t xml:space="preserve">11.4440832138062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.13267993927</t>
+    <t xml:space="preserve">11.1326789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -3008,37 +3008,37 @@
     <t xml:space="preserve">11.3662328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.638710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668907165527</t>
+    <t xml:space="preserve">11.6387119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668916702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5729217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4756088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1836681365967</t>
+    <t xml:space="preserve">12.572922706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4756078720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1836671829224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970996856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299928665161</t>
+    <t xml:space="preserve">11.6971006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299938201904</t>
   </si>
   <si>
     <t xml:space="preserve">10.8991279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8407392501831</t>
+    <t xml:space="preserve">10.8407402038574</t>
   </si>
   <si>
     <t xml:space="preserve">10.976978302002</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9575147628784</t>
+    <t xml:space="preserve">10.9575157165527</t>
   </si>
   <si>
     <t xml:space="preserve">10.198468208313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132183074951</t>
+    <t xml:space="preserve">10.6071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4709482192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132164001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.91858959198</t>
+    <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">11.2105321884155</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9306526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8528003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8917274475098</t>
+    <t xml:space="preserve">11.9695768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9306516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.852801322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8917264938354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1252784729004</t>
@@ -3116,31 +3116,31 @@
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923833847046</t>
+    <t xml:space="preserve">12.8259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843259811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923843383789</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5145330429077</t>
+    <t xml:space="preserve">12.514533996582</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977565765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4366817474365</t>
+    <t xml:space="preserve">12.4366827011108</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447410583496</t>
+    <t xml:space="preserve">12.1447420120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950704574585</t>
+    <t xml:space="preserve">12.3393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">12.7870121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225923538208</t>
+    <t xml:space="preserve">12.2225933074951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762657165527</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9427137374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1373414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0789518356323</t>
+    <t xml:space="preserve">13.0594902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9427146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1373405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0789527893066</t>
   </si>
   <si>
     <t xml:space="preserve">13.4487447738647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4682064056396</t>
+    <t xml:space="preserve">13.468207359314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3215,22 +3215,22 @@
     <t xml:space="preserve">13.9742374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051042556763</t>
+    <t xml:space="preserve">14.3051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">14.616509437561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7527465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279127120972</t>
+    <t xml:space="preserve">14.7527475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279117584229</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909591674805</t>
+    <t xml:space="preserve">16.9909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4191417694092</t>
+    <t xml:space="preserve">17.5359172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4191398620605</t>
   </si>
   <si>
     <t xml:space="preserve">17.788932800293</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2949638366699</t>
+    <t xml:space="preserve">17.7500076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419502258301</t>
+    <t xml:space="preserve">19.0345458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419483184814</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.547981262207</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060108184814</t>
+    <t xml:space="preserve">19.7060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8519821166992</t>
@@ -3314,37 +3314,37 @@
     <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113830566406</t>
+    <t xml:space="preserve">19.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009929656982</t>
+    <t xml:space="preserve">19.0734748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.898307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009948730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.5090522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8788452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9761581420898</t>
+    <t xml:space="preserve">18.8788433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9761600494385</t>
   </si>
   <si>
     <t xml:space="preserve">18.8593826293945</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4701290130615</t>
+    <t xml:space="preserve">18.4701271057129</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486381530762</t>
+    <t xml:space="preserve">19.2486362457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.84299659729</t>
+    <t xml:space="preserve">19.8429946899414</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567638397217</t>
+    <t xml:space="preserve">22.004114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988109588623</t>
+    <t xml:space="preserve">22.3479270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988128662109</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832740783691</t>
+    <t xml:space="preserve">21.3656024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832759857178</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306224822998</t>
+    <t xml:space="preserve">20.5306243896484</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748081207275</t>
+    <t xml:space="preserve">18.0748062133789</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463218688965</t>
+    <t xml:space="preserve">18.5463237762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569301605225</t>
+    <t xml:space="preserve">17.9569282531738</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836448669434</t>
+    <t xml:space="preserve">17.4854125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836429595947</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6032905578613</t>
+    <t xml:space="preserve">17.60329246521</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388439178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.033540725708</t>
+    <t xml:space="preserve">16.7388458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0335426330566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3581,34 +3581,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673282623291</t>
+    <t xml:space="preserve">16.2673263549805</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547487258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.345911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869720458984</t>
+    <t xml:space="preserve">15.8547496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905055999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3459129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869739532471</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154563903809</t>
+    <t xml:space="preserve">15.6189908981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154573440552</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794931411743</t>
+    <t xml:space="preserve">14.4794921875</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3629,37 +3629,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563119888306</t>
+    <t xml:space="preserve">14.9903020858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563110351562</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580787658691</t>
+    <t xml:space="preserve">14.5580778121948</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956043243408</t>
+    <t xml:space="preserve">14.4991397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956052780151</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527774810791</t>
+    <t xml:space="preserve">14.8527765274048</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958106994629</t>
+    <t xml:space="preserve">15.7958097457886</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653532028198</t>
+    <t xml:space="preserve">15.2653541564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567218780518</t>
+    <t xml:space="preserve">16.8567237854004</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370761871338</t>
+    <t xml:space="preserve">16.8370742797852</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549560546875</t>
+    <t xml:space="preserve">16.9549541473389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514186859131</t>
+    <t xml:space="preserve">17.1514205932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247039794922</t>
+    <t xml:space="preserve">17.5247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465282440186</t>
+    <t xml:space="preserve">19.6465301513672</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697113037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838512420654</t>
+    <t xml:space="preserve">19.4697093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838493347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359256744385</t>
+    <t xml:space="preserve">20.0394611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359275817871</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779708862305</t>
+    <t xml:space="preserve">20.6779727935791</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005805969238</t>
+    <t xml:space="preserve">22.2005786895752</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532321929932</t>
+    <t xml:space="preserve">22.0532302856445</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -4551,6 +4551,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1500015258789</t>
   </si>
 </sst>
 </file>
@@ -14397,7 +14400,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14423,7 +14426,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14449,7 +14452,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14475,7 +14478,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14501,7 +14504,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G370" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14527,7 +14530,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14553,7 +14556,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14605,7 +14608,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14631,7 +14634,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G375" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14683,7 +14686,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14709,7 +14712,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14735,7 +14738,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14761,7 +14764,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14787,7 +14790,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14813,7 +14816,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G382" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14839,7 +14842,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14865,7 +14868,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14891,7 +14894,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14917,7 +14920,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14943,7 +14946,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14969,7 +14972,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14995,7 +14998,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15021,7 +15024,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15047,7 +15050,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15073,7 +15076,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15099,7 +15102,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15125,7 +15128,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15151,7 +15154,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15177,7 +15180,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15203,7 +15206,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15229,7 +15232,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15255,7 +15258,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G399" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15281,7 +15284,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15307,7 +15310,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G401" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15359,7 +15362,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15385,7 +15388,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G404" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15411,7 +15414,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15437,7 +15440,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15463,7 +15466,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G407" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15489,7 +15492,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15541,7 +15544,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15567,7 +15570,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15593,7 +15596,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G412" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15619,7 +15622,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G413" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15645,7 +15648,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15671,7 +15674,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15697,7 +15700,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15723,7 +15726,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15775,7 +15778,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G419" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15801,7 +15804,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15827,7 +15830,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15853,7 +15856,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G422" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15879,7 +15882,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G423" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15905,7 +15908,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15931,7 +15934,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G425" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15957,7 +15960,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G426" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15983,7 +15986,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16009,7 +16012,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G428" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16035,7 +16038,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G429" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16061,7 +16064,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16087,7 +16090,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16113,7 +16116,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G432" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16139,7 +16142,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G433" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16165,7 +16168,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16191,7 +16194,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G435" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16217,7 +16220,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G436" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16243,7 +16246,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G437" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16269,7 +16272,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16295,7 +16298,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16321,7 +16324,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G440" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16347,7 +16350,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16373,7 +16376,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16399,7 +16402,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16425,7 +16428,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16451,7 +16454,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16477,7 +16480,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16503,7 +16506,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G447" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16529,7 +16532,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16581,7 +16584,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16607,7 +16610,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16633,7 +16636,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16659,7 +16662,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G453" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16685,7 +16688,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G454" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16711,7 +16714,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G455" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16737,7 +16740,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G456" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16763,7 +16766,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G457" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16789,7 +16792,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16815,7 +16818,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G459" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16841,7 +16844,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16867,7 +16870,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16893,7 +16896,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G462" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16919,7 +16922,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G463" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16945,7 +16948,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16971,7 +16974,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -16997,7 +17000,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G466" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17023,7 +17026,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G467" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17049,7 +17052,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G468" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17075,7 +17078,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17101,7 +17104,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17127,7 +17130,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G471" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17153,7 +17156,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G472" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17179,7 +17182,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G473" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17205,7 +17208,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G474" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17231,7 +17234,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17257,7 +17260,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17283,7 +17286,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17309,7 +17312,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17335,7 +17338,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G479" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17361,7 +17364,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G480" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17387,7 +17390,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G481" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17413,7 +17416,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G482" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17439,7 +17442,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17465,7 +17468,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G484" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17491,7 +17494,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G485" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17517,7 +17520,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G486" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17543,7 +17546,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G487" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17569,7 +17572,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G488" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17595,7 +17598,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17621,7 +17624,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G490" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17647,7 +17650,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17673,7 +17676,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G492" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17699,7 +17702,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17725,7 +17728,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G494" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17751,7 +17754,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17777,7 +17780,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G496" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17803,7 +17806,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17829,7 +17832,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17855,7 +17858,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G499" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17881,7 +17884,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G500" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17907,7 +17910,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G501" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17933,7 +17936,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G502" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17959,7 +17962,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17985,7 +17988,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18011,7 +18014,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18037,7 +18040,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18063,7 +18066,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G507" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18089,7 +18092,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18115,7 +18118,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G509" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18141,7 +18144,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G510" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18167,7 +18170,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G511" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18193,7 +18196,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G512" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18219,7 +18222,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G513" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18245,7 +18248,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18271,7 +18274,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18297,7 +18300,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G516" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18323,7 +18326,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G517" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18349,7 +18352,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18375,7 +18378,7 @@
         <v>10</v>
       </c>
       <c r="G519" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18401,7 +18404,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18427,7 +18430,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G521" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18453,7 +18456,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G522" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18479,7 +18482,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G523" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18505,7 +18508,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G524" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18531,7 +18534,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G525" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18557,7 +18560,7 @@
         <v>10</v>
       </c>
       <c r="G526" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18583,7 +18586,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G527" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18609,7 +18612,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G528" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18635,7 +18638,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G529" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18661,7 +18664,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G530" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18687,7 +18690,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G531" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18713,7 +18716,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18739,7 +18742,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18765,7 +18768,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G534" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18791,7 +18794,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18817,7 +18820,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18843,7 +18846,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G537" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18869,7 +18872,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18895,7 +18898,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G539" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18921,7 +18924,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G540" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18947,7 +18950,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G541" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18973,7 +18976,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -18999,7 +19002,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G543" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19025,7 +19028,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G544" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19051,7 +19054,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G545" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19077,7 +19080,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G546" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19103,7 +19106,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G547" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19129,7 +19132,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19155,7 +19158,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G549" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19181,7 +19184,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G550" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19207,7 +19210,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19233,7 +19236,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G552" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19259,7 +19262,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G553" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19285,7 +19288,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G554" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19311,7 +19314,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19337,7 +19340,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G556" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19363,7 +19366,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G557" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19389,7 +19392,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19415,7 +19418,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19441,7 +19444,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19467,7 +19470,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G561" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19493,7 +19496,7 @@
         <v>11</v>
       </c>
       <c r="G562" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19519,7 +19522,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19545,7 +19548,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19571,7 +19574,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G565" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19597,7 +19600,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19623,7 +19626,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19649,7 +19652,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G568" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19675,7 +19678,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G569" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19701,7 +19704,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19727,7 +19730,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19753,7 +19756,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G572" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19779,7 +19782,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19805,7 +19808,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19831,7 +19834,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19857,7 +19860,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G576" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19883,7 +19886,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G577" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19909,7 +19912,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19935,7 +19938,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19961,7 +19964,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G580" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19987,7 +19990,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G581" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20013,7 +20016,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20039,7 +20042,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20065,7 +20068,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20091,7 +20094,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20117,7 +20120,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G586" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20143,7 +20146,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20169,7 +20172,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G588" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20195,7 +20198,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G589" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20221,7 +20224,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20247,7 +20250,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G591" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20273,7 +20276,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G592" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20299,7 +20302,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G593" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20325,7 +20328,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G594" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20351,7 +20354,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G595" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20377,7 +20380,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G596" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20403,7 +20406,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G597" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20429,7 +20432,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G598" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20455,7 +20458,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20481,7 +20484,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20507,7 +20510,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G601" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20533,7 +20536,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20559,7 +20562,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G603" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20585,7 +20588,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G604" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20611,7 +20614,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G605" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20637,7 +20640,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20663,7 +20666,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G607" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20689,7 +20692,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20715,7 +20718,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G609" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20741,7 +20744,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G610" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20767,7 +20770,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G611" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20793,7 +20796,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G612" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20819,7 +20822,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20845,7 +20848,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20871,7 +20874,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G615" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20897,7 +20900,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G616" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20923,7 +20926,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G617" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20949,7 +20952,7 @@
         <v>11</v>
       </c>
       <c r="G618" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20975,7 +20978,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G619" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21001,7 +21004,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21027,7 +21030,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G621" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21053,7 +21056,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21079,7 +21082,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G623" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21105,7 +21108,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G624" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21131,7 +21134,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21157,7 +21160,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G626" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21183,7 +21186,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G627" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21209,7 +21212,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G628" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21235,7 +21238,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G629" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21261,7 +21264,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G630" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21287,7 +21290,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G631" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21313,7 +21316,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21339,7 +21342,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21365,7 +21368,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G634" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21391,7 +21394,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G635" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21417,7 +21420,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G636" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21443,7 +21446,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G637" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21469,7 +21472,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G638" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21495,7 +21498,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G639" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21521,7 +21524,7 @@
         <v>10.5</v>
       </c>
       <c r="G640" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21547,7 +21550,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G641" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21573,7 +21576,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G642" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21599,7 +21602,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21625,7 +21628,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G644" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21651,7 +21654,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G645" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21677,7 +21680,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21703,7 +21706,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21729,7 +21732,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21755,7 +21758,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G649" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21781,7 +21784,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G650" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21807,7 +21810,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21833,7 +21836,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G652" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21859,7 +21862,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21885,7 +21888,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G654" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21911,7 +21914,7 @@
         <v>9.75</v>
       </c>
       <c r="G655" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21937,7 +21940,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21963,7 +21966,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G657" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -21989,7 +21992,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22015,7 +22018,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22041,7 +22044,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G660" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22067,7 +22070,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G661" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22093,7 +22096,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G662" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22119,7 +22122,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22145,7 +22148,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G664" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22171,7 +22174,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G665" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22197,7 +22200,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G666" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22223,7 +22226,7 @@
         <v>9.5</v>
       </c>
       <c r="G667" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22249,7 +22252,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22275,7 +22278,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22301,7 +22304,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22327,7 +22330,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22353,7 +22356,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G672" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22379,7 +22382,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G673" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22405,7 +22408,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G674" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22431,7 +22434,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22457,7 +22460,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G676" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22483,7 +22486,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G677" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22509,7 +22512,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G678" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22535,7 +22538,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G679" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22561,7 +22564,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G680" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22587,7 +22590,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22613,7 +22616,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22639,7 +22642,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22665,7 +22668,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G684" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22691,7 +22694,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G685" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22717,7 +22720,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G686" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22743,7 +22746,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G687" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22769,7 +22772,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22795,7 +22798,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22821,7 +22824,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G690" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22847,7 +22850,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G691" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22873,7 +22876,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22899,7 +22902,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G693" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22925,7 +22928,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G694" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22951,7 +22954,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G695" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22977,7 +22980,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23003,7 +23006,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G697" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23029,7 +23032,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G698" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23055,7 +23058,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G699" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23081,7 +23084,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G700" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23107,7 +23110,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G701" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23133,7 +23136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23159,7 +23162,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G703" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23185,7 +23188,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23211,7 +23214,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G705" t="s">
-        <v>488</v>
+        <v>392</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23263,7 +23266,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24849,7 +24852,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25083,7 +25086,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G777" t="s">
-        <v>488</v>
+        <v>392</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25109,7 +25112,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G778" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25135,7 +25138,7 @@
         <v>9.5</v>
       </c>
       <c r="G779" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25161,7 +25164,7 @@
         <v>9.75</v>
       </c>
       <c r="G780" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25187,7 +25190,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G781" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25265,7 +25268,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G784" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25317,7 +25320,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G786" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25395,7 +25398,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25447,7 +25450,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G791" t="s">
-        <v>488</v>
+        <v>392</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25499,7 +25502,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25551,7 +25554,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25577,7 +25580,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G796" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25629,7 +25632,7 @@
         <v>9.75</v>
       </c>
       <c r="G798" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25681,7 +25684,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G800" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25707,7 +25710,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G801" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25733,7 +25736,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25863,7 +25866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G807" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25915,7 +25918,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25941,7 +25944,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G810" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26149,7 +26152,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G818" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26305,7 +26308,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26461,7 +26464,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26799,7 +26802,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G843" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26851,7 +26854,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G845" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -69577,7 +69580,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.649525463</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>41986</v>
@@ -69598,6 +69601,32 @@
         <v>1512</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.649525463</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>27227</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>32.2000007629395</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>32.1500015258789</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="1518">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,262 +47,262 @@
     <t xml:space="preserve">6.39007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39808225631714</t>
+    <t xml:space="preserve">6.3980827331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.22992277145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2699613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0937933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582397460938</t>
+    <t xml:space="preserve">6.26996088027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09379386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563390731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9456524848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143888473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7254433631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99770212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762590408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00570917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84956121444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17386913299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20589971542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29398393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.406090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23793077468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183855056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980892181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1138129234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98969459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15785360336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09779691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18187665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373575210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1018009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371717453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766305923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11781644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07377433776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06976985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19342565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22654581069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1603045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16858530044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18928527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170593261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11890506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19756555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1271858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776586532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8125467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470567703247</t>
   </si>
   <si>
     <t xml:space="preserve">6.08578586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92563343048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356473922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94565296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946546554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7254433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74145841598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99770212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00570964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84956121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386960983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20589971542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29398393630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789171218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.406090259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417352676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2379298210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15385055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1138129234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965553283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1578540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09779644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1018009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371669769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764448165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11781692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06976985931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19342517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2265453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16858530044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18928527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19756555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12718534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13960552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776586532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81254577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0402455329895</t>
+    <t xml:space="preserve">6.04024648666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.961585521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394620895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770589828491</t>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394668579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770637512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.8622260093689</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">5.91190576553345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540613174438</t>
+    <t xml:space="preserve">5.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540565490723</t>
   </si>
   <si>
     <t xml:space="preserve">6.10234498977661</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">6.156165599823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03196620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820556640625</t>
+    <t xml:space="preserve">6.03196573257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820508956909</t>
   </si>
   <si>
     <t xml:space="preserve">6.1768651008606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25138568878174</t>
+    <t xml:space="preserve">6.25138521194458</t>
   </si>
   <si>
     <t xml:space="preserve">6.13132524490356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15202474594116</t>
+    <t xml:space="preserve">6.15202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">6.14374589920044</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">6.07750558853149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14788627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0692253112793</t>
+    <t xml:space="preserve">6.14788579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266571044922</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">5.9698657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642587661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92432594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95330572128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03610563278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298595428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668663024902</t>
+    <t xml:space="preserve">6.10648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92432641983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95330619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361065864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298547744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93260622024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668615341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.84980630874634</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">5.75872659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90362596511841</t>
+    <t xml:space="preserve">5.90362644195557</t>
   </si>
   <si>
     <t xml:space="preserve">5.93674612045288</t>
@@ -419,82 +419,82 @@
     <t xml:space="preserve">5.92018604278564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06094551086426</t>
+    <t xml:space="preserve">6.06094598770142</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45010471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
+    <t xml:space="preserve">6.4501051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290510177612</t>
   </si>
   <si>
     <t xml:space="preserve">6.5494647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45424556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29278612136841</t>
+    <t xml:space="preserve">6.45424509048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29278516769409</t>
   </si>
   <si>
     <t xml:space="preserve">6.45838499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38386535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042543411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23482608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33832597732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972450256348</t>
+    <t xml:space="preserve">6.38386487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2348256111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
+    <t xml:space="preserve">6.37558507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
   </si>
   <si>
     <t xml:space="preserve">6.34246492385864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49150562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33418560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3714451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30520439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18514537811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97400617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01954555511475</t>
+    <t xml:space="preserve">6.49150466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33418464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30520486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214468002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18514490127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97400569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01126670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0195460319519</t>
   </si>
   <si>
     <t xml:space="preserve">6.02782583236694</t>
@@ -503,49 +503,49 @@
     <t xml:space="preserve">6.32590532302856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730575561523</t>
+    <t xml:space="preserve">6.36730432510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.28450536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41284513473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24310541152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69850492477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.41284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2431058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69850444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194437026978</t>
   </si>
   <si>
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990488052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874336242676</t>
+    <t xml:space="preserve">6.72334337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03798294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874383926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384304046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01314353942871</t>
+    <t xml:space="preserve">7.01314401626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.0793833732605</t>
@@ -557,64 +557,64 @@
     <t xml:space="preserve">7.05454397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6010217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414287567139</t>
+    <t xml:space="preserve">6.98830318450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772361755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414335250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.59688186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0876636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682237625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810287475586</t>
+    <t xml:space="preserve">7.08766412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48924207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2781023979187</t>
   </si>
   <si>
     <t xml:space="preserve">7.17046308517456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10422277450562</t>
+    <t xml:space="preserve">7.10422420501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.94276475906372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0711030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212379455566</t>
+    <t xml:space="preserve">7.07110357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212284088135</t>
   </si>
   <si>
     <t xml:space="preserve">7.00486373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83512449264526</t>
+    <t xml:space="preserve">6.83512401580811</t>
   </si>
   <si>
     <t xml:space="preserve">6.95518350601196</t>
@@ -623,31 +623,31 @@
     <t xml:space="preserve">7.01728391647339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88894319534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64242029190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210147857666</t>
+    <t xml:space="preserve">6.88894367218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26982307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306221008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64242172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6921010017395</t>
   </si>
   <si>
     <t xml:space="preserve">7.65898132324219</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">7.9032416343689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00674152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158092498779</t>
+    <t xml:space="preserve">8.00674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03158187866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.0729808807373</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">8.19304084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25514030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49526119232178</t>
+    <t xml:space="preserve">8.25513935089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48698043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36278057098389</t>
@@ -689,52 +689,52 @@
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43729972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62774085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59461975097656</t>
+    <t xml:space="preserve">8.43730068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62773990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63602066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5946216583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.52838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32966136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03986072540283</t>
+    <t xml:space="preserve">8.32966041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03986167907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96120166778564</t>
+    <t xml:space="preserve">7.96120023727417</t>
   </si>
   <si>
     <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51181983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6028995513916</t>
+    <t xml:space="preserve">8.51181888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60290050506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.776780128479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85957908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37293815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44745826721191</t>
+    <t xml:space="preserve">8.85957813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37293910980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4474573135376</t>
   </si>
   <si>
     <t xml:space="preserve">10.0850162506104</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">10.6894540786743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7556943893433</t>
+    <t xml:space="preserve">10.7556953430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499774932861</t>
+    <t xml:space="preserve">10.3499755859375</t>
   </si>
   <si>
     <t xml:space="preserve">10.5790328979492</t>
@@ -764,58 +764,55 @@
     <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0530500411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1718215942383</t>
+    <t xml:space="preserve">9.87489604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0530490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1718196868896</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0785007476807</t>
+    <t xml:space="preserve">10.0784997940063</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839101791382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7062854766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6638679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6129655838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3499755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7232542037964</t>
+    <t xml:space="preserve">10.7062864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6638669967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7232532501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.6469011306763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6299343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4178438186646</t>
+    <t xml:space="preserve">10.6299333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384172439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4178447723389</t>
   </si>
   <si>
     <t xml:space="preserve">10.3584594726562</t>
@@ -824,184 +821,184 @@
     <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075571060181</t>
+    <t xml:space="preserve">10.3075580596924</t>
   </si>
   <si>
     <t xml:space="preserve">10.04456615448</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90882873535156</t>
+    <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.83247661590576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78157520294189</t>
+    <t xml:space="preserve">9.78157615661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.61190414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43374824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10288715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16227340698242</t>
+    <t xml:space="preserve">9.43374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1028881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16227436065674</t>
   </si>
   <si>
     <t xml:space="preserve">9.17924022674561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19620800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23862648010254</t>
+    <t xml:space="preserve">9.19620895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23862552642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.23014259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33194637298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37436294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90034580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2312059402466</t>
+    <t xml:space="preserve">9.33194541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37436389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90034484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2312049865723</t>
   </si>
   <si>
     <t xml:space="preserve">10.2821073532104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2566556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3669424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2057552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0191173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9682149887085</t>
+    <t xml:space="preserve">10.2566566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2905902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2057542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.019115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821403503418</t>
   </si>
   <si>
     <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85792827606201</t>
+    <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
     <t xml:space="preserve">9.74764156341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51010131835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919895172119</t>
+    <t xml:space="preserve">9.51010036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522212982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919799804688</t>
   </si>
   <si>
     <t xml:space="preserve">9.35739612579346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161552429199</t>
+    <t xml:space="preserve">9.50161743164062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071697235107</t>
+    <t xml:space="preserve">9.28104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071506500244</t>
   </si>
   <si>
     <t xml:space="preserve">9.51858425140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27256107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20468997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8409595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735294342041</t>
+    <t xml:space="preserve">9.27255916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
     <t xml:space="preserve">9.75612449645996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82399368286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69674015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67128944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62887096405029</t>
+    <t xml:space="preserve">9.82399463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69673919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67128849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62887191772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.79005908966064</t>
@@ -1013,10 +1010,10 @@
     <t xml:space="preserve">9.47616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13682270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108528137207</t>
+    <t xml:space="preserve">9.1368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108432769775</t>
   </si>
   <si>
     <t xml:space="preserve">8.72112655639648</t>
@@ -1028,25 +1025,25 @@
     <t xml:space="preserve">8.07637405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32663917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10182476043701</t>
+    <t xml:space="preserve">8.32664012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10182571411133</t>
   </si>
   <si>
     <t xml:space="preserve">8.12303352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62780666351318</t>
+    <t xml:space="preserve">8.62780857086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.33088207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19514465332031</t>
+    <t xml:space="preserve">8.34360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19514560699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
@@ -1055,31 +1052,31 @@
     <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31391620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29270553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819847106934</t>
+    <t xml:space="preserve">8.31391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29270458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09334087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819942474365</t>
   </si>
   <si>
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610845565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580158233643</t>
+    <t xml:space="preserve">7.82610940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094350814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580110549927</t>
   </si>
   <si>
     <t xml:space="preserve">7.95760440826416</t>
@@ -1088,16 +1085,16 @@
     <t xml:space="preserve">7.97881364822388</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02123069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01274681091309</t>
+    <t xml:space="preserve">8.02123165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0127477645874</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16121006011963</t>
+    <t xml:space="preserve">8.16121101379395</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484842300415</t>
@@ -1106,19 +1103,19 @@
     <t xml:space="preserve">8.05092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08061504364014</t>
+    <t xml:space="preserve">8.08061599731445</t>
   </si>
   <si>
     <t xml:space="preserve">8.17393589019775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2248363494873</t>
+    <t xml:space="preserve">8.22483730316162</t>
   </si>
   <si>
     <t xml:space="preserve">8.28846454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42420101165771</t>
+    <t xml:space="preserve">8.42420196533203</t>
   </si>
   <si>
     <t xml:space="preserve">8.56842231750488</t>
@@ -1127,40 +1124,40 @@
     <t xml:space="preserve">8.51752090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73809432983398</t>
+    <t xml:space="preserve">8.7380952835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48358535766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50055503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58538913726807</t>
+    <t xml:space="preserve">8.48358631134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50055313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58539009094238</t>
   </si>
   <si>
     <t xml:space="preserve">8.46661853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38178253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01698970794678</t>
+    <t xml:space="preserve">8.45813465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38178443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.99153900146484</t>
@@ -1172,22 +1169,22 @@
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32239818572998</t>
+    <t xml:space="preserve">7.97457075119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.90776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75506019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82292938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77202987670898</t>
+    <t xml:space="preserve">8.75506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82293033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
     <t xml:space="preserve">8.61932373046875</t>
@@ -1196,22 +1193,22 @@
     <t xml:space="preserve">8.60235691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83989810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94169998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36588001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24710941314697</t>
+    <t xml:space="preserve">8.83989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94169902801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24710845947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11137199401855</t>
+    <t xml:space="preserve">9.11137104034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.0435037612915</t>
@@ -1223,10 +1220,10 @@
     <t xml:space="preserve">9.26407623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142381668091</t>
+    <t xml:space="preserve">9.41678142547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142391204834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705480575562</t>
@@ -1238,13 +1235,13 @@
     <t xml:space="preserve">10.6214513778687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9607934951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4358749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680057525635</t>
+    <t xml:space="preserve">10.9607944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4358739852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680067062378</t>
   </si>
   <si>
     <t xml:space="preserve">11.4698085784912</t>
@@ -1253,70 +1250,70 @@
     <t xml:space="preserve">11.543098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8729000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.836256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4148416519165</t>
+    <t xml:space="preserve">11.8729009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8362560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4148406982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.3049077987671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.286584854126</t>
+    <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9567823410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834934234619</t>
+    <t xml:space="preserve">10.8834924697876</t>
   </si>
   <si>
     <t xml:space="preserve">10.4987230300903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7002687454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6086568832397</t>
+    <t xml:space="preserve">10.7002696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6086578369141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4804010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689214706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040187835693</t>
+    <t xml:space="preserve">10.4803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.004017829895</t>
   </si>
   <si>
     <t xml:space="preserve">9.98569583892822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0589847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0773086547852</t>
+    <t xml:space="preserve">10.058985710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0773096084595</t>
   </si>
   <si>
     <t xml:space="preserve">10.2238864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1322736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071092605591</t>
+    <t xml:space="preserve">10.2605323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1322755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071111679077</t>
   </si>
   <si>
     <t xml:space="preserve">10.3154993057251</t>
@@ -1328,10 +1325,10 @@
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2055654525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.095630645752</t>
+    <t xml:space="preserve">10.2055644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0956315994263</t>
   </si>
   <si>
     <t xml:space="preserve">9.78415012359619</t>
@@ -1340,85 +1337,85 @@
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.710862159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266960144043</t>
+    <t xml:space="preserve">9.71086120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47267055511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.67421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72918224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65589237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61924839019775</t>
+    <t xml:space="preserve">9.72918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61924743652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253826141357</t>
+    <t xml:space="preserve">9.69253730773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.56428146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30776882171631</t>
+    <t xml:space="preserve">9.30776786804199</t>
   </si>
   <si>
     <t xml:space="preserve">9.25280094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3627347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32608985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711238861084</t>
+    <t xml:space="preserve">9.36273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27112293243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.06957626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93215847015381</t>
+    <t xml:space="preserve">9.08789920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93216037750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95964336395264</t>
+    <t xml:space="preserve">9.03293228149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964241027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94132041931152</t>
+    <t xml:space="preserve">8.94132137298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.51990604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28171443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92299747467041</t>
+    <t xml:space="preserve">8.28171539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92299842834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70312976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900184631348</t>
+    <t xml:space="preserve">8.63900089263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.65732288360596</t>
@@ -1427,28 +1424,28 @@
     <t xml:space="preserve">8.62983989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35500335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44661617279053</t>
+    <t xml:space="preserve">8.35500431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.39937973022461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3810567855835</t>
+    <t xml:space="preserve">9.38105773925781</t>
   </si>
   <si>
     <t xml:space="preserve">9.19783401489258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00544929504395</t>
+    <t xml:space="preserve">9.00544834136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454509735107</t>
+    <t xml:space="preserve">9.12454414367676</t>
   </si>
   <si>
     <t xml:space="preserve">9.04209423065186</t>
@@ -1463,13 +1460,13 @@
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86803150177002</t>
+    <t xml:space="preserve">8.86803245544434</t>
   </si>
   <si>
     <t xml:space="preserve">8.78557968139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83138656616211</t>
+    <t xml:space="preserve">8.83138561248779</t>
   </si>
   <si>
     <t xml:space="preserve">8.84054660797119</t>
@@ -1478,19 +1475,22 @@
     <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7122917175293</t>
+    <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.59319496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40997219085693</t>
+    <t xml:space="preserve">8.60235595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.3091983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24507141113281</t>
+    <t xml:space="preserve">8.2450704574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.7412052154541</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">7.68623781204224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55798053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462594985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4938530921936</t>
+    <t xml:space="preserve">7.55798101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462547302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49385261535645</t>
   </si>
   <si>
     <t xml:space="preserve">7.39307928085327</t>
@@ -1520,43 +1520,43 @@
     <t xml:space="preserve">7.08159923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10908317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391923904419</t>
+    <t xml:space="preserve">7.10908269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391828536987</t>
   </si>
   <si>
     <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30146741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31978940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42056322097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76868772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539833068848</t>
+    <t xml:space="preserve">7.3014669418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31978988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42056274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7686882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539880752563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45720815658569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5854640007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714248657227</t>
+    <t xml:space="preserve">7.58546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714296340942</t>
   </si>
   <si>
     <t xml:space="preserve">7.34727382659912</t>
@@ -1565,61 +1565,61 @@
     <t xml:space="preserve">7.51217460632324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22817802429199</t>
+    <t xml:space="preserve">7.22817850112915</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05411577224731</t>
   </si>
   <si>
     <t xml:space="preserve">7.43888473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53965854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29230690002441</t>
+    <t xml:space="preserve">7.53965759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5304970741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47552967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811235427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29230642318726</t>
   </si>
   <si>
     <t xml:space="preserve">7.2831449508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31062889099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24650096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2739839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707681655884</t>
+    <t xml:space="preserve">7.31062841415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24650049209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27398490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707586288452</t>
   </si>
   <si>
     <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946105957031</t>
+    <t xml:space="preserve">7.86946153640747</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352283477783</t>
@@ -1637,37 +1637,37 @@
     <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3458423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33668231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02377128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13370609283447</t>
+    <t xml:space="preserve">8.34584331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33668327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02377223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10622119903564</t>
+    <t xml:space="preserve">9.10622215270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.05125522613525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7947416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66648578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8588695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01461029052734</t>
+    <t xml:space="preserve">8.79474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66648483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85887050628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01460933685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.91383743286133</t>
@@ -1679,34 +1679,34 @@
     <t xml:space="preserve">8.84970855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80390167236328</t>
+    <t xml:space="preserve">8.8039026260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.813063621521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58403396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68480682373047</t>
+    <t xml:space="preserve">8.58403301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
     <t xml:space="preserve">8.25423145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255344390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12597370147705</t>
+    <t xml:space="preserve">8.38248825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255439758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23591041564941</t>
+    <t xml:space="preserve">8.23590755462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.43745517730713</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">8.47410011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.50158500671387</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829418182373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46493816375732</t>
+    <t xml:space="preserve">8.46493911743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.51074504852295</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">8.53822708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62067794799805</t>
+    <t xml:space="preserve">8.62067890167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.61151695251465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738998413086</t>
+    <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530532836914</t>
@@ -4563,6 +4563,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -14409,7 +14412,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14435,7 +14438,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14461,7 +14464,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14487,7 +14490,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14513,7 +14516,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G370" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14539,7 +14542,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14565,7 +14568,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14617,7 +14620,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14643,7 +14646,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G375" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14695,7 +14698,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14721,7 +14724,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14747,7 +14750,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14773,7 +14776,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14799,7 +14802,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14825,7 +14828,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G382" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14851,7 +14854,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14877,7 +14880,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14903,7 +14906,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14929,7 +14932,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14955,7 +14958,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14981,7 +14984,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15007,7 +15010,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15033,7 +15036,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15059,7 +15062,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15085,7 +15088,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15111,7 +15114,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15137,7 +15140,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15163,7 +15166,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15189,7 +15192,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15215,7 +15218,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15241,7 +15244,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15267,7 +15270,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G399" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15293,7 +15296,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15319,7 +15322,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G401" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15371,7 +15374,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15397,7 +15400,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G404" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15423,7 +15426,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15449,7 +15452,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15475,7 +15478,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G407" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15501,7 +15504,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15553,7 +15556,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15579,7 +15582,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15605,7 +15608,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G412" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15631,7 +15634,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G413" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15657,7 +15660,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15683,7 +15686,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15709,7 +15712,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15735,7 +15738,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15787,7 +15790,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G419" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15813,7 +15816,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15839,7 +15842,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15865,7 +15868,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G422" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15891,7 +15894,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G423" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15917,7 +15920,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15943,7 +15946,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G425" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15969,7 +15972,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G426" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15995,7 +15998,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16021,7 +16024,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G428" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16047,7 +16050,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G429" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16073,7 +16076,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16099,7 +16102,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16125,7 +16128,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G432" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16151,7 +16154,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G433" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16177,7 +16180,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16203,7 +16206,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G435" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16229,7 +16232,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G436" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16255,7 +16258,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G437" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16281,7 +16284,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16307,7 +16310,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16333,7 +16336,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G440" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16359,7 +16362,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16385,7 +16388,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16411,7 +16414,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16437,7 +16440,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16463,7 +16466,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16489,7 +16492,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16515,7 +16518,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G447" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16541,7 +16544,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16593,7 +16596,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16619,7 +16622,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16645,7 +16648,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16671,7 +16674,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G453" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16697,7 +16700,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G454" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16723,7 +16726,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G455" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16749,7 +16752,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G456" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16775,7 +16778,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G457" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16801,7 +16804,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16827,7 +16830,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G459" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16853,7 +16856,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16879,7 +16882,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16905,7 +16908,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G462" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16931,7 +16934,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G463" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16957,7 +16960,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16983,7 +16986,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17009,7 +17012,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G466" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17035,7 +17038,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17061,7 +17064,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G468" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17087,7 +17090,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17113,7 +17116,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17139,7 +17142,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G471" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17165,7 +17168,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G472" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17191,7 +17194,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G473" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17217,7 +17220,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G474" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17243,7 +17246,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17269,7 +17272,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17295,7 +17298,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17321,7 +17324,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17347,7 +17350,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G479" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17373,7 +17376,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G480" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17399,7 +17402,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G481" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17425,7 +17428,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G482" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17451,7 +17454,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17477,7 +17480,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G484" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17503,7 +17506,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G485" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17529,7 +17532,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G486" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17555,7 +17558,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G487" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17581,7 +17584,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G488" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17607,7 +17610,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17633,7 +17636,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G490" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17659,7 +17662,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17685,7 +17688,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G492" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17711,7 +17714,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17737,7 +17740,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G494" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17763,7 +17766,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17789,7 +17792,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G496" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17815,7 +17818,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17841,7 +17844,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17867,7 +17870,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G499" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17893,7 +17896,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G500" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17919,7 +17922,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G501" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17945,7 +17948,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G502" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17971,7 +17974,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17997,7 +18000,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18023,7 +18026,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18049,7 +18052,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18075,7 +18078,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G507" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18101,7 +18104,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18127,7 +18130,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G509" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18153,7 +18156,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G510" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18179,7 +18182,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G511" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18205,7 +18208,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G512" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18231,7 +18234,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G513" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18257,7 +18260,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18283,7 +18286,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18309,7 +18312,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G516" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18335,7 +18338,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G517" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18361,7 +18364,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18387,7 +18390,7 @@
         <v>10</v>
       </c>
       <c r="G519" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18413,7 +18416,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18439,7 +18442,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G521" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18465,7 +18468,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G522" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18491,7 +18494,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G523" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18517,7 +18520,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G524" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18543,7 +18546,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G525" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18569,7 +18572,7 @@
         <v>10</v>
       </c>
       <c r="G526" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18595,7 +18598,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G527" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18621,7 +18624,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G528" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18647,7 +18650,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G529" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18673,7 +18676,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G530" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18699,7 +18702,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G531" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18725,7 +18728,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18751,7 +18754,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18777,7 +18780,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G534" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18803,7 +18806,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18829,7 +18832,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18855,7 +18858,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G537" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18881,7 +18884,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18907,7 +18910,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G539" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18933,7 +18936,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G540" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18959,7 +18962,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G541" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18985,7 +18988,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19011,7 +19014,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G543" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19037,7 +19040,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19063,7 +19066,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G545" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19089,7 +19092,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G546" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19115,7 +19118,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G547" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19141,7 +19144,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19167,7 +19170,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G549" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19193,7 +19196,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G550" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19219,7 +19222,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19245,7 +19248,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G552" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19271,7 +19274,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G553" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19297,7 +19300,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G554" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19323,7 +19326,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19349,7 +19352,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G556" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19375,7 +19378,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G557" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19401,7 +19404,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19427,7 +19430,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19453,7 +19456,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19479,7 +19482,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G561" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19505,7 +19508,7 @@
         <v>11</v>
       </c>
       <c r="G562" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19531,7 +19534,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19557,7 +19560,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19583,7 +19586,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G565" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19609,7 +19612,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19635,7 +19638,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19661,7 +19664,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G568" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19687,7 +19690,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G569" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19713,7 +19716,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19739,7 +19742,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19765,7 +19768,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G572" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19791,7 +19794,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19817,7 +19820,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19843,7 +19846,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19869,7 +19872,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G576" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19895,7 +19898,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G577" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19921,7 +19924,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19947,7 +19950,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19973,7 +19976,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G580" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19999,7 +20002,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G581" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20025,7 +20028,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20051,7 +20054,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20077,7 +20080,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20103,7 +20106,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20129,7 +20132,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G586" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20155,7 +20158,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20181,7 +20184,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G588" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20207,7 +20210,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G589" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20233,7 +20236,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20259,7 +20262,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G591" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20285,7 +20288,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G592" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20311,7 +20314,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G593" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20337,7 +20340,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G594" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20363,7 +20366,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G595" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20389,7 +20392,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G596" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20415,7 +20418,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G597" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20441,7 +20444,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G598" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20467,7 +20470,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20493,7 +20496,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20519,7 +20522,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G601" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20545,7 +20548,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20571,7 +20574,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G603" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20597,7 +20600,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G604" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20623,7 +20626,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G605" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20649,7 +20652,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20675,7 +20678,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G607" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20701,7 +20704,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20727,7 +20730,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G609" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20753,7 +20756,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G610" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20779,7 +20782,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G611" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20805,7 +20808,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G612" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20831,7 +20834,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20857,7 +20860,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20883,7 +20886,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G615" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20909,7 +20912,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G616" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20935,7 +20938,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G617" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20961,7 +20964,7 @@
         <v>11</v>
       </c>
       <c r="G618" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20987,7 +20990,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G619" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21013,7 +21016,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21039,7 +21042,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G621" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21065,7 +21068,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21091,7 +21094,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G623" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21117,7 +21120,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G624" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21143,7 +21146,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21169,7 +21172,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G626" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21195,7 +21198,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G627" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21221,7 +21224,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G628" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21247,7 +21250,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G629" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21273,7 +21276,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G630" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21299,7 +21302,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G631" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21325,7 +21328,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21351,7 +21354,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21377,7 +21380,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G634" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21403,7 +21406,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G635" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21429,7 +21432,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G636" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21455,7 +21458,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G637" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21481,7 +21484,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G638" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21507,7 +21510,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G639" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21533,7 +21536,7 @@
         <v>10.5</v>
       </c>
       <c r="G640" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21559,7 +21562,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G641" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21585,7 +21588,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G642" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21611,7 +21614,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21637,7 +21640,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G644" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21663,7 +21666,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G645" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21689,7 +21692,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21715,7 +21718,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21741,7 +21744,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21767,7 +21770,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G649" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21793,7 +21796,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G650" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21819,7 +21822,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21845,7 +21848,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G652" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21871,7 +21874,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21897,7 +21900,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G654" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21923,7 +21926,7 @@
         <v>9.75</v>
       </c>
       <c r="G655" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21949,7 +21952,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21975,7 +21978,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G657" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22001,7 +22004,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22027,7 +22030,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22053,7 +22056,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G660" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22079,7 +22082,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G661" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22105,7 +22108,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G662" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22131,7 +22134,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22157,7 +22160,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G664" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22183,7 +22186,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G665" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22209,7 +22212,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G666" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22235,7 +22238,7 @@
         <v>9.5</v>
       </c>
       <c r="G667" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22261,7 +22264,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22287,7 +22290,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22313,7 +22316,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22339,7 +22342,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22365,7 +22368,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G672" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22391,7 +22394,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G673" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22417,7 +22420,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G674" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22443,7 +22446,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22469,7 +22472,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G676" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22495,7 +22498,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G677" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22521,7 +22524,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G678" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22547,7 +22550,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G679" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22573,7 +22576,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G680" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22599,7 +22602,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22625,7 +22628,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22651,7 +22654,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22677,7 +22680,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G684" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22703,7 +22706,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G685" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22729,7 +22732,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G686" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22755,7 +22758,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G687" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22781,7 +22784,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22807,7 +22810,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22833,7 +22836,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G690" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22859,7 +22862,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G691" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22885,7 +22888,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22911,7 +22914,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G693" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22937,7 +22940,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G694" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22963,7 +22966,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G695" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22989,7 +22992,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23015,7 +23018,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G697" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23041,7 +23044,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G698" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23067,7 +23070,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G699" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23093,7 +23096,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G700" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23119,7 +23122,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G701" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23145,7 +23148,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23171,7 +23174,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G703" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23197,7 +23200,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23223,7 +23226,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G705" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23275,7 +23278,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24861,7 +24864,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25095,7 +25098,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G777" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25121,7 +25124,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G778" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25147,7 +25150,7 @@
         <v>9.5</v>
       </c>
       <c r="G779" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25173,7 +25176,7 @@
         <v>9.75</v>
       </c>
       <c r="G780" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25199,7 +25202,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G781" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25277,7 +25280,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G784" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25329,7 +25332,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G786" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25407,7 +25410,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25459,7 +25462,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G791" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25511,7 +25514,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25563,7 +25566,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25589,7 +25592,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G796" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25641,7 +25644,7 @@
         <v>9.75</v>
       </c>
       <c r="G798" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25693,7 +25696,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G800" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25719,7 +25722,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G801" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25745,7 +25748,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25875,7 +25878,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G807" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25927,7 +25930,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25953,7 +25956,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G810" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26161,7 +26164,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G818" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26317,7 +26320,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26473,7 +26476,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26811,7 +26814,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G843" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26863,7 +26866,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G845" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -69667,7 +69670,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493865741</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>47200</v>
@@ -69688,6 +69691,32 @@
         <v>1516</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496180556</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>38669</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>33</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>31.9500007629395</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992277145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26996040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
+    <t xml:space="preserve">6.39007425308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26996088027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09379386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.08578538894653</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">5.92563343048096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85356426239014</t>
+    <t xml:space="preserve">5.85356521606445</t>
   </si>
   <si>
     <t xml:space="preserve">5.76548099517822</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">5.9456524848938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143936157227</t>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143983840942</t>
   </si>
   <si>
     <t xml:space="preserve">5.7254433631897</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">5.74145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99770212173462</t>
+    <t xml:space="preserve">5.99770164489746</t>
   </si>
   <si>
     <t xml:space="preserve">5.88559579849243</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">5.91762495040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94164896011353</t>
+    <t xml:space="preserve">5.94164848327637</t>
   </si>
   <si>
     <t xml:space="preserve">6.00570964813232</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">5.84956073760986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77749300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386960983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984655380249</t>
+    <t xml:space="preserve">5.77749347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17387008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984703063965</t>
   </si>
   <si>
     <t xml:space="preserve">6.20590019226074</t>
@@ -122,55 +122,55 @@
     <t xml:space="preserve">6.29398393630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789266586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990371704102</t>
+    <t xml:space="preserve">6.22191572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990324020386</t>
   </si>
   <si>
     <t xml:space="preserve">6.406090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616552352905</t>
+    <t xml:space="preserve">6.45813989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616743087769</t>
   </si>
   <si>
     <t xml:space="preserve">6.50218105316162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49417352676392</t>
+    <t xml:space="preserve">6.49417400360107</t>
   </si>
   <si>
     <t xml:space="preserve">6.23793029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0777792930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388866424561</t>
+    <t xml:space="preserve">6.07777786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388914108276</t>
   </si>
   <si>
     <t xml:space="preserve">6.14183950424194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15385103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980796813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1138129234314</t>
+    <t xml:space="preserve">6.15385007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980892181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11381244659424</t>
   </si>
   <si>
     <t xml:space="preserve">5.98969459533691</t>
@@ -179,91 +179,91 @@
     <t xml:space="preserve">6.0177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94965648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375480651855</t>
+    <t xml:space="preserve">5.94965600967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383197784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375528335571</t>
   </si>
   <si>
     <t xml:space="preserve">6.1578540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09779691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373575210571</t>
+    <t xml:space="preserve">6.09779739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18187665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.1018009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01371717453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11781644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377433776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06977081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19342565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2265453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336616516113</t>
+    <t xml:space="preserve">6.01371765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11781597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0737738609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06976985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19342470169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22654581069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.16030550003052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20998525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406614303589</t>
+    <t xml:space="preserve">6.20998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
     <t xml:space="preserve">6.16858530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18928575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19756555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12718534469604</t>
+    <t xml:space="preserve">6.18928480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170497894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11890554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19756603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1271858215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.13960599899292</t>
@@ -272,61 +272,58 @@
     <t xml:space="preserve">6.11062526702881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04438638687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534616470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776681900024</t>
+    <t xml:space="preserve">6.04438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776586532593</t>
   </si>
   <si>
     <t xml:space="preserve">5.81254625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99470567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04024600982666</t>
+    <t xml:space="preserve">5.99470615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024648666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.961585521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636590957642</t>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8539457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770589828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8622260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190576553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">6.12304592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01540613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10234546661377</t>
+    <t xml:space="preserve">6.01540565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10234594345093</t>
   </si>
   <si>
     <t xml:space="preserve">6.26794528961182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15616512298584</t>
+    <t xml:space="preserve">6.156165599823</t>
   </si>
   <si>
     <t xml:space="preserve">6.0319652557373</t>
@@ -338,28 +335,28 @@
     <t xml:space="preserve">6.1768651008606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25138521194458</t>
+    <t xml:space="preserve">6.25138568878174</t>
   </si>
   <si>
     <t xml:space="preserve">6.13132572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15202569961548</t>
+    <t xml:space="preserve">6.15202522277832</t>
   </si>
   <si>
     <t xml:space="preserve">6.14374542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07750606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14788579940796</t>
+    <t xml:space="preserve">6.07750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1478853225708</t>
   </si>
   <si>
     <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05266523361206</t>
+    <t xml:space="preserve">6.05266571044922</t>
   </si>
   <si>
     <t xml:space="preserve">5.9698657989502</t>
@@ -368,7 +365,7 @@
     <t xml:space="preserve">6.10648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98642587661743</t>
+    <t xml:space="preserve">5.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
@@ -383,31 +380,31 @@
     <t xml:space="preserve">5.95744609832764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00298595428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496643066406</t>
+    <t xml:space="preserve">6.00298547744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93260669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8249659538269</t>
   </si>
   <si>
     <t xml:space="preserve">5.81668663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84980630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75872611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90362644195557</t>
+    <t xml:space="preserve">5.8498067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808610916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75872707366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90362596511841</t>
   </si>
   <si>
     <t xml:space="preserve">5.93674612045288</t>
@@ -425,55 +422,55 @@
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45010471343994</t>
+    <t xml:space="preserve">6.4501051902771</t>
   </si>
   <si>
     <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5494647026062</t>
+    <t xml:space="preserve">6.54946422576904</t>
   </si>
   <si>
     <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29278469085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4583854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38386535644531</t>
+    <t xml:space="preserve">6.29278564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45838499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386487960815</t>
   </si>
   <si>
     <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2348256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33832502365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972497940063</t>
+    <t xml:space="preserve">6.23482513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972450256348</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34246492385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49150514602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33418464660645</t>
+    <t xml:space="preserve">6.37558555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3424654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49150466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3341851234436</t>
   </si>
   <si>
     <t xml:space="preserve">6.3714451789856</t>
@@ -485,16 +482,16 @@
     <t xml:space="preserve">6.39214515686035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18514442443848</t>
+    <t xml:space="preserve">6.18514585494995</t>
   </si>
   <si>
     <t xml:space="preserve">5.97400617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01126670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0195460319519</t>
+    <t xml:space="preserve">6.01126623153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
     <t xml:space="preserve">6.02782583236694</t>
@@ -506,22 +503,22 @@
     <t xml:space="preserve">6.36730480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28450584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41284513473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24310493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69850444793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.28450536727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24310541152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69850492477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194341659546</t>
   </si>
   <si>
     <t xml:space="preserve">6.64882373809814</t>
@@ -530,115 +527,115 @@
     <t xml:space="preserve">6.72334384918213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73990440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03798389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874383926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384399414062</t>
+    <t xml:space="preserve">6.73990392684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03798341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384304046631</t>
   </si>
   <si>
     <t xml:space="preserve">7.01314353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07938385009766</t>
+    <t xml:space="preserve">7.07938241958618</t>
   </si>
   <si>
     <t xml:space="preserve">7.02142333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05454349517822</t>
+    <t xml:space="preserve">7.05454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.98830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20772314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60102272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688329696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08766317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370317459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682237625122</t>
+    <t xml:space="preserve">7.20772218704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102319717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0876636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370365142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682285308838</t>
   </si>
   <si>
     <t xml:space="preserve">7.48924255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9427638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486326217651</t>
+    <t xml:space="preserve">7.43542289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810335159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1704626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94276475906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07110404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486373901367</t>
   </si>
   <si>
     <t xml:space="preserve">6.83512401580811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95518350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932292938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26982259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306125640869</t>
+    <t xml:space="preserve">6.95518398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2698221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306173324585</t>
   </si>
   <si>
     <t xml:space="preserve">7.50994205474854</t>
@@ -647,22 +644,22 @@
     <t xml:space="preserve">7.64242124557495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210147857666</t>
+    <t xml:space="preserve">7.69210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">7.65898180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90324068069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674247741699</t>
+    <t xml:space="preserve">7.9032416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674057006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.03158187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07298183441162</t>
+    <t xml:space="preserve">8.07297992706299</t>
   </si>
   <si>
     <t xml:space="preserve">7.85356187820435</t>
@@ -671,10 +668,10 @@
     <t xml:space="preserve">8.25928115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19304275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514125823975</t>
+    <t xml:space="preserve">8.19304180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25513935089111</t>
   </si>
   <si>
     <t xml:space="preserve">8.48697948455811</t>
@@ -683,10 +680,10 @@
     <t xml:space="preserve">8.49526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39590072631836</t>
+    <t xml:space="preserve">8.3627815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39590167999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.43730068206787</t>
@@ -695,22 +692,22 @@
     <t xml:space="preserve">8.62773990631104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59461975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52837944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03986072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76662158966064</t>
+    <t xml:space="preserve">8.63601875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59462070465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52838134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03986167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
     <t xml:space="preserve">7.96120119094849</t>
@@ -719,34 +716,34 @@
     <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51181983947754</t>
+    <t xml:space="preserve">8.51182079315186</t>
   </si>
   <si>
     <t xml:space="preserve">8.6028995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77677917480469</t>
+    <t xml:space="preserve">8.77678108215332</t>
   </si>
   <si>
     <t xml:space="preserve">8.85957908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37293910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44745922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0850172042847</t>
+    <t xml:space="preserve">9.37293720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.085015296936</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4907360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894550323486</t>
+    <t xml:space="preserve">10.4907350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894559860229</t>
   </si>
   <si>
     <t xml:space="preserve">10.7556943893433</t>
@@ -758,19 +755,19 @@
     <t xml:space="preserve">10.3499765396118</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5790319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4602613449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87489604949951</t>
+    <t xml:space="preserve">10.5790328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87489414215088</t>
   </si>
   <si>
     <t xml:space="preserve">10.0615329742432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1209192276001</t>
+    <t xml:space="preserve">10.1209182739258</t>
   </si>
   <si>
     <t xml:space="preserve">10.0530500411987</t>
@@ -791,7 +788,7 @@
     <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6638679504395</t>
+    <t xml:space="preserve">10.6638669967651</t>
   </si>
   <si>
     <t xml:space="preserve">10.6129665374756</t>
@@ -806,10 +803,10 @@
     <t xml:space="preserve">10.7232522964478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6469020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6299343109131</t>
+    <t xml:space="preserve">10.6469011306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6299333572388</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384172439575</t>
@@ -818,13 +815,13 @@
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584604263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2736234664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075571060181</t>
+    <t xml:space="preserve">10.3584594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2736225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3075580596924</t>
   </si>
   <si>
     <t xml:space="preserve">10.04456615448</t>
@@ -839,19 +836,19 @@
     <t xml:space="preserve">9.78157424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61190319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10288715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17924022674561</t>
+    <t xml:space="preserve">9.61190414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1028881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16227340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17923927307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
@@ -866,28 +863,28 @@
     <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37436199188232</t>
+    <t xml:space="preserve">9.21317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37436294555664</t>
   </si>
   <si>
     <t xml:space="preserve">9.68825626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0954675674438</t>
+    <t xml:space="preserve">10.0954685211182</t>
   </si>
   <si>
     <t xml:space="preserve">10.0360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90034484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227230072021</t>
+    <t xml:space="preserve">9.90034580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944438934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227220535278</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
@@ -905,7 +902,7 @@
     <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057552337646</t>
+    <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
     <t xml:space="preserve">10.019115447998</t>
@@ -917,79 +914,79 @@
     <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8579273223877</t>
+    <t xml:space="preserve">9.85792827606201</t>
   </si>
   <si>
     <t xml:space="preserve">9.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51009941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522212982178</t>
+    <t xml:space="preserve">9.51010131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522403717041</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35739612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56948471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66280460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39133071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284683227539</t>
+    <t xml:space="preserve">9.35739517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56948566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39132976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284778594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.45071601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51858329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27256202697754</t>
+    <t xml:space="preserve">9.51858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27256011962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.20469188690186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58645248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735294342041</t>
+    <t xml:space="preserve">9.58645439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
     <t xml:space="preserve">9.75612449645996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82399272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309131622314</t>
+    <t xml:space="preserve">9.82399463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309322357178</t>
   </si>
   <si>
     <t xml:space="preserve">9.79854202270508</t>
@@ -1010,49 +1007,49 @@
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13682460784912</t>
+    <t xml:space="preserve">9.47616672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1368236541748</t>
   </si>
   <si>
     <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72112655639648</t>
+    <t xml:space="preserve">8.7211275100708</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32664108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12303352355957</t>
+    <t xml:space="preserve">8.07637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32663917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33088207244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19514465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27149677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37329959869385</t>
+    <t xml:space="preserve">8.33088111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.195143699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2714958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37330150604248</t>
   </si>
   <si>
     <t xml:space="preserve">8.31391525268555</t>
@@ -1061,22 +1058,22 @@
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85155916213989</t>
+    <t xml:space="preserve">8.09334087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85155820846558</t>
   </si>
   <si>
     <t xml:space="preserve">7.82610845565796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094398498535</t>
+    <t xml:space="preserve">7.80065774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094446182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.85580110549927</t>
@@ -1085,58 +1082,58 @@
     <t xml:space="preserve">7.95760440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9788122177124</t>
+    <t xml:space="preserve">7.97881269454956</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123069763184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.01274681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1484842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393589019775</t>
+    <t xml:space="preserve">8.14848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393493652344</t>
   </si>
   <si>
     <t xml:space="preserve">8.22483730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2884635925293</t>
+    <t xml:space="preserve">8.28846454620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56842231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51752185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73809432983398</t>
+    <t xml:space="preserve">8.5684232711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5175199508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7380952835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48358631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50055503845215</t>
+    <t xml:space="preserve">8.48358726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50055408477783</t>
   </si>
   <si>
     <t xml:space="preserve">8.65325832366943</t>
@@ -1145,22 +1142,22 @@
     <t xml:space="preserve">8.58538913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45813655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38178443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01698875427246</t>
+    <t xml:space="preserve">8.46661853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45813465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3817834854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698970794678</t>
   </si>
   <si>
     <t xml:space="preserve">7.99153804779053</t>
@@ -1169,103 +1166,103 @@
     <t xml:space="preserve">7.91518640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12727546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97457122802734</t>
+    <t xml:space="preserve">8.12727642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97457075119019</t>
   </si>
   <si>
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75506114959717</t>
+    <t xml:space="preserve">8.90776538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506019592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.82292938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77202892303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61932277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235595703125</t>
+    <t xml:space="preserve">8.77202796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61932373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235786437988</t>
   </si>
   <si>
     <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94169998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36588001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12833881378174</t>
+    <t xml:space="preserve">8.94169902801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24710941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
     <t xml:space="preserve">9.11137199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0435037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09440517425537</t>
+    <t xml:space="preserve">9.04350280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09440422058105</t>
   </si>
   <si>
     <t xml:space="preserve">9.26407623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41678237915039</t>
+    <t xml:space="preserve">9.41678142547607</t>
   </si>
   <si>
     <t xml:space="preserve">10.2142381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5705490112305</t>
+    <t xml:space="preserve">10.5705480575562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6723527908325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6214504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9607944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4358730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680047988892</t>
+    <t xml:space="preserve">10.6214513778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9607934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4358739852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680057525635</t>
   </si>
   <si>
     <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5430994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8729009628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.836256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4148426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
+    <t xml:space="preserve">11.543098449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8729019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8362560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4148416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3049077987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9567823410034</t>
@@ -1274,13 +1271,13 @@
     <t xml:space="preserve">10.8834934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4987239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6086568832397</t>
+    <t xml:space="preserve">10.498722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002687454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6086578369141</t>
   </si>
   <si>
     <t xml:space="preserve">10.645302772522</t>
@@ -1292,13 +1289,13 @@
     <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0040187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">10.004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589866638184</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788543701172</t>
@@ -1307,85 +1304,85 @@
     <t xml:space="preserve">10.0773086547852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2238864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1322746276855</t>
+    <t xml:space="preserve">10.2238874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2605323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4071111679077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3154993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4437561035156</t>
+    <t xml:space="preserve">10.3154983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4437551498413</t>
   </si>
   <si>
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.20556640625</t>
+    <t xml:space="preserve">10.2055644989014</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78415107727051</t>
+    <t xml:space="preserve">9.78415012359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71086025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67421531677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918319702148</t>
+    <t xml:space="preserve">9.71086120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47266864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67421627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918224334717</t>
   </si>
   <si>
     <t xml:space="preserve">9.65589332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61924934387207</t>
+    <t xml:space="preserve">9.61924839019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56428146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776691436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32609176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27112293243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08789920806885</t>
+    <t xml:space="preserve">9.69253826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2528018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3627347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08790016174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.93215942382812</t>
@@ -1394,7 +1391,7 @@
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293323516846</t>
+    <t xml:space="preserve">9.03293132781982</t>
   </si>
   <si>
     <t xml:space="preserve">8.95964336395264</t>
@@ -1403,7 +1400,7 @@
     <t xml:space="preserve">8.97796535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94132041931152</t>
+    <t xml:space="preserve">8.94132137298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.51990699768066</t>
@@ -1418,31 +1415,31 @@
     <t xml:space="preserve">8.70312976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65732192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35500431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44661712646484</t>
+    <t xml:space="preserve">8.63900089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62983894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35500335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44661617279053</t>
   </si>
   <si>
     <t xml:space="preserve">9.39937973022461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3810567855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19783496856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00544929504395</t>
+    <t xml:space="preserve">9.38105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00544834136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
@@ -1454,34 +1451,37 @@
     <t xml:space="preserve">9.04209327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96880531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628829956055</t>
+    <t xml:space="preserve">8.96880435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628734588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8680305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78557968139648</t>
+    <t xml:space="preserve">8.86803245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7855806350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84054851531982</t>
+    <t xml:space="preserve">8.84054660797119</t>
   </si>
   <si>
     <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7122917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59319591522217</t>
+    <t xml:space="preserve">8.71229076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59319496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235691070557</t>
   </si>
   <si>
     <t xml:space="preserve">8.40997219085693</t>
@@ -1493,115 +1493,115 @@
     <t xml:space="preserve">8.2450704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74120473861694</t>
+    <t xml:space="preserve">7.74120426177979</t>
   </si>
   <si>
     <t xml:space="preserve">7.70455980300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68623828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55798101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462594985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4938530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10908269882202</t>
+    <t xml:space="preserve">7.68623781204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55798196792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462642669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159875869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10908317565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.38391876220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16405010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30146741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31978988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469114303589</t>
+    <t xml:space="preserve">7.16405057907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30146789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31978940963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469209671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76868724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5854640007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51217460632324</t>
+    <t xml:space="preserve">7.7686882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539976119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720815658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
   </si>
   <si>
     <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14572763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
+    <t xml:space="preserve">7.14572715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05411577224731</t>
   </si>
   <si>
     <t xml:space="preserve">7.43888521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53965854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049755096436</t>
+    <t xml:space="preserve">7.53965759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">7.47553062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33811235427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29230690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2831449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31062889099121</t>
+    <t xml:space="preserve">7.33811283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29230642318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28314542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31062841415405</t>
   </si>
   <si>
     <t xml:space="preserve">7.24650049209595</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">7.27398443222046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643482208252</t>
+    <t xml:space="preserve">7.35643434524536</t>
   </si>
   <si>
     <t xml:space="preserve">7.67707681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72288227081299</t>
+    <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
     <t xml:space="preserve">7.86946153640747</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.39164924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49242210388184</t>
+    <t xml:space="preserve">8.49242401123047</t>
   </si>
   <si>
     <t xml:space="preserve">8.40081119537354</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">8.3458423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3366813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02377128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13370609283447</t>
+    <t xml:space="preserve">8.33668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02377033233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10622215270996</t>
+    <t xml:space="preserve">9.10622119903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.05125522613525</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8588695526123</t>
+    <t xml:space="preserve">8.66648578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85887050628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.01460933685303</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90467643737793</t>
+    <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.84970855712891</t>
@@ -1682,22 +1682,22 @@
     <t xml:space="preserve">8.80390167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81306457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58403396606445</t>
+    <t xml:space="preserve">8.81306266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58403301239014</t>
   </si>
   <si>
     <t xml:space="preserve">8.68480682373047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25423240661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248825073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255344390869</t>
+    <t xml:space="preserve">8.25423049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255439758301</t>
   </si>
   <si>
     <t xml:space="preserve">8.12597465515137</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2359094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43745517730713</t>
+    <t xml:space="preserve">8.23590850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43745422363281</t>
   </si>
   <si>
     <t xml:space="preserve">8.45577716827393</t>
@@ -1718,28 +1718,28 @@
     <t xml:space="preserve">8.47410011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50158214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42829418182373</t>
+    <t xml:space="preserve">8.50158405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42829322814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.46493816375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51074409484863</t>
+    <t xml:space="preserve">8.51074504852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62067794799805</t>
+    <t xml:space="preserve">8.62067890167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738998413086</t>
+    <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530628204346</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">8.18923187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89883327484131</t>
+    <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
     <t xml:space="preserve">8.06339263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29571056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02467250823975</t>
+    <t xml:space="preserve">7.98595380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0343542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
@@ -1787,19 +1787,19 @@
     <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627305984497</t>
+    <t xml:space="preserve">7.97627258300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.96659183502197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16987133026123</t>
+    <t xml:space="preserve">8.16987228393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.24731159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25699043273926</t>
+    <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
     <t xml:space="preserve">8.14083194732666</t>
@@ -1808,25 +1808,25 @@
     <t xml:space="preserve">7.92787313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">8.073073387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0827522277832</t>
+    <t xml:space="preserve">8.07307243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08275318145752</t>
   </si>
   <si>
     <t xml:space="preserve">7.90851402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755197525024</t>
+    <t xml:space="preserve">7.93755388259888</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13115215301514</t>
+    <t xml:space="preserve">8.11179256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13115310668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.04403305053711</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99563264846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00531387329102</t>
+    <t xml:space="preserve">7.99563360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0053129196167</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947416305542</t>
+    <t xml:space="preserve">7.86979389190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691394805908</t>
+    <t xml:space="preserve">7.95691251754761</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33443069458008</t>
+    <t xml:space="preserve">8.33442974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">8.78938865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14754676818848</t>
+    <t xml:space="preserve">9.14754581451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">9.51538372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3895435333252</t>
+    <t xml:space="preserve">9.38954448699951</t>
   </si>
   <si>
     <t xml:space="preserve">9.48634433746338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45730400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55410289764404</t>
+    <t xml:space="preserve">9.45730495452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44762516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55410385131836</t>
   </si>
   <si>
     <t xml:space="preserve">9.534743309021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506446838379</t>
+    <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
     <t xml:space="preserve">10.0284204483032</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477809906006</t>
+    <t xml:space="preserve">10.0477819442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">9.95098209381104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60250282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6799430847168</t>
+    <t xml:space="preserve">9.60250377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67994403839111</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218357086182</t>
@@ -1949,19 +1949,19 @@
     <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58314228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8735408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40890598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35082530975342</t>
+    <t xml:space="preserve">9.58314418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3508243560791</t>
   </si>
   <si>
     <t xml:space="preserve">9.43794441223145</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146476745605</t>
+    <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.77674293518066</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">9.66058254241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11850643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09914588928223</t>
+    <t xml:space="preserve">9.11850547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09914684295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.08946704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19594478607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16690635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0797872543335</t>
+    <t xml:space="preserve">9.19594573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16690540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07978630065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.10882663726807</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">9.0120267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92490673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94426727294922</t>
+    <t xml:space="preserve">8.92490768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9442663192749</t>
   </si>
   <si>
     <t xml:space="preserve">8.85714721679688</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">8.7216272354126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77002811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9345874786377</t>
+    <t xml:space="preserve">8.77002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93458652496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266719818115</t>
@@ -2030,55 +2030,55 @@
     <t xml:space="preserve">8.96362781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15722560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05074787139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97330760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84075403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60843515396118</t>
+    <t xml:space="preserve">9.1572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05074691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84075450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79235410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60843563079834</t>
   </si>
   <si>
     <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61811542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34707641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428197860718</t>
+    <t xml:space="preserve">7.61811494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428102493286</t>
   </si>
   <si>
     <t xml:space="preserve">6.58236169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44684171676636</t>
+    <t xml:space="preserve">6.44684219360352</t>
   </si>
   <si>
     <t xml:space="preserve">5.14004945755005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47884798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53989362716675</t>
+    <t xml:space="preserve">5.47884750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.64637279510498</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.52053308486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8399715423584</t>
+    <t xml:space="preserve">4.83997201919556</t>
   </si>
   <si>
     <t xml:space="preserve">5.13037014007568</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">6.00156450271606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98220443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88540554046631</t>
+    <t xml:space="preserve">5.98220491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
     <t xml:space="preserve">5.79828596115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96284484863281</t>
+    <t xml:space="preserve">5.96284437179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644359588623</t>
+    <t xml:space="preserve">6.15644454956055</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">6.46620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22420358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42748260498047</t>
+    <t xml:space="preserve">6.43716192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22420310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42748212814331</t>
   </si>
   <si>
     <t xml:space="preserve">6.5339617729187</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
+    <t xml:space="preserve">7.67619466781616</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491432189941</t>
+    <t xml:space="preserve">7.58907508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71491479873657</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
@@ -2165,55 +2165,55 @@
     <t xml:space="preserve">7.39547634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43419599533081</t>
+    <t xml:space="preserve">7.43419551849365</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40515613555908</t>
+    <t xml:space="preserve">7.40515661239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44387626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49227523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46323585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69555425643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043334960938</t>
+    <t xml:space="preserve">7.44387578964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49227571487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4632363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69555473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043287277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56003522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5987548828125</t>
+    <t xml:space="preserve">7.56003570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59875535964966</t>
   </si>
   <si>
     <t xml:space="preserve">7.65683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50195598602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3180365562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30835771560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23091745376587</t>
+    <t xml:space="preserve">7.50195550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31803703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30835723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23091793060303</t>
   </si>
   <si>
     <t xml:space="preserve">7.521315574646</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">7.5406756401062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51163673400879</t>
+    <t xml:space="preserve">7.51163625717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33739709854126</t>
+    <t xml:space="preserve">7.3373966217041</t>
   </si>
   <si>
     <t xml:space="preserve">7.35675668716431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45355606079102</t>
+    <t xml:space="preserve">7.45355653762817</t>
   </si>
   <si>
     <t xml:space="preserve">7.64715528488159</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">7.41483640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
+    <t xml:space="preserve">7.29867649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
   </si>
   <si>
     <t xml:space="preserve">7.47291612625122</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">7.68587493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88915252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7439546585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73427438735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36643743515015</t>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74395418167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73427391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36643648147583</t>
   </si>
   <si>
     <t xml:space="preserve">7.26963758468628</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12443780899048</t>
+    <t xml:space="preserve">7.16315841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12443828582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.22123765945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70523500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7245945930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4825963973999</t>
+    <t xml:space="preserve">7.70523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48259544372559</t>
   </si>
   <si>
     <t xml:space="preserve">7.66651487350464</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">7.42451667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14379787445068</t>
+    <t xml:space="preserve">7.14379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">7.04699897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10507869720459</t>
+    <t xml:space="preserve">7.10507822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.11475801467896</t>
@@ -2318,31 +2318,31 @@
     <t xml:space="preserve">7.17283773422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25027751922607</t>
+    <t xml:space="preserve">7.25027704238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.24059724807739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2018780708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18251752853394</t>
+    <t xml:space="preserve">7.20187759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18251800537109</t>
   </si>
   <si>
     <t xml:space="preserve">7.13411808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02763843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.02763891220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">6.96955871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89211940765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97923898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06635904312134</t>
+    <t xml:space="preserve">6.89211893081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97923946380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06635856628418</t>
   </si>
   <si>
     <t xml:space="preserve">7.0566782951355</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90179967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82435941696167</t>
+    <t xml:space="preserve">6.90179920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436037063599</t>
   </si>
   <si>
     <t xml:space="preserve">6.80500030517578</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">6.78564071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8146800994873</t>
+    <t xml:space="preserve">6.81467962265015</t>
   </si>
   <si>
     <t xml:space="preserve">6.7953200340271</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">6.75660037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73724031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63076114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67916059494019</t>
+    <t xml:space="preserve">6.7372407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">6.93083906173706</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28879070281982</t>
+    <t xml:space="preserve">7.22067213058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
     <t xml:space="preserve">7.17201519012451</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49314975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59046411514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395587921143</t>
+    <t xml:space="preserve">7.49315023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59046363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52234363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395635604858</t>
   </si>
   <si>
     <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83374738693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06729984283447</t>
+    <t xml:space="preserve">7.83374786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06730079650879</t>
   </si>
   <si>
     <t xml:space="preserve">8.03810691833496</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00891208648682</t>
+    <t xml:space="preserve">8.0089111328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.0964937210083</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380855560303</t>
+    <t xml:space="preserve">8.19380760192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.13541889190674</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">7.96998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89213562011719</t>
+    <t xml:space="preserve">7.89213514328003</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019493103027</t>
+    <t xml:space="preserve">7.60019540786743</t>
   </si>
   <si>
     <t xml:space="preserve">7.57100105285645</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">7.65858316421509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73643445968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69750881195068</t>
+    <t xml:space="preserve">7.73643398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69750833511353</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">7.82401657104492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64885139465332</t>
+    <t xml:space="preserve">7.64885234832764</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">7.63912057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62938976287842</t>
+    <t xml:space="preserve">7.6293888092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.56126928329468</t>
@@ -2540,22 +2540,22 @@
     <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79482221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01864433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94079256057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112148284912</t>
+    <t xml:space="preserve">7.79482269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01864337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94079303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112243652344</t>
   </si>
   <si>
     <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0770320892334</t>
+    <t xml:space="preserve">8.07703304290771</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
@@ -2567,16 +2567,16 @@
     <t xml:space="preserve">8.36897373199463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53440570831299</t>
+    <t xml:space="preserve">8.34951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.74849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67064476013184</t>
+    <t xml:space="preserve">8.67064380645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.68037605285645</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097415924072</t>
+    <t xml:space="preserve">9.02097511291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">9.10855674743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04043579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75822734832764</t>
+    <t xml:space="preserve">9.04043674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75822830200195</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789890289307</t>
+    <t xml:space="preserve">8.40789794921875</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43709182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46628570556641</t>
+    <t xml:space="preserve">8.43709278106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46628665924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.4565544128418</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">8.15488338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23273468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17434501647949</t>
+    <t xml:space="preserve">8.23273372650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17434597015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.14515113830566</t>
@@ -2651,19 +2651,19 @@
     <t xml:space="preserve">8.20353984832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25219535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22300243377686</t>
+    <t xml:space="preserve">8.25219631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22300148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.33004760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64144992828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58306312561035</t>
+    <t xml:space="preserve">8.64145088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58306121826172</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2675,31 +2675,31 @@
     <t xml:space="preserve">8.50521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83607769012451</t>
+    <t xml:space="preserve">8.60252571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83607864379883</t>
   </si>
   <si>
     <t xml:space="preserve">8.70957088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84580993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92599010467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75082683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3152446746826</t>
+    <t xml:space="preserve">8.84581089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01124286651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92599105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88706493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3152465820312</t>
   </si>
   <si>
     <t xml:space="preserve">10.3541707992554</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">9.77028846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50754356384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41022777557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13775157928467</t>
+    <t xml:space="preserve">9.50754261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41022872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13775062561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.07936191558838</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">9.14748191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32264709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05990028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0890941619873</t>
+    <t xml:space="preserve">9.32264614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05989933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909320831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2753,25 +2753,25 @@
     <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93339157104492</t>
+    <t xml:space="preserve">8.93339252471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613742828369</t>
+    <t xml:space="preserve">9.19613838195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62431812286377</t>
+    <t xml:space="preserve">9.62431907653809</t>
   </si>
   <si>
     <t xml:space="preserve">9.57566165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5367374420166</t>
+    <t xml:space="preserve">9.53673648834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.82867813110352</t>
@@ -2783,40 +2783,40 @@
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61458778381348</t>
+    <t xml:space="preserve">9.67297458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61458683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.59512424468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45888614654541</t>
+    <t xml:space="preserve">9.45888519287109</t>
   </si>
   <si>
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18640613555908</t>
+    <t xml:space="preserve">9.1864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21560192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20586967468262</t>
+    <t xml:space="preserve">9.21560096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20587062835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204898834229</t>
+    <t xml:space="preserve">8.98204803466797</t>
   </si>
   <si>
     <t xml:space="preserve">8.56360054016113</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41763019561768</t>
+    <t xml:space="preserve">8.76795768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41762924194336</t>
   </si>
   <si>
     <t xml:space="preserve">8.28139019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37870407104492</t>
+    <t xml:space="preserve">8.37870311737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.71930122375488</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04783916473389</t>
+    <t xml:space="preserve">8.95285415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04783821105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500381469727</t>
+    <t xml:space="preserve">8.87500286102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921363830566</t>
+    <t xml:space="preserve">9.80921459197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51727294921875</t>
+    <t xml:space="preserve">9.98437881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51727390289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.47834777832031</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55619812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44915390014648</t>
+    <t xml:space="preserve">9.37130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5561990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4491548538208</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136234283447</t>
+    <t xml:space="preserve">9.73136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038414001465</t>
+    <t xml:space="preserve">10.0038423538208</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595430374146</t>
@@ -2924,43 +2924,43 @@
     <t xml:space="preserve">10.1790065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0233039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0427675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622301101685</t>
+    <t xml:space="preserve">10.02330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33237743377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25452709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63404941558838</t>
+    <t xml:space="preserve">9.90652847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33237838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25452613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48807907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6340503692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347082138062</t>
+    <t xml:space="preserve">10.3347072601318</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689189910889</t>
+    <t xml:space="preserve">11.2689199447632</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5997848510742</t>
+    <t xml:space="preserve">11.5997858047485</t>
   </si>
   <si>
     <t xml:space="preserve">11.6776361465454</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440832138062</t>
+    <t xml:space="preserve">11.4440841674805</t>
   </si>
   <si>
     <t xml:space="preserve">11.4051580429077</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">11.4830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3662338256836</t>
+    <t xml:space="preserve">11.3662328720093</t>
   </si>
   <si>
     <t xml:space="preserve">11.638710975647</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">12.5729217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4756078720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1836671829224</t>
+    <t xml:space="preserve">12.4756088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1836681365967</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">11.2299928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8991270065308</t>
+    <t xml:space="preserve">10.8991279602051</t>
   </si>
   <si>
     <t xml:space="preserve">10.8407392501831</t>
@@ -3056,31 +3056,31 @@
     <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9575157165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1984691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6071853637695</t>
+    <t xml:space="preserve">10.9575147628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.198468208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6071863174438</t>
   </si>
   <si>
     <t xml:space="preserve">10.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132173538208</t>
+    <t xml:space="preserve">11.1132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.860200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9185905456543</t>
+    <t xml:space="preserve">10.8602018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6266489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.91858959198</t>
   </si>
   <si>
     <t xml:space="preserve">11.2105321884155</t>
@@ -3092,43 +3092,43 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695768356323</t>
+    <t xml:space="preserve">11.9695777893066</t>
   </si>
   <si>
     <t xml:space="preserve">11.9306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8917264938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1252794265747</t>
+    <t xml:space="preserve">11.8528003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8917274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1252784729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5339956283569</t>
+    <t xml:space="preserve">12.5339965820312</t>
   </si>
   <si>
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923843383789</t>
+    <t xml:space="preserve">12.8259382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923833847046</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8648633956909</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">12.3977565765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4366827011108</t>
+    <t xml:space="preserve">12.4366817474365</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
@@ -3155,25 +3155,25 @@
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950723648071</t>
+    <t xml:space="preserve">12.3393697738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950704574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.787013053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2225933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1762666702271</t>
+    <t xml:space="preserve">12.7870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1762657165527</t>
   </si>
   <si>
     <t xml:space="preserve">12.962176322937</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594902038574</t>
+    <t xml:space="preserve">13.0594911575317</t>
   </si>
   <si>
     <t xml:space="preserve">12.9427137374878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1373405456543</t>
+    <t xml:space="preserve">13.1373414993286</t>
   </si>
   <si>
     <t xml:space="preserve">13.0789518356323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4487438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.468207359314</t>
+    <t xml:space="preserve">13.4487447738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4682064056396</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3212,25 +3212,25 @@
     <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9742383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3051052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6165084838867</t>
+    <t xml:space="preserve">13.9742374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3051042556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.616509437561</t>
   </si>
   <si>
     <t xml:space="preserve">14.7527465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1809282302856</t>
+    <t xml:space="preserve">15.1809272766113</t>
   </si>
   <si>
     <t xml:space="preserve">14.9473733901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9279117584229</t>
+    <t xml:space="preserve">14.9279127120972</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359191894531</t>
+    <t xml:space="preserve">17.5359153747559</t>
   </si>
   <si>
     <t xml:space="preserve">17.4191417694092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7889347076416</t>
+    <t xml:space="preserve">17.788932800293</t>
   </si>
   <si>
     <t xml:space="preserve">17.6137676239014</t>
@@ -3266,19 +3266,19 @@
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500076293945</t>
+    <t xml:space="preserve">17.7500057220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.2949638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2755031585693</t>
+    <t xml:space="preserve">18.2755012512207</t>
   </si>
   <si>
     <t xml:space="preserve">18.2365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8204555511475</t>
+    <t xml:space="preserve">18.8204574584961</t>
   </si>
   <si>
     <t xml:space="preserve">18.7620697021484</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419483184814</t>
+    <t xml:space="preserve">19.0345478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419502258301</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5479793548584</t>
+    <t xml:space="preserve">18.5479774475098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">19.7060108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8519802093506</t>
+    <t xml:space="preserve">19.8519821166992</t>
   </si>
   <si>
     <t xml:space="preserve">19.7546672821045</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.898307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.50905418396</t>
+    <t xml:space="preserve">19.0734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8983097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5090522766113</t>
   </si>
   <si>
     <t xml:space="preserve">18.8788452148438</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">19.1902484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9761600494385</t>
+    <t xml:space="preserve">18.9761581420898</t>
   </si>
   <si>
     <t xml:space="preserve">18.8593826293945</t>
@@ -3353,16 +3353,16 @@
     <t xml:space="preserve">18.5869064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6452941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4701271057129</t>
+    <t xml:space="preserve">18.6452922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4701290130615</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486362457275</t>
+    <t xml:space="preserve">19.2486381530762</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">19.1513233184814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9177722930908</t>
+    <t xml:space="preserve">18.9177703857422</t>
   </si>
   <si>
     <t xml:space="preserve">18.9956226348877</t>
@@ -7999,7 +7999,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8025,7 +8025,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8051,7 +8051,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8077,7 +8077,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8129,7 +8129,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8155,7 +8155,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8181,7 +8181,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8207,7 +8207,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8233,7 +8233,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8259,7 +8259,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8363,7 +8363,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8389,7 +8389,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8441,7 +8441,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8493,7 +8493,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8519,7 +8519,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8545,7 +8545,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8597,7 +8597,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8649,7 +8649,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8675,7 +8675,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8701,7 +8701,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8753,7 +8753,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8779,7 +8779,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8805,7 +8805,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8857,7 +8857,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8909,7 +8909,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -8987,7 +8987,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9013,7 +9013,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9039,7 +9039,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9065,7 +9065,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9091,7 +9091,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9143,7 +9143,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9169,7 +9169,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9195,7 +9195,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9221,7 +9221,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9273,7 +9273,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9325,7 +9325,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9351,7 +9351,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9377,7 +9377,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9403,7 +9403,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9429,7 +9429,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9455,7 +9455,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9481,7 +9481,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9507,7 +9507,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9533,7 +9533,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9559,7 +9559,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9585,7 +9585,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9637,7 +9637,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9663,7 +9663,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9689,7 +9689,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9715,7 +9715,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9741,7 +9741,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9767,7 +9767,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9793,7 +9793,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9819,7 +9819,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9845,7 +9845,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9871,7 +9871,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9897,7 +9897,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9923,7 +9923,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9949,7 +9949,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9975,7 +9975,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10001,7 +10001,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10027,7 +10027,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10053,7 +10053,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10105,7 +10105,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10131,7 +10131,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10209,7 +10209,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10235,7 +10235,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10261,7 +10261,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10287,7 +10287,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10313,7 +10313,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10339,7 +10339,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10365,7 +10365,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10391,7 +10391,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10417,7 +10417,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10443,7 +10443,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10469,7 +10469,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10495,7 +10495,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10521,7 +10521,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10547,7 +10547,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10573,7 +10573,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10599,7 +10599,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10625,7 +10625,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10651,7 +10651,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10677,7 +10677,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10703,7 +10703,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10729,7 +10729,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10755,7 +10755,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10781,7 +10781,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10807,7 +10807,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10833,7 +10833,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10859,7 +10859,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10885,7 +10885,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10911,7 +10911,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10937,7 +10937,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10963,7 +10963,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10989,7 +10989,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11015,7 +11015,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11041,7 +11041,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11067,7 +11067,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11093,7 +11093,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11145,7 +11145,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11223,7 +11223,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11249,7 +11249,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11275,7 +11275,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11301,7 +11301,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11327,7 +11327,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11353,7 +11353,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11431,7 +11431,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11457,7 +11457,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11509,7 +11509,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11535,7 +11535,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11613,7 +11613,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11639,7 +11639,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11665,7 +11665,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11691,7 +11691,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11717,7 +11717,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11743,7 +11743,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11769,7 +11769,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11795,7 +11795,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11821,7 +11821,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11847,7 +11847,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11873,7 +11873,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11899,7 +11899,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11925,7 +11925,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11951,7 +11951,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -11977,7 +11977,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12003,7 +12003,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12029,7 +12029,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12055,7 +12055,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12081,7 +12081,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12107,7 +12107,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12133,7 +12133,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12159,7 +12159,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12185,7 +12185,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12211,7 +12211,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12237,7 +12237,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12263,7 +12263,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12289,7 +12289,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12315,7 +12315,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12341,7 +12341,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12367,7 +12367,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12393,7 +12393,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12419,7 +12419,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12445,7 +12445,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12471,7 +12471,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12497,7 +12497,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12523,7 +12523,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12549,7 +12549,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12575,7 +12575,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12601,7 +12601,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12627,7 +12627,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12653,7 +12653,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12679,7 +12679,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12705,7 +12705,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12731,7 +12731,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12757,7 +12757,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12783,7 +12783,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12809,7 +12809,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12835,7 +12835,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12861,7 +12861,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12887,7 +12887,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12913,7 +12913,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12939,7 +12939,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12965,7 +12965,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12991,7 +12991,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13017,7 +13017,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13043,7 +13043,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13069,7 +13069,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13095,7 +13095,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13121,7 +13121,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13147,7 +13147,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13173,7 +13173,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13199,7 +13199,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13225,7 +13225,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13251,7 +13251,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13277,7 +13277,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13303,7 +13303,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13329,7 +13329,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13355,7 +13355,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13381,7 +13381,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13407,7 +13407,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13433,7 +13433,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13459,7 +13459,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13485,7 +13485,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13511,7 +13511,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13537,7 +13537,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13563,7 +13563,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13589,7 +13589,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13615,7 +13615,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13641,7 +13641,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13667,7 +13667,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13693,7 +13693,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13719,7 +13719,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13745,7 +13745,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13771,7 +13771,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13797,7 +13797,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13823,7 +13823,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13849,7 +13849,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13875,7 +13875,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13901,7 +13901,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13927,7 +13927,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13953,7 +13953,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13979,7 +13979,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14005,7 +14005,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14031,7 +14031,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14057,7 +14057,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14083,7 +14083,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14109,7 +14109,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14135,7 +14135,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14161,7 +14161,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14187,7 +14187,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14213,7 +14213,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14239,7 +14239,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14265,7 +14265,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14291,7 +14291,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14317,7 +14317,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14343,7 +14343,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14369,7 +14369,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14395,7 +14395,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14421,7 +14421,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14447,7 +14447,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14473,7 +14473,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14499,7 +14499,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14525,7 +14525,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G370" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14551,7 +14551,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14577,7 +14577,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14603,7 +14603,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14629,7 +14629,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14655,7 +14655,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G375" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14681,7 +14681,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14707,7 +14707,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14733,7 +14733,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14759,7 +14759,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14785,7 +14785,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14811,7 +14811,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14837,7 +14837,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G382" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14863,7 +14863,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14889,7 +14889,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14915,7 +14915,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14941,7 +14941,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14967,7 +14967,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14993,7 +14993,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15019,7 +15019,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15045,7 +15045,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15071,7 +15071,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15097,7 +15097,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15123,7 +15123,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G399" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G401" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15357,7 +15357,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G404" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15435,7 +15435,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15461,7 +15461,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G407" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15513,7 +15513,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15539,7 +15539,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15617,7 +15617,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G412" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15643,7 +15643,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G413" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15721,7 +15721,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G419" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15825,7 +15825,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15851,7 +15851,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G422" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15903,7 +15903,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G423" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15929,7 +15929,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G425" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G426" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16007,7 +16007,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16033,7 +16033,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G428" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G429" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16111,7 +16111,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G432" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G433" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G435" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16241,7 +16241,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G436" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16267,7 +16267,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G437" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16319,7 +16319,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G440" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16371,7 +16371,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16397,7 +16397,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16423,7 +16423,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16449,7 +16449,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16475,7 +16475,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16501,7 +16501,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16527,7 +16527,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G447" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16579,7 +16579,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G453" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G454" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G455" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G456" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G457" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16813,7 +16813,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16839,7 +16839,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G459" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16865,7 +16865,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16891,7 +16891,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16917,7 +16917,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G462" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16943,7 +16943,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G463" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16969,7 +16969,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16995,7 +16995,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17021,7 +17021,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G466" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17047,7 +17047,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17073,7 +17073,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G468" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17099,7 +17099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17125,7 +17125,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17151,7 +17151,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G471" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17177,7 +17177,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G472" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17203,7 +17203,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G473" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17229,7 +17229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G474" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17255,7 +17255,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17281,7 +17281,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17307,7 +17307,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17333,7 +17333,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G479" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17385,7 +17385,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G480" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G481" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G482" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17463,7 +17463,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G484" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G485" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G486" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G487" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G488" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G490" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G492" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G494" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G496" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G499" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G500" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G501" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G502" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18035,7 +18035,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18061,7 +18061,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G506" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18087,7 +18087,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G507" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18113,7 +18113,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18139,7 +18139,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G509" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18165,7 +18165,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G510" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G511" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18217,7 +18217,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G512" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18243,7 +18243,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G513" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G516" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G517" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>10</v>
       </c>
       <c r="G519" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G521" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G522" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G523" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G524" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G525" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>10</v>
       </c>
       <c r="G526" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G527" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G528" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G529" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G530" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G531" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G534" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G537" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G538" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G539" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G540" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G541" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G543" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G545" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G546" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G547" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G549" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G550" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G552" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G553" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G554" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G556" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G557" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G561" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>11</v>
       </c>
       <c r="G562" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G565" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G568" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G569" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G572" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19803,7 +19803,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19829,7 +19829,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19855,7 +19855,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19881,7 +19881,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G576" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19907,7 +19907,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G577" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19933,7 +19933,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19959,7 +19959,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19985,7 +19985,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G580" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20011,7 +20011,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G581" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20037,7 +20037,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20063,7 +20063,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20089,7 +20089,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20115,7 +20115,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20141,7 +20141,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G586" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20167,7 +20167,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20193,7 +20193,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G588" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20219,7 +20219,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G589" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20245,7 +20245,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20271,7 +20271,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G591" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20297,7 +20297,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G592" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20323,7 +20323,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G593" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20349,7 +20349,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G594" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20375,7 +20375,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G595" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20401,7 +20401,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G596" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20427,7 +20427,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G597" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20453,7 +20453,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G598" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20479,7 +20479,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20505,7 +20505,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20531,7 +20531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G601" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20557,7 +20557,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20583,7 +20583,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G603" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20609,7 +20609,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G604" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20635,7 +20635,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G605" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20661,7 +20661,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20687,7 +20687,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G607" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20713,7 +20713,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20739,7 +20739,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G609" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20765,7 +20765,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G610" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20791,7 +20791,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G611" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20817,7 +20817,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G612" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20843,7 +20843,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20869,7 +20869,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20895,7 +20895,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G615" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20921,7 +20921,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G616" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20947,7 +20947,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G617" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20973,7 +20973,7 @@
         <v>11</v>
       </c>
       <c r="G618" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20999,7 +20999,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G619" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21025,7 +21025,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21051,7 +21051,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G621" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21077,7 +21077,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21103,7 +21103,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G623" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21129,7 +21129,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G624" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21155,7 +21155,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21181,7 +21181,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G626" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21207,7 +21207,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G627" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21233,7 +21233,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G628" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21259,7 +21259,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G629" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21285,7 +21285,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G630" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21311,7 +21311,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G631" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21337,7 +21337,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21363,7 +21363,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21389,7 +21389,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G634" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21415,7 +21415,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G635" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21441,7 +21441,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G636" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21467,7 +21467,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G637" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21493,7 +21493,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G638" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21519,7 +21519,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G639" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21545,7 +21545,7 @@
         <v>10.5</v>
       </c>
       <c r="G640" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21571,7 +21571,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G641" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21597,7 +21597,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G642" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21623,7 +21623,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21649,7 +21649,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G644" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21675,7 +21675,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G645" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21701,7 +21701,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21727,7 +21727,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21753,7 +21753,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21779,7 +21779,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G649" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21805,7 +21805,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G650" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21831,7 +21831,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21857,7 +21857,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G652" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21883,7 +21883,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21909,7 +21909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G654" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21935,7 +21935,7 @@
         <v>9.75</v>
       </c>
       <c r="G655" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21961,7 +21961,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21987,7 +21987,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G657" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22013,7 +22013,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22039,7 +22039,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22065,7 +22065,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G660" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22091,7 +22091,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G661" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22117,7 +22117,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G662" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22143,7 +22143,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22169,7 +22169,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G664" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22195,7 +22195,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G665" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22221,7 +22221,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G666" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22247,7 +22247,7 @@
         <v>9.5</v>
       </c>
       <c r="G667" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22273,7 +22273,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22299,7 +22299,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22325,7 +22325,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22351,7 +22351,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22377,7 +22377,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G672" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22403,7 +22403,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G673" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22429,7 +22429,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G674" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22455,7 +22455,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22481,7 +22481,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G676" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22507,7 +22507,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G677" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22533,7 +22533,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G678" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22559,7 +22559,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G679" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22585,7 +22585,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G680" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22611,7 +22611,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22637,7 +22637,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22663,7 +22663,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22689,7 +22689,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G684" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22715,7 +22715,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G685" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22741,7 +22741,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G686" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22767,7 +22767,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G687" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22793,7 +22793,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22819,7 +22819,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22845,7 +22845,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G690" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22871,7 +22871,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G691" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22897,7 +22897,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22923,7 +22923,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G693" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22949,7 +22949,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G694" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22975,7 +22975,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G695" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23001,7 +23001,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23027,7 +23027,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G697" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23053,7 +23053,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G698" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23079,7 +23079,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G699" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23105,7 +23105,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G700" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23131,7 +23131,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G701" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23157,7 +23157,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23183,7 +23183,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G703" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23209,7 +23209,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23235,7 +23235,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G705" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23287,7 +23287,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24873,7 +24873,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25107,7 +25107,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G777" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25133,7 +25133,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G778" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25159,7 +25159,7 @@
         <v>9.5</v>
       </c>
       <c r="G779" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25185,7 +25185,7 @@
         <v>9.75</v>
       </c>
       <c r="G780" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25211,7 +25211,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G781" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25289,7 +25289,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G784" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25341,7 +25341,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G786" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25419,7 +25419,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25471,7 +25471,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G791" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25523,7 +25523,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25575,7 +25575,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25601,7 +25601,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G796" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25653,7 +25653,7 @@
         <v>9.75</v>
       </c>
       <c r="G798" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25705,7 +25705,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G800" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25731,7 +25731,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G801" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25757,7 +25757,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25887,7 +25887,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G807" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25939,7 +25939,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25965,7 +25965,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G810" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26173,7 +26173,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G818" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26329,7 +26329,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26485,7 +26485,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26823,7 +26823,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G843" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26875,7 +26875,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G845" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -69861,7 +69861,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909837963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>17857</v>
@@ -69882,6 +69882,32 @@
         <v>1520</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6912615741</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>18225</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>34.5499992370605</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>33.5499992370605</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>33.7999992370605</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="1524">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007520675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2299222946167</t>
+    <t xml:space="preserve">6.39007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992277145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.26996088027954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0937933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
+    <t xml:space="preserve">6.09379386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.08578586578369</t>
@@ -80,43 +80,43 @@
     <t xml:space="preserve">5.74946594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72143888473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7254433631897</t>
+    <t xml:space="preserve">5.72143936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72544288635254</t>
   </si>
   <si>
     <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9977011680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164896011353</t>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559532165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164848327637</t>
   </si>
   <si>
     <t xml:space="preserve">6.00570964813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84956121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386960983276</t>
+    <t xml:space="preserve">5.84956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749300003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17387008666992</t>
   </si>
   <si>
     <t xml:space="preserve">6.14984655380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20589971542358</t>
+    <t xml:space="preserve">6.20590019226074</t>
   </si>
   <si>
     <t xml:space="preserve">6.29398345947266</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">6.22191572189331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19789171218872</t>
+    <t xml:space="preserve">6.19789218902588</t>
   </si>
   <si>
     <t xml:space="preserve">6.20990324020386</t>
@@ -134,49 +134,49 @@
     <t xml:space="preserve">6.406090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394582748413</t>
+    <t xml:space="preserve">6.45813894271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417448043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2379298210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394535064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.19388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14183855056763</t>
+    <t xml:space="preserve">6.14183950424194</t>
   </si>
   <si>
     <t xml:space="preserve">6.15385007858276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10980844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1138129234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969411849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0177206993103</t>
+    <t xml:space="preserve">6.10980892181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11381244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98969459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
   </si>
   <si>
     <t xml:space="preserve">5.94965600967407</t>
@@ -185,61 +185,61 @@
     <t xml:space="preserve">6.13383150100708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05375480651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785455703735</t>
+    <t xml:space="preserve">6.05375528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15785360336304</t>
   </si>
   <si>
     <t xml:space="preserve">6.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1018009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371717453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764448165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11781597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377481460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06977033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19342517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2265453338623</t>
+    <t xml:space="preserve">6.18187665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390676498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10180044174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11781644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07377433776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06976985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19342470169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22654581069946</t>
   </si>
   <si>
     <t xml:space="preserve">6.07336616516113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16030645370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998573303223</t>
+    <t xml:space="preserve">6.16030550003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998477935791</t>
   </si>
   <si>
     <t xml:space="preserve">6.09406566619873</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">6.16858530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18928527832031</t>
+    <t xml:space="preserve">6.18928480148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.20170497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19756555557251</t>
+    <t xml:space="preserve">6.11890554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19756603240967</t>
   </si>
   <si>
     <t xml:space="preserve">6.12718534469604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1396050453186</t>
+    <t xml:space="preserve">6.13960552215576</t>
   </si>
   <si>
     <t xml:space="preserve">6.11062526702881</t>
@@ -278,37 +278,37 @@
     <t xml:space="preserve">5.89534568786621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8125467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04024600982666</t>
+    <t xml:space="preserve">5.90776586532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81254625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024648666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.961585521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394668579102</t>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394620895386</t>
   </si>
   <si>
     <t xml:space="preserve">5.78770637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8622260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636638641357</t>
+    <t xml:space="preserve">5.86222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190576553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636686325073</t>
   </si>
   <si>
     <t xml:space="preserve">6.12304544448853</t>
@@ -317,25 +317,25 @@
     <t xml:space="preserve">6.01540565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10234546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26794528961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15616512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0319652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820604324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17686557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25138521194458</t>
+    <t xml:space="preserve">6.10234594345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26794481277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.156165599823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03196477890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1768651008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25138568878174</t>
   </si>
   <si>
     <t xml:space="preserve">6.13132572174072</t>
@@ -344,61 +344,61 @@
     <t xml:space="preserve">6.15202522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14374542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07750558853149</t>
+    <t xml:space="preserve">6.14374494552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07750511169434</t>
   </si>
   <si>
     <t xml:space="preserve">6.14788579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06922626495361</t>
+    <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96986627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10648536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642587661743</t>
+    <t xml:space="preserve">5.96986532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10648584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95330572128296</t>
+    <t xml:space="preserve">5.9533052444458</t>
   </si>
   <si>
     <t xml:space="preserve">6.03610563278198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95744657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298643112183</t>
+    <t xml:space="preserve">5.95744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298547744751</t>
   </si>
   <si>
     <t xml:space="preserve">5.88706636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93260622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8249659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668615341187</t>
+    <t xml:space="preserve">5.93260669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668663024902</t>
   </si>
   <si>
     <t xml:space="preserve">5.84980630874634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85808658599854</t>
+    <t xml:space="preserve">5.85808610916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.75872659683228</t>
@@ -416,37 +416,37 @@
     <t xml:space="preserve">5.92018604278564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06094598770142</t>
+    <t xml:space="preserve">6.06094551086426</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290367126465</t>
+    <t xml:space="preserve">6.45010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
     <t xml:space="preserve">6.5494647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45424461364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29278564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45838499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38386535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042543411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2348256111145</t>
+    <t xml:space="preserve">6.45424509048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29278516769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4583854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23482513427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.33832550048828</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40870428085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37558460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34246492385864</t>
+    <t xml:space="preserve">6.40870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37558507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3424654006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.49150514602661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33418464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37144565582275</t>
+    <t xml:space="preserve">6.33418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144470214844</t>
   </si>
   <si>
     <t xml:space="preserve">6.30520486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39214515686035</t>
+    <t xml:space="preserve">6.39214468002319</t>
   </si>
   <si>
     <t xml:space="preserve">6.18514537811279</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">5.97400569915771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01126575469971</t>
+    <t xml:space="preserve">6.01126623153687</t>
   </si>
   <si>
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782583236694</t>
+    <t xml:space="preserve">6.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
@@ -506,55 +506,55 @@
     <t xml:space="preserve">6.28450536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41284465789795</t>
+    <t xml:space="preserve">6.41284513473511</t>
   </si>
   <si>
     <t xml:space="preserve">6.24310541152954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69850397109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.17272567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69850444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194341659546</t>
   </si>
   <si>
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334384918213</t>
+    <t xml:space="preserve">6.72334432601929</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990440368652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03798389434814</t>
+    <t xml:space="preserve">7.03798341751099</t>
   </si>
   <si>
     <t xml:space="preserve">7.20358228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17874240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384256362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01314449310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07938289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142333984375</t>
+    <t xml:space="preserve">7.1787428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384304046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01314353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07938241958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">7.05454349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98830413818359</t>
+    <t xml:space="preserve">6.98830270767212</t>
   </si>
   <si>
     <t xml:space="preserve">7.20772314071655</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">7.60102272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63414335250854</t>
+    <t xml:space="preserve">7.63414287567139</t>
   </si>
   <si>
     <t xml:space="preserve">7.59688282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08766412734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370269775391</t>
+    <t xml:space="preserve">7.0876636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370365142822</t>
   </si>
   <si>
     <t xml:space="preserve">7.47682285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48924207687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542194366455</t>
+    <t xml:space="preserve">7.48924255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542289733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.27810335159302</t>
@@ -593,40 +593,40 @@
     <t xml:space="preserve">7.1704626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10422325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94276428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0711030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486373901367</t>
+    <t xml:space="preserve">7.10422229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9427638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07110404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486421585083</t>
   </si>
   <si>
     <t xml:space="preserve">6.83512401580811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894319534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932292938232</t>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.22842216491699</t>
@@ -635,79 +635,79 @@
     <t xml:space="preserve">7.2698221206665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54306221008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64242172241211</t>
+    <t xml:space="preserve">7.54306173324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64242219924927</t>
   </si>
   <si>
     <t xml:space="preserve">7.69210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07297992706299</t>
+    <t xml:space="preserve">7.65898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9032416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00673961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03158187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0729808807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.85356092453003</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25928211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19304180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514125823975</t>
+    <t xml:space="preserve">8.25928020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25513935089111</t>
   </si>
   <si>
     <t xml:space="preserve">8.48697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49526023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39590072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43730068206787</t>
+    <t xml:space="preserve">8.49526119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3627815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39590167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43729877471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.62773990631104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63602066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5946216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52838134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966041564941</t>
+    <t xml:space="preserve">8.63601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59461879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52838039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966136932373</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986072540283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76662111282349</t>
+    <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
     <t xml:space="preserve">7.96120119094849</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51181888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60290050506592</t>
+    <t xml:space="preserve">8.51181983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60289859771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.77677917480469</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">9.37293720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4474573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.085015296936</t>
+    <t xml:space="preserve">9.44745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595363616943</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">10.4907350540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6894540786743</t>
+    <t xml:space="preserve">10.6894550323486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7556943893433</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4602632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87489414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615329742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209192276001</t>
+    <t xml:space="preserve">10.460262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615339279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209182739258</t>
   </si>
   <si>
     <t xml:space="preserve">10.0530500411987</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">10.1803035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0784997940063</t>
+    <t xml:space="preserve">10.078501701355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839092254639</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6638689041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6129674911499</t>
+    <t xml:space="preserve">10.6638669967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772291183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7232532501221</t>
+    <t xml:space="preserve">10.7232542037964</t>
   </si>
   <si>
     <t xml:space="preserve">10.6469011306763</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">10.6299333572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384181976318</t>
+    <t xml:space="preserve">10.6384172439575</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584575653076</t>
+    <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2736225128174</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">10.3075580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0445671081543</t>
+    <t xml:space="preserve">10.04456615448</t>
   </si>
   <si>
     <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247756958008</t>
+    <t xml:space="preserve">9.83247661590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.78157424926758</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">9.43374824523926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1028881072998</t>
+    <t xml:space="preserve">9.10288906097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924022674561</t>
+    <t xml:space="preserve">9.17923927307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23862552642822</t>
+    <t xml:space="preserve">9.23862648010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.23014259338379</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37436389923096</t>
+    <t xml:space="preserve">9.21317386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37436294555664</t>
   </si>
   <si>
     <t xml:space="preserve">9.68825531005859</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">10.0954685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90034484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944248199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227210998535</t>
+    <t xml:space="preserve">10.0360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90034580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227220535278</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2821073532104</t>
+    <t xml:space="preserve">10.2821063995361</t>
   </si>
   <si>
     <t xml:space="preserve">10.2566566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2905902862549</t>
+    <t xml:space="preserve">10.2905912399292</t>
   </si>
   <si>
     <t xml:space="preserve">10.366943359375</t>
@@ -902,49 +902,49 @@
     <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0191164016724</t>
+    <t xml:space="preserve">10.019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.96821403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89186096191406</t>
+    <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764060974121</t>
+    <t xml:space="preserve">9.74764156341553</t>
   </si>
   <si>
     <t xml:space="preserve">9.51010036468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.70522403717041</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56948471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66280555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39133071899414</t>
+    <t xml:space="preserve">9.35739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56948566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66280460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50161647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39132976531982</t>
   </si>
   <si>
     <t xml:space="preserve">9.28104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38284587860107</t>
+    <t xml:space="preserve">9.38284778594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.45071601867676</t>
@@ -953,31 +953,31 @@
     <t xml:space="preserve">9.51858425140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27255916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645343780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583873748779</t>
+    <t xml:space="preserve">9.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583778381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612354278564</t>
+    <t xml:space="preserve">9.75612449645996</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399368286133</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">9.77309322357178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79854393005371</t>
+    <t xml:space="preserve">9.79854202270508</t>
   </si>
   <si>
     <t xml:space="preserve">9.69673919677734</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">9.67128849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79005908966064</t>
+    <t xml:space="preserve">9.62887001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79005813598633</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">9.47616672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1368236541748</t>
+    <t xml:space="preserve">9.13682270050049</t>
   </si>
   <si>
     <t xml:space="preserve">9.00108432769775</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">8.59387397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32664012908936</t>
+    <t xml:space="preserve">8.07637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32663917541504</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182571411133</t>
@@ -1031,28 +1031,28 @@
     <t xml:space="preserve">8.12303352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62780666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33088207244873</t>
+    <t xml:space="preserve">8.6278076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3308801651001</t>
   </si>
   <si>
     <t xml:space="preserve">8.34360694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19514560699463</t>
+    <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37330150604248</t>
+    <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.31391620635986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29270553588867</t>
+    <t xml:space="preserve">8.29270648956299</t>
   </si>
   <si>
     <t xml:space="preserve">8.09334087371826</t>
@@ -1070,52 +1070,52 @@
     <t xml:space="preserve">7.80065727233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91094350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580205917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881269454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02122974395752</t>
+    <t xml:space="preserve">7.91094541549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580015182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881174087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02123069763184</t>
   </si>
   <si>
     <t xml:space="preserve">8.0127477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16121101379395</t>
+    <t xml:space="preserve">8.25452995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2248363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2884635925293</t>
+    <t xml:space="preserve">8.05092334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28846549987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56842231750488</t>
+    <t xml:space="preserve">8.5684232711792</t>
   </si>
   <si>
     <t xml:space="preserve">8.5175199508667</t>
@@ -1124,37 +1124,37 @@
     <t xml:space="preserve">8.73809432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5514554977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48358726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50055503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325832366943</t>
+    <t xml:space="preserve">8.55145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48358535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50055408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.58538913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3817834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01699066162109</t>
+    <t xml:space="preserve">8.46661853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45813465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38178443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.99153995513916</t>
@@ -1166,16 +1166,16 @@
     <t xml:space="preserve">8.12727642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3223991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75506019592285</t>
+    <t xml:space="preserve">7.97457075119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32239818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90776538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506114959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.82292938232422</t>
@@ -1184,43 +1184,43 @@
     <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235595703125</t>
+    <t xml:space="preserve">8.61932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235786437988</t>
   </si>
   <si>
     <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94169902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36588001251221</t>
+    <t xml:space="preserve">8.94169998168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36587905883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.24710941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12834072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11137104034424</t>
+    <t xml:space="preserve">9.12833976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11137199401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.04350280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09440422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26407623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142372131348</t>
+    <t xml:space="preserve">9.09440517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26407718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41678142547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142381668091</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705490112305</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">10.6723518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6214513778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9607944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4358749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698085784912</t>
+    <t xml:space="preserve">10.6214504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9607934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4358739852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680067062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.543098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8729000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.836256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4148416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3049068450928</t>
+    <t xml:space="preserve">11.8729009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8362560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4148426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3049077987671</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865839004517</t>
@@ -1265,37 +1265,37 @@
     <t xml:space="preserve">10.9567823410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4987239837646</t>
+    <t xml:space="preserve">10.8834934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">10.7002696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6086578369141</t>
+    <t xml:space="preserve">10.6086568832397</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4803991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.004017829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569583892822</t>
+    <t xml:space="preserve">10.4804000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569488525391</t>
   </si>
   <si>
     <t xml:space="preserve">10.058985710144</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788543701172</t>
+    <t xml:space="preserve">10.2788553237915</t>
   </si>
   <si>
     <t xml:space="preserve">10.0773086547852</t>
@@ -1304,19 +1304,19 @@
     <t xml:space="preserve">10.2238864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2605323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1322765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071102142334</t>
+    <t xml:space="preserve">10.2605314254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1322755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071111679077</t>
   </si>
   <si>
     <t xml:space="preserve">10.3154993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437561035156</t>
+    <t xml:space="preserve">10.4437551498413</t>
   </si>
   <si>
     <t xml:space="preserve">10.3338212966919</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">10.2055644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0956315994263</t>
+    <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
     <t xml:space="preserve">9.78415012359619</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71086025238037</t>
+    <t xml:space="preserve">9.71085929870605</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65589237213135</t>
+    <t xml:space="preserve">9.67421722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65589427947998</t>
   </si>
   <si>
     <t xml:space="preserve">9.61924839019775</t>
@@ -1355,40 +1355,40 @@
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56428146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32609081268311</t>
+    <t xml:space="preserve">9.69253730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2528018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3627347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609176635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.2711238861084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06957626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08789920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93215942382812</t>
+    <t xml:space="preserve">9.06957721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08790016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93216037750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293323516846</t>
+    <t xml:space="preserve">9.03293132781982</t>
   </si>
   <si>
     <t xml:space="preserve">8.95964241027832</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94132041931152</t>
+    <t xml:space="preserve">8.94132137298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.51990604400635</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">8.28171539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92299842834473</t>
+    <t xml:space="preserve">8.92299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.70312976837158</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">8.63900089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65732383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62983989715576</t>
+    <t xml:space="preserve">8.65732288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62984085083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.35500431060791</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">8.44661617279053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39937973022461</t>
+    <t xml:space="preserve">9.39938068389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.38105773925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19783401489258</t>
+    <t xml:space="preserve">9.19783306121826</t>
   </si>
   <si>
     <t xml:space="preserve">9.00544834136963</t>
@@ -1442,34 +1442,34 @@
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04209423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96880531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628734588623</t>
+    <t xml:space="preserve">9.12454509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04209327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96880435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628639221191</t>
   </si>
   <si>
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86803245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7855806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83138561248779</t>
+    <t xml:space="preserve">8.86803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78557968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
     <t xml:space="preserve">8.84054660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77641868591309</t>
+    <t xml:space="preserve">8.7764196395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.7122917175293</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">8.59319496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40997219085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3091983795166</t>
+    <t xml:space="preserve">8.40997123718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30919742584229</t>
   </si>
   <si>
     <t xml:space="preserve">8.24506950378418</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">7.7412052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70455980300903</t>
+    <t xml:space="preserve">7.70456075668335</t>
   </si>
   <si>
     <t xml:space="preserve">7.68623781204224</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">7.59462547302246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49385213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
+    <t xml:space="preserve">7.49385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
   </si>
   <si>
     <t xml:space="preserve">7.40224075317383</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">7.08159923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10908269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16405010223389</t>
+    <t xml:space="preserve">7.10908317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16405057907104</t>
   </si>
   <si>
     <t xml:space="preserve">7.30146741867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31978940963745</t>
+    <t xml:space="preserve">7.31978988647461</t>
   </si>
   <si>
     <t xml:space="preserve">7.48469114303589</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7686882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533409118652</t>
+    <t xml:space="preserve">7.76868724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533218383789</t>
   </si>
   <si>
     <t xml:space="preserve">7.69539880752563</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">7.45720863342285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58546447753906</t>
+    <t xml:space="preserve">7.58546543121338</t>
   </si>
   <si>
     <t xml:space="preserve">7.56714296340942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817850112915</t>
+    <t xml:space="preserve">7.34727430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5121750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
@@ -1568,31 +1568,31 @@
     <t xml:space="preserve">7.15488862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06327676773071</t>
+    <t xml:space="preserve">7.06327724456787</t>
   </si>
   <si>
     <t xml:space="preserve">7.05411577224731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53965759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5304970741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47552967071533</t>
+    <t xml:space="preserve">7.43888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53965854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553014755249</t>
   </si>
   <si>
     <t xml:space="preserve">7.33811235427856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29230690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28314447402954</t>
+    <t xml:space="preserve">7.29230642318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28314590454102</t>
   </si>
   <si>
     <t xml:space="preserve">7.31062841415405</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">7.35643482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67707586288452</t>
+    <t xml:space="preserve">7.67707681655884</t>
   </si>
   <si>
     <t xml:space="preserve">7.72288274765015</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">7.86946153640747</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04352283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37332725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39165019989014</t>
+    <t xml:space="preserve">8.04352378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37332820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39164924621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.49242305755615</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">8.40081119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34584331512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33668327331543</t>
+    <t xml:space="preserve">8.3458423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
     <t xml:space="preserve">9.02377128601074</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10622119903564</t>
+    <t xml:space="preserve">9.10622215270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.05125522613525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79474258422852</t>
+    <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.66648483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85887050628662</t>
+    <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">9.01460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91383743286133</t>
+    <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467643737793</t>
@@ -1676,49 +1676,49 @@
     <t xml:space="preserve">8.8039026260376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.813063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58403396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68480682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25423049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248825073242</t>
+    <t xml:space="preserve">8.81306266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58403301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68480587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25423145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248729705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255439758301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26339244842529</t>
+    <t xml:space="preserve">8.12597465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26339340209961</t>
   </si>
   <si>
     <t xml:space="preserve">8.23590850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43745422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45577812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47410106658936</t>
+    <t xml:space="preserve">8.43745517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45577716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47410011291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.50158405303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42829322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46493911743164</t>
+    <t xml:space="preserve">8.42829418182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46493816375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.51074409484863</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">8.62067890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61151599884033</t>
+    <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.54738903045654</t>
@@ -1745,25 +1745,25 @@
     <t xml:space="preserve">8.40219116210938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18923187255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06339263916016</t>
+    <t xml:space="preserve">8.18923282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89883327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06339168548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.98595285415649</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29571056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435230255127</t>
+    <t xml:space="preserve">8.29571151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435325622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.05371189117432</t>
@@ -1778,31 +1778,31 @@
     <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15051174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97627210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96659183502197</t>
+    <t xml:space="preserve">8.1505126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97627353668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96659278869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.16987133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24731254577637</t>
+    <t xml:space="preserve">8.24731063842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14083194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92787218093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.073073387146</t>
+    <t xml:space="preserve">8.14083290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92787313461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07307243347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.08275318145752</t>
@@ -1811,25 +1811,25 @@
     <t xml:space="preserve">7.90851306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755292892456</t>
+    <t xml:space="preserve">7.93755340576172</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
+    <t xml:space="preserve">8.11179256439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.13115215301514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04403209686279</t>
+    <t xml:space="preserve">8.04403305053711</t>
   </si>
   <si>
     <t xml:space="preserve">7.94723320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20859146118164</t>
+    <t xml:space="preserve">8.20859050750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.16019248962402</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">8.00531387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01499271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979341506958</t>
+    <t xml:space="preserve">8.01499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8697943687439</t>
   </si>
   <si>
     <t xml:space="preserve">7.87947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91819286346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95691299438477</t>
+    <t xml:space="preserve">7.91819334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95691347122192</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33443164825439</t>
+    <t xml:space="preserve">8.33443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5280294418335</t>
+    <t xml:space="preserve">8.52803039550781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78938770294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14754581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13786602020264</t>
+    <t xml:space="preserve">9.14754486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13786506652832</t>
   </si>
   <si>
     <t xml:space="preserve">9.51538372039795</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">9.4863452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45730495452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55410480499268</t>
+    <t xml:space="preserve">9.45730590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44762516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55410289764404</t>
   </si>
   <si>
     <t xml:space="preserve">9.53474426269531</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0284214019775</t>
+    <t xml:space="preserve">10.0284204483032</t>
   </si>
   <si>
     <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477809906006</t>
+    <t xml:space="preserve">10.0477800369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">9.95098114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60250282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6799430847168</t>
+    <t xml:space="preserve">9.60250377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71866321563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50570392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58314228057861</t>
+    <t xml:space="preserve">9.69930362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71866226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50570297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58314323425293</t>
   </si>
   <si>
     <t xml:space="preserve">9.46698379516602</t>
@@ -1958,31 +1958,31 @@
     <t xml:space="preserve">9.35082530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43794441223145</t>
+    <t xml:space="preserve">9.43794536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77674198150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64122295379639</t>
+    <t xml:space="preserve">9.33146572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77674293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6412239074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.66058254241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11850643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09914493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0894660949707</t>
+    <t xml:space="preserve">9.11850738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09914684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08946800231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.19594573974609</t>
@@ -1997,31 +1997,31 @@
     <t xml:space="preserve">9.10882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94426822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85714817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72162818908691</t>
+    <t xml:space="preserve">8.9442663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85714721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72162914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93458843231201</t>
+    <t xml:space="preserve">8.9345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266624450684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96362781524658</t>
+    <t xml:space="preserve">8.96362686157227</t>
   </si>
   <si>
     <t xml:space="preserve">9.15722560882568</t>
@@ -2033,64 +2033,64 @@
     <t xml:space="preserve">8.97330760955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79906940460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475090026855</t>
+    <t xml:space="preserve">8.79906845092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475185394287</t>
   </si>
   <si>
     <t xml:space="preserve">7.84075403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60843563079834</t>
+    <t xml:space="preserve">7.79235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60843467712402</t>
   </si>
   <si>
     <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61811542510986</t>
+    <t xml:space="preserve">7.61811494827271</t>
   </si>
   <si>
     <t xml:space="preserve">7.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14004945755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47884798049927</t>
+    <t xml:space="preserve">6.52428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14004993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64637327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48181390762329</t>
+    <t xml:space="preserve">4.64637279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48181343078613</t>
   </si>
   <si>
     <t xml:space="preserve">4.52053356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8399715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13036966323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51756763458252</t>
+    <t xml:space="preserve">4.83997106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13036918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51756715774536</t>
   </si>
   <si>
     <t xml:space="preserve">6.04028415679932</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">5.98220443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88540554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79828548431396</t>
+    <t xml:space="preserve">5.88540506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79828596115112</t>
   </si>
   <si>
     <t xml:space="preserve">5.96284437179565</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644454956055</t>
+    <t xml:space="preserve">6.15644407272339</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22420358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42748212814331</t>
+    <t xml:space="preserve">6.43716192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22420310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42748165130615</t>
   </si>
   <si>
     <t xml:space="preserve">6.53396129608154</t>
@@ -2141,31 +2141,31 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
+    <t xml:space="preserve">7.67619466781616</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
+    <t xml:space="preserve">7.58907604217529</t>
   </si>
   <si>
     <t xml:space="preserve">7.71491432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63747549057007</t>
+    <t xml:space="preserve">7.63747501373291</t>
   </si>
   <si>
     <t xml:space="preserve">7.39547634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43419599533081</t>
+    <t xml:space="preserve">7.43419551849365</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40515661239624</t>
+    <t xml:space="preserve">7.4051570892334</t>
   </si>
   <si>
     <t xml:space="preserve">7.2793173789978</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46323585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69555377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043287277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32771730422974</t>
+    <t xml:space="preserve">7.4632363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69555521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">7.56003522872925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5987548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65683460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
+    <t xml:space="preserve">7.59875535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65683507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.31803703308105</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">7.521315574646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5406756401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51163578033447</t>
+    <t xml:space="preserve">7.54067516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51163625717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33739709854126</t>
+    <t xml:space="preserve">7.3373966217041</t>
   </si>
   <si>
     <t xml:space="preserve">7.35675621032715</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">7.45355606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64715528488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57939577102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41483592987061</t>
+    <t xml:space="preserve">7.64715480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57939529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41483640670776</t>
   </si>
   <si>
     <t xml:space="preserve">7.29867744445801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25995683670044</t>
+    <t xml:space="preserve">7.2599573135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.47291564941406</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">7.88915300369263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83107376098633</t>
+    <t xml:space="preserve">7.83107423782349</t>
   </si>
   <si>
     <t xml:space="preserve">7.74395418167114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73427391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36643743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26963758468628</t>
+    <t xml:space="preserve">7.73427438735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36643695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26963710784912</t>
   </si>
   <si>
     <t xml:space="preserve">7.21155738830566</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">7.16315793991089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12443780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22123718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70523500442505</t>
+    <t xml:space="preserve">7.12443828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22123765945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">7.72459411621094</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">7.42451620101929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14379835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04699850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11475801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17283725738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25027704238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24059772491455</t>
+    <t xml:space="preserve">7.14379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04699945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11475849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17283773422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25027656555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24059724807739</t>
   </si>
   <si>
     <t xml:space="preserve">7.20187759399414</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">7.18251752853394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.134117603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.13411808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96955919265747</t>
+    <t xml:space="preserve">6.96955871582031</t>
   </si>
   <si>
     <t xml:space="preserve">6.89211893081665</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">6.97923898696899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06635904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05667877197266</t>
+    <t xml:space="preserve">7.06635808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0566782951355</t>
   </si>
   <si>
     <t xml:space="preserve">6.8727593421936</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">6.90179967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82435941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80500078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77596044540405</t>
+    <t xml:space="preserve">6.82435989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80500030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77595996856689</t>
   </si>
   <si>
     <t xml:space="preserve">6.76628017425537</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">6.83403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8146800994873</t>
+    <t xml:space="preserve">6.78563976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81467962265015</t>
   </si>
   <si>
     <t xml:space="preserve">6.7953200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75660037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73724031448364</t>
+    <t xml:space="preserve">6.75660085678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
     <t xml:space="preserve">6.63076114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67916059494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93083953857422</t>
+    <t xml:space="preserve">6.67916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93083906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28879117965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17201471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174648284912</t>
+    <t xml:space="preserve">7.28879070281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17201519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174600601196</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49315023422241</t>
+    <t xml:space="preserve">7.49314975738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.59046411514282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5223445892334</t>
+    <t xml:space="preserve">7.52234411239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.46395587921143</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83374786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06730079650879</t>
+    <t xml:space="preserve">7.83374738693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06729984283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.03810691833496</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">8.00891208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09649467468262</t>
+    <t xml:space="preserve">8.0964937210083</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380760192871</t>
+    <t xml:space="preserve">8.19380855560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9699854850769</t>
+    <t xml:space="preserve">7.96998643875122</t>
   </si>
   <si>
     <t xml:space="preserve">7.89213562011719</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">7.65858316421509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73643398284912</t>
+    <t xml:space="preserve">7.73643445968628</t>
   </si>
   <si>
     <t xml:space="preserve">7.69750881195068</t>
@@ -2510,28 +2510,28 @@
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64885187149048</t>
+    <t xml:space="preserve">7.82401657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64885139465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912010192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56126976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84347915649414</t>
+    <t xml:space="preserve">7.60992670059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912057876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62938976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56126928329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8434796333313</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">7.79482221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01864337921143</t>
+    <t xml:space="preserve">8.01864433288574</t>
   </si>
   <si>
     <t xml:space="preserve">7.94079256057739</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29112243652344</t>
+    <t xml:space="preserve">8.29112148284912</t>
   </si>
   <si>
     <t xml:space="preserve">8.2716588973999</t>
@@ -2558,25 +2558,25 @@
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977794647217</t>
+    <t xml:space="preserve">8.33977890014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5344066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74849510192871</t>
+    <t xml:space="preserve">8.34950923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53440570831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74849605560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.67064476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68037700653076</t>
+    <t xml:space="preserve">8.68037605285645</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">9.10855674743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04043674468994</t>
+    <t xml:space="preserve">9.04043579101562</t>
   </si>
   <si>
     <t xml:space="preserve">8.75822734832764</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43709278106689</t>
+    <t xml:space="preserve">8.43709182739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.46628570556641</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488243103027</t>
+    <t xml:space="preserve">8.15488338470459</t>
   </si>
   <si>
     <t xml:space="preserve">8.23273468017578</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">8.20353984832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25219631195068</t>
+    <t xml:space="preserve">8.25219535827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.22300243377686</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">8.33004760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64145088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58306217193604</t>
+    <t xml:space="preserve">8.64144992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2672,49 +2672,49 @@
     <t xml:space="preserve">8.50521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60252571105957</t>
+    <t xml:space="preserve">8.60252666473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.83607769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70956993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84581089019775</t>
+    <t xml:space="preserve">8.70957088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.0112419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92599105834961</t>
+    <t xml:space="preserve">9.92599010467529</t>
   </si>
   <si>
     <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88706493377686</t>
+    <t xml:space="preserve">9.88706588745117</t>
   </si>
   <si>
     <t xml:space="preserve">10.3152446746826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3541717529297</t>
+    <t xml:space="preserve">10.3541707992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028942108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50754261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41022872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13775062561035</t>
+    <t xml:space="preserve">9.77028846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50754356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41022777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13775157928467</t>
   </si>
   <si>
     <t xml:space="preserve">9.07936191558838</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14748096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32264614105225</t>
+    <t xml:space="preserve">8.90419673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14748191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32264709472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.05990028381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08909511566162</t>
+    <t xml:space="preserve">9.0890941619873</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">9.5367374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8286771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86760234832764</t>
+    <t xml:space="preserve">9.82867813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86760330200195</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">9.61458778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59512519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45888519287109</t>
+    <t xml:space="preserve">9.59512424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45888614654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1864070892334</t>
+    <t xml:space="preserve">9.18640613555908</t>
   </si>
   <si>
     <t xml:space="preserve">9.17667579650879</t>
@@ -2816,40 +2816,40 @@
     <t xml:space="preserve">8.98204898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56359958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49548053741455</t>
+    <t xml:space="preserve">8.56360054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49547958374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41762924194336</t>
+    <t xml:space="preserve">8.76795959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41763019561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.28139019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37870311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39816570281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601890563965</t>
+    <t xml:space="preserve">8.37870407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71930122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39816665649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601795196533</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285415649414</t>
+    <t xml:space="preserve">8.95285511016846</t>
   </si>
   <si>
     <t xml:space="preserve">8.04783916473389</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">9.51727294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47834873199463</t>
+    <t xml:space="preserve">9.47834777832031</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5561990737915</t>
+    <t xml:space="preserve">9.37130260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55619812011719</t>
   </si>
   <si>
     <t xml:space="preserve">9.44915390014648</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136329650879</t>
+    <t xml:space="preserve">9.73136234283447</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">10.1790065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.02330493927</t>
+    <t xml:space="preserve">10.0233039855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427675247192</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">9.90652942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22533226013184</t>
+    <t xml:space="preserve">9.22533130645752</t>
   </si>
   <si>
     <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25452613830566</t>
+    <t xml:space="preserve">9.25452709197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.40049743652344</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347091674805</t>
+    <t xml:space="preserve">10.3347082138062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689199447632</t>
+    <t xml:space="preserve">11.2689189910889</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5997858047485</t>
+    <t xml:space="preserve">11.5997848510742</t>
   </si>
   <si>
     <t xml:space="preserve">11.6776361465454</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1326789855957</t>
+    <t xml:space="preserve">11.13267993927</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">11.4830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3662328720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6387119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668916702271</t>
+    <t xml:space="preserve">11.3662338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.638710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668907165527</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.572922706604</t>
+    <t xml:space="preserve">12.5729217529297</t>
   </si>
   <si>
     <t xml:space="preserve">12.4756078720093</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8991279602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8407402038574</t>
+    <t xml:space="preserve">11.6970996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299928665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8991270065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8407392501831</t>
   </si>
   <si>
     <t xml:space="preserve">10.976978302002</t>
@@ -3056,25 +3056,25 @@
     <t xml:space="preserve">10.9575157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.198468208313</t>
+    <t xml:space="preserve">10.1984691619873</t>
   </si>
   <si>
     <t xml:space="preserve">10.6071853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4709482192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132164001465</t>
+    <t xml:space="preserve">10.470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132173538208</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8602018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6266489028931</t>
+    <t xml:space="preserve">10.860200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185905456543</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">11.9695768356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9306516647339</t>
+    <t xml:space="preserve">11.9306526184082</t>
   </si>
   <si>
     <t xml:space="preserve">11.852801322937</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">11.8917264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1252784729004</t>
+    <t xml:space="preserve">12.1252794265747</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5339965820312</t>
+    <t xml:space="preserve">12.5339956283569</t>
   </si>
   <si>
     <t xml:space="preserve">12.6507730484009</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">12.8259372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8843259811401</t>
+    <t xml:space="preserve">12.8843250274658</t>
   </si>
   <si>
     <t xml:space="preserve">12.5923843383789</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.514533996582</t>
+    <t xml:space="preserve">12.5145330429077</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977565765381</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447420120239</t>
+    <t xml:space="preserve">12.1447410583496</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
@@ -3158,19 +3158,19 @@
     <t xml:space="preserve">12.5534582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4950714111328</t>
+    <t xml:space="preserve">12.4950723648071</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7870121002197</t>
+    <t xml:space="preserve">12.787013053894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2225933074951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1762657165527</t>
+    <t xml:space="preserve">13.1762666702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.962176322937</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">13.0594902038574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9427146911621</t>
+    <t xml:space="preserve">12.9427137374878</t>
   </si>
   <si>
     <t xml:space="preserve">13.1373405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0789527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4487447738647</t>
+    <t xml:space="preserve">13.0789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4487438201904</t>
   </si>
   <si>
     <t xml:space="preserve">13.468207359314</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9742374420166</t>
+    <t xml:space="preserve">13.9742383956909</t>
   </si>
   <si>
     <t xml:space="preserve">14.3051052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616509437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7527475357056</t>
+    <t xml:space="preserve">14.6165084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7527465820312</t>
   </si>
   <si>
     <t xml:space="preserve">15.1809282302856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9473743438721</t>
+    <t xml:space="preserve">14.9473733901978</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279117584229</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909610748291</t>
+    <t xml:space="preserve">16.9909591674805</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4191398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.788932800293</t>
+    <t xml:space="preserve">17.5359191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4191417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7889347076416</t>
   </si>
   <si>
     <t xml:space="preserve">17.6137676239014</t>
@@ -3266,16 +3266,16 @@
     <t xml:space="preserve">17.7500076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2949619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2755012512207</t>
+    <t xml:space="preserve">18.2949638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2755031585693</t>
   </si>
   <si>
     <t xml:space="preserve">18.2365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8204574584961</t>
+    <t xml:space="preserve">18.8204555511475</t>
   </si>
   <si>
     <t xml:space="preserve">18.7620697021484</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.547981262207</t>
+    <t xml:space="preserve">18.5479793548584</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8519821166992</t>
+    <t xml:space="preserve">19.7060108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8519802093506</t>
   </si>
   <si>
     <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.511381149292</t>
+    <t xml:space="preserve">19.5113830566406</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
@@ -3332,13 +3332,13 @@
     <t xml:space="preserve">18.8009948730469</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5090522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8788433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902503967285</t>
+    <t xml:space="preserve">18.50905418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8788452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902484893799</t>
   </si>
   <si>
     <t xml:space="preserve">18.9761600494385</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">18.5869064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6452922821045</t>
+    <t xml:space="preserve">18.6452941894531</t>
   </si>
   <si>
     <t xml:space="preserve">18.4701271057129</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">19.1513233184814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9177703857422</t>
+    <t xml:space="preserve">18.9177722930908</t>
   </si>
   <si>
     <t xml:space="preserve">18.9956226348877</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8429946899414</t>
+    <t xml:space="preserve">19.84299659729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.004114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567657470703</t>
+    <t xml:space="preserve">22.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988128662109</t>
+    <t xml:space="preserve">22.3479290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988109588623</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656024932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832759857178</t>
+    <t xml:space="preserve">21.3656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832740783691</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306243896484</t>
+    <t xml:space="preserve">20.5306224822998</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748062133789</t>
+    <t xml:space="preserve">18.0748081207275</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463237762451</t>
+    <t xml:space="preserve">18.5463218688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569282531738</t>
+    <t xml:space="preserve">17.9569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836429595947</t>
+    <t xml:space="preserve">17.4854106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836448669434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.60329246521</t>
+    <t xml:space="preserve">17.6032905578613</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0335426330566</t>
+    <t xml:space="preserve">16.7388439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.033540725708</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3578,34 +3578,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673263549805</t>
+    <t xml:space="preserve">16.2673282623291</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3459129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869739532471</t>
+    <t xml:space="preserve">15.8547487258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.345911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869720458984</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189908981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154573440552</t>
+    <t xml:space="preserve">15.6189918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154563903809</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794921875</t>
+    <t xml:space="preserve">14.4794931411743</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3626,37 +3626,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903020858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563110351562</t>
+    <t xml:space="preserve">14.9903030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563119888306</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580778121948</t>
+    <t xml:space="preserve">14.5580787658691</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956052780151</t>
+    <t xml:space="preserve">14.4991388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956043243408</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527765274048</t>
+    <t xml:space="preserve">14.8527774810791</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958097457886</t>
+    <t xml:space="preserve">15.7958106994629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653541564941</t>
+    <t xml:space="preserve">15.2653532028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567237854004</t>
+    <t xml:space="preserve">16.8567218780518</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370742797852</t>
+    <t xml:space="preserve">16.8370761871338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549541473389</t>
+    <t xml:space="preserve">16.9549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514205932617</t>
+    <t xml:space="preserve">17.1514186859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247058868408</t>
+    <t xml:space="preserve">17.5247039794922</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465301513672</t>
+    <t xml:space="preserve">19.6465282440186</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697093963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838493347168</t>
+    <t xml:space="preserve">19.4697113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838512420654</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394611358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359275817871</t>
+    <t xml:space="preserve">20.0394592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779727935791</t>
+    <t xml:space="preserve">20.6779708862305</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005786895752</t>
+    <t xml:space="preserve">22.2005805969238</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532302856445</t>
+    <t xml:space="preserve">22.0532321929932</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -4578,6 +4578,12 @@
   </si>
   <si>
     <t xml:space="preserve">33.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -70020,27 +70026,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911921296</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>31273</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>33.3499984741211</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>33.3499984741211</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>32.2000007629395</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1522</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>13837</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>33.1500015258789</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>31.2999992370605</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>32.4000015258789</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>30570</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>31.9500007629395</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>30.8999996185303</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>31.3500003814697</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>31.3999996185303</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1481</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6910185185</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>13335</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>32.4500007629395</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>32.0999984741211</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1523</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="1526">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,289 +44,292 @@
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26996040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379291534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582397460938</t>
+    <t xml:space="preserve">6.39007520675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2299222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26996088027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0937933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582445144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563343048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356473922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94565296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946546554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72544384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00570917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17386960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29398441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.406090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409730911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980796813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11381244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98969411849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965600967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15785455703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09779691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18187665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373575210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10180044174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764448165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11781597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07377481460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06977033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19342565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2265453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1685848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18928527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11890554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19756555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1271858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1396050453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81254625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470615386963</t>
   </si>
   <si>
     <t xml:space="preserve">6.08578538894653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92563343048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94565296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946641921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143888473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7254433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99770164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00570964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386913299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20589971542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2939829826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40609073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23793029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15385007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980844497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11381244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969411849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965696334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1578540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09779739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10180044174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764448165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11781644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377481460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06977033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19342565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22654485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16858577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18928527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19756603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1271858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1396050453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776586532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81254625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0402455329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94502592086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.961585521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190671920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10234498977661</t>
+    <t xml:space="preserve">6.04024600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394620895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770685195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86222553253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190576553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10234546661377</t>
   </si>
   <si>
     <t xml:space="preserve">6.26794528961182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.156165599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0319652557373</t>
+    <t xml:space="preserve">6.15616512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03196573257446</t>
   </si>
   <si>
     <t xml:space="preserve">6.09820556640625</t>
@@ -338,7 +341,7 @@
     <t xml:space="preserve">6.25138568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13132572174072</t>
+    <t xml:space="preserve">6.13132619857788</t>
   </si>
   <si>
     <t xml:space="preserve">6.15202522277832</t>
@@ -350,88 +353,88 @@
     <t xml:space="preserve">6.07750606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1478853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06922626495361</t>
+    <t xml:space="preserve">6.14788579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96986627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10648632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92432689666748</t>
+    <t xml:space="preserve">5.9698657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10648584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92432641983032</t>
   </si>
   <si>
     <t xml:space="preserve">5.95330572128296</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03610563278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298643112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496690750122</t>
+    <t xml:space="preserve">6.03610515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298595428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706684112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8249659538269</t>
   </si>
   <si>
     <t xml:space="preserve">5.81668663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84980583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75872611999512</t>
+    <t xml:space="preserve">5.84980630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75872659683228</t>
   </si>
   <si>
     <t xml:space="preserve">5.90362644195557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93674612045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87878656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92018604278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06094598770142</t>
+    <t xml:space="preserve">5.93674564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92018699645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06094646453857</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45424461364746</t>
+    <t xml:space="preserve">6.45010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290414810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45424556732178</t>
   </si>
   <si>
     <t xml:space="preserve">6.29278516769409</t>
@@ -446,7 +449,7 @@
     <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2348256111145</t>
+    <t xml:space="preserve">6.23482608795166</t>
   </si>
   <si>
     <t xml:space="preserve">6.33832550048828</t>
@@ -455,13 +458,13 @@
     <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40870428085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37558460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806427001953</t>
+    <t xml:space="preserve">6.40870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3755841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
   </si>
   <si>
     <t xml:space="preserve">6.34246492385864</t>
@@ -470,19 +473,19 @@
     <t xml:space="preserve">6.49150466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3341851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3714451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30520439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18514585494995</t>
+    <t xml:space="preserve">6.33418607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144565582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30520534515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214468002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18514490127563</t>
   </si>
   <si>
     <t xml:space="preserve">5.97400569915771</t>
@@ -491,7 +494,7 @@
     <t xml:space="preserve">6.01126623153687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01954555511475</t>
+    <t xml:space="preserve">6.0195460319519</t>
   </si>
   <si>
     <t xml:space="preserve">6.0278263092041</t>
@@ -500,34 +503,34 @@
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28450584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24310493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272567749023</t>
+    <t xml:space="preserve">6.36730575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28450536727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41284418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24310541152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272520065308</t>
   </si>
   <si>
     <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.68194484710693</t>
   </si>
   <si>
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990440368652</t>
+    <t xml:space="preserve">6.72334432601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990488052368</t>
   </si>
   <si>
     <t xml:space="preserve">7.03798389434814</t>
@@ -536,7 +539,7 @@
     <t xml:space="preserve">7.20358276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17874336242676</t>
+    <t xml:space="preserve">7.17874383926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384351730347</t>
@@ -545,10 +548,10 @@
     <t xml:space="preserve">7.01314401626587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07938385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142286300659</t>
+    <t xml:space="preserve">7.0793833732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142381668091</t>
   </si>
   <si>
     <t xml:space="preserve">7.05454397201538</t>
@@ -560,16 +563,16 @@
     <t xml:space="preserve">7.20772314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60102224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08766412734985</t>
+    <t xml:space="preserve">7.60102319717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766460418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.30294227600098</t>
@@ -578,16 +581,16 @@
     <t xml:space="preserve">7.44370222091675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47682189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810335159302</t>
+    <t xml:space="preserve">7.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4892430305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810287475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.1704626083374</t>
@@ -596,13 +599,13 @@
     <t xml:space="preserve">7.10422325134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9427638053894</t>
+    <t xml:space="preserve">6.94276428222656</t>
   </si>
   <si>
     <t xml:space="preserve">7.07110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05868291854858</t>
+    <t xml:space="preserve">7.05868339538574</t>
   </si>
   <si>
     <t xml:space="preserve">7.04212379455566</t>
@@ -611,64 +614,64 @@
     <t xml:space="preserve">7.00486326217651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83512449264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932292938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842216491699</t>
+    <t xml:space="preserve">6.83512353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894319534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842264175415</t>
   </si>
   <si>
     <t xml:space="preserve">7.26982259750366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54306125640869</t>
+    <t xml:space="preserve">7.54306173324585</t>
   </si>
   <si>
     <t xml:space="preserve">7.50994205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64242172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9032416343689</t>
+    <t xml:space="preserve">7.64242124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65898275375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324211120605</t>
   </si>
   <si>
     <t xml:space="preserve">8.00674152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03158092498779</t>
+    <t xml:space="preserve">8.03157901763916</t>
   </si>
   <si>
     <t xml:space="preserve">8.0729808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85356092453003</t>
+    <t xml:space="preserve">7.85356044769287</t>
   </si>
   <si>
     <t xml:space="preserve">8.25928115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19304275512695</t>
+    <t xml:space="preserve">8.19304180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.25514030456543</t>
@@ -677,16 +680,16 @@
     <t xml:space="preserve">8.48698043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49525928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36277961730957</t>
+    <t xml:space="preserve">8.49525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36278057098389</t>
   </si>
   <si>
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43730068206787</t>
+    <t xml:space="preserve">8.43729782104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.62773990631104</t>
@@ -707,10 +710,10 @@
     <t xml:space="preserve">8.03986167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76662015914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120119094849</t>
+    <t xml:space="preserve">7.76662158966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96120071411133</t>
   </si>
   <si>
     <t xml:space="preserve">8.17648124694824</t>
@@ -722,7 +725,7 @@
     <t xml:space="preserve">8.60290050506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.776780128479</t>
+    <t xml:space="preserve">8.77677917480469</t>
   </si>
   <si>
     <t xml:space="preserve">8.85957908630371</t>
@@ -734,37 +737,37 @@
     <t xml:space="preserve">9.4474573135376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595373153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907350540161</t>
+    <t xml:space="preserve">10.085015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1595363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907341003418</t>
   </si>
   <si>
     <t xml:space="preserve">10.6894540786743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7556943893433</t>
+    <t xml:space="preserve">10.7556953430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5790328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4602632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87489414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615329742432</t>
+    <t xml:space="preserve">10.3499746322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5790338516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615339279175</t>
   </si>
   <si>
     <t xml:space="preserve">10.1209182739258</t>
@@ -773,19 +776,19 @@
     <t xml:space="preserve">10.0530500411987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1718196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1803045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0784997940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7062873840332</t>
+    <t xml:space="preserve">10.171820640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1803035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0785007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638679504395</t>
@@ -794,10 +797,7 @@
     <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3499755859375</t>
+    <t xml:space="preserve">10.4772300720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.7232532501221</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">10.6469020843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6299324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384181976318</t>
+    <t xml:space="preserve">10.6299333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384191513062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075580596924</t>
+    <t xml:space="preserve">10.3075571060181</t>
   </si>
   <si>
     <t xml:space="preserve">10.0445680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90882873535156</t>
+    <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.83247756958008</t>
@@ -839,37 +839,37 @@
     <t xml:space="preserve">9.61190414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43374919891357</t>
+    <t xml:space="preserve">9.43374824523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.1028881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16227340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17923927307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19620800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23862552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23014259338379</t>
+    <t xml:space="preserve">9.16227245330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17924022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19620704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23862648010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23014163970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317386627197</t>
+    <t xml:space="preserve">9.21317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.37436389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825626373291</t>
+    <t xml:space="preserve">9.68825435638428</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954675674438</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">10.0360832214355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90034580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944248199463</t>
+    <t xml:space="preserve">9.90034484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944343566895</t>
   </si>
   <si>
     <t xml:space="preserve">10.2227220535278</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2821073532104</t>
+    <t xml:space="preserve">10.2821063995361</t>
   </si>
   <si>
     <t xml:space="preserve">10.2566556930542</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3669424057007</t>
+    <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057542800903</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">10.019115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96821403503418</t>
+    <t xml:space="preserve">9.9682149887085</t>
   </si>
   <si>
     <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8579273223877</t>
+    <t xml:space="preserve">9.85792636871338</t>
   </si>
   <si>
     <t xml:space="preserve">9.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51010131835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.51010227203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522403717041</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919799804688</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">9.35739517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.56948661804199</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280460357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161647796631</t>
+    <t xml:space="preserve">9.50161743164062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39132976531982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284587860107</t>
+    <t xml:space="preserve">9.28104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284683227539</t>
   </si>
   <si>
     <t xml:space="preserve">9.45071506500244</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">9.51858425140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20468997955322</t>
+    <t xml:space="preserve">9.27256107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469093322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.58645343780518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49313354492188</t>
+    <t xml:space="preserve">9.49313259124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.84096050262451</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">9.67977142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75612449645996</t>
+    <t xml:space="preserve">9.64583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75612354278564</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399368286133</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">9.77309226989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79854297637939</t>
+    <t xml:space="preserve">9.79854202270508</t>
   </si>
   <si>
     <t xml:space="preserve">9.69673919677734</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">9.47616672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108432769775</t>
+    <t xml:space="preserve">9.13682270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
     <t xml:space="preserve">8.72112560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59387397766113</t>
+    <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.07637500762939</t>
@@ -1028,43 +1028,43 @@
     <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12303352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6278076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33088111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34360790252686</t>
+    <t xml:space="preserve">8.10182476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62780666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33088302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34360694885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27149772644043</t>
+    <t xml:space="preserve">8.27149677276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31391620635986</t>
+    <t xml:space="preserve">8.31391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85155916213989</t>
+    <t xml:space="preserve">8.09334182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85155963897705</t>
   </si>
   <si>
     <t xml:space="preserve">7.82610750198364</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">7.95760440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97881269454956</t>
+    <t xml:space="preserve">7.9788122177124</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123069763184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0127477645874</t>
+    <t xml:space="preserve">8.01274681091309</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452899932861</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">8.1484842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061695098877</t>
+    <t xml:space="preserve">8.05092430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061599731445</t>
   </si>
   <si>
     <t xml:space="preserve">8.17393589019775</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56842231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5175199508667</t>
+    <t xml:space="preserve">8.5684232711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51752090454102</t>
   </si>
   <si>
     <t xml:space="preserve">8.73809432983398</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">8.50055408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325736999512</t>
+    <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.58538913726807</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">8.46661853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38178443908691</t>
+    <t xml:space="preserve">8.45813655853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3817834854126</t>
   </si>
   <si>
     <t xml:space="preserve">8.20362854003906</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">7.91518640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12727642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9745717048645</t>
+    <t xml:space="preserve">8.12727546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97457075119019</t>
   </si>
   <si>
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90776634216309</t>
+    <t xml:space="preserve">8.9077672958374</t>
   </si>
   <si>
     <t xml:space="preserve">8.75506019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77202892303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61932373046875</t>
+    <t xml:space="preserve">8.82292938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77202987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61932277679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83989715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94169902801514</t>
+    <t xml:space="preserve">8.83989810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36588001251221</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">9.24710941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12833976745605</t>
+    <t xml:space="preserve">9.12833881378174</t>
   </si>
   <si>
     <t xml:space="preserve">9.11137199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04350280761719</t>
+    <t xml:space="preserve">9.0435037612915</t>
   </si>
   <si>
     <t xml:space="preserve">9.09440422058105</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">9.41678047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142381668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705480575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6723527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6214504241943</t>
+    <t xml:space="preserve">10.2142372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6723508834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6214513778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.9607944488525</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.543098449707</t>
+    <t xml:space="preserve">11.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729009628296</t>
@@ -1256,37 +1256,37 @@
     <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4148426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9567823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
+    <t xml:space="preserve">11.4148416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9567813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834934234619</t>
   </si>
   <si>
     <t xml:space="preserve">10.4987230300903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.700270652771</t>
+    <t xml:space="preserve">10.7002696990967</t>
   </si>
   <si>
     <t xml:space="preserve">10.6086568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.645302772522</t>
+    <t xml:space="preserve">10.6453008651733</t>
   </si>
   <si>
     <t xml:space="preserve">10.4804000854492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1689195632935</t>
+    <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
     <t xml:space="preserve">10.004017829895</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">9.98569583892822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.058985710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0773086547852</t>
+    <t xml:space="preserve">10.0589847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0773077011108</t>
   </si>
   <si>
     <t xml:space="preserve">10.2238864898682</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3155002593994</t>
+    <t xml:space="preserve">10.4071102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3154983520508</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437551498413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3338203430176</t>
+    <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
     <t xml:space="preserve">10.2055654525757</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78414916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80247211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71086120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67421722412109</t>
+    <t xml:space="preserve">9.78415012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8024730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71086025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47266864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67421531677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.72918224334717</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">9.30776786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2528018951416</t>
+    <t xml:space="preserve">9.25280094146729</t>
   </si>
   <si>
     <t xml:space="preserve">9.36273574829102</t>
@@ -1376,31 +1376,31 @@
     <t xml:space="preserve">9.32609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2711238861084</t>
+    <t xml:space="preserve">9.27112293243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.06957626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08790016174316</t>
+    <t xml:space="preserve">9.08789920806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.93215942382812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87719249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03293228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.959641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94132041931152</t>
+    <t xml:space="preserve">8.8771915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03293132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94132137298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.51990604400635</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">8.70312976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900089263916</t>
+    <t xml:space="preserve">8.63900279998779</t>
   </si>
   <si>
     <t xml:space="preserve">8.65732383728027</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">8.35500431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44661521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39937973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38105773925781</t>
+    <t xml:space="preserve">8.44661617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39938068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3810567855835</t>
   </si>
   <si>
     <t xml:space="preserve">9.19783306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00544834136963</t>
+    <t xml:space="preserve">9.00544929504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454509735107</t>
+    <t xml:space="preserve">9.12454414367676</t>
   </si>
   <si>
     <t xml:space="preserve">9.04209327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96880340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628734588623</t>
+    <t xml:space="preserve">8.96880435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628829956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.88635349273682</t>
@@ -1463,19 +1463,19 @@
     <t xml:space="preserve">8.86803150177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7855806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83138561248779</t>
+    <t xml:space="preserve">8.78557968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
     <t xml:space="preserve">8.84054756164551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7764196395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7122917175293</t>
+    <t xml:space="preserve">8.77641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.59319591522217</t>
@@ -1484,37 +1484,37 @@
     <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24506950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74120426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70455980300903</t>
+    <t xml:space="preserve">8.3091983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2450704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74120473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70456027984619</t>
   </si>
   <si>
     <t xml:space="preserve">7.68623781204224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55798101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49385261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307928085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159923553467</t>
+    <t xml:space="preserve">7.55798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5946249961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938530921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307880401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159875869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.10908317565918</t>
@@ -1523,46 +1523,46 @@
     <t xml:space="preserve">7.38391876220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16405057907104</t>
+    <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
     <t xml:space="preserve">7.30146789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31978988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469114303589</t>
+    <t xml:space="preserve">7.31979036331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469161987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7686882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714200973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817802429199</t>
+    <t xml:space="preserve">7.76868724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720815658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5854640007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817850112915</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
@@ -1574,55 +1574,55 @@
     <t xml:space="preserve">7.06327676773071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05411577224731</t>
+    <t xml:space="preserve">7.05411529541016</t>
   </si>
   <si>
     <t xml:space="preserve">7.43888568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53965759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5304970741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553014755249</t>
+    <t xml:space="preserve">7.5396580696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553062438965</t>
   </si>
   <si>
     <t xml:space="preserve">7.33811235427856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29230690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2831449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31062841415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24650049209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27398443222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72288179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946058273315</t>
+    <t xml:space="preserve">7.29230642318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28314542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31062889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24650001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2739839553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.677077293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72288274765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946153640747</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37332725524902</t>
+    <t xml:space="preserve">8.37332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.39164924621582</t>
@@ -1631,25 +1631,25 @@
     <t xml:space="preserve">8.49242305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40081119537354</t>
+    <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
     <t xml:space="preserve">8.34584331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33668327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02377128601074</t>
+    <t xml:space="preserve">8.33668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73977470397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10622215270996</t>
+    <t xml:space="preserve">8.73977375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10622119903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.05125522613525</t>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648483276367</t>
+    <t xml:space="preserve">8.66648578643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01460933685303</t>
+    <t xml:space="preserve">9.01461124420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90467643737793</t>
+    <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.84970855712891</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">8.80390167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.813063621521</t>
+    <t xml:space="preserve">8.81306457519531</t>
   </si>
   <si>
     <t xml:space="preserve">8.58403396606445</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">8.68480682373047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25423049926758</t>
+    <t xml:space="preserve">8.25423145294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.38248729705811</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">8.43745517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45577716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47410011291504</t>
+    <t xml:space="preserve">8.45577621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47410106658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.50158309936523</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">8.46493911743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51074409484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62067794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61151695251465</t>
+    <t xml:space="preserve">8.51074314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62067890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21530532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70226955413818</t>
+    <t xml:space="preserve">9.21530628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70226860046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.40219116210938</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">8.18923187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89883327484131</t>
+    <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
     <t xml:space="preserve">8.06339263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98595285415649</t>
+    <t xml:space="preserve">7.98595380783081</t>
   </si>
   <si>
     <t xml:space="preserve">8.29571151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09243202209473</t>
+    <t xml:space="preserve">8.09243106842041</t>
   </si>
   <si>
     <t xml:space="preserve">8.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02467155456543</t>
+    <t xml:space="preserve">8.05371189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02467250823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">8.1505126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627401351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96659183502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16987037658691</t>
+    <t xml:space="preserve">7.97627353668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96659278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16987228393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.24731159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25699043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14083194732666</t>
+    <t xml:space="preserve">8.25699138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14083290100098</t>
   </si>
   <si>
     <t xml:space="preserve">7.92787313461304</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">7.90851306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11179161071777</t>
+    <t xml:space="preserve">7.93755388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11179256439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.13115215301514</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">7.94723320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16019153594971</t>
+    <t xml:space="preserve">8.20859050750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
     <t xml:space="preserve">7.99563264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00531387329102</t>
+    <t xml:space="preserve">8.0053129196167</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947416305542</t>
+    <t xml:space="preserve">7.8697943687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691299438477</t>
+    <t xml:space="preserve">7.95691347122192</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5280294418335</t>
+    <t xml:space="preserve">8.52803039550781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78938770294189</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">9.38954448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4863452911377</t>
+    <t xml:space="preserve">9.48634433746338</t>
   </si>
   <si>
     <t xml:space="preserve">9.45730495452881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44762420654297</t>
+    <t xml:space="preserve">9.44762516021729</t>
   </si>
   <si>
     <t xml:space="preserve">9.55410385131836</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0284214019775</t>
+    <t xml:space="preserve">9.52506446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0284204483032</t>
   </si>
   <si>
     <t xml:space="preserve">10.3188199996948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477800369263</t>
+    <t xml:space="preserve">10.0477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58314228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4669828414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8735408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40890502929688</t>
+    <t xml:space="preserve">9.58314323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40890407562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.35082530975342</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">9.43794441223145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37986469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33146476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77674293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6412239074707</t>
+    <t xml:space="preserve">9.37986373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33146572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77674198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64122295379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.66058254241943</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">9.11850643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914588928223</t>
+    <t xml:space="preserve">9.09914684295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.08946704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19594573974609</t>
+    <t xml:space="preserve">9.19594478607178</t>
   </si>
   <si>
     <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0797872543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10882568359375</t>
+    <t xml:space="preserve">9.07978630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10882663726807</t>
   </si>
   <si>
     <t xml:space="preserve">9.0120267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92490673065186</t>
+    <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
     <t xml:space="preserve">8.94426727294922</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">8.72162818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77002906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9345874786377</t>
+    <t xml:space="preserve">8.77003002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93458652496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266624450684</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">8.96362781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15722560882568</t>
+    <t xml:space="preserve">9.1572265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.05074691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97330760955811</t>
+    <t xml:space="preserve">8.97330856323242</t>
   </si>
   <si>
     <t xml:space="preserve">8.79906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32475090026855</t>
+    <t xml:space="preserve">8.32475185394287</t>
   </si>
   <si>
     <t xml:space="preserve">7.84075403213501</t>
@@ -2051,31 +2051,31 @@
     <t xml:space="preserve">7.60843515396118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53099584579468</t>
+    <t xml:space="preserve">7.53099632263184</t>
   </si>
   <si>
     <t xml:space="preserve">7.61811494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34707689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428150177002</t>
+    <t xml:space="preserve">7.34707736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428102493286</t>
   </si>
   <si>
     <t xml:space="preserve">6.58236122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14004945755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47884798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53989362716675</t>
+    <t xml:space="preserve">6.44684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14004993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47884702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.64637279510498</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037014007568</t>
+    <t xml:space="preserve">5.13036966323853</t>
   </si>
   <si>
     <t xml:space="preserve">5.51756715774536</t>
@@ -2099,37 +2099,37 @@
     <t xml:space="preserve">6.04028415679932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00156450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9822039604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88540601730347</t>
+    <t xml:space="preserve">6.00156402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98220443725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
     <t xml:space="preserve">5.79828596115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96284484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9918851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15644407272339</t>
+    <t xml:space="preserve">5.96284437179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99188470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15644454956055</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46620225906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22420358657837</t>
+    <t xml:space="preserve">6.46620178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43716192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55035591125488</t>
+    <t xml:space="preserve">7.67619466781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55035543441772</t>
   </si>
   <si>
     <t xml:space="preserve">7.58907556533813</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">7.71491479873657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63747501373291</t>
+    <t xml:space="preserve">7.63747549057007</t>
   </si>
   <si>
     <t xml:space="preserve">7.39547634124756</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44387674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49227523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46323585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69555425643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043334960938</t>
+    <t xml:space="preserve">7.44387626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49227571487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4632363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69555473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043287277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">7.59875535964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65683507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
+    <t xml:space="preserve">7.65683460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.31803703308105</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.30835723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23091697692871</t>
+    <t xml:space="preserve">7.23091745376587</t>
   </si>
   <si>
     <t xml:space="preserve">7.521315574646</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33739709854126</t>
+    <t xml:space="preserve">7.3373966217041</t>
   </si>
   <si>
     <t xml:space="preserve">7.35675621032715</t>
@@ -2240,37 +2240,37 @@
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867744445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
+    <t xml:space="preserve">7.41483640670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">7.68587493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88915348052979</t>
+    <t xml:space="preserve">7.88915300369263</t>
   </si>
   <si>
     <t xml:space="preserve">7.83107471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7439546585083</t>
+    <t xml:space="preserve">7.74395418167114</t>
   </si>
   <si>
     <t xml:space="preserve">7.73427438735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36643743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26963758468628</t>
+    <t xml:space="preserve">7.36643648147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26963710784912</t>
   </si>
   <si>
     <t xml:space="preserve">7.21155738830566</t>
@@ -2279,19 +2279,19 @@
     <t xml:space="preserve">7.16315793991089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12443780899048</t>
+    <t xml:space="preserve">7.12443828582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.22123765945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70523500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72459411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48259592056274</t>
+    <t xml:space="preserve">7.70523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7245945930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48259544372559</t>
   </si>
   <si>
     <t xml:space="preserve">7.66651439666748</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">7.14379787445068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04699897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
+    <t xml:space="preserve">7.04699945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.11475801467896</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">7.20187759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18251800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13411855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.18251752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13411808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
@@ -2354,31 +2354,31 @@
     <t xml:space="preserve">6.97923898696899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06635856628418</t>
+    <t xml:space="preserve">7.06635808944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.0566782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87275981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94051885604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90180015563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82435989379883</t>
+    <t xml:space="preserve">6.8727593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94051933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90179967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436037063599</t>
   </si>
   <si>
     <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77596044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76628017425537</t>
+    <t xml:space="preserve">6.77595996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76627969741821</t>
   </si>
   <si>
     <t xml:space="preserve">6.83403968811035</t>
@@ -2393,19 +2393,19 @@
     <t xml:space="preserve">6.7953200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75660037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73724031448364</t>
+    <t xml:space="preserve">6.75660085678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
     <t xml:space="preserve">6.63076114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67916059494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93083953857422</t>
+    <t xml:space="preserve">6.67916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93083906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28879070281982</t>
+    <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
     <t xml:space="preserve">7.17201519012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18174600601196</t>
+    <t xml:space="preserve">7.18174648284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">7.49314975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59046411514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70724010467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83374738693237</t>
+    <t xml:space="preserve">7.59046363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52234363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395635604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70723962783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83374786376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.06729984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03810691833496</t>
+    <t xml:space="preserve">8.03810596466064</t>
   </si>
   <si>
     <t xml:space="preserve">8.08676338195801</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">7.96998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89213562011719</t>
+    <t xml:space="preserve">7.89213514328003</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">7.60019493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57100105285645</t>
+    <t xml:space="preserve">7.5710015296936</t>
   </si>
   <si>
     <t xml:space="preserve">7.72670269012451</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">7.65858316421509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73643445968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69750881195068</t>
+    <t xml:space="preserve">7.73643398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69750833511353</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">7.82401657104492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64885139465332</t>
+    <t xml:space="preserve">7.64885187149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">7.63912057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62938976287842</t>
+    <t xml:space="preserve">7.62938928604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.56126928329468</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">7.8434796333313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80455446243286</t>
+    <t xml:space="preserve">7.8045539855957</t>
   </si>
   <si>
     <t xml:space="preserve">7.79482221603394</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">8.01864433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079256057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112148284912</t>
+    <t xml:space="preserve">7.94079303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112243652344</t>
   </si>
   <si>
     <t xml:space="preserve">8.2716588973999</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">8.68037605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81661605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02097415924072</t>
+    <t xml:space="preserve">8.81661701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02097511291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">8.75822734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80688381195068</t>
+    <t xml:space="preserve">8.806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">8.57333183288574</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">8.51494312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24246501922607</t>
+    <t xml:space="preserve">8.24246406555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.30085277557373</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">8.15488338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23273468017578</t>
+    <t xml:space="preserve">8.23273372650146</t>
   </si>
   <si>
     <t xml:space="preserve">8.17434501647949</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">8.64144992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58306312561035</t>
+    <t xml:space="preserve">8.58306217193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2684,37 +2684,37 @@
     <t xml:space="preserve">8.84580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0112419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92599010467529</t>
+    <t xml:space="preserve">9.01124286651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
     <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3152446746826</t>
+    <t xml:space="preserve">9.88706493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3152456283569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3541707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3736333847046</t>
+    <t xml:space="preserve">10.3736343383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.77028846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50754356384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41022777557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13775157928467</t>
+    <t xml:space="preserve">9.50754261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41022872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13775062561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.07936191558838</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">9.14748191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32264709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05990028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0890941619873</t>
+    <t xml:space="preserve">9.32264614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05989933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909320831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.11828708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24479579925537</t>
+    <t xml:space="preserve">9.24479484558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.93339157104492</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36157131195068</t>
+    <t xml:space="preserve">9.19613838195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.361572265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57566165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5367374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82867813110352</t>
+    <t xml:space="preserve">9.57566261291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53673648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8286771774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.86760330200195</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297554016113</t>
+    <t xml:space="preserve">9.67297458648682</t>
   </si>
   <si>
     <t xml:space="preserve">9.61458778381348</t>
@@ -2789,16 +2789,16 @@
     <t xml:space="preserve">9.59512424468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45888614654541</t>
+    <t xml:space="preserve">9.45888519287109</t>
   </si>
   <si>
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18640613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17667579650879</t>
+    <t xml:space="preserve">9.1864070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17667675018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.21560192108154</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">9.23506355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20586967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0015115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98204898834229</t>
+    <t xml:space="preserve">9.20587062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98204803466797</t>
   </si>
   <si>
     <t xml:space="preserve">8.56360054016113</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795959472656</t>
+    <t xml:space="preserve">8.76795864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41763019561768</t>
@@ -2849,28 +2849,28 @@
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04783916473389</t>
+    <t xml:space="preserve">8.95285415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04783821105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500381469727</t>
+    <t xml:space="preserve">8.87500286102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969131469727</t>
+    <t xml:space="preserve">9.42969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921363830566</t>
+    <t xml:space="preserve">9.80921459197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55619812011719</t>
+    <t xml:space="preserve">9.37130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
     <t xml:space="preserve">9.44915390014648</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136234283447</t>
+    <t xml:space="preserve">9.73136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595430374146</t>
+    <t xml:space="preserve">10.0038423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1595439910889</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816926956177</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">10.0233039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622301101685</t>
+    <t xml:space="preserve">10.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533130645752</t>
+    <t xml:space="preserve">9.90652847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
     <t xml:space="preserve">9.33237743377686</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">9.40049743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48808002471924</t>
+    <t xml:space="preserve">9.48807907104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.63404941558838</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">11.5803232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5997848510742</t>
+    <t xml:space="preserve">11.5997858047485</t>
   </si>
   <si>
     <t xml:space="preserve">11.6776361465454</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">11.6192474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4830093383789</t>
+    <t xml:space="preserve">11.4830083847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.3662338256836</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">11.638710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0668907165527</t>
+    <t xml:space="preserve">12.0668897628784</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">12.4756078720093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1836671829224</t>
+    <t xml:space="preserve">12.1836681365967</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970996856689</t>
+    <t xml:space="preserve">11.6970987319946</t>
   </si>
   <si>
     <t xml:space="preserve">11.2299928665161</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159034729004</t>
+    <t xml:space="preserve">11.0159025192261</t>
   </si>
   <si>
     <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7434253692627</t>
+    <t xml:space="preserve">10.743426322937</t>
   </si>
   <si>
     <t xml:space="preserve">10.9575157165527</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">10.1984691619873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071853637695</t>
+    <t xml:space="preserve">10.6071863174438</t>
   </si>
   <si>
     <t xml:space="preserve">10.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132173538208</t>
+    <t xml:space="preserve">11.1132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">10.860200881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6266498565674</t>
+    <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2105321884155</t>
+    <t xml:space="preserve">11.2105312347412</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219345092773</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695768356323</t>
+    <t xml:space="preserve">11.9695777893066</t>
   </si>
   <si>
     <t xml:space="preserve">11.9306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852801322937</t>
+    <t xml:space="preserve">11.8528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917264938354</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">12.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5339956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6507730484009</t>
+    <t xml:space="preserve">12.5339965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6507720947266</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259372711182</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8648633956909</t>
+    <t xml:space="preserve">12.8648624420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.5145330429077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3977565765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4366827011108</t>
+    <t xml:space="preserve">12.3977575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4366817474365</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2809810638428</t>
+    <t xml:space="preserve">12.2809801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447410583496</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950723648071</t>
+    <t xml:space="preserve">12.3393697738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">12.787013053894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225933074951</t>
+    <t xml:space="preserve">12.2225923538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762666702271</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">12.9427137374878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1373405456543</t>
+    <t xml:space="preserve">13.1373414993286</t>
   </si>
   <si>
     <t xml:space="preserve">13.0789518356323</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">13.9742383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051052093506</t>
+    <t xml:space="preserve">14.3051042556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.6165084838867</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">14.7527465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1809282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279117584229</t>
+    <t xml:space="preserve">15.1809272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279127120972</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359191894531</t>
+    <t xml:space="preserve">17.5359172821045</t>
   </si>
   <si>
     <t xml:space="preserve">17.4191417694092</t>
@@ -3257,25 +3257,25 @@
     <t xml:space="preserve">17.7889347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6137676239014</t>
+    <t xml:space="preserve">17.61376953125</t>
   </si>
   <si>
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500076293945</t>
+    <t xml:space="preserve">17.7500057220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.2949638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2755031585693</t>
+    <t xml:space="preserve">18.2755012512207</t>
   </si>
   <si>
     <t xml:space="preserve">18.2365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8204555511475</t>
+    <t xml:space="preserve">18.8204574584961</t>
   </si>
   <si>
     <t xml:space="preserve">18.7620697021484</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">19.0345458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0419483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.003023147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5479793548584</t>
+    <t xml:space="preserve">18.0419502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0030250549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5479774475098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">19.7060108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8519802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7546672821045</t>
+    <t xml:space="preserve">19.8519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7546653747559</t>
   </si>
   <si>
     <t xml:space="preserve">19.5113830566406</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036819458008</t>
+    <t xml:space="preserve">19.0734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036800384521</t>
   </si>
   <si>
     <t xml:space="preserve">18.898307800293</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">19.1902484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8593826293945</t>
+    <t xml:space="preserve">18.9761581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8593807220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6452941894531</t>
+    <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
     <t xml:space="preserve">18.4701271057129</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">19.0540103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1513233184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9177722930908</t>
+    <t xml:space="preserve">19.1513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9177703857422</t>
   </si>
   <si>
     <t xml:space="preserve">18.9956226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7231426239014</t>
+    <t xml:space="preserve">18.72314453125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -4587,6 +4587,9 @@
   </si>
   <si>
     <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3500003814697</t>
   </si>
 </sst>
 </file>
@@ -8011,7 +8014,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8037,7 +8040,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8063,7 +8066,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8089,7 +8092,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8141,7 +8144,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8167,7 +8170,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8193,7 +8196,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8219,7 +8222,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8245,7 +8248,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8271,7 +8274,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8375,7 +8378,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8401,7 +8404,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8453,7 +8456,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8505,7 +8508,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8531,7 +8534,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8557,7 +8560,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8609,7 +8612,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8661,7 +8664,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8687,7 +8690,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8713,7 +8716,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8765,7 +8768,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8791,7 +8794,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8817,7 +8820,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8869,7 +8872,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8921,7 +8924,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -8999,7 +9002,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9025,7 +9028,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9051,7 +9054,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9077,7 +9080,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9103,7 +9106,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9155,7 +9158,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9181,7 +9184,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9207,7 +9210,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9233,7 +9236,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9285,7 +9288,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9337,7 +9340,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9363,7 +9366,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9389,7 +9392,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9415,7 +9418,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9441,7 +9444,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9467,7 +9470,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9493,7 +9496,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9519,7 +9522,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9545,7 +9548,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9571,7 +9574,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9597,7 +9600,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9649,7 +9652,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9675,7 +9678,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9701,7 +9704,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9727,7 +9730,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9753,7 +9756,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9779,7 +9782,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9805,7 +9808,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9831,7 +9834,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9857,7 +9860,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9883,7 +9886,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9909,7 +9912,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9935,7 +9938,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9961,7 +9964,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9987,7 +9990,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10013,7 +10016,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10039,7 +10042,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10065,7 +10068,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10117,7 +10120,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10143,7 +10146,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10221,7 +10224,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10247,7 +10250,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10273,7 +10276,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10299,7 +10302,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10325,7 +10328,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10351,7 +10354,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10377,7 +10380,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10403,7 +10406,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10429,7 +10432,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10455,7 +10458,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10481,7 +10484,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10507,7 +10510,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10533,7 +10536,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10559,7 +10562,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10585,7 +10588,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10611,7 +10614,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10637,7 +10640,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10663,7 +10666,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10689,7 +10692,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10715,7 +10718,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10741,7 +10744,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10767,7 +10770,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10793,7 +10796,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10819,7 +10822,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10845,7 +10848,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10871,7 +10874,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10897,7 +10900,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10923,7 +10926,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10949,7 +10952,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10975,7 +10978,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11001,7 +11004,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11027,7 +11030,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11053,7 +11056,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11079,7 +11082,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11105,7 +11108,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11157,7 +11160,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11235,7 +11238,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11261,7 +11264,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11287,7 +11290,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11313,7 +11316,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11339,7 +11342,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11365,7 +11368,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11443,7 +11446,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11469,7 +11472,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11521,7 +11524,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11547,7 +11550,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11625,7 +11628,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11651,7 +11654,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11677,7 +11680,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11703,7 +11706,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11729,7 +11732,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11755,7 +11758,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11781,7 +11784,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11807,7 +11810,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11833,7 +11836,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11859,7 +11862,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11885,7 +11888,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11911,7 +11914,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11937,7 +11940,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11963,7 +11966,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -11989,7 +11992,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12015,7 +12018,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12041,7 +12044,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12067,7 +12070,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12093,7 +12096,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12119,7 +12122,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12145,7 +12148,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12171,7 +12174,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12197,7 +12200,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12223,7 +12226,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12249,7 +12252,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12275,7 +12278,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12301,7 +12304,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12327,7 +12330,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12353,7 +12356,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12379,7 +12382,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12405,7 +12408,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12431,7 +12434,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12457,7 +12460,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12483,7 +12486,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12509,7 +12512,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12535,7 +12538,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12561,7 +12564,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12587,7 +12590,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12613,7 +12616,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12639,7 +12642,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12665,7 +12668,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12691,7 +12694,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12717,7 +12720,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12743,7 +12746,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12769,7 +12772,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12795,7 +12798,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12821,7 +12824,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12847,7 +12850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12873,7 +12876,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12899,7 +12902,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12925,7 +12928,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12951,7 +12954,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12977,7 +12980,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13003,7 +13006,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13029,7 +13032,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13055,7 +13058,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13081,7 +13084,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13107,7 +13110,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13133,7 +13136,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13159,7 +13162,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13185,7 +13188,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13211,7 +13214,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13237,7 +13240,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13263,7 +13266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13289,7 +13292,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13315,7 +13318,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13341,7 +13344,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13367,7 +13370,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13393,7 +13396,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13419,7 +13422,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13445,7 +13448,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13471,7 +13474,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13497,7 +13500,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13523,7 +13526,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13549,7 +13552,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13575,7 +13578,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13601,7 +13604,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13627,7 +13630,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13653,7 +13656,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13679,7 +13682,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13705,7 +13708,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13731,7 +13734,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13757,7 +13760,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13783,7 +13786,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13809,7 +13812,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13835,7 +13838,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13861,7 +13864,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13887,7 +13890,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13913,7 +13916,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13939,7 +13942,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13965,7 +13968,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13991,7 +13994,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14017,7 +14020,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14043,7 +14046,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14069,7 +14072,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14095,7 +14098,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14121,7 +14124,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14147,7 +14150,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14173,7 +14176,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14199,7 +14202,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14225,7 +14228,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14251,7 +14254,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14277,7 +14280,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14303,7 +14306,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14329,7 +14332,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14355,7 +14358,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14381,7 +14384,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14407,7 +14410,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14433,7 +14436,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14615,7 +14618,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14693,7 +14696,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15369,7 +15372,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15525,7 +15528,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15551,7 +15554,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15785,7 +15788,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16591,7 +16594,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -70159,7 +70162,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911458333</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>34158</v>
@@ -70180,6 +70183,32 @@
         <v>1515</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911921296</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>43462</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>33</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>30.7000007629395</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>31.3500003814697</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="1529">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009378433228</t>
+    <t xml:space="preserve">6.41009426116943</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">6.39007472991943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39808225631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992277145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2699613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379386901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
+    <t xml:space="preserve">6.3980827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26996088027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0937933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.08578586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92563390731812</t>
+    <t xml:space="preserve">5.92563343048096</t>
   </si>
   <si>
     <t xml:space="preserve">5.85356473922729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76548147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9456524848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946546554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72144031524658</t>
+    <t xml:space="preserve">5.76548099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94565200805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143936157227</t>
   </si>
   <si>
     <t xml:space="preserve">5.72544288635254</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9977011680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00570964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84956121444702</t>
+    <t xml:space="preserve">5.99770212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762590408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164800643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00570917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84956073760986</t>
   </si>
   <si>
     <t xml:space="preserve">5.77749252319336</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">6.17386960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14984655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20589971542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29398345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191524505615</t>
+    <t xml:space="preserve">6.14984607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29398441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191476821899</t>
   </si>
   <si>
     <t xml:space="preserve">6.19789266586304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20990467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40609073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813941955566</t>
+    <t xml:space="preserve">6.20990371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.406090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813989639282</t>
   </si>
   <si>
     <t xml:space="preserve">6.41409778594971</t>
@@ -143,52 +143,52 @@
     <t xml:space="preserve">6.48616647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50218200683594</t>
+    <t xml:space="preserve">6.50218105316162</t>
   </si>
   <si>
     <t xml:space="preserve">6.49417352676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2379298210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388818740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15384960174561</t>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183950424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385055541992</t>
   </si>
   <si>
     <t xml:space="preserve">6.10980844497681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11381244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383102416992</t>
+    <t xml:space="preserve">6.1138129234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98969411849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383054733276</t>
   </si>
   <si>
     <t xml:space="preserve">6.05375528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15785455703735</t>
+    <t xml:space="preserve">6.1578540802002</t>
   </si>
   <si>
     <t xml:space="preserve">6.09779691696167</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">6.18187713623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12181997299194</t>
+    <t xml:space="preserve">6.12181949615479</t>
   </si>
   <si>
     <t xml:space="preserve">6.21390771865845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03373575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1018009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766401290894</t>
+    <t xml:space="preserve">6.03373527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10180044174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766448974609</t>
   </si>
   <si>
     <t xml:space="preserve">5.93764495849609</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">6.11781597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07377481460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06977033615112</t>
+    <t xml:space="preserve">6.07377433776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06976985931396</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22654581069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030550003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16858530044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18928527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11890602111816</t>
+    <t xml:space="preserve">6.2265453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16858577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18928575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11890554428101</t>
   </si>
   <si>
     <t xml:space="preserve">6.28864526748657</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1271858215332</t>
+    <t xml:space="preserve">6.12718534469604</t>
   </si>
   <si>
     <t xml:space="preserve">6.13960552215576</t>
@@ -275,37 +275,34 @@
     <t xml:space="preserve">6.04438638687134</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89534616470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776681900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81254625320435</t>
+    <t xml:space="preserve">5.89534568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776586532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8125467300415</t>
   </si>
   <si>
     <t xml:space="preserve">5.99470567703247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08578538894653</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.04024600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94502544403076</t>
+    <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
     <t xml:space="preserve">5.96158647537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85394620895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222648620605</t>
+    <t xml:space="preserve">5.85394668579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770589828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8622260093689</t>
   </si>
   <si>
     <t xml:space="preserve">5.91190576553345</t>
@@ -314,25 +311,25 @@
     <t xml:space="preserve">5.86636638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12304544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540565490723</t>
+    <t xml:space="preserve">6.12304496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540517807007</t>
   </si>
   <si>
     <t xml:space="preserve">6.10234546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26794481277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.156165599823</t>
+    <t xml:space="preserve">6.26794576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15616607666016</t>
   </si>
   <si>
     <t xml:space="preserve">6.03196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09820604324341</t>
+    <t xml:space="preserve">6.09820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">6.17686557769775</t>
@@ -344,13 +341,13 @@
     <t xml:space="preserve">6.13132572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15202522277832</t>
+    <t xml:space="preserve">6.15202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">6.14374542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07750606536865</t>
+    <t xml:space="preserve">6.07750558853149</t>
   </si>
   <si>
     <t xml:space="preserve">6.1478853225708</t>
@@ -365,58 +362,58 @@
     <t xml:space="preserve">5.96986627578735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642587661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92432641983032</t>
+    <t xml:space="preserve">6.10648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92432594299316</t>
   </si>
   <si>
     <t xml:space="preserve">5.95330619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03610563278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298595428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8249659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668615341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84980583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808610916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75872707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90362644195557</t>
+    <t xml:space="preserve">6.03610610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298547744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8498067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808563232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75872659683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90362596511841</t>
   </si>
   <si>
     <t xml:space="preserve">5.93674612045288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87878608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92018604278564</t>
+    <t xml:space="preserve">5.87878656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92018556594849</t>
   </si>
   <si>
     <t xml:space="preserve">6.06094551086426</t>
@@ -425,25 +422,25 @@
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45010423660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54946517944336</t>
+    <t xml:space="preserve">6.45010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290462493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
   </si>
   <si>
     <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29278564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38386487960815</t>
+    <t xml:space="preserve">6.29278516769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45838499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386583328247</t>
   </si>
   <si>
     <t xml:space="preserve">6.40042543411255</t>
@@ -452,22 +449,22 @@
     <t xml:space="preserve">6.2348256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33832550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972497940063</t>
+    <t xml:space="preserve">6.33832502365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972593307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34246444702148</t>
+    <t xml:space="preserve">6.37558555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806474685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34246397018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.49150514602661</t>
@@ -482,28 +479,28 @@
     <t xml:space="preserve">6.30520486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39214468002319</t>
+    <t xml:space="preserve">6.39214515686035</t>
   </si>
   <si>
     <t xml:space="preserve">6.18514537811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97400569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01126623153687</t>
+    <t xml:space="preserve">5.97400617599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01126670837402</t>
   </si>
   <si>
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782535552979</t>
+    <t xml:space="preserve">6.02782583236694</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730527877808</t>
+    <t xml:space="preserve">6.36730480194092</t>
   </si>
   <si>
     <t xml:space="preserve">6.28450536727905</t>
@@ -521,82 +518,82 @@
     <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.68194437026978</t>
   </si>
   <si>
     <t xml:space="preserve">6.64882469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334432601929</t>
+    <t xml:space="preserve">6.72334384918213</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990440368652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874240875244</t>
+    <t xml:space="preserve">7.03798294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874383926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384304046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01314449310303</t>
+    <t xml:space="preserve">7.01314401626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.0793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02142381668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05454349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6010217666626</t>
+    <t xml:space="preserve">7.02142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05454397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830270767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772314071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102224349976</t>
   </si>
   <si>
     <t xml:space="preserve">7.63414287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59688329696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0876636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370126724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924398422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542194366455</t>
+    <t xml:space="preserve">7.59688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48924255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542242050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.27810335159302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422277450562</t>
+    <t xml:space="preserve">7.17046403884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422325134277</t>
   </si>
   <si>
     <t xml:space="preserve">6.94276428222656</t>
@@ -605,88 +602,88 @@
     <t xml:space="preserve">7.07110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05868244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9551830291748</t>
+    <t xml:space="preserve">7.05868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486326217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518398284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.01728343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88894367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
+    <t xml:space="preserve">6.88894414901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378355026245</t>
   </si>
   <si>
     <t xml:space="preserve">6.95932340621948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22842264175415</t>
+    <t xml:space="preserve">7.22842359542847</t>
   </si>
   <si>
     <t xml:space="preserve">7.26982307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54306125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64242124557495</t>
+    <t xml:space="preserve">7.54306077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64242219924927</t>
   </si>
   <si>
     <t xml:space="preserve">7.69210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65898180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324068069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674057006836</t>
+    <t xml:space="preserve">7.65898275375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674152374268</t>
   </si>
   <si>
     <t xml:space="preserve">8.03158187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07297992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356044769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.193039894104</t>
+    <t xml:space="preserve">8.0729808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19304084777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.25514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48697948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49526023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36278057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39590072631836</t>
+    <t xml:space="preserve">8.48698043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36277961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39589977264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.43729972839355</t>
@@ -698,7 +695,7 @@
     <t xml:space="preserve">8.63602066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59462070465088</t>
+    <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.52838039398193</t>
@@ -707,37 +704,37 @@
     <t xml:space="preserve">8.32966136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03986072540283</t>
+    <t xml:space="preserve">8.03986167907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96120166778564</t>
+    <t xml:space="preserve">7.96120119094849</t>
   </si>
   <si>
     <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51182079315186</t>
+    <t xml:space="preserve">8.51181888580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.6028995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77677917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85958003997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37293720245361</t>
+    <t xml:space="preserve">8.77677822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85957908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37293815612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.4474573135376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0850162506104</t>
+    <t xml:space="preserve">10.0850172042847</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595363616943</t>
@@ -746,7 +743,7 @@
     <t xml:space="preserve">10.4907350540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6894540786743</t>
+    <t xml:space="preserve">10.6894550323486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7556943893433</t>
@@ -755,40 +752,40 @@
     <t xml:space="preserve">10.2920169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5790328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.460262298584</t>
+    <t xml:space="preserve">10.3499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5790319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
     <t xml:space="preserve">9.8748950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0615329742432</t>
+    <t xml:space="preserve">10.0615339279175</t>
   </si>
   <si>
     <t xml:space="preserve">10.1209192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0530490875244</t>
+    <t xml:space="preserve">10.0530500411987</t>
   </si>
   <si>
     <t xml:space="preserve">10.1718196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1803045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0785007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7062864303589</t>
+    <t xml:space="preserve">10.1803035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.078501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7062854766846</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638669967651</t>
@@ -797,7 +794,10 @@
     <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772291183472</t>
+    <t xml:space="preserve">10.4772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3499746322632</t>
   </si>
   <si>
     <t xml:space="preserve">10.7232532501221</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">10.6384181976318</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4178438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3584604263306</t>
+    <t xml:space="preserve">10.4178447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2736225128174</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">10.3075571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.04456615448</t>
+    <t xml:space="preserve">10.0445671081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.90882873535156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247661590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78157424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61190319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10288715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16227245330811</t>
+    <t xml:space="preserve">9.83247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78157520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61190509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1028881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.17924118041992</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">9.19620800018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23862552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23014354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33194541931152</t>
+    <t xml:space="preserve">9.23862648010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23014259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33194637298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.21317481994629</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">9.37436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825626373291</t>
+    <t xml:space="preserve">9.68825531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954675674438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90034580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944343566895</t>
+    <t xml:space="preserve">10.0360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90034484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944248199463</t>
   </si>
   <si>
     <t xml:space="preserve">10.2227220535278</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2821063995361</t>
+    <t xml:space="preserve">10.2821073532104</t>
   </si>
   <si>
     <t xml:space="preserve">10.2566556930542</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.019115447998</t>
+    <t xml:space="preserve">10.2057552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0191173553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.96821403503418</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">9.89186096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85792636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74763965606689</t>
+    <t xml:space="preserve">9.8579273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74764060974121</t>
   </si>
   <si>
     <t xml:space="preserve">9.51010036468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70522403717041</t>
+    <t xml:space="preserve">9.70522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">9.35739517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">9.50161647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39133071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071697235107</t>
+    <t xml:space="preserve">9.39132976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071601867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.51858425140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27256107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645248413086</t>
+    <t xml:space="preserve">9.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645343780518</t>
   </si>
   <si>
     <t xml:space="preserve">9.49313354492188</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">9.67977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309226989746</t>
+    <t xml:space="preserve">9.64583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75612449645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399368286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309131622314</t>
   </si>
   <si>
     <t xml:space="preserve">9.79854202270508</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">9.69674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67128944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62887001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79005813598633</t>
+    <t xml:space="preserve">9.67128849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62887096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79005908966064</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13682270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7211275100708</t>
+    <t xml:space="preserve">9.47616577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108337402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72112655639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">8.07637500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32664012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10182571411133</t>
+    <t xml:space="preserve">8.32663917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10182476043701</t>
   </si>
   <si>
     <t xml:space="preserve">8.12303352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6278076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33088207244873</t>
+    <t xml:space="preserve">8.62780666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33088111877441</t>
   </si>
   <si>
     <t xml:space="preserve">8.34360790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19514465332031</t>
+    <t xml:space="preserve">8.19514560699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
@@ -1052,46 +1052,46 @@
     <t xml:space="preserve">8.37329959869385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31391620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29270648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819942474365</t>
+    <t xml:space="preserve">8.31391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29270458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09334182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819847106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.85156011581421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610845565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580110549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957603931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9788122177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02123165130615</t>
+    <t xml:space="preserve">7.82610893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580205917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881364822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02123069763184</t>
   </si>
   <si>
     <t xml:space="preserve">8.01274681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452995300293</t>
+    <t xml:space="preserve">8.25453090667725</t>
   </si>
   <si>
     <t xml:space="preserve">8.16121101379395</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">8.1484842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22483730316162</t>
+    <t xml:space="preserve">8.05092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2248363494873</t>
   </si>
   <si>
     <t xml:space="preserve">8.2884635925293</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7380952835083</t>
+    <t xml:space="preserve">8.51752090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73809432983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.55145454406738</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">8.48358726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50055503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58539009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45813655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40723323822021</t>
+    <t xml:space="preserve">8.50055408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4581356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40723419189453</t>
   </si>
   <si>
     <t xml:space="preserve">8.3817834854126</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">8.20362854003906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01698970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99153852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518688201904</t>
+    <t xml:space="preserve">8.01698875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518640518188</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727546691895</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">8.90776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75506210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82293033599854</t>
+    <t xml:space="preserve">8.75506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82292938232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235786437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8398962020874</t>
+    <t xml:space="preserve">8.61932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
     <t xml:space="preserve">8.94169902801514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36587810516357</t>
+    <t xml:space="preserve">9.36587905883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.24710941314697</t>
@@ -1211,40 +1211,40 @@
     <t xml:space="preserve">9.11137199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04350280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09440422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26407718658447</t>
+    <t xml:space="preserve">9.04350185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09440517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26407623291016</t>
   </si>
   <si>
     <t xml:space="preserve">9.41678142547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142381668091</t>
+    <t xml:space="preserve">10.2142372131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6723527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6214513778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9607934951782</t>
+    <t xml:space="preserve">10.6723508834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.62144947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9607944488525</t>
   </si>
   <si>
     <t xml:space="preserve">11.4358739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680047988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698085784912</t>
+    <t xml:space="preserve">11.3680057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.5430994033813</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">11.8729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8362560272217</t>
+    <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2865839004517</t>
+    <t xml:space="preserve">11.3049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.286584854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.9567832946777</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.6453008651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4804010391235</t>
+    <t xml:space="preserve">10.4804000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0040187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569583892822</t>
+    <t xml:space="preserve">10.004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569679260254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0589847564697</t>
@@ -1310,22 +1310,22 @@
     <t xml:space="preserve">10.2605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1322746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071092605591</t>
+    <t xml:space="preserve">10.1322755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071102142334</t>
   </si>
   <si>
     <t xml:space="preserve">10.3155002593994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3338203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.20556640625</t>
+    <t xml:space="preserve">10.4437551498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3338212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2055654525757</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71086120605469</t>
+    <t xml:space="preserve">9.71086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">9.67421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7291841506958</t>
+    <t xml:space="preserve">9.72918319702148</t>
   </si>
   <si>
     <t xml:space="preserve">9.65589237213135</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">9.69253826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56428146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776786804199</t>
+    <t xml:space="preserve">9.56428050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776882171631</t>
   </si>
   <si>
     <t xml:space="preserve">9.25280094146729</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">9.3627347946167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957626342773</t>
+    <t xml:space="preserve">9.32608985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27112293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957721710205</t>
   </si>
   <si>
     <t xml:space="preserve">9.08789920806885</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">8.95964336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97796630859375</t>
+    <t xml:space="preserve">8.97796535491943</t>
   </si>
   <si>
     <t xml:space="preserve">8.94132137298584</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">8.28171539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92299842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7031307220459</t>
+    <t xml:space="preserve">8.92299938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70312976837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.63900089263916</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">8.65732383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62983989715576</t>
+    <t xml:space="preserve">8.62984085083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.35500335693359</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">8.44661712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39937973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3810567855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19783306121826</t>
+    <t xml:space="preserve">9.39938068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19783401489258</t>
   </si>
   <si>
     <t xml:space="preserve">9.00544929504395</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454414367676</t>
+    <t xml:space="preserve">9.12454319000244</t>
   </si>
   <si>
     <t xml:space="preserve">9.04209327697754</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">8.8863525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8680305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7855806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83138656616211</t>
+    <t xml:space="preserve">8.86803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78557968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83138561248779</t>
   </si>
   <si>
     <t xml:space="preserve">8.84054660797119</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">8.40997219085693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3091983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2450704574585</t>
+    <t xml:space="preserve">8.30919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24506950378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.7412052154541</t>
@@ -1514,52 +1514,52 @@
     <t xml:space="preserve">7.39307975769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159875869751</t>
+    <t xml:space="preserve">7.40224123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159923553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.10908317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38391876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16405010223389</t>
+    <t xml:space="preserve">7.38391828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16404962539673</t>
   </si>
   <si>
     <t xml:space="preserve">7.30146789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31978940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469161987305</t>
+    <t xml:space="preserve">7.31978988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469114303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76868772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539833068848</t>
+    <t xml:space="preserve">7.7686882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539880752563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45720815658569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5854640007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727430343628</t>
+    <t xml:space="preserve">7.58546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.5121750831604</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
+    <t xml:space="preserve">7.15488862991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05411577224731</t>
   </si>
   <si>
     <t xml:space="preserve">7.43888473510742</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">7.5396580696106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53049802780151</t>
+    <t xml:space="preserve">7.53049755096436</t>
   </si>
   <si>
     <t xml:space="preserve">7.47553062438965</t>
@@ -1598,31 +1598,31 @@
     <t xml:space="preserve">7.29230690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2831449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31062889099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24650096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27398443222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72288274765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04352378845215</t>
+    <t xml:space="preserve">7.28314542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31062841415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24650049209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2739839553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643529891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707586288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72288227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946153640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04352474212646</t>
   </si>
   <si>
     <t xml:space="preserve">8.37332725524902</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34584331512451</t>
+    <t xml:space="preserve">8.3458423614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13370609283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73977565765381</t>
+    <t xml:space="preserve">9.02377223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.10622119903564</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648578643799</t>
+    <t xml:space="preserve">8.66648483276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.85887050628662</t>
@@ -1670,31 +1670,31 @@
     <t xml:space="preserve">9.01461029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91383743286133</t>
+    <t xml:space="preserve">8.91383838653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84970855712891</t>
+    <t xml:space="preserve">8.84970951080322</t>
   </si>
   <si>
     <t xml:space="preserve">8.80390167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81306457519531</t>
+    <t xml:space="preserve">8.813063621521</t>
   </si>
   <si>
     <t xml:space="preserve">8.58403396606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68480777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25423145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248729705811</t>
+    <t xml:space="preserve">8.68480682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25423049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248825073242</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255344390869</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">8.12597370147705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26339340209961</t>
+    <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
     <t xml:space="preserve">8.2359094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43745517730713</t>
+    <t xml:space="preserve">8.43745613098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.45577812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47409915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.47410011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50158405303955</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829418182373</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">8.46493911743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51074409484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822803497314</t>
+    <t xml:space="preserve">8.51074504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822708129883</t>
   </si>
   <si>
     <t xml:space="preserve">8.62067890167236</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">8.61151695251465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738998413086</t>
+    <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530532836914</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">8.70226860046387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40219116210938</t>
+    <t xml:space="preserve">8.40219020843506</t>
   </si>
   <si>
     <t xml:space="preserve">8.18923187255859</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06339263916016</t>
+    <t xml:space="preserve">8.06339359283447</t>
   </si>
   <si>
     <t xml:space="preserve">7.98595285415649</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">8.29571056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02467346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10211277008057</t>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02467250823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.12147235870361</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627258300781</t>
+    <t xml:space="preserve">7.97627210617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.96659278869629</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">8.16987037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24731063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25699138641357</t>
+    <t xml:space="preserve">8.24731159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25699234008789</t>
   </si>
   <si>
     <t xml:space="preserve">8.14083194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92787313461304</t>
+    <t xml:space="preserve">7.92787218093872</t>
   </si>
   <si>
     <t xml:space="preserve">8.07307243347168</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">8.08275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90851402282715</t>
+    <t xml:space="preserve">7.90851306915283</t>
   </si>
   <si>
     <t xml:space="preserve">7.93755292892456</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17955112457275</t>
+    <t xml:space="preserve">8.17955207824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.11179161071777</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">8.13115215301514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04403209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94723320007324</t>
+    <t xml:space="preserve">8.04403305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94723415374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.20859146118164</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99563264846802</t>
+    <t xml:space="preserve">7.99563360214233</t>
   </si>
   <si>
     <t xml:space="preserve">8.00531387329102</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979341506958</t>
+    <t xml:space="preserve">7.8697943687439</t>
   </si>
   <si>
     <t xml:space="preserve">7.87947368621826</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">7.95691299438477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44090938568115</t>
+    <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
     <t xml:space="preserve">8.33443069458008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28603172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.227952003479</t>
+    <t xml:space="preserve">8.28603076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.45059013366699</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">8.52803039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78938865661621</t>
+    <t xml:space="preserve">8.78938770294189</t>
   </si>
   <si>
     <t xml:space="preserve">9.14754581451416</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.55410480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53474426269531</t>
+    <t xml:space="preserve">9.53474521636963</t>
   </si>
   <si>
     <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0284204483032</t>
+    <t xml:space="preserve">10.0284214019775</t>
   </si>
   <si>
     <t xml:space="preserve">10.3188190460205</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">10.0477809906006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0671415328979</t>
+    <t xml:space="preserve">10.0671405792236</t>
   </si>
   <si>
     <t xml:space="preserve">9.98970031738281</t>
@@ -1931,31 +1931,31 @@
     <t xml:space="preserve">9.95098114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60250282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67994403839111</t>
+    <t xml:space="preserve">9.60250377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6799430847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71866226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50570297241211</t>
+    <t xml:space="preserve">9.69930362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71866321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.58314323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46698379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87354278564453</t>
+    <t xml:space="preserve">9.4669828414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
     <t xml:space="preserve">9.40890407562256</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">9.33146476745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77674293518066</t>
+    <t xml:space="preserve">9.77674198150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.64122295379639</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">9.11850643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08946704864502</t>
+    <t xml:space="preserve">9.09914588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0894660949707</t>
   </si>
   <si>
     <t xml:space="preserve">9.19594573974609</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">9.07978630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10882663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.10882759094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9442663192749</t>
+    <t xml:space="preserve">8.94426727294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.85714817047119</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93458652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99266815185547</t>
+    <t xml:space="preserve">8.9345874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99266719818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.96362686157227</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.05074787139893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97330856323242</t>
+    <t xml:space="preserve">8.97330760955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.79906940460205</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">8.32475185394287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84075450897217</t>
+    <t xml:space="preserve">7.84075403213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.79235458374023</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">7.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236122131348</t>
+    <t xml:space="preserve">6.52428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236074447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.44684171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14004945755005</t>
+    <t xml:space="preserve">5.14004993438721</t>
   </si>
   <si>
     <t xml:space="preserve">5.47884798049927</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">4.52053356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83997201919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13037061691284</t>
+    <t xml:space="preserve">4.8399715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13037014007568</t>
   </si>
   <si>
     <t xml:space="preserve">5.51756763458252</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">6.46620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716192245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22420263290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42748212814331</t>
+    <t xml:space="preserve">6.43716239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22420310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42748165130615</t>
   </si>
   <si>
     <t xml:space="preserve">6.53396129608154</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.676194190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55035543441772</t>
+    <t xml:space="preserve">7.67619466781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
     <t xml:space="preserve">7.58907556533813</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">7.63747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39547634124756</t>
+    <t xml:space="preserve">7.39547681808472</t>
   </si>
   <si>
     <t xml:space="preserve">7.43419599533081</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">7.44387626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49227571487427</t>
+    <t xml:space="preserve">7.49227619171143</t>
   </si>
   <si>
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555473327637</t>
+    <t xml:space="preserve">7.69555425643921</t>
   </si>
   <si>
     <t xml:space="preserve">7.85043334960938</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">7.50195598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31803703308105</t>
+    <t xml:space="preserve">7.3180365562439</t>
   </si>
   <si>
     <t xml:space="preserve">7.30835723876953</t>
@@ -2222,37 +2222,37 @@
     <t xml:space="preserve">7.5406756401062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51163625717163</t>
+    <t xml:space="preserve">7.51163578033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3373966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35675668716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.33739709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35675621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45355606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
+    <t xml:space="preserve">7.41483592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">7.68587493896484</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">7.88915348052979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83107471466064</t>
+    <t xml:space="preserve">7.83107423782349</t>
   </si>
   <si>
     <t xml:space="preserve">7.74395418167114</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315793991089</t>
+    <t xml:space="preserve">7.16315746307373</t>
   </si>
   <si>
     <t xml:space="preserve">7.12443828582764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22123765945435</t>
+    <t xml:space="preserve">7.22123718261719</t>
   </si>
   <si>
     <t xml:space="preserve">7.70523500442505</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">7.48259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6665153503418</t>
+    <t xml:space="preserve">7.66651487350464</t>
   </si>
   <si>
     <t xml:space="preserve">7.42451620101929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14379787445068</t>
+    <t xml:space="preserve">7.14379835128784</t>
   </si>
   <si>
     <t xml:space="preserve">7.04699850082397</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">7.25027704238892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24059724807739</t>
+    <t xml:space="preserve">7.24059772491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.20187759399414</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">7.18251800537109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13411808013916</t>
+    <t xml:space="preserve">7.134117603302</t>
   </si>
   <si>
     <t xml:space="preserve">7.15347766876221</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">6.82435989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80499982833862</t>
+    <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
     <t xml:space="preserve">6.77595996856689</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">6.79531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75659990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73724031448364</t>
+    <t xml:space="preserve">6.75660037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73723983764648</t>
   </si>
   <si>
     <t xml:space="preserve">6.63076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67916059494019</t>
+    <t xml:space="preserve">6.67916011810303</t>
   </si>
   <si>
     <t xml:space="preserve">6.93083906173706</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174600601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43476152420044</t>
+    <t xml:space="preserve">7.17201471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4347620010376</t>
   </si>
   <si>
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49314975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59046363830566</t>
+    <t xml:space="preserve">7.49315023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59046411514282</t>
   </si>
   <si>
     <t xml:space="preserve">7.52234411239624</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">7.46395587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70724058151245</t>
+    <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.83374786376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06730079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03810691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08676242828369</t>
+    <t xml:space="preserve">8.06729984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03810787200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.00891208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0964937210083</t>
+    <t xml:space="preserve">8.09649467468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">8.19380855560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13541984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96998643875122</t>
+    <t xml:space="preserve">8.13541889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9699854850769</t>
   </si>
   <si>
     <t xml:space="preserve">7.89213514328003</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">7.72670269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55153846740723</t>
+    <t xml:space="preserve">7.55153799057007</t>
   </si>
   <si>
     <t xml:space="preserve">7.61965751647949</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">7.65858316421509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73643398284912</t>
+    <t xml:space="preserve">7.73643350601196</t>
   </si>
   <si>
     <t xml:space="preserve">7.69750833511353</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992670059204</t>
+    <t xml:space="preserve">7.60992622375488</t>
   </si>
   <si>
     <t xml:space="preserve">7.63912057876587</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">7.56126976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8434796333313</t>
+    <t xml:space="preserve">7.84347867965698</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
@@ -2543,22 +2543,22 @@
     <t xml:space="preserve">7.79482269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01864337921143</t>
+    <t xml:space="preserve">8.01864242553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.94079303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29112148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07703304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4468240737915</t>
+    <t xml:space="preserve">8.29112243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2716588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44682312011719</t>
   </si>
   <si>
     <t xml:space="preserve">8.33977794647217</t>
@@ -2570,34 +2570,34 @@
     <t xml:space="preserve">8.34951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53440570831299</t>
+    <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.74849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67064380645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68037605285645</t>
+    <t xml:space="preserve">8.67064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68037700653076</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10855579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04043769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75822734832764</t>
+    <t xml:space="preserve">9.10855674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04043674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789794921875</t>
+    <t xml:space="preserve">8.40789890289307</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">8.24246501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085277557373</t>
+    <t xml:space="preserve">8.30085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.32031631469727</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46628665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45655536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48574924468994</t>
+    <t xml:space="preserve">8.46628570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4565544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48575019836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.15488243103027</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">8.17434501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14515209197998</t>
+    <t xml:space="preserve">8.14515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.20353984832764</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22300148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33004856109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64145183563232</t>
+    <t xml:space="preserve">8.22300243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33004760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.58306217193604</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">8.50521183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60252475738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83607864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70957088470459</t>
+    <t xml:space="preserve">8.60252571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">8.84581089019775</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">9.01124286651611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92599105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75082588195801</t>
+    <t xml:space="preserve">9.92599010467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152465820312</t>
+    <t xml:space="preserve">10.3152456283569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3541707992554</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028846740723</t>
+    <t xml:space="preserve">9.77028942108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">8.90419769287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14748191833496</t>
+    <t xml:space="preserve">9.14748096466064</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05989933013916</t>
+    <t xml:space="preserve">9.05990028381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.0890941619873</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">9.5367374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82867813110352</t>
+    <t xml:space="preserve">9.8286771774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.86760330200195</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">9.67297554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61458778381348</t>
+    <t xml:space="preserve">9.61458683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.59512424468994</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">9.18640613555908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17667579650879</t>
+    <t xml:space="preserve">9.17667675018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.21560192108154</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56360054016113</t>
+    <t xml:space="preserve">8.98204803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56359958648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.49547958374023</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">8.76795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41762924194336</t>
+    <t xml:space="preserve">8.41763019561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.28139019012451</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">8.7193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79715251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95285511016846</t>
+    <t xml:space="preserve">8.39816570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79715347290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
     <t xml:space="preserve">8.04783821105957</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">9.98437976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51727390289307</t>
+    <t xml:space="preserve">9.51727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.47834777832031</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55619812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4491548538208</t>
+    <t xml:space="preserve">9.37130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5561990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1206188201904</t>
+    <t xml:space="preserve">9.73136329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
     <t xml:space="preserve">10.0038414001465</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">10.1595430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0816917419434</t>
+    <t xml:space="preserve">10.0816926956177</t>
   </si>
   <si>
     <t xml:space="preserve">10.1790065765381</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">9.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33237838745117</t>
+    <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.25452613830566</t>
@@ -2957,16 +2957,16 @@
     <t xml:space="preserve">9.63404941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813976287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3347072601318</t>
+    <t xml:space="preserve">9.84814071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3347082138062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.191068649292</t>
+    <t xml:space="preserve">11.1910676956177</t>
   </si>
   <si>
     <t xml:space="preserve">11.2689189910889</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.405158996582</t>
+    <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
     <t xml:space="preserve">11.13267993927</t>
@@ -3014,43 +3014,43 @@
     <t xml:space="preserve">12.0668907165527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3199062347412</t>
+    <t xml:space="preserve">12.3199071884155</t>
   </si>
   <si>
     <t xml:space="preserve">12.5729217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4756088256836</t>
+    <t xml:space="preserve">12.4756078720093</t>
   </si>
   <si>
     <t xml:space="preserve">12.1836681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.358832359314</t>
+    <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
     <t xml:space="preserve">11.6970996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2299928665161</t>
+    <t xml:space="preserve">11.2299938201904</t>
   </si>
   <si>
     <t xml:space="preserve">10.8991270065308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8407392501831</t>
+    <t xml:space="preserve">10.8407402038574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9769773483276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7045001983643</t>
+    <t xml:space="preserve">10.7045011520386</t>
   </si>
   <si>
     <t xml:space="preserve">11.0159044265747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8796653747559</t>
+    <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7434253692627</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">10.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132173538208</t>
+    <t xml:space="preserve">11.1132164001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.91858959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2105321884155</t>
+    <t xml:space="preserve">10.9185905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2105312347412</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219345092773</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
+    <t xml:space="preserve">11.9695768356323</t>
   </si>
   <si>
     <t xml:space="preserve">11.9306516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852801322937</t>
+    <t xml:space="preserve">11.8528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917274475098</t>
@@ -3116,28 +3116,28 @@
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843240737915</t>
+    <t xml:space="preserve">12.8259382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843250274658</t>
   </si>
   <si>
     <t xml:space="preserve">12.5923833847046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6313095092773</t>
+    <t xml:space="preserve">12.6313104629517</t>
   </si>
   <si>
     <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8648633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5145330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977565765381</t>
+    <t xml:space="preserve">12.8648624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.514533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977575302124</t>
   </si>
   <si>
     <t xml:space="preserve">12.4366817474365</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">12.2615184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2809810638428</t>
+    <t xml:space="preserve">12.2809801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447410583496</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">12.3393697738647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5534591674805</t>
+    <t xml:space="preserve">12.5534582138062</t>
   </si>
   <si>
     <t xml:space="preserve">12.4950704574585</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">13.0594911575317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9427137374878</t>
+    <t xml:space="preserve">12.9427146911621</t>
   </si>
   <si>
     <t xml:space="preserve">13.1373405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0789518356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4487447738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4682064056396</t>
+    <t xml:space="preserve">13.0789527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4487438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.468207359314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">14.6165084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7527465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809272766113</t>
+    <t xml:space="preserve">14.7527475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809282302856</t>
   </si>
   <si>
     <t xml:space="preserve">14.9473733901978</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">15.8621225357056</t>
   </si>
   <si>
-    <t xml:space="preserve">16.893648147583</t>
+    <t xml:space="preserve">16.8936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">16.9909591674805</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">17.5359172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4191417694092</t>
+    <t xml:space="preserve">17.4191398620605</t>
   </si>
   <si>
     <t xml:space="preserve">17.788932800293</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">17.7500057220459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2949638366699</t>
+    <t xml:space="preserve">18.2949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419502258301</t>
+    <t xml:space="preserve">19.0345458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419483184814</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.5479793548584</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8519821166992</t>
+    <t xml:space="preserve">19.7060127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8519802093506</t>
   </si>
   <si>
     <t xml:space="preserve">19.7546672821045</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">19.0734748840332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7036819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707878112793</t>
+    <t xml:space="preserve">18.7036800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.898307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707897186279</t>
   </si>
   <si>
     <t xml:space="preserve">18.8009948730469</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">18.4701271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3144264221191</t>
+    <t xml:space="preserve">18.3144283294678</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486381530762</t>
@@ -4596,6 +4596,9 @@
   </si>
   <si>
     <t xml:space="preserve">30.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5</t>
   </si>
 </sst>
 </file>
@@ -8020,7 +8023,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8046,7 +8049,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8072,7 +8075,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8098,7 +8101,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8150,7 +8153,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8176,7 +8179,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8202,7 +8205,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8228,7 +8231,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8254,7 +8257,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8280,7 +8283,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8384,7 +8387,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8410,7 +8413,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8462,7 +8465,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8514,7 +8517,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8540,7 +8543,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8566,7 +8569,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8618,7 +8621,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8670,7 +8673,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8696,7 +8699,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8722,7 +8725,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8774,7 +8777,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8800,7 +8803,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8826,7 +8829,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8878,7 +8881,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8930,7 +8933,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9008,7 +9011,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9034,7 +9037,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9060,7 +9063,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9086,7 +9089,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9112,7 +9115,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9164,7 +9167,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9190,7 +9193,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9216,7 +9219,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9242,7 +9245,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9294,7 +9297,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9346,7 +9349,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9372,7 +9375,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9398,7 +9401,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9424,7 +9427,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9450,7 +9453,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9476,7 +9479,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9502,7 +9505,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9528,7 +9531,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9554,7 +9557,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9580,7 +9583,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9606,7 +9609,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9658,7 +9661,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9684,7 +9687,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9710,7 +9713,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9736,7 +9739,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9762,7 +9765,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9788,7 +9791,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9814,7 +9817,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9840,7 +9843,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9866,7 +9869,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9892,7 +9895,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9918,7 +9921,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9944,7 +9947,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9970,7 +9973,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9996,7 +9999,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10022,7 +10025,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10048,7 +10051,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10074,7 +10077,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10126,7 +10129,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10152,7 +10155,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10230,7 +10233,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10256,7 +10259,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10282,7 +10285,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10308,7 +10311,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10334,7 +10337,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10360,7 +10363,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10386,7 +10389,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10412,7 +10415,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10438,7 +10441,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10464,7 +10467,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10490,7 +10493,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10516,7 +10519,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10542,7 +10545,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10568,7 +10571,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10594,7 +10597,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10620,7 +10623,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10646,7 +10649,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10672,7 +10675,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10698,7 +10701,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10724,7 +10727,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10750,7 +10753,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10776,7 +10779,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10802,7 +10805,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10828,7 +10831,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10854,7 +10857,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10880,7 +10883,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10906,7 +10909,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10932,7 +10935,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10958,7 +10961,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10984,7 +10987,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11010,7 +11013,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11036,7 +11039,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11062,7 +11065,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11088,7 +11091,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11114,7 +11117,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11166,7 +11169,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11244,7 +11247,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11270,7 +11273,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11296,7 +11299,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11322,7 +11325,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11348,7 +11351,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11374,7 +11377,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11452,7 +11455,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11478,7 +11481,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11530,7 +11533,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11556,7 +11559,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11634,7 +11637,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11660,7 +11663,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11686,7 +11689,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11712,7 +11715,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11738,7 +11741,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11764,7 +11767,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11790,7 +11793,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11816,7 +11819,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11842,7 +11845,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11868,7 +11871,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11894,7 +11897,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11920,7 +11923,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11946,7 +11949,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11972,7 +11975,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -11998,7 +12001,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12024,7 +12027,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12050,7 +12053,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12076,7 +12079,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12102,7 +12105,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12128,7 +12131,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12154,7 +12157,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12180,7 +12183,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12206,7 +12209,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12232,7 +12235,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12258,7 +12261,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12284,7 +12287,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12310,7 +12313,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12336,7 +12339,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12362,7 +12365,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12388,7 +12391,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12414,7 +12417,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12440,7 +12443,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12466,7 +12469,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12492,7 +12495,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12518,7 +12521,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12544,7 +12547,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12570,7 +12573,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12596,7 +12599,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12622,7 +12625,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12648,7 +12651,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12674,7 +12677,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12700,7 +12703,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12726,7 +12729,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12752,7 +12755,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12778,7 +12781,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12804,7 +12807,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12830,7 +12833,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12856,7 +12859,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12882,7 +12885,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12908,7 +12911,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12934,7 +12937,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12960,7 +12963,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12986,7 +12989,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13012,7 +13015,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13038,7 +13041,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13064,7 +13067,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13090,7 +13093,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13116,7 +13119,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13142,7 +13145,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13168,7 +13171,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13194,7 +13197,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13220,7 +13223,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13246,7 +13249,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13272,7 +13275,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13298,7 +13301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13324,7 +13327,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13350,7 +13353,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13376,7 +13379,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13402,7 +13405,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13428,7 +13431,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13454,7 +13457,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13480,7 +13483,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13506,7 +13509,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13532,7 +13535,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13558,7 +13561,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13584,7 +13587,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13610,7 +13613,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13636,7 +13639,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13662,7 +13665,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13688,7 +13691,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13714,7 +13717,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13740,7 +13743,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13766,7 +13769,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13792,7 +13795,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13818,7 +13821,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13844,7 +13847,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13870,7 +13873,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13896,7 +13899,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13922,7 +13925,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13948,7 +13951,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13974,7 +13977,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14000,7 +14003,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14026,7 +14029,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14052,7 +14055,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14078,7 +14081,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14104,7 +14107,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14130,7 +14133,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14156,7 +14159,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14182,7 +14185,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14208,7 +14211,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14234,7 +14237,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14260,7 +14263,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14286,7 +14289,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14312,7 +14315,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14338,7 +14341,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14364,7 +14367,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14390,7 +14393,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14416,7 +14419,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14442,7 +14445,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14624,7 +14627,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14702,7 +14705,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15378,7 +15381,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15534,7 +15537,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15560,7 +15563,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15794,7 +15797,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16600,7 +16603,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -70324,7 +70327,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910069444</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>39850</v>
@@ -70333,7 +70336,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="D2516" t="n">
-        <v>30.2999992370605</v>
+        <v>30.2000007629395</v>
       </c>
       <c r="E2516" t="n">
         <v>30.5</v>
@@ -70345,6 +70348,32 @@
         <v>1494</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6912615741</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>54838</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009378433228</t>
+    <t xml:space="preserve">6.41009426116943</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
+    <t xml:space="preserve">6.39007520675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
   </si>
   <si>
     <t xml:space="preserve">6.22992324829102</t>
@@ -59,61 +59,61 @@
     <t xml:space="preserve">6.09379291534424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92563390731812</t>
+    <t xml:space="preserve">6.12582445144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563343048096</t>
   </si>
   <si>
     <t xml:space="preserve">5.85356473922729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76548099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94565200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946641921997</t>
+    <t xml:space="preserve">5.76548051834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94565296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946594238281</t>
   </si>
   <si>
     <t xml:space="preserve">5.72143936157227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7254433631897</t>
+    <t xml:space="preserve">5.72544288635254</t>
   </si>
   <si>
     <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99770212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164800643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00570964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84956026077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749300003052</t>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00571012496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749252319336</t>
   </si>
   <si>
     <t xml:space="preserve">6.17386960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14984607696533</t>
+    <t xml:space="preserve">6.14984560012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.20590019226074</t>
@@ -122,31 +122,31 @@
     <t xml:space="preserve">6.29398393630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22191476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789266586304</t>
+    <t xml:space="preserve">6.22191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789171218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.20990371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.406090259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813941955566</t>
+    <t xml:space="preserve">6.40609073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813989639282</t>
   </si>
   <si>
     <t xml:space="preserve">6.41409778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48616647720337</t>
+    <t xml:space="preserve">6.48616695404053</t>
   </si>
   <si>
     <t xml:space="preserve">6.50218105316162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49417400360107</t>
+    <t xml:space="preserve">6.49417352676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.23793077468872</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">6.07777786254883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25394582748413</t>
+    <t xml:space="preserve">6.25394535064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.19388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14183950424194</t>
+    <t xml:space="preserve">6.14183855056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.15385007858276</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">6.1138129234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98969459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965648651123</t>
+    <t xml:space="preserve">5.98969411849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0177206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965600967407</t>
   </si>
   <si>
     <t xml:space="preserve">6.13383150100708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05375576019287</t>
+    <t xml:space="preserve">6.05375528335571</t>
   </si>
   <si>
     <t xml:space="preserve">6.1578540802002</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">6.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373527526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10180044174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371717453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764495849609</t>
+    <t xml:space="preserve">6.18187761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1018009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764448165894</t>
   </si>
   <si>
     <t xml:space="preserve">6.11781597137451</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">6.06977033615112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19342565536499</t>
+    <t xml:space="preserve">6.19342517852783</t>
   </si>
   <si>
     <t xml:space="preserve">6.2265453338623</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">6.07336568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16030597686768</t>
+    <t xml:space="preserve">6.16030550003052</t>
   </si>
   <si>
     <t xml:space="preserve">6.20998525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09406566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16858530044556</t>
+    <t xml:space="preserve">6.09406614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1685848236084</t>
   </si>
   <si>
     <t xml:space="preserve">6.18928527832031</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">6.20170545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890506744385</t>
+    <t xml:space="preserve">6.11890554428101</t>
   </si>
   <si>
     <t xml:space="preserve">6.28864526748657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19756603240967</t>
+    <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.1271858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13960552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062622070312</t>
+    <t xml:space="preserve">6.1396050453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062574386597</t>
   </si>
   <si>
     <t xml:space="preserve">6.04438591003418</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">5.89534616470337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90776538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8125467300415</t>
+    <t xml:space="preserve">5.90776634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81254625320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.99470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04024648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94502639770508</t>
+    <t xml:space="preserve">6.04024600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
     <t xml:space="preserve">5.96158599853516</t>
@@ -299,100 +299,100 @@
     <t xml:space="preserve">5.85394620895386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304544448853</t>
+    <t xml:space="preserve">5.78770685195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8622260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
   </si>
   <si>
     <t xml:space="preserve">6.01540613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10234546661377</t>
+    <t xml:space="preserve">6.10234594345093</t>
   </si>
   <si>
     <t xml:space="preserve">6.26794576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15616607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0319652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17686557769775</t>
+    <t xml:space="preserve">6.15616512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03196573257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1768651008606</t>
   </si>
   <si>
     <t xml:space="preserve">6.25138568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13132619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202569961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14374494552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07750606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1478853225708</t>
+    <t xml:space="preserve">6.13132572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14374542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07750558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14788579940796</t>
   </si>
   <si>
     <t xml:space="preserve">6.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05266523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96986627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642587661743</t>
+    <t xml:space="preserve">6.05266571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9698657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95330619812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03610610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744657516479</t>
+    <t xml:space="preserve">5.95330667495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03610563278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744609832764</t>
   </si>
   <si>
     <t xml:space="preserve">6.00298595428467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88706636428833</t>
+    <t xml:space="preserve">5.88706588745117</t>
   </si>
   <si>
     <t xml:space="preserve">5.9326057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82496690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668663024902</t>
+    <t xml:space="preserve">5.82496547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668615341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.84980630874634</t>
@@ -401,67 +401,67 @@
     <t xml:space="preserve">5.85808658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75872611999512</t>
+    <t xml:space="preserve">5.75872659683228</t>
   </si>
   <si>
     <t xml:space="preserve">5.90362596511841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93674612045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87878608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92018604278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06094646453857</t>
+    <t xml:space="preserve">5.93674564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87878561019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9201865196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06094598770142</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45010471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4542441368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29278564453125</t>
+    <t xml:space="preserve">6.4501051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290414810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45424509048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29278516769409</t>
   </si>
   <si>
     <t xml:space="preserve">6.45838499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38386535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042543411255</t>
+    <t xml:space="preserve">6.38386487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
     <t xml:space="preserve">6.2348256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33832502365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37558507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
+    <t xml:space="preserve">6.33832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40870428085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37558460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
   </si>
   <si>
     <t xml:space="preserve">6.34246492385864</t>
@@ -470,37 +470,37 @@
     <t xml:space="preserve">6.49150466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33418464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3714451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30520486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18514490127563</t>
+    <t xml:space="preserve">6.33418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144565582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30520534515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214563369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18514537811279</t>
   </si>
   <si>
     <t xml:space="preserve">5.97400617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01126623153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01954555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02782535552979</t>
+    <t xml:space="preserve">6.01126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0195460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730480194092</t>
+    <t xml:space="preserve">6.36730527877808</t>
   </si>
   <si>
     <t xml:space="preserve">6.28450536727905</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">6.17272520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69850397109985</t>
+    <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64882373809814</t>
+    <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
     <t xml:space="preserve">6.72334384918213</t>
@@ -530,37 +530,37 @@
     <t xml:space="preserve">6.73990488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358324050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874336242676</t>
+    <t xml:space="preserve">7.03798389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787428855896</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384304046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01314306259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07938385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142238616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05454444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60102224349976</t>
+    <t xml:space="preserve">7.01314401626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0793833732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05454397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772266387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102319717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.63414239883423</t>
@@ -572,112 +572,112 @@
     <t xml:space="preserve">7.08766412734985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30294370651245</t>
+    <t xml:space="preserve">7.30294227600098</t>
   </si>
   <si>
     <t xml:space="preserve">7.44370222091675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47682189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94276428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486326217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512449264526</t>
+    <t xml:space="preserve">7.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48924207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17046308517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94276475906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0711030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0586838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512353897095</t>
   </si>
   <si>
     <t xml:space="preserve">6.95518350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01728296279907</t>
+    <t xml:space="preserve">7.01728439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.88894319534302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91378355026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842264175415</t>
+    <t xml:space="preserve">6.91378402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842216491699</t>
   </si>
   <si>
     <t xml:space="preserve">7.2698221206665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54306268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994157791138</t>
+    <t xml:space="preserve">7.54306125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994253158569</t>
   </si>
   <si>
     <t xml:space="preserve">7.64242219924927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65898180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9032416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0729808807373</t>
+    <t xml:space="preserve">7.6921010017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65898084640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03158092498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07298183441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.85356187820435</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25928211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.193039894104</t>
+    <t xml:space="preserve">8.25928115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19304084777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.25514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49525928497314</t>
+    <t xml:space="preserve">8.48697948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36277961730957</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43729972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62773895263672</t>
+    <t xml:space="preserve">8.43729877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62773990631104</t>
   </si>
   <si>
     <t xml:space="preserve">8.63601970672607</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">8.52838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03986167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7666220664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120119094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51182079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60290050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.776780128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85957813262939</t>
+    <t xml:space="preserve">8.32966136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03986072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76662158966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96120071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51181888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6028995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77677917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85957908630371</t>
   </si>
   <si>
     <t xml:space="preserve">9.37293815612793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44745922088623</t>
+    <t xml:space="preserve">9.44745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">10.0850162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.15953540802</t>
+    <t xml:space="preserve">10.1595363616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907350540161</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">10.7556943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2920169830322</t>
+    <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
     <t xml:space="preserve">10.3499746322632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5790319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4602603912354</t>
+    <t xml:space="preserve">10.5790338516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460262298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.87489604949951</t>
@@ -767,28 +767,28 @@
     <t xml:space="preserve">10.0615329742432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1209192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0530490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1718187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1803035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.078501701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7062854766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6638679504395</t>
+    <t xml:space="preserve">10.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0530500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.171820640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1803026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0785007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7062864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6638689041138</t>
   </si>
   <si>
     <t xml:space="preserve">10.6129665374756</t>
@@ -800,34 +800,34 @@
     <t xml:space="preserve">10.7232542037964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6469020843506</t>
+    <t xml:space="preserve">10.6469011306763</t>
   </si>
   <si>
     <t xml:space="preserve">10.6299343109131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384181976318</t>
+    <t xml:space="preserve">10.6384191513062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584604263306</t>
+    <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90882873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83247756958008</t>
+    <t xml:space="preserve">10.3075580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0445671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90882968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83247661590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.78157424926758</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">9.61190414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43374729156494</t>
+    <t xml:space="preserve">9.43374824523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.1028881072998</t>
@@ -845,55 +845,55 @@
     <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924213409424</t>
+    <t xml:space="preserve">9.17924118041992</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23862552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23014163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33194541931152</t>
+    <t xml:space="preserve">9.23862743377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23014259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33194637298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.21317481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37436199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68825531005859</t>
+    <t xml:space="preserve">9.37436389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68825435638428</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954675674438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360822677612</t>
+    <t xml:space="preserve">10.0360832214355</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84944343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227220535278</t>
+    <t xml:space="preserve">9.84944248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227210998535</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2821073532104</t>
+    <t xml:space="preserve">10.2821063995361</t>
   </si>
   <si>
     <t xml:space="preserve">10.2566566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2905902862549</t>
+    <t xml:space="preserve">10.2905912399292</t>
   </si>
   <si>
     <t xml:space="preserve">10.366943359375</t>
@@ -902,46 +902,46 @@
     <t xml:space="preserve">10.2057552337646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0191164016724</t>
+    <t xml:space="preserve">10.019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.96821403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89186191558838</t>
+    <t xml:space="preserve">9.89186096191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764060974121</t>
+    <t xml:space="preserve">9.74763965606689</t>
   </si>
   <si>
     <t xml:space="preserve">9.51010036468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.70522212982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.35739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161647796631</t>
+    <t xml:space="preserve">9.50161743164062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104209899902</t>
+    <t xml:space="preserve">9.28104305267334</t>
   </si>
   <si>
     <t xml:space="preserve">9.38284683227539</t>
@@ -950,100 +950,100 @@
     <t xml:space="preserve">9.45071601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51858425140381</t>
+    <t xml:space="preserve">9.51858329772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.27256107330322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20469188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645439147949</t>
+    <t xml:space="preserve">9.20469284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645248413086</t>
   </si>
   <si>
     <t xml:space="preserve">9.49313354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8409595489502</t>
+    <t xml:space="preserve">9.84096050262451</t>
   </si>
   <si>
     <t xml:space="preserve">9.67977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75612449645996</t>
+    <t xml:space="preserve">9.64583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75612354278564</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399368286133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77309131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69674015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67128944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79005813598633</t>
+    <t xml:space="preserve">9.77309226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69673919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67128753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62887001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79005908966064</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7211275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59387493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07637405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32664012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12303352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62780666351318</t>
+    <t xml:space="preserve">9.47616672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13682270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72112655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59387302398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07637500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32663917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10182666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6278076171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.33088111877441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.195143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2714958190918</t>
+    <t xml:space="preserve">8.34360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19514560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27149677276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.37329959869385</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">8.31391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29270458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03819847106934</t>
+    <t xml:space="preserve">8.29270553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09334182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03819942474365</t>
   </si>
   <si>
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610893249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094398498535</t>
+    <t xml:space="preserve">7.82610988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094446182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.85580110549927</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">7.95760440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97881174087524</t>
+    <t xml:space="preserve">7.97881317138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123165130615</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16121101379395</t>
+    <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484842300415</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">8.08061599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17393493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2248363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28846263885498</t>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2884635925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.42420101165771</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">8.51752090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73809432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5514554977417</t>
+    <t xml:space="preserve">8.7380952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55145454406738</t>
   </si>
   <si>
     <t xml:space="preserve">8.48358631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50055503845215</t>
+    <t xml:space="preserve">8.50055313110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58538913726807</t>
+    <t xml:space="preserve">8.58538818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.46661949157715</t>
@@ -1145,46 +1145,46 @@
     <t xml:space="preserve">8.4581356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40723419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3817834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362758636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01698780059814</t>
+    <t xml:space="preserve">8.40723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38178253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.99153900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91518640518188</t>
+    <t xml:space="preserve">7.91518592834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3223991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90776538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75506019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8229284286499</t>
+    <t xml:space="preserve">7.97457075119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32239818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90776634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82292938232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61932373046875</t>
+    <t xml:space="preserve">8.61932182312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
@@ -1193,40 +1193,40 @@
     <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94169902801514</t>
+    <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36588001251221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24710845947266</t>
+    <t xml:space="preserve">9.24710941314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11137104034424</t>
+    <t xml:space="preserve">9.11137199401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.0435037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09440422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26407718658447</t>
+    <t xml:space="preserve">9.09440517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26407623291016</t>
   </si>
   <si>
     <t xml:space="preserve">9.41678237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6723518371582</t>
+    <t xml:space="preserve">10.2142381668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6723527908325</t>
   </si>
   <si>
     <t xml:space="preserve">10.6214504241943</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">11.3680057525635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4698104858398</t>
+    <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8729000091553</t>
+    <t xml:space="preserve">11.8729009628296</t>
   </si>
   <si>
     <t xml:space="preserve">11.836256980896</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
+    <t xml:space="preserve">11.3049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9567823410034</t>
@@ -1268,55 +1268,55 @@
     <t xml:space="preserve">10.8834924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4987230300903</t>
+    <t xml:space="preserve">10.498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">10.7002687454224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6086568832397</t>
+    <t xml:space="preserve">10.6086578369141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453008651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4804000854492</t>
+    <t xml:space="preserve">10.4803991317749</t>
   </si>
   <si>
     <t xml:space="preserve">10.1689214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0040187835693</t>
+    <t xml:space="preserve">10.004017829895</t>
   </si>
   <si>
     <t xml:space="preserve">9.98569583892822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">10.0589847564697</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0773077011108</t>
+    <t xml:space="preserve">10.0773086547852</t>
   </si>
   <si>
     <t xml:space="preserve">10.2238874435425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1322746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3154993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4437561035156</t>
+    <t xml:space="preserve">10.2605323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1322755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071092605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3154983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.443754196167</t>
   </si>
   <si>
     <t xml:space="preserve">10.3338203430176</t>
@@ -1328,49 +1328,49 @@
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80247211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71086120605469</t>
+    <t xml:space="preserve">9.78415107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8024730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421627044678</t>
+    <t xml:space="preserve">9.67421531677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.72918319702148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65589237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61924839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74750518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69253826141357</t>
+    <t xml:space="preserve">9.65589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69253730773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.56428146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30776786804199</t>
+    <t xml:space="preserve">9.30776691436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.25280094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32609081268311</t>
+    <t xml:space="preserve">9.3627347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609176635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.27112293243408</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">9.08789920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93215847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8771915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03293228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95964336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796535491943</t>
+    <t xml:space="preserve">8.93215942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87719249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03293132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.94132137298584</t>
@@ -1403,52 +1403,52 @@
     <t xml:space="preserve">8.51990604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28171443939209</t>
+    <t xml:space="preserve">8.28171539306641</t>
   </si>
   <si>
     <t xml:space="preserve">8.92299842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70312976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63899993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65732288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35500335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39937877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3810567855835</t>
+    <t xml:space="preserve">8.7031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63900184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62984085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35500431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44661617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39937973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105773925781</t>
   </si>
   <si>
     <t xml:space="preserve">9.19783401489258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00544929504395</t>
+    <t xml:space="preserve">9.00544834136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04209327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96880531311035</t>
+    <t xml:space="preserve">9.12454319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04209232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96880435943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.99628734588623</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86803150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78557968139648</t>
+    <t xml:space="preserve">8.8680305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7855806350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.83138656616211</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7122917175293</t>
+    <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40997219085693</t>
+    <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.30919742584229</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">8.2450704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74120473861694</t>
+    <t xml:space="preserve">7.7412052154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.70455980300903</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">7.4938530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39307975769043</t>
+    <t xml:space="preserve">7.39307928085327</t>
   </si>
   <si>
     <t xml:space="preserve">7.40224075317383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08159875869751</t>
+    <t xml:space="preserve">7.08159971237183</t>
   </si>
   <si>
     <t xml:space="preserve">7.10908317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38391923904419</t>
+    <t xml:space="preserve">7.38391780853271</t>
   </si>
   <si>
     <t xml:space="preserve">7.16405010223389</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">7.31978988647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48469161987305</t>
+    <t xml:space="preserve">7.48469114303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76868772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533361434937</t>
+    <t xml:space="preserve">7.76868867874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">7.69539833068848</t>
@@ -1547,40 +1547,40 @@
     <t xml:space="preserve">7.45720863342285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5854640007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714200973511</t>
+    <t xml:space="preserve">7.58546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714248657227</t>
   </si>
   <si>
     <t xml:space="preserve">7.34727430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51217412948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817802429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14572811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5396580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049802780151</t>
+    <t xml:space="preserve">7.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817754745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14572763442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05411577224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53965854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
   </si>
   <si>
     <t xml:space="preserve">7.47553014755249</t>
@@ -1595,46 +1595,46 @@
     <t xml:space="preserve">7.2831449508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31062936782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24650096893311</t>
+    <t xml:space="preserve">7.31062889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
     <t xml:space="preserve">7.2739839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707681655884</t>
+    <t xml:space="preserve">7.35643482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707633972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946153640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04352283477783</t>
+    <t xml:space="preserve">7.86946105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
     <t xml:space="preserve">8.37332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39164924621582</t>
+    <t xml:space="preserve">8.39165019989014</t>
   </si>
   <si>
     <t xml:space="preserve">8.49242210388184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40081119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3458423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33668231964111</t>
+    <t xml:space="preserve">8.40081024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34584426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33668327331543</t>
   </si>
   <si>
     <t xml:space="preserve">9.02377223968506</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73977565765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10622215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05125522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79474067687988</t>
+    <t xml:space="preserve">8.73977470397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10622119903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05125427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79474258422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.66648578643799</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84970760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80390167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81306457519531</t>
+    <t xml:space="preserve">8.84970951080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80390357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.813063621521</t>
   </si>
   <si>
     <t xml:space="preserve">8.58403396606445</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25423240661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12597465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26339340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2359094619751</t>
+    <t xml:space="preserve">8.25423145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26339244842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23590850830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.43745517730713</t>
@@ -1715,37 +1715,37 @@
     <t xml:space="preserve">8.50158309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42829418182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46493911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51074314117432</t>
+    <t xml:space="preserve">8.42829322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46493816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51074504852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62067794799805</t>
+    <t xml:space="preserve">8.62067985534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738998413086</t>
+    <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70226860046387</t>
+    <t xml:space="preserve">8.70226764678955</t>
   </si>
   <si>
     <t xml:space="preserve">8.40219116210938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18923187255859</t>
+    <t xml:space="preserve">8.18923282623291</t>
   </si>
   <si>
     <t xml:space="preserve">7.89883327484131</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">8.29571056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05371189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02467250823975</t>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12147331237793</t>
+    <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.15051174163818</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">7.96659278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16987228393555</t>
+    <t xml:space="preserve">8.16987133026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.24731159210205</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14083194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92787313461304</t>
+    <t xml:space="preserve">8.14083290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92787218093872</t>
   </si>
   <si>
     <t xml:space="preserve">8.07307243347168</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">8.08275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
+    <t xml:space="preserve">7.90851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.11179161071777</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">8.20859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99563264846802</t>
+    <t xml:space="preserve">8.16019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99563360214233</t>
   </si>
   <si>
     <t xml:space="preserve">8.00531387329102</t>
@@ -1844,40 +1844,40 @@
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979389190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91819429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95691394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33443164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28603267669678</t>
+    <t xml:space="preserve">7.8697943687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947463989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91819334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95691347122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33442974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">8.22795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45059108734131</t>
+    <t xml:space="preserve">8.45059013366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.52803039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78938865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14754581451416</t>
+    <t xml:space="preserve">8.78938770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14754486083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">9.4863452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45730400085449</t>
+    <t xml:space="preserve">9.45730495452881</t>
   </si>
   <si>
     <t xml:space="preserve">9.44762516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55410385131836</t>
+    <t xml:space="preserve">9.55410289764404</t>
   </si>
   <si>
     <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506446838379</t>
+    <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
     <t xml:space="preserve">10.0284204483032</t>
@@ -1916,31 +1916,31 @@
     <t xml:space="preserve">10.0477809906006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0671415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95098209381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60250282287598</t>
+    <t xml:space="preserve">10.0671405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98970127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95098114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60250377655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.6799430847168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61218452453613</t>
+    <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.69930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71866226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50570297241211</t>
+    <t xml:space="preserve">9.71866321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.58314323425293</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40890502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3508243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43794441223145</t>
+    <t xml:space="preserve">9.40890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35082530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43794536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77674293518066</t>
+    <t xml:space="preserve">9.77674198150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.64122295379639</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">9.11850738525391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0894660949707</t>
+    <t xml:space="preserve">9.09914588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08946704864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16690731048584</t>
+    <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.07978630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10882568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.10882663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">8.9442663192749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85714721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72162914276123</t>
+    <t xml:space="preserve">8.85714817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72162818908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93458652496338</t>
+    <t xml:space="preserve">8.9345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266719818115</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">9.15722560882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05074787139893</t>
+    <t xml:space="preserve">9.05074691772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.97330760955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84075355529785</t>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84075403213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.79235410690308</t>
@@ -2057,19 +2057,19 @@
     <t xml:space="preserve">7.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52428197860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14004993438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47884702682495</t>
+    <t xml:space="preserve">6.52428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14005041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.53989315032959</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">4.48181343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52053356170654</t>
+    <t xml:space="preserve">4.5205340385437</t>
   </si>
   <si>
     <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04028415679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00156402587891</t>
+    <t xml:space="preserve">5.13036918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51756715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04028463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00156497955322</t>
   </si>
   <si>
     <t xml:space="preserve">5.98220491409302</t>
@@ -2108,31 +2108,31 @@
     <t xml:space="preserve">5.79828596115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96284484863281</t>
+    <t xml:space="preserve">5.96284437179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3887619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46620178222656</t>
+    <t xml:space="preserve">6.15644407272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38876247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42748212814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5339617729187</t>
+    <t xml:space="preserve">6.22420358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42748165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.54364156723022</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55035543441772</t>
+    <t xml:space="preserve">7.67619466781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
     <t xml:space="preserve">7.58907556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71491384506226</t>
+    <t xml:space="preserve">7.71491432189941</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">7.39547634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43419647216797</t>
+    <t xml:space="preserve">7.43419599533081</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40515613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44387578964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49227619171143</t>
+    <t xml:space="preserve">7.40515661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44387626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555425643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043382644653</t>
+    <t xml:space="preserve">7.69555473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043334960938</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">7.56003522872925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59875535964966</t>
+    <t xml:space="preserve">7.5987548828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.65683507919312</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30835771560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23091697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.521315574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5406756401062</t>
+    <t xml:space="preserve">7.3180365562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30835723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23091745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52131605148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54067516326904</t>
   </si>
   <si>
     <t xml:space="preserve">7.51163625717163</t>
@@ -2222,40 +2222,40 @@
     <t xml:space="preserve">7.38579607009888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3373966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35675668716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.33739709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35675621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45355653762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25995683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
+    <t xml:space="preserve">7.41483592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2599573135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">7.68587493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88915252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107423782349</t>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107376098633</t>
   </si>
   <si>
     <t xml:space="preserve">7.74395418167114</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">7.73427438735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36643743515015</t>
+    <t xml:space="preserve">7.36643695831299</t>
   </si>
   <si>
     <t xml:space="preserve">7.26963758468628</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">7.22123765945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70523452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72459506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48259592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6665153503418</t>
+    <t xml:space="preserve">7.70523500442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4825963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66651487350464</t>
   </si>
   <si>
     <t xml:space="preserve">7.42451620101929</t>
@@ -2303,49 +2303,49 @@
     <t xml:space="preserve">7.04699897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11475801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17283773422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24059724807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2018780708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18251800537109</t>
+    <t xml:space="preserve">7.10507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11475849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17283725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25027704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24059772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20187711715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18251752853394</t>
   </si>
   <si>
     <t xml:space="preserve">7.134117603302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02763843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0760383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0179591178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96955823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89211988449097</t>
+    <t xml:space="preserve">7.02763891220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07603788375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01795864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96955871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89211893081665</t>
   </si>
   <si>
     <t xml:space="preserve">6.97923898696899</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">7.05667877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8727593421936</t>
+    <t xml:space="preserve">6.87275981903076</t>
   </si>
   <si>
     <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90179920196533</t>
+    <t xml:space="preserve">6.90179967880249</t>
   </si>
   <si>
     <t xml:space="preserve">6.82435989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80499982833862</t>
+    <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
     <t xml:space="preserve">6.77595996856689</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">6.76627969741821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564023971558</t>
+    <t xml:space="preserve">6.83404016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78563976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.8146800994873</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">6.67916059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9308385848999</t>
+    <t xml:space="preserve">6.93083906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067213058472</t>
+    <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174600601196</t>
+    <t xml:space="preserve">7.17201471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174648284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49314975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234411239624</t>
+    <t xml:space="preserve">7.49315023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59046411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5223445892334</t>
   </si>
   <si>
     <t xml:space="preserve">7.46395587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70724058151245</t>
+    <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.83374786376953</t>
@@ -2453,28 +2453,28 @@
     <t xml:space="preserve">8.03810691833496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08676242828369</t>
+    <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.00891208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0964937210083</t>
+    <t xml:space="preserve">8.09649467468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13541984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96998643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89213514328003</t>
+    <t xml:space="preserve">8.19380760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13541889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9699854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89213562011719</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">7.73643398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69750833511353</t>
+    <t xml:space="preserve">7.69750881195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">7.82401609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64885234832764</t>
+    <t xml:space="preserve">7.64885187149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992670059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912057876587</t>
+    <t xml:space="preserve">7.60992622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912010192871</t>
   </si>
   <si>
     <t xml:space="preserve">7.62938928604126</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">7.56126976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8434796333313</t>
+    <t xml:space="preserve">7.84347915649414</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79482269287109</t>
+    <t xml:space="preserve">7.79482221603394</t>
   </si>
   <si>
     <t xml:space="preserve">8.01864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079303741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07703304290771</t>
+    <t xml:space="preserve">7.94079256057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2716588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0770320892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
@@ -2564,31 +2564,31 @@
     <t xml:space="preserve">8.34951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53440570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74849605560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67064380645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68037605285645</t>
+    <t xml:space="preserve">8.5344066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74849510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68037700653076</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10855579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04043769836426</t>
+    <t xml:space="preserve">9.10855674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04043674468994</t>
   </si>
   <si>
     <t xml:space="preserve">8.75822734832764</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789794921875</t>
+    <t xml:space="preserve">8.40789890289307</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2615,16 +2615,16 @@
     <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32031631469727</t>
+    <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
     <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46628665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45655536651611</t>
+    <t xml:space="preserve">8.46628570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4565544128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.48574924468994</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">8.15488243103027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23273372650146</t>
+    <t xml:space="preserve">8.23273468017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.17434501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14515209197998</t>
+    <t xml:space="preserve">8.14515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.20353984832764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22300148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33004856109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64145183563232</t>
+    <t xml:space="preserve">8.22300243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33004760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.58306217193604</t>
@@ -2666,43 +2666,43 @@
     <t xml:space="preserve">8.42736053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60252475738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83607864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70957088470459</t>
+    <t xml:space="preserve">8.50521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60252571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">8.84581089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01124286651611</t>
+    <t xml:space="preserve">9.0112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75082588195801</t>
+    <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3541707992554</t>
+    <t xml:space="preserve">10.3152446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3541717529297</t>
   </si>
   <si>
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028846740723</t>
+    <t xml:space="preserve">9.77028942108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">8.90419769287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14748191833496</t>
+    <t xml:space="preserve">9.14748096466064</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05989933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0890941619873</t>
+    <t xml:space="preserve">9.05990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909511566162</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93339252471924</t>
+    <t xml:space="preserve">8.93339157104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.361572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62431907653809</t>
+    <t xml:space="preserve">9.19613742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36157131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
     <t xml:space="preserve">9.57566165924072</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">9.5367374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82867813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86760330200195</t>
+    <t xml:space="preserve">9.8286771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86760234832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">9.61458778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59512424468994</t>
+    <t xml:space="preserve">9.59512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">9.45888519287109</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18640613555908</t>
+    <t xml:space="preserve">9.1864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.17667579650879</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49547958374023</t>
+    <t xml:space="preserve">8.98204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56359958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49548053741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
@@ -2837,37 +2837,37 @@
     <t xml:space="preserve">8.7193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601699829102</t>
+    <t xml:space="preserve">8.39816570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601890563965</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04783821105957</t>
+    <t xml:space="preserve">8.95285415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04783916473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500286102295</t>
+    <t xml:space="preserve">8.87500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49781036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80921459197998</t>
+    <t xml:space="preserve">9.42969131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49781131744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80921363830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">9.98437976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51727390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47834777832031</t>
+    <t xml:space="preserve">9.51727294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47834873199463</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55619812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4491548538208</t>
+    <t xml:space="preserve">9.37130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5561990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1206188201904</t>
+    <t xml:space="preserve">9.73136329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
     <t xml:space="preserve">10.0038414001465</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">10.1595430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0816917419434</t>
+    <t xml:space="preserve">10.0816926956177</t>
   </si>
   <si>
     <t xml:space="preserve">10.1790065765381</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">10.02330493927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427665710449</t>
+    <t xml:space="preserve">10.0427675247192</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622301101685</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533321380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33237838745117</t>
+    <t xml:space="preserve">9.90652942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.25452613830566</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347072601318</t>
+    <t xml:space="preserve">10.3347091674805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689189910889</t>
+    <t xml:space="preserve">11.2689199447632</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.405158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.13267993927</t>
+    <t xml:space="preserve">11.4440832138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4051580429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1326789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -3002,49 +3002,49 @@
     <t xml:space="preserve">11.3662328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.638710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668907165527</t>
+    <t xml:space="preserve">11.6387119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668916702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5729217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4756088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1836681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.358832359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6970996856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299928665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8991270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8407392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9769773483276</t>
+    <t xml:space="preserve">12.572922706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4756078720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1836671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3588314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6971006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8991279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8407402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.976978302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159044265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8796653747559</t>
+    <t xml:space="preserve">11.0159034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7434253692627</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">10.198468208313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132173538208</t>
+    <t xml:space="preserve">10.6071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4709482192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132164001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.91858959198</t>
+    <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">11.2105321884155</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
+    <t xml:space="preserve">11.9695768356323</t>
   </si>
   <si>
     <t xml:space="preserve">11.9306516647339</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">11.852801322937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917274475098</t>
+    <t xml:space="preserve">11.8917264938354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1252784729004</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">12.8259372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8843240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923833847046</t>
+    <t xml:space="preserve">12.8843259811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923843383789</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5145330429077</t>
+    <t xml:space="preserve">12.514533996582</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977565765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4366817474365</t>
+    <t xml:space="preserve">12.4366827011108</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447410583496</t>
+    <t xml:space="preserve">12.1447420120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950704574585</t>
+    <t xml:space="preserve">12.3393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3176,22 +3176,22 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9427137374878</t>
+    <t xml:space="preserve">13.0594902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9427146911621</t>
   </si>
   <si>
     <t xml:space="preserve">13.1373405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0789518356323</t>
+    <t xml:space="preserve">13.0789527893066</t>
   </si>
   <si>
     <t xml:space="preserve">13.4487447738647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4682064056396</t>
+    <t xml:space="preserve">13.468207359314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3203,37 +3203,37 @@
     <t xml:space="preserve">13.6628341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9353132247925</t>
+    <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
     <t xml:space="preserve">13.9742374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6165084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7527465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473733901978</t>
+    <t xml:space="preserve">14.3051052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.616509437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7527475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473743438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8621225357056</t>
+    <t xml:space="preserve">15.8621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909591674805</t>
+    <t xml:space="preserve">16.9909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">17.5359172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4191417694092</t>
+    <t xml:space="preserve">17.4191398620605</t>
   </si>
   <si>
     <t xml:space="preserve">17.788932800293</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2949638366699</t>
+    <t xml:space="preserve">17.7500076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419502258301</t>
+    <t xml:space="preserve">19.0345458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419483184814</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.547981262207</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060108184814</t>
+    <t xml:space="preserve">19.7060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8519821166992</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113830566406</t>
+    <t xml:space="preserve">19.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">18.7036819458008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8983097076416</t>
+    <t xml:space="preserve">18.898307800293</t>
   </si>
   <si>
     <t xml:space="preserve">19.1707878112793</t>
@@ -3332,16 +3332,16 @@
     <t xml:space="preserve">18.5090522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8788452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902484893799</t>
+    <t xml:space="preserve">18.8788433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902503967285</t>
   </si>
   <si>
     <t xml:space="preserve">18.9761600494385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8593807220459</t>
+    <t xml:space="preserve">18.8593826293945</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486381530762</t>
+    <t xml:space="preserve">19.2486362457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
@@ -3368,10 +3368,10 @@
     <t xml:space="preserve">18.9177703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9956207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.72314453125</t>
+    <t xml:space="preserve">18.9956226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -70425,7 +70425,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912962963</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>7819</v>
@@ -70446,6 +70446,32 @@
         <v>1493</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6910763889</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>18508</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>30.8500003814697</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>30.1499996185303</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1504</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009426116943</t>
+    <t xml:space="preserve">6.41009473800659</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007616043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39808225631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26996088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0937933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92563438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356473922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94565200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143936157227</t>
+    <t xml:space="preserve">6.39007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3980827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992277145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26996040344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09379386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563390731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9456524848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143983840942</t>
   </si>
   <si>
     <t xml:space="preserve">5.7254433631897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9977011680603</t>
+    <t xml:space="preserve">5.74145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99770164489746</t>
   </si>
   <si>
     <t xml:space="preserve">5.88559579849243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91762590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164848327637</t>
+    <t xml:space="preserve">5.91762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164896011353</t>
   </si>
   <si>
     <t xml:space="preserve">6.00570964813232</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">5.84956073760986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77749252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386913299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20590019226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29398393630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789218902588</t>
+    <t xml:space="preserve">5.77749300003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17387008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20589971542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29398441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789266586304</t>
   </si>
   <si>
     <t xml:space="preserve">6.20990371704102</t>
@@ -134,31 +134,31 @@
     <t xml:space="preserve">6.40609073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813989639282</t>
+    <t xml:space="preserve">6.45813941955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.41409778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48616695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218057632446</t>
+    <t xml:space="preserve">6.48616743087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218105316162</t>
   </si>
   <si>
     <t xml:space="preserve">6.49417352676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777881622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388818740845</t>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388866424561</t>
   </si>
   <si>
     <t xml:space="preserve">6.14183902740479</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">6.15385055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10980892181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1138129234314</t>
+    <t xml:space="preserve">6.10980844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11381244659424</t>
   </si>
   <si>
     <t xml:space="preserve">5.98969459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383150100708</t>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383197784424</t>
   </si>
   <si>
     <t xml:space="preserve">6.05375576019287</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">6.18187713623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12181949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373527526855</t>
+    <t xml:space="preserve">6.1218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.1018009185791</t>
@@ -212,58 +212,58 @@
     <t xml:space="preserve">6.01371765136719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95766401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764495849609</t>
+    <t xml:space="preserve">5.95766448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764543533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.11781597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07377433776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06976985931396</t>
+    <t xml:space="preserve">6.07377481460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06977081298828</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22654485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030550003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998573303223</t>
+    <t xml:space="preserve">6.2265453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998525619507</t>
   </si>
   <si>
     <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16858530044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18928575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864574432373</t>
+    <t xml:space="preserve">6.1685848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18928480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11890554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864526748657</t>
   </si>
   <si>
     <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12718629837036</t>
+    <t xml:space="preserve">6.1271858215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.13960552215576</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">6.11062574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04438543319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534616470337</t>
+    <t xml:space="preserve">6.04438638687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534568786621</t>
   </si>
   <si>
     <t xml:space="preserve">5.90776634216309</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">5.99470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0402455329895</t>
+    <t xml:space="preserve">6.08578634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024600982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502639770508</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">5.96158599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85394620895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770637512207</t>
+    <t xml:space="preserve">5.85394716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770589828491</t>
   </si>
   <si>
     <t xml:space="preserve">5.8622260093689</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">6.01540565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10234594345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.156165599823</t>
+    <t xml:space="preserve">6.10234498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26794576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15616512298584</t>
   </si>
   <si>
     <t xml:space="preserve">6.0319652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09820508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17686557769775</t>
+    <t xml:space="preserve">6.09820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17686605453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.25138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13132572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202522277832</t>
+    <t xml:space="preserve">6.13132619857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">6.14374494552612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07750606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1478853225708</t>
+    <t xml:space="preserve">6.07750558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14788579940796</t>
   </si>
   <si>
     <t xml:space="preserve">6.06922578811646</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">5.9698657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648584365845</t>
+    <t xml:space="preserve">6.10648536682129</t>
   </si>
   <si>
     <t xml:space="preserve">5.98642587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92432641983032</t>
+    <t xml:space="preserve">5.92432594299316</t>
   </si>
   <si>
     <t xml:space="preserve">5.95330619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03610610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95744609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298643112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260669708252</t>
+    <t xml:space="preserve">6.03610563278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95744657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298595428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93260622024536</t>
   </si>
   <si>
     <t xml:space="preserve">5.82496643066406</t>
@@ -398,40 +398,40 @@
     <t xml:space="preserve">5.81668663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84980583190918</t>
+    <t xml:space="preserve">5.84980630874634</t>
   </si>
   <si>
     <t xml:space="preserve">5.85808610916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75872659683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90362596511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93674612045288</t>
+    <t xml:space="preserve">5.75872564315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90362644195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93674564361572</t>
   </si>
   <si>
     <t xml:space="preserve">5.87878608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92018604278564</t>
+    <t xml:space="preserve">5.9201865196228</t>
   </si>
   <si>
     <t xml:space="preserve">6.06094598770142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42526483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494647026062</t>
+    <t xml:space="preserve">6.42526531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
   </si>
   <si>
     <t xml:space="preserve">6.45424461364746</t>
@@ -443,43 +443,43 @@
     <t xml:space="preserve">6.45838499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38386487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042495727539</t>
+    <t xml:space="preserve">6.38386535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042448043823</t>
   </si>
   <si>
     <t xml:space="preserve">6.2348256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33832502365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972450256348</t>
+    <t xml:space="preserve">6.33832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3424654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49150466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33418464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30520486831665</t>
+    <t xml:space="preserve">6.37558460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34246492385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49150514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144565582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30520534515381</t>
   </si>
   <si>
     <t xml:space="preserve">6.39214515686035</t>
@@ -497,28 +497,28 @@
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782583236694</t>
+    <t xml:space="preserve">6.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28450584411621</t>
+    <t xml:space="preserve">6.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28450536727905</t>
   </si>
   <si>
     <t xml:space="preserve">6.41284465789795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24310493469238</t>
+    <t xml:space="preserve">6.24310541152954</t>
   </si>
   <si>
     <t xml:space="preserve">6.17272520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69850397109985</t>
+    <t xml:space="preserve">6.69850492477417</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194437026978</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.64882373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990440368652</t>
+    <t xml:space="preserve">6.72334337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990392684937</t>
   </si>
   <si>
     <t xml:space="preserve">7.03798389434814</t>
@@ -539,106 +539,106 @@
     <t xml:space="preserve">7.20358276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17874431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384351730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01314306259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0793833732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142286300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05454444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830270767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60102224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0876636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924207687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542289733887</t>
+    <t xml:space="preserve">7.17874383926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384256362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01314449310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07938289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05454397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830318450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772218704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414144515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688234329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4892430305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542242050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.27810287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17046403884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94276428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110404968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0586838722229</t>
+    <t xml:space="preserve">7.17046308517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9427638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0711030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868339538574</t>
   </si>
   <si>
     <t xml:space="preserve">7.04212331771851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00486326217651</t>
+    <t xml:space="preserve">7.00486373901367</t>
   </si>
   <si>
     <t xml:space="preserve">6.83512449264526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.88894367218018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932340621948</t>
+    <t xml:space="preserve">6.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932292938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.22842264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306221008301</t>
+    <t xml:space="preserve">7.26982307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306077957153</t>
   </si>
   <si>
     <t xml:space="preserve">7.50994253158569</t>
@@ -647,76 +647,76 @@
     <t xml:space="preserve">7.64242172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210147857666</t>
+    <t xml:space="preserve">7.69210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">7.65898132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90324068069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07298183441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356187820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928115844727</t>
+    <t xml:space="preserve">7.90324115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0729808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928211212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.19304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25514125823975</t>
+    <t xml:space="preserve">8.25514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">8.48698043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49526023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36277961730957</t>
+    <t xml:space="preserve">8.49525928497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36278057098389</t>
   </si>
   <si>
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43730068206787</t>
+    <t xml:space="preserve">8.43729877471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.62773895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63602066040039</t>
+    <t xml:space="preserve">8.63601970672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52838134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966136932373</t>
+    <t xml:space="preserve">8.52838039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966041564941</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986072540283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7666220664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648029327393</t>
+    <t xml:space="preserve">7.76662158966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96119976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.51181983947754</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">9.4474573135376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595363616943</t>
+    <t xml:space="preserve">10.0850172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15953540802</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907350540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6894540786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2920169830322</t>
+    <t xml:space="preserve">10.6894550323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
     <t xml:space="preserve">10.3499746322632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5790328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.460262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8748950958252</t>
+    <t xml:space="preserve">10.5790338516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4602613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87489414215088</t>
   </si>
   <si>
     <t xml:space="preserve">10.0615329742432</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">10.1209182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0530490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.171820640564</t>
+    <t xml:space="preserve">10.0530500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1718215942383</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0785007476807</t>
+    <t xml:space="preserve">10.078501701355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7062854766846</t>
+    <t xml:space="preserve">10.7062873840332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638679504395</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772291183472</t>
+    <t xml:space="preserve">10.4772300720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.7232532501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6469020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6299343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4178438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3584604263306</t>
+    <t xml:space="preserve">10.646900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6299333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384172439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4178428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90882873535156</t>
+    <t xml:space="preserve">10.3075580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0445671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9088306427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.83247756958008</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">9.78157424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61190319061279</t>
+    <t xml:space="preserve">9.61190414428711</t>
   </si>
   <si>
     <t xml:space="preserve">9.43374824523926</t>
@@ -848,10 +848,10 @@
     <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19620800018311</t>
+    <t xml:space="preserve">9.17924022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19620704650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.23862552642822</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37436294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68825531005859</t>
+    <t xml:space="preserve">9.21317577362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37436389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954675674438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360832214355</t>
+    <t xml:space="preserve">10.0360822677612</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84944438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227220535278</t>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227210998535</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">10.2821073532104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2566566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2905912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3669424057007</t>
+    <t xml:space="preserve">10.2566556930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2905902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057542800903</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74763965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51010036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919895172119</t>
+    <t xml:space="preserve">9.74764156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51010227203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522308349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919799804688</t>
   </si>
   <si>
     <t xml:space="preserve">9.35739517211914</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66280555725098</t>
+    <t xml:space="preserve">9.66280460357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.50161647796631</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104305267334</t>
+    <t xml:space="preserve">9.28104209899902</t>
   </si>
   <si>
     <t xml:space="preserve">9.38284683227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45071697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51858520507812</t>
+    <t xml:space="preserve">9.45071506500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51858329772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.27256107330322</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">9.58645343780518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49313354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583683013916</t>
+    <t xml:space="preserve">9.49313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399368286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854202270508</t>
+    <t xml:space="preserve">9.75612354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854297637939</t>
   </si>
   <si>
     <t xml:space="preserve">9.69673919677734</t>
@@ -1010,28 +1010,28 @@
     <t xml:space="preserve">9.47616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108432769775</t>
+    <t xml:space="preserve">9.13682270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
     <t xml:space="preserve">8.72112655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59387397766113</t>
+    <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.07637500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32664012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1018238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12303352355957</t>
+    <t xml:space="preserve">8.32663917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278076171875</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">8.33088207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.195143699646</t>
+    <t xml:space="preserve">8.34360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31391620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29270648956299</t>
+    <t xml:space="preserve">8.31391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
     <t xml:space="preserve">8.09334182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03819942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85155963897705</t>
+    <t xml:space="preserve">8.03819847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85156011581421</t>
   </si>
   <si>
     <t xml:space="preserve">7.82610845565796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80065774917603</t>
+    <t xml:space="preserve">7.80065822601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.91094446182251</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">7.85580062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881269454956</t>
+    <t xml:space="preserve">7.957603931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881412506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123165130615</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16121101379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1484842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092430114746</t>
+    <t xml:space="preserve">8.16121006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">8.08061599731445</t>
@@ -1112,37 +1112,37 @@
     <t xml:space="preserve">8.22483730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2884635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42420196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56842136383057</t>
+    <t xml:space="preserve">8.28846454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42420101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.5175199508667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7380952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55145454406738</t>
+    <t xml:space="preserve">8.73809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.48358631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50055408477783</t>
+    <t xml:space="preserve">8.50055313110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58539009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46662044525146</t>
+    <t xml:space="preserve">8.58538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.4581356048584</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">8.40723419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3817834854126</t>
+    <t xml:space="preserve">8.38178253173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.20362854003906</t>
@@ -1160,34 +1160,34 @@
     <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99153804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518640518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12727546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97457075119019</t>
+    <t xml:space="preserve">7.99153900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12727642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9745717048645</t>
   </si>
   <si>
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90776538848877</t>
+    <t xml:space="preserve">8.90776634216309</t>
   </si>
   <si>
     <t xml:space="preserve">8.75506114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82292938232422</t>
+    <t xml:space="preserve">8.82293033599854</t>
   </si>
   <si>
     <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61932373046875</t>
+    <t xml:space="preserve">8.61932277679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94169902801514</t>
+    <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36587905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24710750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12833976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11137199401855</t>
+    <t xml:space="preserve">9.24710941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12833881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11137294769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.04350280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09440422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26407718658447</t>
+    <t xml:space="preserve">9.09440517425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26407527923584</t>
   </si>
   <si>
     <t xml:space="preserve">9.41678142547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142381668091</t>
+    <t xml:space="preserve">10.2142372131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705499649048</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">10.6723518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6214513778687</t>
+    <t xml:space="preserve">10.6214504241943</t>
   </si>
   <si>
     <t xml:space="preserve">10.9607934951782</t>
@@ -1241,55 +1241,55 @@
     <t xml:space="preserve">11.4358739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698085784912</t>
+    <t xml:space="preserve">11.3680067062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8729009628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8362560272217</t>
+    <t xml:space="preserve">11.8729019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
+    <t xml:space="preserve">11.3049068450928</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9567832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
+    <t xml:space="preserve">10.9567823410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834934234619</t>
   </si>
   <si>
     <t xml:space="preserve">10.4987230300903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7002687454224</t>
+    <t xml:space="preserve">10.7002696990967</t>
   </si>
   <si>
     <t xml:space="preserve">10.6086568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6453008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4804010391235</t>
+    <t xml:space="preserve">10.6453018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4804000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0040187835693</t>
+    <t xml:space="preserve">10.0040168762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.98569583892822</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">10.2788543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0773086547852</t>
+    <t xml:space="preserve">10.0773077011108</t>
   </si>
   <si>
     <t xml:space="preserve">10.2238864898682</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">10.2605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1322746276855</t>
+    <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4071092605591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3155002593994</t>
+    <t xml:space="preserve">10.3154983520508</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437561035156</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">10.3338203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.20556640625</t>
+    <t xml:space="preserve">10.2055644989014</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78415012359619</t>
+    <t xml:space="preserve">9.78415107727051</t>
   </si>
   <si>
     <t xml:space="preserve">9.80247211456299</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">9.67421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7291841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65589237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61924839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7475061416626</t>
+    <t xml:space="preserve">9.72918224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
     <t xml:space="preserve">9.69253826141357</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">9.25280094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3627347946167</t>
+    <t xml:space="preserve">9.36273384094238</t>
   </si>
   <si>
     <t xml:space="preserve">9.32609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2711238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957626342773</t>
+    <t xml:space="preserve">9.27112293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957721710205</t>
   </si>
   <si>
     <t xml:space="preserve">9.08789920806885</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94132137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51990604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28171539306641</t>
+    <t xml:space="preserve">8.94132041931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51990699768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.92299842834473</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">8.7031307220459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900089263916</t>
+    <t xml:space="preserve">8.63900184631348</t>
   </si>
   <si>
     <t xml:space="preserve">8.65732383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35500335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39937973022461</t>
+    <t xml:space="preserve">8.62984085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35500431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44661617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39937877655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.3810567855835</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">9.04209327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96880531311035</t>
+    <t xml:space="preserve">8.96880435943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.99628734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8680305480957</t>
+    <t xml:space="preserve">8.88635349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86803150177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.7855806350708</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">8.84054660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77641868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71229076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59319496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40997219085693</t>
+    <t xml:space="preserve">8.7764196395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59319591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235786437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.3091983795166</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">8.2450704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7412052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68623828887939</t>
+    <t xml:space="preserve">7.74120473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70455980300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68623781204224</t>
   </si>
   <si>
     <t xml:space="preserve">7.55798053741455</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">7.59462594985962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49385261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224075317383</t>
+    <t xml:space="preserve">7.49385356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224123001099</t>
   </si>
   <si>
     <t xml:space="preserve">7.08159875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10908317565918</t>
+    <t xml:space="preserve">7.10908269882202</t>
   </si>
   <si>
     <t xml:space="preserve">7.38391876220703</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">7.30146789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31978940963745</t>
+    <t xml:space="preserve">7.31978988647461</t>
   </si>
   <si>
     <t xml:space="preserve">7.48469161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42056322097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76868772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539833068848</t>
+    <t xml:space="preserve">7.4205641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7686882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539880752563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45720815658569</t>
@@ -1556,43 +1556,43 @@
     <t xml:space="preserve">7.5854640007019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817850112915</t>
+    <t xml:space="preserve">7.56714200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5396580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049802780151</t>
+    <t xml:space="preserve">7.15488862991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.054114818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53965759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
   </si>
   <si>
     <t xml:space="preserve">7.47553062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33811235427856</t>
+    <t xml:space="preserve">7.33811283111572</t>
   </si>
   <si>
     <t xml:space="preserve">7.29230690002441</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24650096893311</t>
+    <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
     <t xml:space="preserve">7.27398443222046</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946201324463</t>
+    <t xml:space="preserve">7.86946153640747</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.39164924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49242210388184</t>
+    <t xml:space="preserve">8.49242305755615</t>
   </si>
   <si>
     <t xml:space="preserve">8.40081024169922</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377128601074</t>
+    <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.13370609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73977565765381</t>
+    <t xml:space="preserve">8.73977375030518</t>
   </si>
   <si>
     <t xml:space="preserve">9.10622119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05125522613525</t>
+    <t xml:space="preserve">9.05125427246094</t>
   </si>
   <si>
     <t xml:space="preserve">8.7947416305542</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">8.66648578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85887050628662</t>
+    <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">9.01461029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91383743286133</t>
+    <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467548370361</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">8.84970855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80390167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81306457519531</t>
+    <t xml:space="preserve">8.8039026260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.813063621521</t>
   </si>
   <si>
     <t xml:space="preserve">8.58403396606445</t>
@@ -1694,31 +1694,31 @@
     <t xml:space="preserve">8.25423145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248729705811</t>
+    <t xml:space="preserve">8.38248825073242</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255344390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26339340209961</t>
+    <t xml:space="preserve">8.12597465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
     <t xml:space="preserve">8.2359094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43745517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45577812194824</t>
+    <t xml:space="preserve">8.43745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45577716827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.47409915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.50158405303955</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829418182373</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">8.51074409484863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62067890167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54738998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21530532836914</t>
+    <t xml:space="preserve">8.53822708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62067794799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61151790618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54738903045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.70226860046387</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">8.06339263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29571056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0537109375</t>
+    <t xml:space="preserve">7.98595380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0343542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371189117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.02467346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10211277008057</t>
+    <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.12147235870361</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">7.97627258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96659278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16987037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24731063842773</t>
+    <t xml:space="preserve">7.96659183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16987228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24731159210205</t>
   </si>
   <si>
     <t xml:space="preserve">8.25699138641357</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">7.90851402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755292892456</t>
+    <t xml:space="preserve">7.93755388259888</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13115215301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04403209686279</t>
+    <t xml:space="preserve">8.11179256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13115310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04403305053711</t>
   </si>
   <si>
     <t xml:space="preserve">7.94723320007324</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99563264846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00531387329102</t>
+    <t xml:space="preserve">7.99563360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0053129196167</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979341506958</t>
+    <t xml:space="preserve">7.86979389190674</t>
   </si>
   <si>
     <t xml:space="preserve">7.87947368621826</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33443069458008</t>
+    <t xml:space="preserve">7.95691251754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33442974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.227952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45059013366699</t>
+    <t xml:space="preserve">8.22795104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.52803039550781</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">9.14754581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13786506652832</t>
+    <t xml:space="preserve">9.13786602020264</t>
   </si>
   <si>
     <t xml:space="preserve">9.51538372039795</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">9.38954448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4863452911377</t>
+    <t xml:space="preserve">9.48634433746338</t>
   </si>
   <si>
     <t xml:space="preserve">9.45730495452881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55410480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53474426269531</t>
+    <t xml:space="preserve">9.44762516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55410385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.534743309021</t>
   </si>
   <si>
     <t xml:space="preserve">9.52506351470947</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0671415328979</t>
+    <t xml:space="preserve">10.0477819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0671405792236</t>
   </si>
   <si>
     <t xml:space="preserve">9.98970031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95098114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60250282287598</t>
+    <t xml:space="preserve">9.95098209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60250377655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.67994403839111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61218452453613</t>
+    <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.69930267333984</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">9.71866226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50570297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58314323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87354278564453</t>
+    <t xml:space="preserve">9.50570392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58314418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
     <t xml:space="preserve">9.40890407562256</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">9.3508243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43794536590576</t>
+    <t xml:space="preserve">9.43794441223145</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146476745605</t>
+    <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.77674293518066</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">9.66058254241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11850643157959</t>
+    <t xml:space="preserve">9.11850547790527</t>
   </si>
   <si>
     <t xml:space="preserve">9.09914684295654</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16690731048584</t>
+    <t xml:space="preserve">9.16690540313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.07978630065918</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">8.9442663192749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85714817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72162914276123</t>
+    <t xml:space="preserve">8.85714721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7216272354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.77002906799316</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">8.93458652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99266815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96362686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15722560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05074787139893</t>
+    <t xml:space="preserve">8.99266719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96362781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05074691772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.97330856323242</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">7.84075450897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79235458374023</t>
+    <t xml:space="preserve">7.79235410690308</t>
   </si>
   <si>
     <t xml:space="preserve">7.60843563079834</t>
@@ -2063,43 +2063,43 @@
     <t xml:space="preserve">7.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44684171676636</t>
+    <t xml:space="preserve">6.52428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44684219360352</t>
   </si>
   <si>
     <t xml:space="preserve">5.14004945755005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47884798049927</t>
+    <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64637327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48181343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52053356170654</t>
+    <t xml:space="preserve">4.64637279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48181390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52053308486938</t>
   </si>
   <si>
     <t xml:space="preserve">4.83997201919556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037061691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04028463363647</t>
+    <t xml:space="preserve">5.13037014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51756715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04028415679932</t>
   </si>
   <si>
     <t xml:space="preserve">6.00156450271606</t>
@@ -2108,22 +2108,22 @@
     <t xml:space="preserve">5.98220491409302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88540554046631</t>
+    <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
     <t xml:space="preserve">5.79828596115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96284484863281</t>
+    <t xml:space="preserve">5.96284437179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3887619972229</t>
+    <t xml:space="preserve">6.15644454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38876247406006</t>
   </si>
   <si>
     <t xml:space="preserve">6.46620178222656</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">6.43716192245483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420263290405</t>
+    <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.5339617729187</t>
   </si>
   <si>
     <t xml:space="preserve">6.54364156723022</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.676194190979</t>
+    <t xml:space="preserve">7.67619466781616</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491432189941</t>
+    <t xml:space="preserve">7.58907508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71491479873657</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">7.39547634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43419599533081</t>
+    <t xml:space="preserve">7.43419551849365</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44387626647949</t>
+    <t xml:space="preserve">7.44387578964233</t>
   </si>
   <si>
     <t xml:space="preserve">7.49227571487427</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">7.69555473327637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85043334960938</t>
+    <t xml:space="preserve">7.85043287277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">7.59875535964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65683507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
+    <t xml:space="preserve">7.65683460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.31803703308105</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">7.30835723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23091697692871</t>
+    <t xml:space="preserve">7.23091793060303</t>
   </si>
   <si>
     <t xml:space="preserve">7.521315574646</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">7.35675668716431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.45355653762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">7.41483640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
+    <t xml:space="preserve">7.29867649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
   </si>
   <si>
     <t xml:space="preserve">7.47291612625122</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">7.68587493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88915348052979</t>
+    <t xml:space="preserve">7.88915300369263</t>
   </si>
   <si>
     <t xml:space="preserve">7.83107471466064</t>
@@ -2267,10 +2267,10 @@
     <t xml:space="preserve">7.74395418167114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73427438735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36643695831299</t>
+    <t xml:space="preserve">7.73427391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36643648147583</t>
   </si>
   <si>
     <t xml:space="preserve">7.26963758468628</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315793991089</t>
+    <t xml:space="preserve">7.16315841674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.12443828582764</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">7.22123765945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70523500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7245945930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48259592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6665153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42451620101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04699850082397</t>
+    <t xml:space="preserve">7.70523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48259544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66651487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42451667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04699897766113</t>
   </si>
   <si>
     <t xml:space="preserve">7.10507822036743</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">7.13411808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">6.89211893081665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97923898696899</t>
+    <t xml:space="preserve">6.97923946380615</t>
   </si>
   <si>
     <t xml:space="preserve">7.06635856628418</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">7.0566782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8727593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94051885604858</t>
+    <t xml:space="preserve">6.87275981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
     <t xml:space="preserve">6.90179920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82435989379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80499982833862</t>
+    <t xml:space="preserve">6.82436037063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
     <t xml:space="preserve">6.77595996856689</t>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">6.83403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8146800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75659990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73724031448364</t>
+    <t xml:space="preserve">6.78564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81467962265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7953200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75660037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
     <t xml:space="preserve">6.63076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67916059494019</t>
+    <t xml:space="preserve">6.67916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">6.93083906173706</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49314975738525</t>
+    <t xml:space="preserve">7.49315023422241</t>
   </si>
   <si>
     <t xml:space="preserve">7.59046363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52234411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70724058151245</t>
+    <t xml:space="preserve">7.52234363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395635604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.83374786376953</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">8.03810691833496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08676242828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00891208648682</t>
+    <t xml:space="preserve">8.08676338195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0089111328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.0964937210083</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13541984558105</t>
+    <t xml:space="preserve">8.19380760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
     <t xml:space="preserve">7.96998643875122</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019493103027</t>
+    <t xml:space="preserve">7.60019540786743</t>
   </si>
   <si>
     <t xml:space="preserve">7.57100105285645</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401609420776</t>
+    <t xml:space="preserve">7.82401657104492</t>
   </si>
   <si>
     <t xml:space="preserve">7.64885234832764</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">7.63912057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56126976013184</t>
+    <t xml:space="preserve">7.6293888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56126928329468</t>
   </si>
   <si>
     <t xml:space="preserve">7.8434796333313</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">7.94079303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29112148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27165985107422</t>
+    <t xml:space="preserve">8.29112243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
     <t xml:space="preserve">8.07703304290771</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977794647217</t>
+    <t xml:space="preserve">8.33977890014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">8.34951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53440570831299</t>
+    <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.74849605560303</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">8.97231769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10855579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04043769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75822734832764</t>
+    <t xml:space="preserve">9.10855674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04043674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75822830200195</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32031631469727</t>
+    <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
     <t xml:space="preserve">8.43709278106689</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">8.46628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45655536651611</t>
+    <t xml:space="preserve">8.4565544128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488243103027</t>
+    <t xml:space="preserve">8.15488338470459</t>
   </si>
   <si>
     <t xml:space="preserve">8.23273372650146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17434501647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14515209197998</t>
+    <t xml:space="preserve">8.17434597015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.20353984832764</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">8.22300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33004856109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64145183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58306217193604</t>
+    <t xml:space="preserve">8.33004760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64145088195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58306121826172</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">8.42736053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60252475738525</t>
+    <t xml:space="preserve">8.50521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60252571105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.83607864379883</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419769287109</t>
+    <t xml:space="preserve">8.90419673919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.14748191833496</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">9.05989933013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0890941619873</t>
+    <t xml:space="preserve">9.08909320831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">9.19613838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.361572265625</t>
+    <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
     <t xml:space="preserve">9.62431907653809</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">9.57566165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5367374420166</t>
+    <t xml:space="preserve">9.53673648834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.82867813110352</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61458778381348</t>
+    <t xml:space="preserve">9.67297458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61458683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.59512424468994</t>
@@ -2798,25 +2798,25 @@
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18640613555908</t>
+    <t xml:space="preserve">9.1864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21560192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20586967468262</t>
+    <t xml:space="preserve">9.21560096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20587062835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204708099365</t>
+    <t xml:space="preserve">8.98204803466797</t>
   </si>
   <si>
     <t xml:space="preserve">8.56360054016113</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795864105225</t>
+    <t xml:space="preserve">8.76795768737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.41762924194336</t>
@@ -2840,19 +2840,19 @@
     <t xml:space="preserve">8.37870311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7193021774292</t>
+    <t xml:space="preserve">8.71930122375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.39816665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47601699829102</t>
+    <t xml:space="preserve">8.47601795196533</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285511016846</t>
+    <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
     <t xml:space="preserve">8.04783821105957</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49781036376953</t>
+    <t xml:space="preserve">9.42969131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
     <t xml:space="preserve">9.80921459197998</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437976837158</t>
+    <t xml:space="preserve">9.98437881469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.51727390289307</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55619812011719</t>
+    <t xml:space="preserve">9.37130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
     <t xml:space="preserve">9.4491548538208</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">9.73136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1206188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0038414001465</t>
+    <t xml:space="preserve">10.1206178665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0038423538208</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0816917419434</t>
+    <t xml:space="preserve">10.0816926956177</t>
   </si>
   <si>
     <t xml:space="preserve">10.1790065765381</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">10.0427665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0622301101685</t>
+    <t xml:space="preserve">10.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">9.90652847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22533321380615</t>
+    <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
     <t xml:space="preserve">9.33237838745117</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">9.25452613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63404941558838</t>
+    <t xml:space="preserve">9.40049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48807907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6340503692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689189910889</t>
+    <t xml:space="preserve">11.2689199447632</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.4440841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.405158996582</t>
+    <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
     <t xml:space="preserve">11.13267993927</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">12.1836681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.358832359314</t>
+    <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
     <t xml:space="preserve">11.6970996856689</t>
@@ -3035,28 +3035,28 @@
     <t xml:space="preserve">11.2299928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8991270065308</t>
+    <t xml:space="preserve">10.8991279602051</t>
   </si>
   <si>
     <t xml:space="preserve">10.8407392501831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9769773483276</t>
+    <t xml:space="preserve">10.976978302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159044265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8796653747559</t>
+    <t xml:space="preserve">11.0159034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9575157165527</t>
+    <t xml:space="preserve">10.9575147628784</t>
   </si>
   <si>
     <t xml:space="preserve">10.198468208313</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">10.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132173538208</t>
+    <t xml:space="preserve">11.1132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">11.9695777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9306516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.852801322937</t>
+    <t xml:space="preserve">11.9306526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917274475098</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259372711182</t>
+    <t xml:space="preserve">12.8259382247925</t>
   </si>
   <si>
     <t xml:space="preserve">12.8843240737915</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">12.7870121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225933074951</t>
+    <t xml:space="preserve">12.2225923538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762657165527</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">12.9427137374878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1373405456543</t>
+    <t xml:space="preserve">13.1373414993286</t>
   </si>
   <si>
     <t xml:space="preserve">13.0789518356323</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">13.6628341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9353132247925</t>
+    <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
     <t xml:space="preserve">13.9742374420166</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">14.3051042556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6165084838867</t>
+    <t xml:space="preserve">14.616509437561</t>
   </si>
   <si>
     <t xml:space="preserve">14.7527465820312</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">14.9473733901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9279117584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621225357056</t>
+    <t xml:space="preserve">14.9279127120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">16.893648147583</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359172821045</t>
+    <t xml:space="preserve">17.5359153747559</t>
   </si>
   <si>
     <t xml:space="preserve">17.4191417694092</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036819458008</t>
+    <t xml:space="preserve">19.0734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036800384521</t>
   </si>
   <si>
     <t xml:space="preserve">18.8983097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1707878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009948730469</t>
+    <t xml:space="preserve">19.1707859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009929656982</t>
   </si>
   <si>
     <t xml:space="preserve">18.5090522766113</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">19.1902484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8593807220459</t>
+    <t xml:space="preserve">18.9761581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8593826293945</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4701271057129</t>
+    <t xml:space="preserve">18.4701290130615</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">18.9177703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9956207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.72314453125</t>
+    <t xml:space="preserve">18.9956226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8429946899414</t>
+    <t xml:space="preserve">19.84299659729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.004114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567657470703</t>
+    <t xml:space="preserve">22.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988128662109</t>
+    <t xml:space="preserve">22.3479290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988109588623</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656024932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832759857178</t>
+    <t xml:space="preserve">21.3656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832740783691</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306243896484</t>
+    <t xml:space="preserve">20.5306224822998</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748062133789</t>
+    <t xml:space="preserve">18.0748081207275</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463237762451</t>
+    <t xml:space="preserve">18.5463218688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569282531738</t>
+    <t xml:space="preserve">17.9569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836429595947</t>
+    <t xml:space="preserve">17.4854106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836448669434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.60329246521</t>
+    <t xml:space="preserve">17.6032905578613</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0335426330566</t>
+    <t xml:space="preserve">16.7388439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.033540725708</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3581,34 +3581,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673263549805</t>
+    <t xml:space="preserve">16.2673282623291</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3459129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869739532471</t>
+    <t xml:space="preserve">15.8547487258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.345911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869720458984</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189908981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154573440552</t>
+    <t xml:space="preserve">15.6189918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154563903809</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794921875</t>
+    <t xml:space="preserve">14.4794931411743</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3629,37 +3629,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903020858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563110351562</t>
+    <t xml:space="preserve">14.9903030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563119888306</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580778121948</t>
+    <t xml:space="preserve">14.5580787658691</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956052780151</t>
+    <t xml:space="preserve">14.4991388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956043243408</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527765274048</t>
+    <t xml:space="preserve">14.8527774810791</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958097457886</t>
+    <t xml:space="preserve">15.7958106994629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653541564941</t>
+    <t xml:space="preserve">15.2653532028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567237854004</t>
+    <t xml:space="preserve">16.8567218780518</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370742797852</t>
+    <t xml:space="preserve">16.8370761871338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549541473389</t>
+    <t xml:space="preserve">16.9549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514205932617</t>
+    <t xml:space="preserve">17.1514186859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247058868408</t>
+    <t xml:space="preserve">17.5247039794922</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465301513672</t>
+    <t xml:space="preserve">19.6465282440186</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697093963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838493347168</t>
+    <t xml:space="preserve">19.4697113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838512420654</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394611358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359275817871</t>
+    <t xml:space="preserve">20.0394592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779727935791</t>
+    <t xml:space="preserve">20.6779708862305</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005786895752</t>
+    <t xml:space="preserve">22.2005805969238</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532302856445</t>
+    <t xml:space="preserve">22.0532321929932</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -70567,7 +70567,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6913078704</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>13585</v>
@@ -70588,6 +70588,32 @@
         <v>1530</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6911574074</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>12100</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>29.8500003814697</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>30.1499996185303</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992277145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26996040344238</t>
+    <t xml:space="preserve">6.39007520675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26996088027954</t>
   </si>
   <si>
     <t xml:space="preserve">6.0937933921814</t>
@@ -65,73 +65,73 @@
     <t xml:space="preserve">6.08578586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92563343048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356473922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548051834106</t>
+    <t xml:space="preserve">5.9256329536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548099517822</t>
   </si>
   <si>
     <t xml:space="preserve">5.9456524848938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946546554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143983840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7254433631897</t>
+    <t xml:space="preserve">5.74946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72544288635254</t>
   </si>
   <si>
     <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99770164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559532165527</t>
+    <t xml:space="preserve">5.99770212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559484481812</t>
   </si>
   <si>
     <t xml:space="preserve">5.91762590408325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94164848327637</t>
+    <t xml:space="preserve">5.94164943695068</t>
   </si>
   <si>
     <t xml:space="preserve">6.00571012496948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386913299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984655380249</t>
+    <t xml:space="preserve">5.84956121444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7774920463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17386960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984607696533</t>
   </si>
   <si>
     <t xml:space="preserve">6.20590019226074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29398393630981</t>
+    <t xml:space="preserve">6.29398441314697</t>
   </si>
   <si>
     <t xml:space="preserve">6.22191524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19789218902588</t>
+    <t xml:space="preserve">6.19789171218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.20990371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.406090259552</t>
+    <t xml:space="preserve">6.40609073638916</t>
   </si>
   <si>
     <t xml:space="preserve">6.45813941955566</t>
@@ -140,52 +140,52 @@
     <t xml:space="preserve">6.41409826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48616695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417448043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23793077468872</t>
+    <t xml:space="preserve">6.48616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23793029785156</t>
   </si>
   <si>
     <t xml:space="preserve">6.07777833938599</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25394582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388914108276</t>
+    <t xml:space="preserve">6.25394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388866424561</t>
   </si>
   <si>
     <t xml:space="preserve">6.14183902740479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15385007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980892181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375480651855</t>
+    <t xml:space="preserve">6.15385055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11381244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9896936416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772165298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375576019287</t>
   </si>
   <si>
     <t xml:space="preserve">6.1578540802002</t>
@@ -194,55 +194,55 @@
     <t xml:space="preserve">6.09779739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18187665939331</t>
+    <t xml:space="preserve">6.18187761306763</t>
   </si>
   <si>
     <t xml:space="preserve">6.12181997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21390771865845</t>
+    <t xml:space="preserve">6.21390724182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1018009185791</t>
+    <t xml:space="preserve">6.10180044174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.01371717453003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95766448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11781597137451</t>
+    <t xml:space="preserve">5.95766401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764448165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11781644821167</t>
   </si>
   <si>
     <t xml:space="preserve">6.07377433776855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06976985931396</t>
+    <t xml:space="preserve">6.06977033615112</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2265453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406614303589</t>
+    <t xml:space="preserve">6.22654628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
     <t xml:space="preserve">6.16858530044556</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">6.18928527832031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20170497894287</t>
+    <t xml:space="preserve">6.20170593261719</t>
   </si>
   <si>
     <t xml:space="preserve">6.11890554428101</t>
@@ -263,43 +263,40 @@
     <t xml:space="preserve">6.19756603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12718534469604</t>
+    <t xml:space="preserve">6.1271858215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.13960552215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11062622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534616470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8125467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578538894653</t>
+    <t xml:space="preserve">6.11062526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438638687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776586532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81254577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470567703247</t>
   </si>
   <si>
     <t xml:space="preserve">6.04024600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96158504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394620895386</t>
+    <t xml:space="preserve">5.94502639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394716262817</t>
   </si>
   <si>
     <t xml:space="preserve">5.78770637512207</t>
@@ -308,7 +305,7 @@
     <t xml:space="preserve">5.8622260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91190624237061</t>
+    <t xml:space="preserve">5.91190576553345</t>
   </si>
   <si>
     <t xml:space="preserve">5.86636590957642</t>
@@ -320,28 +317,28 @@
     <t xml:space="preserve">6.01540613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10234594345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26794528961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15616512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03196573257446</t>
+    <t xml:space="preserve">6.10234546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26794576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.156165599823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0319652557373</t>
   </si>
   <si>
     <t xml:space="preserve">6.09820556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17686557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25138568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13132619857788</t>
+    <t xml:space="preserve">6.1768651008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25138521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13132572174072</t>
   </si>
   <si>
     <t xml:space="preserve">6.15202522277832</t>
@@ -353,10 +350,10 @@
     <t xml:space="preserve">6.07750558853149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1478853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06922578811646</t>
+    <t xml:space="preserve">6.14788579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266571044922</t>
@@ -365,7 +362,7 @@
     <t xml:space="preserve">5.9698657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648536682129</t>
+    <t xml:space="preserve">6.10648584365845</t>
   </si>
   <si>
     <t xml:space="preserve">5.98642587661743</t>
@@ -380,10 +377,10 @@
     <t xml:space="preserve">6.03610610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95744609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298595428467</t>
+    <t xml:space="preserve">5.95744657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298547744751</t>
   </si>
   <si>
     <t xml:space="preserve">5.88706636428833</t>
@@ -392,19 +389,19 @@
     <t xml:space="preserve">5.93260622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8249659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8498067855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75872659683228</t>
+    <t xml:space="preserve">5.82496643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668615341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84980630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808610916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75872611999512</t>
   </si>
   <si>
     <t xml:space="preserve">5.90362596511841</t>
@@ -413,37 +410,37 @@
     <t xml:space="preserve">5.93674612045288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87878656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9201865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06094551086426</t>
+    <t xml:space="preserve">5.87878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92018604278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06094646453857</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
+    <t xml:space="preserve">6.45010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290414810181</t>
   </si>
   <si>
     <t xml:space="preserve">6.5494647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45424509048462</t>
+    <t xml:space="preserve">6.45424556732178</t>
   </si>
   <si>
     <t xml:space="preserve">6.29278516769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.383864402771</t>
+    <t xml:space="preserve">6.45838499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386535644531</t>
   </si>
   <si>
     <t xml:space="preserve">6.40042543411255</t>
@@ -452,7 +449,7 @@
     <t xml:space="preserve">6.23482608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33832502365112</t>
+    <t xml:space="preserve">6.33832550048828</t>
   </si>
   <si>
     <t xml:space="preserve">6.37972450256348</t>
@@ -464,10 +461,10 @@
     <t xml:space="preserve">6.37558460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50806474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3424654006958</t>
+    <t xml:space="preserve">6.50806522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34246444702148</t>
   </si>
   <si>
     <t xml:space="preserve">6.49150466918945</t>
@@ -488,28 +485,28 @@
     <t xml:space="preserve">6.18514490127563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97400617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01126623153687</t>
+    <t xml:space="preserve">5.97400522232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01126670837402</t>
   </si>
   <si>
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782583236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32590484619141</t>
+    <t xml:space="preserve">6.0278263092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32590532302856</t>
   </si>
   <si>
     <t xml:space="preserve">6.36730480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28450536727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41284561157227</t>
+    <t xml:space="preserve">6.28450489044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41284465789795</t>
   </si>
   <si>
     <t xml:space="preserve">6.24310541152954</t>
@@ -518,19 +515,19 @@
     <t xml:space="preserve">6.17272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69850397109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.69850444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194437026978</t>
   </si>
   <si>
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334432601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990440368652</t>
+    <t xml:space="preserve">6.72334384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990488052368</t>
   </si>
   <si>
     <t xml:space="preserve">7.03798341751099</t>
@@ -539,7 +536,7 @@
     <t xml:space="preserve">7.20358228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1787428855896</t>
+    <t xml:space="preserve">7.17874383926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384304046631</t>
@@ -554,82 +551,82 @@
     <t xml:space="preserve">7.02142333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05454349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60102272033691</t>
+    <t xml:space="preserve">7.0545449256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772266387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">7.63414239883423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59688282012939</t>
+    <t xml:space="preserve">7.59688234329224</t>
   </si>
   <si>
     <t xml:space="preserve">7.08766412734985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682189941406</t>
+    <t xml:space="preserve">7.30294179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4768214225769</t>
   </si>
   <si>
     <t xml:space="preserve">7.48924255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810335159302</t>
+    <t xml:space="preserve">7.43542337417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810287475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.17046308517456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10422277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9427638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0711030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486326217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95518350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894319534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932292938232</t>
+    <t xml:space="preserve">7.10422372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94276475906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07110357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9551830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894414901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.22842311859131</t>
@@ -641,88 +638,88 @@
     <t xml:space="preserve">7.54306173324585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50994205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64242172241211</t>
+    <t xml:space="preserve">7.50994110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64242219924927</t>
   </si>
   <si>
     <t xml:space="preserve">7.69210243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65898275375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9032416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00673961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158283233643</t>
+    <t xml:space="preserve">7.65898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03157997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.07298183441162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85356140136719</t>
+    <t xml:space="preserve">7.85356187820435</t>
   </si>
   <si>
     <t xml:space="preserve">8.25928020477295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19304084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48697948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49525928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36278057098389</t>
+    <t xml:space="preserve">8.19304180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48698043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36277961730957</t>
   </si>
   <si>
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43729877471924</t>
+    <t xml:space="preserve">8.43730068206787</t>
   </si>
   <si>
     <t xml:space="preserve">8.62773895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63602066040039</t>
+    <t xml:space="preserve">8.63601970672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52838039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03986167907715</t>
+    <t xml:space="preserve">8.52838134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03986072540283</t>
   </si>
   <si>
     <t xml:space="preserve">7.76662158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96120071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51181888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6028995513916</t>
+    <t xml:space="preserve">7.96120166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51181983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60290050506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.77677917480469</t>
@@ -731,10 +728,10 @@
     <t xml:space="preserve">8.85957908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44745635986328</t>
+    <t xml:space="preserve">9.37293815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">10.085015296936</t>
@@ -743,10 +740,10 @@
     <t xml:space="preserve">10.1595363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4907350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.689453125</t>
+    <t xml:space="preserve">10.4907360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894540786743</t>
   </si>
   <si>
     <t xml:space="preserve">10.7556943893433</t>
@@ -755,28 +752,28 @@
     <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499765396118</t>
+    <t xml:space="preserve">10.3499755859375</t>
   </si>
   <si>
     <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.460262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615339279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.053050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1718196868896</t>
+    <t xml:space="preserve">10.4602613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87489604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0530500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.171820640564</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803035736084</t>
@@ -785,7 +782,7 @@
     <t xml:space="preserve">10.0785007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3839092254639</t>
+    <t xml:space="preserve">10.3839082717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7062864303589</t>
@@ -794,31 +791,34 @@
     <t xml:space="preserve">10.6638679504395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6129674911499</t>
+    <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7232542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.646900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6299343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384172439575</t>
+    <t xml:space="preserve">10.3499746322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7232532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6469011306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6299333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384181976318</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2736225128174</t>
+    <t xml:space="preserve">10.3584604263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2736234664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.3075580596924</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">10.04456615448</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90882873535156</t>
+    <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.83247756958008</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">9.78157520294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61190319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1028881072998</t>
+    <t xml:space="preserve">9.61190414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10288715362549</t>
   </si>
   <si>
     <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924022674561</t>
+    <t xml:space="preserve">9.17924118041992</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">9.23014259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33194446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21317577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37436199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68825626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360832214355</t>
+    <t xml:space="preserve">9.33194541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21317481994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68825531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360841751099</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84944438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2312049865723</t>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
     <t xml:space="preserve">10.2821063995361</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">10.2566556930542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2905893325806</t>
+    <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
     <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057552337646</t>
+    <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
     <t xml:space="preserve">10.019115447998</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">9.9682149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89186096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85792827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74764251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51010131835938</t>
+    <t xml:space="preserve">9.89186191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8579273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74763965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51010036468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.70522308349609</t>
@@ -932,67 +932,67 @@
     <t xml:space="preserve">9.35739517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948566436768</t>
+    <t xml:space="preserve">9.56948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39132976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51858329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645343780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583778381348</t>
+    <t xml:space="preserve">9.50161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39133071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071506500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27256107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612545013428</t>
+    <t xml:space="preserve">9.75612449645996</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399272918701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77309226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69673824310303</t>
+    <t xml:space="preserve">9.77309322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69673919677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.67128849029541</t>
@@ -1001,40 +1001,40 @@
     <t xml:space="preserve">9.62887096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79005813598633</t>
+    <t xml:space="preserve">9.79005908966064</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7211275100708</t>
+    <t xml:space="preserve">9.47616577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13682270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72112655639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637596130371</t>
+    <t xml:space="preserve">8.07637500762939</t>
   </si>
   <si>
     <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1230354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6278076171875</t>
+    <t xml:space="preserve">8.10182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62780857086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.33088207244873</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27149677276611</t>
+    <t xml:space="preserve">8.27149772644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.37329959869385</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334182739258</t>
+    <t xml:space="preserve">8.09334087371826</t>
   </si>
   <si>
     <t xml:space="preserve">8.03819847106934</t>
@@ -1067,43 +1067,43 @@
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610845565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094446182251</t>
+    <t xml:space="preserve">7.82610940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094398498535</t>
   </si>
   <si>
     <t xml:space="preserve">7.85580110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02123260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01274681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">7.957603931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9788122177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0127477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14848518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061695098877</t>
+    <t xml:space="preserve">8.1484842300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">8.17393493652344</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">8.2884635925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42420291900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5684232711792</t>
+    <t xml:space="preserve">8.42420101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.51752090454102</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">8.7380952835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5514554977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48358631134033</t>
+    <t xml:space="preserve">8.55145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48358535766602</t>
   </si>
   <si>
     <t xml:space="preserve">8.50055408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58539009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661758422852</t>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.45813655853271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40723419189453</t>
+    <t xml:space="preserve">8.40723323822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.3817834854126</t>
@@ -1157,55 +1157,55 @@
     <t xml:space="preserve">8.20362854003906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01698970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.991539478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518592834473</t>
+    <t xml:space="preserve">8.01698780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518545150757</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
+    <t xml:space="preserve">7.97457075119019</t>
   </si>
   <si>
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9077672958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75505924224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77202796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61932468414307</t>
+    <t xml:space="preserve">8.90776634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82292938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77202892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61932277679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8398962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94169998168945</t>
+    <t xml:space="preserve">8.83989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94170093536377</t>
   </si>
   <si>
     <t xml:space="preserve">9.36588001251221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24710941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12833881378174</t>
+    <t xml:space="preserve">9.24710750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
     <t xml:space="preserve">9.11137199401855</t>
@@ -1217,58 +1217,58 @@
     <t xml:space="preserve">9.09440517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26407718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6723527908325</t>
+    <t xml:space="preserve">9.26407623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41678142547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142381668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705480575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6723518371582</t>
   </si>
   <si>
     <t xml:space="preserve">10.6214504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9607944488525</t>
+    <t xml:space="preserve">10.9607934951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.4358739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680067062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.543098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8729019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8362560272217</t>
+    <t xml:space="preserve">11.3680057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8729009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
+    <t xml:space="preserve">11.3049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9567823410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834934234619</t>
+    <t xml:space="preserve">10.8834924697876</t>
   </si>
   <si>
     <t xml:space="preserve">10.498722076416</t>
@@ -1277,31 +1277,31 @@
     <t xml:space="preserve">10.7002687454224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6086568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.645299911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4804010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0773067474365</t>
+    <t xml:space="preserve">10.6086578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6453008651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0773086547852</t>
   </si>
   <si>
     <t xml:space="preserve">10.2238874435425</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3154993057251</t>
+    <t xml:space="preserve">10.4071092605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3154983520508</t>
   </si>
   <si>
     <t xml:space="preserve">10.443754196167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3338212966919</t>
+    <t xml:space="preserve">10.3338203430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.2055654525757</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78415012359619</t>
+    <t xml:space="preserve">9.78415107727051</t>
   </si>
   <si>
     <t xml:space="preserve">9.8024730682373</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421627044678</t>
+    <t xml:space="preserve">9.67421531677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.72918319702148</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">9.7475061416626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56428050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2528018951416</t>
+    <t xml:space="preserve">9.69253730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25280094146729</t>
   </si>
   <si>
     <t xml:space="preserve">9.3627347946167</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">9.32609176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2711238861084</t>
+    <t xml:space="preserve">9.27112293243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.06957626342773</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">9.08789920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93215847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8771915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03293228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95964336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94132041931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51990699768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28171443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70312881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63900089263916</t>
+    <t xml:space="preserve">8.93215942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87719249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03293132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94132137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51990604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28171539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92299842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63900184631348</t>
   </si>
   <si>
     <t xml:space="preserve">8.65732383728027</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">8.62984085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35500335693359</t>
+    <t xml:space="preserve">8.35500431060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.44661617279053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39938068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3810567855835</t>
+    <t xml:space="preserve">9.39937973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105773925781</t>
   </si>
   <si>
     <t xml:space="preserve">9.19783401489258</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454509735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04209327697754</t>
+    <t xml:space="preserve">9.12454319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04209232330322</t>
   </si>
   <si>
     <t xml:space="preserve">8.96880435943604</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">8.99628734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8863525390625</t>
+    <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.8680305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78557968139648</t>
+    <t xml:space="preserve">8.7855806350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84054660797119</t>
+    <t xml:space="preserve">8.84054756164551</t>
   </si>
   <si>
     <t xml:space="preserve">8.77641868591309</t>
@@ -1481,46 +1481,46 @@
     <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40997219085693</t>
+    <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.30919742584229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24506950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74120426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70456027984619</t>
+    <t xml:space="preserve">8.2450704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7412052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70455980300903</t>
   </si>
   <si>
     <t xml:space="preserve">7.68623828887939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55798053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49385213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
+    <t xml:space="preserve">7.55798101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938530921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
   </si>
   <si>
     <t xml:space="preserve">7.40224075317383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08159923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10908365249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391876220703</t>
+    <t xml:space="preserve">7.08159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10908317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391780853271</t>
   </si>
   <si>
     <t xml:space="preserve">7.16405010223389</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">7.31978988647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48469161987305</t>
+    <t xml:space="preserve">7.48469114303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056322097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76868772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720815658569</t>
+    <t xml:space="preserve">7.76868867874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720863342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.58546447753906</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">7.56714248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34727334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817802429199</t>
+    <t xml:space="preserve">7.34727430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817754745483</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4388861656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5396580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811283111572</t>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05411577224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53965854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811235427856</t>
   </si>
   <si>
     <t xml:space="preserve">7.29230642318726</t>
@@ -1601,82 +1601,82 @@
     <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24650001525879</t>
+    <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
     <t xml:space="preserve">7.2739839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7228832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946201324463</t>
+    <t xml:space="preserve">7.35643482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72288274765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946105957031</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37332630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39164924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49242401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40081119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3458423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33668231964111</t>
+    <t xml:space="preserve">8.37332725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39165019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49242210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40081024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34584426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33668327331543</t>
   </si>
   <si>
     <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13370609283447</t>
+    <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10622215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05125617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7947416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66648483276367</t>
+    <t xml:space="preserve">9.10622119903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05125427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66648578643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01461124420166</t>
+    <t xml:space="preserve">9.01461029052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90467643737793</t>
+    <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.84970951080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80390167236328</t>
+    <t xml:space="preserve">8.80390357971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.813063621521</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">8.58403396606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68480682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25423049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38248825073242</t>
+    <t xml:space="preserve">8.68480777740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25423145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38248920440674</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255344390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12597465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26339340209961</t>
+    <t xml:space="preserve">8.12597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
     <t xml:space="preserve">8.23590850830078</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">8.47410011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50158214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42829418182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46493911743164</t>
+    <t xml:space="preserve">8.50158309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42829322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46493816375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.51074504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822898864746</t>
+    <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.62067985534668</t>
@@ -1742,37 +1742,37 @@
     <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70226860046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40219211578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923187255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89883375167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06339168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98595333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29570960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05371189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02467250823975</t>
+    <t xml:space="preserve">8.70226764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40219116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89883327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06339263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98595285415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15051078796387</t>
+    <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
     <t xml:space="preserve">7.97627258300781</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14083194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9278736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.073073387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0827522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90851402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11179256439209</t>
+    <t xml:space="preserve">8.14083290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92787218093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07307243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11179161071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.13115215301514</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">7.94723320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20859050750732</t>
+    <t xml:space="preserve">8.20859146118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99563312530518</t>
+    <t xml:space="preserve">7.99563360214233</t>
   </si>
   <si>
     <t xml:space="preserve">8.00531387329102</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979389190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947416305542</t>
+    <t xml:space="preserve">7.8697943687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947463989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691394805908</t>
+    <t xml:space="preserve">7.95691347122192</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">8.45059013366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52803134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78938865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14754676818848</t>
+    <t xml:space="preserve">8.52803039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78938770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14754486083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">9.51538372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38954448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45730400085449</t>
+    <t xml:space="preserve">9.3895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4863452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45730495452881</t>
   </si>
   <si>
     <t xml:space="preserve">9.44762516021729</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0284194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3188180923462</t>
+    <t xml:space="preserve">9.52506351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0284204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0477809906006</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">9.98970127105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95098209381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60250282287598</t>
+    <t xml:space="preserve">9.95098114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60250377655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.6799430847168</t>
@@ -1937,31 +1937,31 @@
     <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69930267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71866226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50570297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58314228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698474884033</t>
+    <t xml:space="preserve">9.69930362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71866321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50570392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58314323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698379516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40890598297119</t>
+    <t xml:space="preserve">9.40890407562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.35082530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43794441223145</t>
+    <t xml:space="preserve">9.43794536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">9.11850738525391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914684295654</t>
+    <t xml:space="preserve">9.09914588928223</t>
   </si>
   <si>
     <t xml:space="preserve">9.08946704864502</t>
@@ -1994,31 +1994,31 @@
     <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0797872543335</t>
+    <t xml:space="preserve">9.07978630065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.10882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94426727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85714721679688</t>
+    <t xml:space="preserve">8.9442663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85714817047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.72162818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77002811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93458652496338</t>
+    <t xml:space="preserve">8.77002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266719818115</t>
@@ -2027,55 +2027,55 @@
     <t xml:space="preserve">8.96362686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05074787139893</t>
+    <t xml:space="preserve">9.15722560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05074691772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.97330760955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475090026855</t>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475185394287</t>
   </si>
   <si>
     <t xml:space="preserve">7.84075403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79235363006592</t>
+    <t xml:space="preserve">7.79235410690308</t>
   </si>
   <si>
     <t xml:space="preserve">7.60843515396118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53099632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61811542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34707641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236169815063</t>
+    <t xml:space="preserve">7.53099584579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61811494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236122131348</t>
   </si>
   <si>
     <t xml:space="preserve">6.44684219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14004993438721</t>
+    <t xml:space="preserve">5.14005041122437</t>
   </si>
   <si>
     <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53989362716675</t>
+    <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.64637279510498</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">4.48181343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52053308486938</t>
+    <t xml:space="preserve">4.5205340385437</t>
   </si>
   <si>
     <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037014007568</t>
+    <t xml:space="preserve">5.13036918640137</t>
   </si>
   <si>
     <t xml:space="preserve">5.51756715774536</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">6.04028463363647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00156450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98220443725586</t>
+    <t xml:space="preserve">6.00156497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98220491409302</t>
   </si>
   <si>
     <t xml:space="preserve">5.88540506362915</t>
@@ -2117,25 +2117,25 @@
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644359588623</t>
+    <t xml:space="preserve">6.15644407272339</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46620178222656</t>
+    <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5339617729187</t>
+    <t xml:space="preserve">6.22420358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42748165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.54364156723022</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55035543441772</t>
+    <t xml:space="preserve">7.67619466781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
     <t xml:space="preserve">7.58907556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71491384506226</t>
+    <t xml:space="preserve">7.71491432189941</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">7.39547634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43419551849365</t>
+    <t xml:space="preserve">7.43419599533081</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40515613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931690216064</t>
+    <t xml:space="preserve">7.40515661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
     <t xml:space="preserve">7.44387626647949</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555425643921</t>
+    <t xml:space="preserve">7.69555473327637</t>
   </si>
   <si>
     <t xml:space="preserve">7.85043334960938</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">7.5987548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65683460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
+    <t xml:space="preserve">7.65683507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.3180365562439</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">7.52131605148315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5406756401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51163673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38579654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3373966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35675668716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45355606079102</t>
+    <t xml:space="preserve">7.54067516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51163625717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38579607009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33739709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35675621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45355653762817</t>
   </si>
   <si>
     <t xml:space="preserve">7.64715528488159</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">7.41483592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29867649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25995779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68587446212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88915252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107423782349</t>
+    <t xml:space="preserve">7.29867744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2599573135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68587493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107376098633</t>
   </si>
   <si>
     <t xml:space="preserve">7.74395418167114</t>
@@ -2285,16 +2285,16 @@
     <t xml:space="preserve">7.22123765945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70523452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7245945930481</t>
+    <t xml:space="preserve">7.70523500442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
   </si>
   <si>
     <t xml:space="preserve">7.4825963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6665153503418</t>
+    <t xml:space="preserve">7.66651487350464</t>
   </si>
   <si>
     <t xml:space="preserve">7.42451620101929</t>
@@ -2303,52 +2303,52 @@
     <t xml:space="preserve">7.14379787445068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04699850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
+    <t xml:space="preserve">7.04699897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.11475849151611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17283773422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24059724807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2018780708313</t>
+    <t xml:space="preserve">7.17283725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25027704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24059772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20187711715698</t>
   </si>
   <si>
     <t xml:space="preserve">7.18251752853394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13411808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15347766876221</t>
+    <t xml:space="preserve">7.134117603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15347814559937</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02763843536377</t>
+    <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
     <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01795816421509</t>
+    <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
     <t xml:space="preserve">6.96955871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89211940765381</t>
+    <t xml:space="preserve">6.89211893081665</t>
   </si>
   <si>
     <t xml:space="preserve">6.97923898696899</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">7.06635856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0566782951355</t>
+    <t xml:space="preserve">7.05667877197266</t>
   </si>
   <si>
     <t xml:space="preserve">6.87275981903076</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90179920196533</t>
+    <t xml:space="preserve">6.90179967880249</t>
   </si>
   <si>
     <t xml:space="preserve">6.82435989379883</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">6.76627969741821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564071655273</t>
+    <t xml:space="preserve">6.83404016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78563976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.8146800994873</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">6.75660037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7372407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63076066970825</t>
+    <t xml:space="preserve">6.73724031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63076114654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.67916059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9308385848999</t>
+    <t xml:space="preserve">6.93083906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201519012451</t>
+    <t xml:space="preserve">7.17201471328735</t>
   </si>
   <si>
     <t xml:space="preserve">7.18174648284912</t>
@@ -2432,28 +2432,28 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49314975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395635604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70723962783813</t>
+    <t xml:space="preserve">7.49315023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59046411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5223445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70724010467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.83374786376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06729984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03810596466064</t>
+    <t xml:space="preserve">8.06730079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03810691833496</t>
   </si>
   <si>
     <t xml:space="preserve">8.08676338195801</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">8.00891208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0964937210083</t>
+    <t xml:space="preserve">8.09649467468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380855560303</t>
+    <t xml:space="preserve">8.19380760192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96998643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89213514328003</t>
+    <t xml:space="preserve">7.9699854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89213562011719</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">7.60019493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5710015296936</t>
+    <t xml:space="preserve">7.57100105285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.72670269012451</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">7.73643398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69750833511353</t>
+    <t xml:space="preserve">7.69750881195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401657104492</t>
+    <t xml:space="preserve">7.82401609420776</t>
   </si>
   <si>
     <t xml:space="preserve">7.64885187149048</t>
@@ -2519,31 +2519,31 @@
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992670059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912057876587</t>
+    <t xml:space="preserve">7.60992622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912010192871</t>
   </si>
   <si>
     <t xml:space="preserve">7.62938928604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56126928329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8434796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8045539855957</t>
+    <t xml:space="preserve">7.56126976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84347915649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.79482221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01864433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94079303741455</t>
+    <t xml:space="preserve">8.01864337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94079256057739</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112243652344</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977890014648</t>
+    <t xml:space="preserve">8.33977794647217</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53440570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74849605560303</t>
+    <t xml:space="preserve">8.34951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5344066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74849510192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.67064476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68037605285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81661701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">8.68037700653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81661605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">9.10855674743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04043579101562</t>
+    <t xml:space="preserve">9.04043674468994</t>
   </si>
   <si>
     <t xml:space="preserve">8.75822734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.806884765625</t>
+    <t xml:space="preserve">8.80688381195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.57333183288574</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">8.51494312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24246406555176</t>
+    <t xml:space="preserve">8.24246501922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.30085277557373</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43709182739258</t>
+    <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
     <t xml:space="preserve">8.46628570556641</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23273372650146</t>
+    <t xml:space="preserve">8.15488243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23273468017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.17434501647949</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">8.20353984832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25219535827637</t>
+    <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.22300243377686</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">8.33004760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64144992828369</t>
+    <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.58306217193604</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">8.50521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60252666473389</t>
+    <t xml:space="preserve">8.60252571105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.83607769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70957088470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84580993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01124286651611</t>
+    <t xml:space="preserve">8.70956993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84581089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.92599105834961</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152456283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3541707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3736343383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77028846740723</t>
+    <t xml:space="preserve">10.3152446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3541717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3736333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77028942108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14748191833496</t>
+    <t xml:space="preserve">8.90419769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14748096466064</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05989933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08909320831299</t>
+    <t xml:space="preserve">9.05990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909511566162</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.11828708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24479484558105</t>
+    <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
     <t xml:space="preserve">8.93339157104492</t>
@@ -2756,37 +2756,37 @@
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.361572265625</t>
+    <t xml:space="preserve">9.19613742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
     <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57566261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53673648834229</t>
+    <t xml:space="preserve">9.57566165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5367374420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.8286771774292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86760330200195</t>
+    <t xml:space="preserve">9.86760234832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297458648682</t>
+    <t xml:space="preserve">9.67297554016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.61458778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59512424468994</t>
+    <t xml:space="preserve">9.59512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">9.45888519287109</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">9.1864070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17667675018311</t>
+    <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.21560192108154</t>
@@ -2807,19 +2807,19 @@
     <t xml:space="preserve">9.23506355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20587062835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00151252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49547958374023</t>
+    <t xml:space="preserve">9.20586967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0015115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56359958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49548053741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">8.76795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41763019561768</t>
+    <t xml:space="preserve">8.41762924194336</t>
   </si>
   <si>
     <t xml:space="preserve">8.28139019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37870407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71930122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601795196533</t>
+    <t xml:space="preserve">8.37870311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39816570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601890563965</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04783821105957</t>
+    <t xml:space="preserve">8.04783916473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500286102295</t>
+    <t xml:space="preserve">8.87500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969036102295</t>
+    <t xml:space="preserve">9.42969131469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921459197998</t>
+    <t xml:space="preserve">9.80921363830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">9.51727294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47834777832031</t>
+    <t xml:space="preserve">9.47834873199463</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595439910889</t>
+    <t xml:space="preserve">10.0038414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1595430374146</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816926956177</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">10.1790065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0233039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622291564941</t>
+    <t xml:space="preserve">10.02330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622301101685</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652847290039</t>
+    <t xml:space="preserve">9.90652942657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533226013184</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25452709197998</t>
+    <t xml:space="preserve">9.25452613830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.40049743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48807907104492</t>
+    <t xml:space="preserve">9.48808002471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.63404941558838</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347082138062</t>
+    <t xml:space="preserve">10.3347091674805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689189910889</t>
+    <t xml:space="preserve">11.2689199447632</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.13267993927</t>
+    <t xml:space="preserve">11.1326789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -2999,43 +2999,43 @@
     <t xml:space="preserve">11.6192474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4830083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3662338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.638710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668897628784</t>
+    <t xml:space="preserve">11.4830093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3662328720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6387119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668916702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5729217529297</t>
+    <t xml:space="preserve">12.572922706604</t>
   </si>
   <si>
     <t xml:space="preserve">12.4756078720093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1836681365967</t>
+    <t xml:space="preserve">12.1836671829224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970987319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299928665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8991270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8407392501831</t>
+    <t xml:space="preserve">11.6971006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8991279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8407402038574</t>
   </si>
   <si>
     <t xml:space="preserve">10.976978302002</t>
@@ -3044,34 +3044,34 @@
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159025192261</t>
+    <t xml:space="preserve">11.0159034729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.743426322937</t>
+    <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.9575157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1984691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6071863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132183074951</t>
+    <t xml:space="preserve">10.198468208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4709482192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132164001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.860200881958</t>
+    <t xml:space="preserve">10.8602018356323</t>
   </si>
   <si>
     <t xml:space="preserve">10.6266489028931</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2105312347412</t>
+    <t xml:space="preserve">11.2105321884155</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219345092773</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9306526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8528003692627</t>
+    <t xml:space="preserve">11.9695768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9306516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.852801322937</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1252794265747</t>
+    <t xml:space="preserve">12.1252784729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058158874512</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">12.5339965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6507720947266</t>
+    <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8843250274658</t>
+    <t xml:space="preserve">12.8843259811401</t>
   </si>
   <si>
     <t xml:space="preserve">12.5923843383789</t>
@@ -3128,34 +3128,34 @@
     <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8648624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5145330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4366817474365</t>
+    <t xml:space="preserve">12.8648633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.514533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977565765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4366827011108</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2809801101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1447410583496</t>
+    <t xml:space="preserve">12.2809810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1447420120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534591674805</t>
+    <t xml:space="preserve">12.3393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534582138062</t>
   </si>
   <si>
     <t xml:space="preserve">12.4950714111328</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">12.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.787013053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1762666702271</t>
+    <t xml:space="preserve">12.7870121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2225933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1762657165527</t>
   </si>
   <si>
     <t xml:space="preserve">12.962176322937</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">13.0594902038574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9427137374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1373414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0789518356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4487438201904</t>
+    <t xml:space="preserve">12.9427146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1373405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0789527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4487447738647</t>
   </si>
   <si>
     <t xml:space="preserve">13.468207359314</t>
@@ -3209,25 +3209,25 @@
     <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9742383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3051042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6165084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7527465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809272766113</t>
+    <t xml:space="preserve">13.9742374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3051052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.616509437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7527475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809282302856</t>
   </si>
   <si>
     <t xml:space="preserve">14.9473743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9279127120972</t>
+    <t xml:space="preserve">14.9279117584229</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909591674805</t>
+    <t xml:space="preserve">16.9909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">17.5359172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4191417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7889347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.61376953125</t>
+    <t xml:space="preserve">17.4191398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.788932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6137676239014</t>
   </si>
   <si>
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2949638366699</t>
+    <t xml:space="preserve">17.7500076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">19.0345458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0419502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0030250549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.0419483184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.003023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.547981262207</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3302,25 +3302,25 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060108184814</t>
+    <t xml:space="preserve">19.7060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8519821166992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7546653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113830566406</t>
+    <t xml:space="preserve">19.7546672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036800384521</t>
+    <t xml:space="preserve">19.0734748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036819458008</t>
   </si>
   <si>
     <t xml:space="preserve">18.898307800293</t>
@@ -3332,19 +3332,19 @@
     <t xml:space="preserve">18.8009948730469</t>
   </si>
   <si>
-    <t xml:space="preserve">18.50905418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8788452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9761581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8593807220459</t>
+    <t xml:space="preserve">18.5090522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8788433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8593826293945</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">19.0540103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1513252258301</t>
+    <t xml:space="preserve">19.1513233184814</t>
   </si>
   <si>
     <t xml:space="preserve">18.9177703857422</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">18.9956226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.72314453125</t>
+    <t xml:space="preserve">18.7231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.84299659729</t>
+    <t xml:space="preserve">19.8429946899414</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567638397217</t>
+    <t xml:space="preserve">22.004114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988109588623</t>
+    <t xml:space="preserve">22.3479270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988128662109</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832740783691</t>
+    <t xml:space="preserve">21.3656024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832759857178</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306224822998</t>
+    <t xml:space="preserve">20.5306243896484</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748081207275</t>
+    <t xml:space="preserve">18.0748062133789</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463218688965</t>
+    <t xml:space="preserve">18.5463237762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569301605225</t>
+    <t xml:space="preserve">17.9569282531738</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836448669434</t>
+    <t xml:space="preserve">17.4854125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836429595947</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6032905578613</t>
+    <t xml:space="preserve">17.60329246521</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388439178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.033540725708</t>
+    <t xml:space="preserve">16.7388458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0335426330566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3578,34 +3578,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673282623291</t>
+    <t xml:space="preserve">16.2673263549805</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547487258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.345911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869720458984</t>
+    <t xml:space="preserve">15.8547496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905055999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3459129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869739532471</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154563903809</t>
+    <t xml:space="preserve">15.6189908981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154573440552</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794931411743</t>
+    <t xml:space="preserve">14.4794921875</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3626,37 +3626,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563119888306</t>
+    <t xml:space="preserve">14.9903020858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563110351562</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580787658691</t>
+    <t xml:space="preserve">14.5580778121948</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956043243408</t>
+    <t xml:space="preserve">14.4991397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956052780151</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527774810791</t>
+    <t xml:space="preserve">14.8527765274048</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958106994629</t>
+    <t xml:space="preserve">15.7958097457886</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653532028198</t>
+    <t xml:space="preserve">15.2653541564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567218780518</t>
+    <t xml:space="preserve">16.8567237854004</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370761871338</t>
+    <t xml:space="preserve">16.8370742797852</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549560546875</t>
+    <t xml:space="preserve">16.9549541473389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514186859131</t>
+    <t xml:space="preserve">17.1514205932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247039794922</t>
+    <t xml:space="preserve">17.5247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465282440186</t>
+    <t xml:space="preserve">19.6465301513672</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697113037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838512420654</t>
+    <t xml:space="preserve">19.4697093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838493347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359256744385</t>
+    <t xml:space="preserve">20.0394611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359275817871</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779708862305</t>
+    <t xml:space="preserve">20.6779727935791</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005805969238</t>
+    <t xml:space="preserve">22.2005786895752</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532321929932</t>
+    <t xml:space="preserve">22.0532302856445</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -8029,7 +8029,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8055,7 +8055,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8081,7 +8081,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8107,7 +8107,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8159,7 +8159,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8185,7 +8185,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8211,7 +8211,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8237,7 +8237,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8263,7 +8263,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8289,7 +8289,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8393,7 +8393,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8419,7 +8419,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8471,7 +8471,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8523,7 +8523,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8549,7 +8549,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8575,7 +8575,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8627,7 +8627,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8679,7 +8679,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8705,7 +8705,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8731,7 +8731,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8783,7 +8783,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8809,7 +8809,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8835,7 +8835,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8887,7 +8887,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8939,7 +8939,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9017,7 +9017,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9043,7 +9043,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9069,7 +9069,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9095,7 +9095,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9121,7 +9121,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9173,7 +9173,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9199,7 +9199,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9225,7 +9225,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9251,7 +9251,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9303,7 +9303,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9355,7 +9355,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9381,7 +9381,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9407,7 +9407,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9433,7 +9433,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9459,7 +9459,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9485,7 +9485,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9511,7 +9511,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9537,7 +9537,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9563,7 +9563,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9589,7 +9589,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9615,7 +9615,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9667,7 +9667,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9693,7 +9693,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9719,7 +9719,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9745,7 +9745,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9771,7 +9771,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9797,7 +9797,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9823,7 +9823,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9849,7 +9849,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9875,7 +9875,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9901,7 +9901,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9927,7 +9927,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9953,7 +9953,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9979,7 +9979,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10005,7 +10005,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10031,7 +10031,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10057,7 +10057,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10083,7 +10083,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10135,7 +10135,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10161,7 +10161,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10239,7 +10239,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10265,7 +10265,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10291,7 +10291,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10317,7 +10317,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10343,7 +10343,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10369,7 +10369,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10395,7 +10395,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10421,7 +10421,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10447,7 +10447,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10473,7 +10473,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10499,7 +10499,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10525,7 +10525,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10551,7 +10551,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10577,7 +10577,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10603,7 +10603,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10629,7 +10629,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10655,7 +10655,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10681,7 +10681,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10707,7 +10707,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10733,7 +10733,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10759,7 +10759,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10785,7 +10785,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10811,7 +10811,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10837,7 +10837,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10863,7 +10863,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10889,7 +10889,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10915,7 +10915,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10941,7 +10941,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10967,7 +10967,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10993,7 +10993,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11019,7 +11019,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11045,7 +11045,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11071,7 +11071,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11097,7 +11097,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11123,7 +11123,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11175,7 +11175,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11253,7 +11253,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11279,7 +11279,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11305,7 +11305,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11331,7 +11331,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11357,7 +11357,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11383,7 +11383,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11461,7 +11461,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11487,7 +11487,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11539,7 +11539,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11565,7 +11565,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11643,7 +11643,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11669,7 +11669,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11695,7 +11695,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11721,7 +11721,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11747,7 +11747,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11773,7 +11773,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11799,7 +11799,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11825,7 +11825,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11851,7 +11851,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11877,7 +11877,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11903,7 +11903,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11929,7 +11929,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11955,7 +11955,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11981,7 +11981,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12007,7 +12007,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12033,7 +12033,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12059,7 +12059,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12085,7 +12085,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12111,7 +12111,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12137,7 +12137,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12163,7 +12163,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12189,7 +12189,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12215,7 +12215,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12241,7 +12241,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12267,7 +12267,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12293,7 +12293,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12319,7 +12319,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12345,7 +12345,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12371,7 +12371,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12397,7 +12397,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12423,7 +12423,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12449,7 +12449,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12475,7 +12475,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12501,7 +12501,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12527,7 +12527,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12553,7 +12553,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12579,7 +12579,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12605,7 +12605,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12631,7 +12631,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12657,7 +12657,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12683,7 +12683,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12709,7 +12709,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12735,7 +12735,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12761,7 +12761,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12787,7 +12787,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12813,7 +12813,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12839,7 +12839,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12865,7 +12865,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12891,7 +12891,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12917,7 +12917,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12943,7 +12943,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12969,7 +12969,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12995,7 +12995,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13021,7 +13021,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13047,7 +13047,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13073,7 +13073,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13099,7 +13099,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13125,7 +13125,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13151,7 +13151,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13177,7 +13177,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13203,7 +13203,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13229,7 +13229,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13255,7 +13255,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13281,7 +13281,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13307,7 +13307,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13333,7 +13333,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13359,7 +13359,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13385,7 +13385,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13411,7 +13411,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13437,7 +13437,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13463,7 +13463,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13489,7 +13489,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13515,7 +13515,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13541,7 +13541,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13567,7 +13567,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13593,7 +13593,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13619,7 +13619,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13645,7 +13645,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13671,7 +13671,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13697,7 +13697,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13723,7 +13723,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13749,7 +13749,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13775,7 +13775,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13801,7 +13801,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13827,7 +13827,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13853,7 +13853,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13879,7 +13879,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13905,7 +13905,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13931,7 +13931,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13957,7 +13957,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13983,7 +13983,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14009,7 +14009,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14035,7 +14035,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14061,7 +14061,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14087,7 +14087,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14113,7 +14113,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14139,7 +14139,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14165,7 +14165,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14191,7 +14191,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14217,7 +14217,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14243,7 +14243,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14269,7 +14269,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14295,7 +14295,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14321,7 +14321,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14347,7 +14347,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14373,7 +14373,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14399,7 +14399,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14425,7 +14425,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14451,7 +14451,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14633,7 +14633,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14711,7 +14711,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15387,7 +15387,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15543,7 +15543,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15569,7 +15569,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15803,7 +15803,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16609,7 +16609,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -70801,7 +70801,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6911805556</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>23218</v>
@@ -70822,6 +70822,32 @@
         <v>1491</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6910185185</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>13168</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>30.2999992370605</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>29.6499996185303</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>30.1499996185303</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>29.9500007629395</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009426116943</t>
+    <t xml:space="preserve">6.41009378433228</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">6.39007520675659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39808225631714</t>
+    <t xml:space="preserve">6.3980827331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.22992277145386</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">6.26996040344238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0937933921814</t>
+    <t xml:space="preserve">6.09379291534424</t>
   </si>
   <si>
     <t xml:space="preserve">6.12582397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08578634262085</t>
+    <t xml:space="preserve">6.08578586578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.92563343048096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85356426239014</t>
+    <t xml:space="preserve">5.85356473922729</t>
   </si>
   <si>
     <t xml:space="preserve">5.76548099517822</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">5.94565296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72544288635254</t>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143888473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7254433631897</t>
   </si>
   <si>
     <t xml:space="preserve">5.74145841598511</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">5.88559579849243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91762590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164848327637</t>
+    <t xml:space="preserve">5.91762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164896011353</t>
   </si>
   <si>
     <t xml:space="preserve">6.00570964813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84956121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386913299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984607696533</t>
+    <t xml:space="preserve">5.84956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17386960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984655380249</t>
   </si>
   <si>
     <t xml:space="preserve">6.20590019226074</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">6.29398393630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22191429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789218902588</t>
+    <t xml:space="preserve">6.22191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789266586304</t>
   </si>
   <si>
     <t xml:space="preserve">6.20990371704102</t>
@@ -134,82 +134,82 @@
     <t xml:space="preserve">6.406090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813894271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616743087769</t>
+    <t xml:space="preserve">6.45813941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">6.50218152999878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49417400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183855056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15385055541992</t>
+    <t xml:space="preserve">6.49417352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385007858276</t>
   </si>
   <si>
     <t xml:space="preserve">6.10980892181396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98969459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94965553283691</t>
+    <t xml:space="preserve">6.11381244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98969411849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94965600967407</t>
   </si>
   <si>
     <t xml:space="preserve">6.13383102416992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785455703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09779739379883</t>
+    <t xml:space="preserve">6.05375480651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09779644012451</t>
   </si>
   <si>
     <t xml:space="preserve">6.18187713623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12181997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373527526855</t>
+    <t xml:space="preserve">6.12181949615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.1018009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01371669769287</t>
+    <t xml:space="preserve">6.01371812820435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95766401290894</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">5.93764495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11781644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377433776855</t>
+    <t xml:space="preserve">6.11781692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07377481460571</t>
   </si>
   <si>
     <t xml:space="preserve">6.06977033615112</t>
@@ -230,133 +230,130 @@
     <t xml:space="preserve">6.19342565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22654485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07336616516113</t>
+    <t xml:space="preserve">6.2265453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07336568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.16030550003052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20998525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406614303589</t>
+    <t xml:space="preserve">6.20998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
     <t xml:space="preserve">6.16858530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18928527832031</t>
+    <t xml:space="preserve">6.18928480148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.20170545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890554428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19756603240967</t>
+    <t xml:space="preserve">6.11890506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.12718534469604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13960552215576</t>
+    <t xml:space="preserve">6.1396050453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.11062574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04438638687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89534616470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81254625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0402455329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94502592086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.961585521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394668579102</t>
+    <t xml:space="preserve">6.04438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89534664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776681900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8125467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394620895386</t>
   </si>
   <si>
     <t xml:space="preserve">5.78770637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190576553345</t>
+    <t xml:space="preserve">5.8622260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190624237061</t>
   </si>
   <si>
     <t xml:space="preserve">5.86636638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12304592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540517807007</t>
+    <t xml:space="preserve">6.12304496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540565490723</t>
   </si>
   <si>
     <t xml:space="preserve">6.10234546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26794576644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.156165599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0319652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1768651008606</t>
+    <t xml:space="preserve">6.26794481277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15616512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03196620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17686605453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.25138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13132572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14374542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07750606536865</t>
+    <t xml:space="preserve">6.13132524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14374589920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07750558853149</t>
   </si>
   <si>
     <t xml:space="preserve">6.14788579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06922626495361</t>
+    <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266523361206</t>
@@ -365,46 +362,46 @@
     <t xml:space="preserve">5.96986627578735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648536682129</t>
+    <t xml:space="preserve">6.10648584365845</t>
   </si>
   <si>
     <t xml:space="preserve">5.98642587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92432641983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9533052444458</t>
+    <t xml:space="preserve">5.92432689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95330667495728</t>
   </si>
   <si>
     <t xml:space="preserve">6.03610563278198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95744657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298595428467</t>
+    <t xml:space="preserve">5.95744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298643112183</t>
   </si>
   <si>
     <t xml:space="preserve">5.88706636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93260669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8249659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84980630874634</t>
+    <t xml:space="preserve">5.9326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496690750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668710708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84980583190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.85808610916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75872659683228</t>
+    <t xml:space="preserve">5.75872611999512</t>
   </si>
   <si>
     <t xml:space="preserve">5.90362644195557</t>
@@ -413,10 +410,10 @@
     <t xml:space="preserve">5.93674612045288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87878656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92018604278564</t>
+    <t xml:space="preserve">5.87878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9201865196228</t>
   </si>
   <si>
     <t xml:space="preserve">6.06094598770142</t>
@@ -425,28 +422,28 @@
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45424461364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29278564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45838499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38386487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042543411255</t>
+    <t xml:space="preserve">6.45010566711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290462493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45424556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29278516769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4583854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
     <t xml:space="preserve">6.2348256111145</t>
@@ -455,13 +452,13 @@
     <t xml:space="preserve">6.33832550048828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37972497940063</t>
+    <t xml:space="preserve">6.37972545623779</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558460235596</t>
+    <t xml:space="preserve">6.37558507919312</t>
   </si>
   <si>
     <t xml:space="preserve">6.50806474685669</t>
@@ -470,19 +467,19 @@
     <t xml:space="preserve">6.34246492385864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49150466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3341851234436</t>
+    <t xml:space="preserve">6.49150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33418416976929</t>
   </si>
   <si>
     <t xml:space="preserve">6.3714451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30520534515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214515686035</t>
+    <t xml:space="preserve">6.30520439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214563369751</t>
   </si>
   <si>
     <t xml:space="preserve">6.18514537811279</t>
@@ -494,22 +491,22 @@
     <t xml:space="preserve">6.01126623153687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01954555511475</t>
+    <t xml:space="preserve">6.0195460319519</t>
   </si>
   <si>
     <t xml:space="preserve">6.02782583236694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32590532302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36730527877808</t>
+    <t xml:space="preserve">6.32590436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">6.28450536727905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41284513473511</t>
+    <t xml:space="preserve">6.41284418106079</t>
   </si>
   <si>
     <t xml:space="preserve">6.24310541152954</t>
@@ -521,40 +518,40 @@
     <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6488242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72334432601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73990535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01314353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07938289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142286300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05454397201538</t>
+    <t xml:space="preserve">6.68194341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72334384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73990440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0379843711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384351730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01314401626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07938385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05454349517822</t>
   </si>
   <si>
     <t xml:space="preserve">6.98830366134644</t>
@@ -563,25 +560,25 @@
     <t xml:space="preserve">7.20772314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60102272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0876636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682189941406</t>
+    <t xml:space="preserve">7.6010217666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682285308838</t>
   </si>
   <si>
     <t xml:space="preserve">7.48924207687378</t>
@@ -590,10 +587,10 @@
     <t xml:space="preserve">7.43542146682739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27810287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1704626083374</t>
+    <t xml:space="preserve">7.27810335159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17046308517456</t>
   </si>
   <si>
     <t xml:space="preserve">7.10422325134277</t>
@@ -602,73 +599,73 @@
     <t xml:space="preserve">6.94276428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0711030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212427139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894319534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91378355026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26982259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306173324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994110107422</t>
+    <t xml:space="preserve">7.07110357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518255233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91378402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2698221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306221008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994253158569</t>
   </si>
   <si>
     <t xml:space="preserve">7.64242172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210290908813</t>
+    <t xml:space="preserve">7.69210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">7.65898132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90324115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07297992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85355997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928020477295</t>
+    <t xml:space="preserve">7.90324068069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03158092498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07298278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928115844727</t>
   </si>
   <si>
     <t xml:space="preserve">8.19304180145264</t>
@@ -677,34 +674,34 @@
     <t xml:space="preserve">8.25514125823975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48697948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49525928497314</t>
+    <t xml:space="preserve">8.48698043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36278057098389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39590072631836</t>
+    <t xml:space="preserve">8.39589977264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.43729972839355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62773990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59462070465088</t>
+    <t xml:space="preserve">8.62774085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63602161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.52838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32966136932373</t>
+    <t xml:space="preserve">8.32966041564941</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986167907715</t>
@@ -713,7 +710,7 @@
     <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9612021446228</t>
+    <t xml:space="preserve">7.96120119094849</t>
   </si>
   <si>
     <t xml:space="preserve">8.17648124694824</t>
@@ -722,46 +719,46 @@
     <t xml:space="preserve">8.51181888580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6028995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.776780128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85957813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3729362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44745826721191</t>
+    <t xml:space="preserve">8.60290050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77677917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85957908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37293815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44745635986328</t>
   </si>
   <si>
     <t xml:space="preserve">10.0850162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1595363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556934356689</t>
+    <t xml:space="preserve">10.1595373153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894550323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556943893433</t>
   </si>
   <si>
     <t xml:space="preserve">10.2920169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499755859375</t>
+    <t xml:space="preserve">10.3499774932861</t>
   </si>
   <si>
     <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.460262298584</t>
+    <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
     <t xml:space="preserve">9.87489414215088</t>
@@ -773,34 +770,37 @@
     <t xml:space="preserve">10.1209192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0530500411987</t>
+    <t xml:space="preserve">10.053050994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.171820640564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1803045272827</t>
+    <t xml:space="preserve">10.1803035736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.0785007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3839101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7062854766846</t>
+    <t xml:space="preserve">10.3839092254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638679504395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6129674911499</t>
+    <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772291183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7232532501221</t>
+    <t xml:space="preserve">10.3499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7232542037964</t>
   </si>
   <si>
     <t xml:space="preserve">10.6469011306763</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">10.6299333572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384172439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4178438186646</t>
+    <t xml:space="preserve">10.6384181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4178428649902</t>
   </si>
   <si>
     <t xml:space="preserve">10.3584585189819</t>
@@ -821,46 +821,46 @@
     <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0445671081543</t>
+    <t xml:space="preserve">10.3075580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.04456615448</t>
   </si>
   <si>
     <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78157329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374919891357</t>
+    <t xml:space="preserve">9.83247661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78157424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61190319061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374824523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.1028881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17923927307129</t>
+    <t xml:space="preserve">9.16227340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17924022674561</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23862552642822</t>
+    <t xml:space="preserve">9.23862743377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.23014259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33194541931152</t>
+    <t xml:space="preserve">9.33194637298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.21317481994629</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">9.37436389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825626373291</t>
+    <t xml:space="preserve">9.68825531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.0954675674438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360832214355</t>
+    <t xml:space="preserve">10.0360822677612</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034484863281</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">9.84944343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2227230072021</t>
+    <t xml:space="preserve">10.2227210998535</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">10.2821073532104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2566556930542</t>
+    <t xml:space="preserve">10.2566576004028</t>
   </si>
   <si>
     <t xml:space="preserve">10.2905912399292</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057542800903</t>
+    <t xml:space="preserve">10.2057552337646</t>
   </si>
   <si>
     <t xml:space="preserve">10.0191164016724</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96821403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89186096191406</t>
+    <t xml:space="preserve">9.9682149887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764060974121</t>
+    <t xml:space="preserve">9.74764156341553</t>
   </si>
   <si>
     <t xml:space="preserve">9.51010036468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.70522403717041</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919895172119</t>
@@ -932,40 +932,40 @@
     <t xml:space="preserve">9.35739612579346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948566436768</t>
+    <t xml:space="preserve">9.56948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280460357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39132976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071506500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27256011962891</t>
+    <t xml:space="preserve">9.50161647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39133071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51858329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27256107330322</t>
   </si>
   <si>
     <t xml:space="preserve">9.20469093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58645439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313354492188</t>
+    <t xml:space="preserve">9.58645343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313163757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.84096050262451</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">9.67977142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63735389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75612354278564</t>
+    <t xml:space="preserve">9.64583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63735294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75612258911133</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399368286133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77309131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854202270508</t>
+    <t xml:space="preserve">9.77309226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854297637939</t>
   </si>
   <si>
     <t xml:space="preserve">9.69673919677734</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">9.79005908966064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73067378997803</t>
+    <t xml:space="preserve">9.73067474365234</t>
   </si>
   <si>
     <t xml:space="preserve">9.47616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13682460784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108337402344</t>
+    <t xml:space="preserve">9.13682270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
     <t xml:space="preserve">8.72112655639648</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">8.59387397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32663917541504</t>
+    <t xml:space="preserve">8.07637500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182571411133</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">8.12303352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6278076171875</t>
+    <t xml:space="preserve">8.62780666351318</t>
   </si>
   <si>
     <t xml:space="preserve">8.33088302612305</t>
@@ -1049,40 +1049,40 @@
     <t xml:space="preserve">8.27149772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37329959869385</t>
+    <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.31391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29270553588867</t>
+    <t xml:space="preserve">8.29270648956299</t>
   </si>
   <si>
     <t xml:space="preserve">8.09334182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03819942474365</t>
+    <t xml:space="preserve">8.03819847106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610940933228</t>
+    <t xml:space="preserve">7.82610845565796</t>
   </si>
   <si>
     <t xml:space="preserve">7.80065727233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91094350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580205917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881269454956</t>
+    <t xml:space="preserve">7.91094398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9788122177124</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123069763184</t>
@@ -1094,139 +1094,139 @@
     <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16121101379395</t>
+    <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092430114746</t>
+    <t xml:space="preserve">8.05092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">8.08061599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17393589019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2248363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28846454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4242000579834</t>
+    <t xml:space="preserve">8.17393684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2884635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73809432983398</t>
+    <t xml:space="preserve">8.51752090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48358535766602</t>
+    <t xml:space="preserve">8.48358726501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.50055408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58538913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4581356048584</t>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58538818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45813655853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.40723419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38178443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01698875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99153804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518640518188</t>
+    <t xml:space="preserve">8.3817834854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698970794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518592834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3223991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90776538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75506114959717</t>
+    <t xml:space="preserve">7.97457218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32239818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90776634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506019592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.82292938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77202892303467</t>
+    <t xml:space="preserve">8.77202987670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.61932373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60235786437988</t>
+    <t xml:space="preserve">8.60235595703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94169902801514</t>
+    <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36588001251221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24710941314697</t>
+    <t xml:space="preserve">9.24710845947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11137199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0435037612915</t>
+    <t xml:space="preserve">9.11137104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04350280761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.09440517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26407623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41678142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705490112305</t>
+    <t xml:space="preserve">9.26407718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41678237915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705480575562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6723518371582</t>
@@ -1241,43 +1241,43 @@
     <t xml:space="preserve">11.4358739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680067062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4698095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.543098449707</t>
+    <t xml:space="preserve">11.3680057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4698076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8362560272217</t>
+    <t xml:space="preserve">11.8362579345703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2865839004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.498722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6086578369141</t>
+    <t xml:space="preserve">11.3049077987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.286584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9567823410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4987239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002687454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6086568832397</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453018188477</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">10.4804000854492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1689205169678</t>
+    <t xml:space="preserve">10.1689195632935</t>
   </si>
   <si>
     <t xml:space="preserve">10.004017829895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98569583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0589866638184</t>
+    <t xml:space="preserve">9.98569679260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589847564697</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788534164429</t>
@@ -1304,19 +1304,19 @@
     <t xml:space="preserve">10.0773086547852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2238874435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2605323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1322755813599</t>
+    <t xml:space="preserve">10.2238864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2605304718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1322746276855</t>
   </si>
   <si>
     <t xml:space="preserve">10.4071102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3154983520508</t>
+    <t xml:space="preserve">10.3155002593994</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437551498413</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2055644989014</t>
+    <t xml:space="preserve">10.2055654525757</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">9.78415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80247211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71086120605469</t>
+    <t xml:space="preserve">9.8024730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">9.69253826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56428050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2528018951416</t>
+    <t xml:space="preserve">9.56428146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">9.36273574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32609176635742</t>
+    <t xml:space="preserve">9.32609081268311</t>
   </si>
   <si>
     <t xml:space="preserve">9.27112293243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06957721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08790016174316</t>
+    <t xml:space="preserve">9.06957626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08789920806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.93215942382812</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293132781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95964336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796535491943</t>
+    <t xml:space="preserve">9.03293323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796630859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.94132041931152</t>
@@ -1406,55 +1406,55 @@
     <t xml:space="preserve">8.51990604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28171539306641</t>
+    <t xml:space="preserve">8.28171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.92299747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7031307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63900089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65732383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62983989715576</t>
+    <t xml:space="preserve">8.70312976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63900279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65732288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62984085083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.35500431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44661617279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39937973022461</t>
+    <t xml:space="preserve">8.44661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39938068389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.38105773925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19783306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00544834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14286613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12454414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04209327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96880340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628734588623</t>
+    <t xml:space="preserve">9.19783401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00544929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14286708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12454319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04209423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628829956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.88635349273682</t>
@@ -1463,64 +1463,64 @@
     <t xml:space="preserve">8.86803245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7855806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83138656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84054660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7764196395874</t>
+    <t xml:space="preserve">8.78557872772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83138561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84054756164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59319591522217</t>
+    <t xml:space="preserve">8.59319496154785</t>
   </si>
   <si>
     <t xml:space="preserve">8.40997219085693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3091983795166</t>
+    <t xml:space="preserve">8.30919742584229</t>
   </si>
   <si>
     <t xml:space="preserve">8.2450704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74120426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70455884933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68623876571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55798149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4938530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307928085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224123001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10908317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391876220703</t>
+    <t xml:space="preserve">7.74120473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70455980300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68623828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55798053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10908269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391828536987</t>
   </si>
   <si>
     <t xml:space="preserve">7.16405010223389</t>
@@ -1529,46 +1529,46 @@
     <t xml:space="preserve">7.30146741867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31978940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469209671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4205641746521</t>
+    <t xml:space="preserve">7.31978988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42056369781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.7686882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720815658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51217555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817754745483</t>
+    <t xml:space="preserve">7.80533361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58546495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5121750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488910675049</t>
+    <t xml:space="preserve">7.15488815307617</t>
   </si>
   <si>
     <t xml:space="preserve">7.06327724456787</t>
@@ -1580,52 +1580,52 @@
     <t xml:space="preserve">7.43888521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53965759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5304970741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811235427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29230642318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28314542770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31062841415405</t>
+    <t xml:space="preserve">7.53965854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29230690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2831449508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
     <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2739839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72288179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946153640747</t>
+    <t xml:space="preserve">7.27398443222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72288227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946105957031</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37332630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3916482925415</t>
+    <t xml:space="preserve">8.37332725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39164924621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.49242305755615</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3458423614502</t>
+    <t xml:space="preserve">8.34584331512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13370513916016</t>
+    <t xml:space="preserve">9.02377223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13370609283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.73977470397949</t>
@@ -1658,22 +1658,22 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648578643799</t>
+    <t xml:space="preserve">8.66648387908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.85887050628662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01460933685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91383647918701</t>
+    <t xml:space="preserve">9.01461029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91383743286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84970855712891</t>
+    <t xml:space="preserve">8.84970951080322</t>
   </si>
   <si>
     <t xml:space="preserve">8.8039026260376</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">8.813063621521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58403301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68480777740479</t>
+    <t xml:space="preserve">8.58403396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68480682373047</t>
   </si>
   <si>
     <t xml:space="preserve">8.25423049926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255344390869</t>
+    <t xml:space="preserve">8.38248825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255249023438</t>
   </si>
   <si>
     <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26339244842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2359094619751</t>
+    <t xml:space="preserve">8.26339149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23590850830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.43745422363281</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">8.45577716827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47410011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.47410106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50158405303955</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829322814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46493816375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51074504852295</t>
+    <t xml:space="preserve">8.46493911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51074600219727</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822803497314</t>
@@ -1733,58 +1733,58 @@
     <t xml:space="preserve">8.62067890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61151790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54738807678223</t>
+    <t xml:space="preserve">8.61151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70226955413818</t>
+    <t xml:space="preserve">8.70226860046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.40219116210938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18923091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89883375167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06339168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98595333099365</t>
+    <t xml:space="preserve">8.18923187255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89883279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06339263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98595285415649</t>
   </si>
   <si>
     <t xml:space="preserve">8.29571056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09243106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435325622559</t>
+    <t xml:space="preserve">8.09243202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.05371189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02467346191406</t>
+    <t xml:space="preserve">8.02467250823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12147331237793</t>
+    <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627258300781</t>
+    <t xml:space="preserve">7.97627210617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.96659183502197</t>
@@ -1793,40 +1793,40 @@
     <t xml:space="preserve">8.16987133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24731159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25699043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14083099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92787313461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07307243347168</t>
+    <t xml:space="preserve">8.24731254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25699138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14083194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92787218093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.073073387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.08275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90851402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11179256439209</t>
+    <t xml:space="preserve">7.90851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11179161071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.13115215301514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04403305053711</t>
+    <t xml:space="preserve">8.04403209686279</t>
   </si>
   <si>
     <t xml:space="preserve">7.94723320007324</t>
@@ -1835,37 +1835,37 @@
     <t xml:space="preserve">8.20859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99563312530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0053129196167</t>
+    <t xml:space="preserve">8.16019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99563360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979389190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91819381713867</t>
+    <t xml:space="preserve">7.86979341506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91819286346436</t>
   </si>
   <si>
     <t xml:space="preserve">7.95691299438477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44091129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33442974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28603076934814</t>
+    <t xml:space="preserve">8.44091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33443164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28603172302246</t>
   </si>
   <si>
     <t xml:space="preserve">8.22795104980469</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52803039550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78938865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14754676818848</t>
+    <t xml:space="preserve">8.5280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78938770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14754581451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.38954448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48634433746338</t>
+    <t xml:space="preserve">9.4863452911377</t>
   </si>
   <si>
     <t xml:space="preserve">9.45730495452881</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">9.44762420654297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55410385131836</t>
+    <t xml:space="preserve">9.55410480499268</t>
   </si>
   <si>
     <t xml:space="preserve">9.53474426269531</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0284204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3188180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0477819442749</t>
+    <t xml:space="preserve">10.0284214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3188190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
@@ -1925,40 +1925,40 @@
     <t xml:space="preserve">9.98970127105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95098209381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60250377655029</t>
+    <t xml:space="preserve">9.95098114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60250282287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.6799430847168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6121826171875</t>
+    <t xml:space="preserve">9.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.69930267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71866226196289</t>
+    <t xml:space="preserve">9.71866321563721</t>
   </si>
   <si>
     <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58314323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87354183197021</t>
+    <t xml:space="preserve">9.58314228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.40890502929688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3508243560791</t>
+    <t xml:space="preserve">9.35082530975342</t>
   </si>
   <si>
     <t xml:space="preserve">9.43794441223145</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77674293518066</t>
+    <t xml:space="preserve">9.33146476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77674198150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.64122295379639</t>
@@ -1982,19 +1982,19 @@
     <t xml:space="preserve">9.11850643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09914684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08946800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19594669342041</t>
+    <t xml:space="preserve">9.09914493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0894660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
     <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0797872543335</t>
+    <t xml:space="preserve">9.07978630065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.10882663726807</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9442663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85714721679688</t>
+    <t xml:space="preserve">8.94426822662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85714817047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.72162818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77002811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93458652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99266719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96362686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1572265625</t>
+    <t xml:space="preserve">8.77002906799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93458843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99266624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96362781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15722560882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.05074691772461</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">8.32475090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84075498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79235410690308</t>
+    <t xml:space="preserve">7.84075403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79235458374023</t>
   </si>
   <si>
     <t xml:space="preserve">7.60843563079834</t>
@@ -2054,61 +2054,61 @@
     <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61811494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34707641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44684219360352</t>
+    <t xml:space="preserve">7.61811542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44684171676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.14004945755005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47884750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53989362716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64637279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48181343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52053308486938</t>
+    <t xml:space="preserve">5.47884798049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53989315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64637327194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48181390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52053356170654</t>
   </si>
   <si>
     <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51756715774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04028463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00156497955322</t>
+    <t xml:space="preserve">5.13036966323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51756763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04028415679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00156450271606</t>
   </si>
   <si>
     <t xml:space="preserve">5.98220443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88540506362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79828596115112</t>
+    <t xml:space="preserve">5.88540554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79828548431396</t>
   </si>
   <si>
     <t xml:space="preserve">5.96284437179565</t>
@@ -2117,25 +2117,25 @@
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644407272339</t>
+    <t xml:space="preserve">6.15644454956055</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46620178222656</t>
+    <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.43716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420310974121</t>
+    <t xml:space="preserve">6.22420358657837</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5339617729187</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.54364156723022</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619466781616</t>
+    <t xml:space="preserve">7.67619514465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907508850098</t>
+    <t xml:space="preserve">7.58907556533813</t>
   </si>
   <si>
     <t xml:space="preserve">7.71491432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63747453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3954758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43419551849365</t>
+    <t xml:space="preserve">7.63747549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39547634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43419599533081</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4632363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69555473327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043334960938</t>
+    <t xml:space="preserve">7.46323585510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69555377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043287277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771730422974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56003570556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59875535964966</t>
+    <t xml:space="preserve">7.56003522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5987548828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.65683460235596</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.30835723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23091793060303</t>
+    <t xml:space="preserve">7.23091745376587</t>
   </si>
   <si>
     <t xml:space="preserve">7.521315574646</t>
@@ -2219,55 +2219,55 @@
     <t xml:space="preserve">7.5406756401062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51163625717163</t>
+    <t xml:space="preserve">7.51163578033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3373966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35675668716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45355653762817</t>
+    <t xml:space="preserve">7.33739709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35675621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45355606079102</t>
   </si>
   <si>
     <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57939529418945</t>
+    <t xml:space="preserve">7.57939577102661</t>
   </si>
   <si>
     <t xml:space="preserve">7.41483592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29867649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68587446212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88915348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107471466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7439546585083</t>
+    <t xml:space="preserve">7.29867744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68587493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74395418167114</t>
   </si>
   <si>
     <t xml:space="preserve">7.73427391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36643648147583</t>
+    <t xml:space="preserve">7.36643743515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.26963758468628</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12443828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22123765945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70523452758789</t>
+    <t xml:space="preserve">7.16315793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12443780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22123718261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70523500442505</t>
   </si>
   <si>
     <t xml:space="preserve">7.72459411621094</t>
@@ -2297,37 +2297,37 @@
     <t xml:space="preserve">7.66651487350464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42451667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14379787445068</t>
+    <t xml:space="preserve">7.42451620101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14379835128784</t>
   </si>
   <si>
     <t xml:space="preserve">7.04699850082397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10507822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11475849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17283773422241</t>
+    <t xml:space="preserve">7.10507869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11475801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17283725738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.25027704238892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24059724807739</t>
+    <t xml:space="preserve">7.24059772491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.20187759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18251848220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13411855697632</t>
+    <t xml:space="preserve">7.18251752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.134117603302</t>
   </si>
   <si>
     <t xml:space="preserve">7.15347766876221</t>
@@ -2339,55 +2339,55 @@
     <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07603788375854</t>
+    <t xml:space="preserve">7.0760383605957</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96955871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89211940765381</t>
+    <t xml:space="preserve">6.96955919265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89211893081665</t>
   </si>
   <si>
     <t xml:space="preserve">6.97923898696899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06635856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05667781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87275981903076</t>
+    <t xml:space="preserve">7.06635904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05667877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8727593421936</t>
   </si>
   <si>
     <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90179920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436037063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80500030517578</t>
+    <t xml:space="preserve">6.90179967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82435941696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80500078201294</t>
   </si>
   <si>
     <t xml:space="preserve">6.77596044540405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76627969741821</t>
+    <t xml:space="preserve">6.76628017425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.83403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81467962265015</t>
+    <t xml:space="preserve">6.78564023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8146800994873</t>
   </si>
   <si>
     <t xml:space="preserve">6.7953200340271</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">6.75660037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7372407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63076066970825</t>
+    <t xml:space="preserve">6.73724031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63076114654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.67916059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93083906173706</t>
+    <t xml:space="preserve">6.93083953857422</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067213058472</t>
+    <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174600601196</t>
+    <t xml:space="preserve">7.17201471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174648284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">7.49315023422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395635604858</t>
+    <t xml:space="preserve">7.59046411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5223445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395587921143</t>
   </si>
   <si>
     <t xml:space="preserve">7.70724010467529</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0089111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0964937210083</t>
+    <t xml:space="preserve">8.00891208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09649467468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96998643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89213514328003</t>
+    <t xml:space="preserve">7.9699854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89213562011719</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019540786743</t>
+    <t xml:space="preserve">7.60019493103027</t>
   </si>
   <si>
     <t xml:space="preserve">7.57100105285645</t>
@@ -2507,46 +2507,46 @@
     <t xml:space="preserve">7.73643398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69750833511353</t>
+    <t xml:space="preserve">7.69750881195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64885234832764</t>
+    <t xml:space="preserve">7.82401609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64885187149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992670059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912057876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6293888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56126928329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8434796333313</t>
+    <t xml:space="preserve">7.60992622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912010192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62938928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56126976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84347915649414</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79482269287109</t>
+    <t xml:space="preserve">7.79482221603394</t>
   </si>
   <si>
     <t xml:space="preserve">8.01864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079303741455</t>
+    <t xml:space="preserve">7.94079256057739</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112243652344</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07703304290771</t>
+    <t xml:space="preserve">8.0770320892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977890014648</t>
+    <t xml:space="preserve">8.33977794647217</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74849605560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67064380645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68037605285645</t>
+    <t xml:space="preserve">8.74849510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68037700653076</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">9.04043674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75822830200195</t>
+    <t xml:space="preserve">8.75822734832764</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789794921875</t>
+    <t xml:space="preserve">8.40789890289307</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46628665924072</t>
+    <t xml:space="preserve">8.46628570556641</t>
   </si>
   <si>
     <t xml:space="preserve">8.4565544128418</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23273372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17434597015381</t>
+    <t xml:space="preserve">8.15488243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23273468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17434501647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.14515113830566</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22300148010254</t>
+    <t xml:space="preserve">8.22300243377686</t>
   </si>
   <si>
     <t xml:space="preserve">8.33004760742188</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58306121826172</t>
+    <t xml:space="preserve">8.58306217193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2678,37 +2678,37 @@
     <t xml:space="preserve">8.60252571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83607864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70957088470459</t>
+    <t xml:space="preserve">8.83607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">8.84581089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01124286651611</t>
+    <t xml:space="preserve">9.0112419128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75082588195801</t>
+    <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3541707992554</t>
+    <t xml:space="preserve">10.3152446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3541717529297</t>
   </si>
   <si>
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028846740723</t>
+    <t xml:space="preserve">9.77028942108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14748191833496</t>
+    <t xml:space="preserve">8.90419769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14748096466064</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05989933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08909320831299</t>
+    <t xml:space="preserve">9.05990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909511566162</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2753,43 +2753,43 @@
     <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93339252471924</t>
+    <t xml:space="preserve">8.93339157104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613838195801</t>
+    <t xml:space="preserve">9.19613742828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62431907653809</t>
+    <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
     <t xml:space="preserve">9.57566165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53673648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82867813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86760330200195</t>
+    <t xml:space="preserve">9.5367374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8286771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86760234832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61458683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59512424468994</t>
+    <t xml:space="preserve">9.67297554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61458778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">9.45888519287109</t>
@@ -2804,31 +2804,31 @@
     <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21560096740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20587062835693</t>
+    <t xml:space="preserve">9.21560192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20586967468262</t>
   </si>
   <si>
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49547958374023</t>
+    <t xml:space="preserve">8.98204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56359958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49548053741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795768737793</t>
+    <t xml:space="preserve">8.76795864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41762924194336</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">8.37870311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71930122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601795196533</t>
+    <t xml:space="preserve">8.7193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39816570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601890563965</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04783821105957</t>
+    <t xml:space="preserve">8.04783916473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500286102295</t>
+    <t xml:space="preserve">8.87500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921459197998</t>
+    <t xml:space="preserve">9.80921363830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51727390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47834777832031</t>
+    <t xml:space="preserve">9.98437976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51727294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47834873199463</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4491548538208</t>
+    <t xml:space="preserve">9.44915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136425018311</t>
+    <t xml:space="preserve">9.73136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038423538208</t>
+    <t xml:space="preserve">10.0038414001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595430374146</t>
@@ -2927,40 +2927,40 @@
     <t xml:space="preserve">10.02330493927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622291564941</t>
+    <t xml:space="preserve">10.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622301101685</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652847290039</t>
+    <t xml:space="preserve">9.90652942657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33237838745117</t>
+    <t xml:space="preserve">9.33237743377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.25452613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40049648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48807907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6340503692627</t>
+    <t xml:space="preserve">9.40049743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48808002471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63404941558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347072601318</t>
+    <t xml:space="preserve">10.3347091674805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440841674805</t>
+    <t xml:space="preserve">11.4440832138062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.13267993927</t>
+    <t xml:space="preserve">11.1326789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -3008,37 +3008,37 @@
     <t xml:space="preserve">11.3662328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.638710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668907165527</t>
+    <t xml:space="preserve">11.6387119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668916702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5729217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4756088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1836681365967</t>
+    <t xml:space="preserve">12.572922706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4756078720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1836671829224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970996856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299928665161</t>
+    <t xml:space="preserve">11.6971006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299938201904</t>
   </si>
   <si>
     <t xml:space="preserve">10.8991279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8407392501831</t>
+    <t xml:space="preserve">10.8407402038574</t>
   </si>
   <si>
     <t xml:space="preserve">10.976978302002</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9575147628784</t>
+    <t xml:space="preserve">10.9575157165527</t>
   </si>
   <si>
     <t xml:space="preserve">10.198468208313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132183074951</t>
+    <t xml:space="preserve">10.6071853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4709482192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132164001465</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.91858959198</t>
+    <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">11.2105321884155</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9306526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8528003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8917274475098</t>
+    <t xml:space="preserve">11.9695768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9306516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.852801322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8917264938354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1252784729004</t>
@@ -3116,31 +3116,31 @@
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923833847046</t>
+    <t xml:space="preserve">12.8259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843259811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923843383789</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5145330429077</t>
+    <t xml:space="preserve">12.514533996582</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977565765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4366817474365</t>
+    <t xml:space="preserve">12.4366827011108</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447410583496</t>
+    <t xml:space="preserve">12.1447420120239</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950704574585</t>
+    <t xml:space="preserve">12.3393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">12.7870121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225923538208</t>
+    <t xml:space="preserve">12.2225933074951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762657165527</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9427137374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1373414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0789518356323</t>
+    <t xml:space="preserve">13.0594902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9427146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1373405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0789527893066</t>
   </si>
   <si>
     <t xml:space="preserve">13.4487447738647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4682064056396</t>
+    <t xml:space="preserve">13.468207359314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3215,22 +3215,22 @@
     <t xml:space="preserve">13.9742374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051042556763</t>
+    <t xml:space="preserve">14.3051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">14.616509437561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7527465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279127120972</t>
+    <t xml:space="preserve">14.7527475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279117584229</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909591674805</t>
+    <t xml:space="preserve">16.9909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4191417694092</t>
+    <t xml:space="preserve">17.5359172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4191398620605</t>
   </si>
   <si>
     <t xml:space="preserve">17.788932800293</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2949638366699</t>
+    <t xml:space="preserve">17.7500076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419502258301</t>
+    <t xml:space="preserve">19.0345458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419483184814</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.547981262207</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060108184814</t>
+    <t xml:space="preserve">19.7060127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8519821166992</t>
@@ -3314,37 +3314,37 @@
     <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113830566406</t>
+    <t xml:space="preserve">19.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009929656982</t>
+    <t xml:space="preserve">19.0734748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.898307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009948730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.5090522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8788452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9761581420898</t>
+    <t xml:space="preserve">18.8788433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9761600494385</t>
   </si>
   <si>
     <t xml:space="preserve">18.8593826293945</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4701290130615</t>
+    <t xml:space="preserve">18.4701271057129</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486381530762</t>
+    <t xml:space="preserve">19.2486362457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.84299659729</t>
+    <t xml:space="preserve">19.8429946899414</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567638397217</t>
+    <t xml:space="preserve">22.004114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988109588623</t>
+    <t xml:space="preserve">22.3479270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988128662109</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832740783691</t>
+    <t xml:space="preserve">21.3656024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832759857178</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306224822998</t>
+    <t xml:space="preserve">20.5306243896484</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748081207275</t>
+    <t xml:space="preserve">18.0748062133789</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463218688965</t>
+    <t xml:space="preserve">18.5463237762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569301605225</t>
+    <t xml:space="preserve">17.9569282531738</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836448669434</t>
+    <t xml:space="preserve">17.4854125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836429595947</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6032905578613</t>
+    <t xml:space="preserve">17.60329246521</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388439178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.033540725708</t>
+    <t xml:space="preserve">16.7388458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0335426330566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3581,34 +3581,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673282623291</t>
+    <t xml:space="preserve">16.2673263549805</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547487258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.345911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869720458984</t>
+    <t xml:space="preserve">15.8547496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905055999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3459129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869739532471</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154563903809</t>
+    <t xml:space="preserve">15.6189908981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154573440552</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794931411743</t>
+    <t xml:space="preserve">14.4794921875</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3629,37 +3629,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563119888306</t>
+    <t xml:space="preserve">14.9903020858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563110351562</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580787658691</t>
+    <t xml:space="preserve">14.5580778121948</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956043243408</t>
+    <t xml:space="preserve">14.4991397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956052780151</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527774810791</t>
+    <t xml:space="preserve">14.8527765274048</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958106994629</t>
+    <t xml:space="preserve">15.7958097457886</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653532028198</t>
+    <t xml:space="preserve">15.2653541564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567218780518</t>
+    <t xml:space="preserve">16.8567237854004</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370761871338</t>
+    <t xml:space="preserve">16.8370742797852</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549560546875</t>
+    <t xml:space="preserve">16.9549541473389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514186859131</t>
+    <t xml:space="preserve">17.1514205932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247039794922</t>
+    <t xml:space="preserve">17.5247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465282440186</t>
+    <t xml:space="preserve">19.6465301513672</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697113037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838512420654</t>
+    <t xml:space="preserve">19.4697093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838493347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359256744385</t>
+    <t xml:space="preserve">20.0394611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359275817871</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779708862305</t>
+    <t xml:space="preserve">20.6779727935791</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005805969238</t>
+    <t xml:space="preserve">22.2005786895752</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532321929932</t>
+    <t xml:space="preserve">22.0532302856445</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -8032,7 +8032,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8084,7 +8084,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9436,7 +9436,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9774,7 +9774,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9982,7 +9982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10008,7 +10008,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10320,7 +10320,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10502,7 +10502,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10528,7 +10528,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10554,7 +10554,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10580,7 +10580,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13102,7 +13102,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13700,7 +13700,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13726,7 +13726,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13752,7 +13752,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13778,7 +13778,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13804,7 +13804,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13830,7 +13830,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13856,7 +13856,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13882,7 +13882,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13908,7 +13908,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13934,7 +13934,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13960,7 +13960,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13986,7 +13986,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14012,7 +14012,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14038,7 +14038,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14064,7 +14064,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14090,7 +14090,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14116,7 +14116,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14142,7 +14142,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14168,7 +14168,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14194,7 +14194,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14220,7 +14220,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14246,7 +14246,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14272,7 +14272,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14298,7 +14298,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14324,7 +14324,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14350,7 +14350,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14376,7 +14376,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14402,7 +14402,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14428,7 +14428,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14454,7 +14454,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14636,7 +14636,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14714,7 +14714,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15390,7 +15390,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15546,7 +15546,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15572,7 +15572,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15806,7 +15806,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16612,7 +16612,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -70856,7 +70856,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6912268518</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>11584</v>
@@ -70877,6 +70877,32 @@
         <v>1491</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6911805556</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>10906</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>30.4500007629395</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>29.8999996185303</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009330749512</t>
+    <t xml:space="preserve">6.41009378433228</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">6.22992277145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26996088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379291534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578634262085</t>
+    <t xml:space="preserve">6.26996040344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0937933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578538894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.92563343048096</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">5.85356521606445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76548099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94565296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946594238281</t>
+    <t xml:space="preserve">5.76548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9456524848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946641921997</t>
   </si>
   <si>
     <t xml:space="preserve">5.72143936157227</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">5.99770164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88559532165527</t>
+    <t xml:space="preserve">5.88559484481812</t>
   </si>
   <si>
     <t xml:space="preserve">5.91762542724609</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">5.94164896011353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00571060180664</t>
+    <t xml:space="preserve">6.00570917129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.84956121444702</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">5.77749252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17386960983276</t>
+    <t xml:space="preserve">6.17387008666992</t>
   </si>
   <si>
     <t xml:space="preserve">6.14984655380249</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">6.20589971542358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2939829826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191476821899</t>
+    <t xml:space="preserve">6.29398393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191524505615</t>
   </si>
   <si>
     <t xml:space="preserve">6.19789218902588</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">6.40609073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813894271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48616743087769</t>
+    <t xml:space="preserve">6.45813989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48616647720337</t>
   </si>
   <si>
     <t xml:space="preserve">6.50218200683594</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">6.14183902740479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15385055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980892181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11381244659424</t>
+    <t xml:space="preserve">6.15385007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980844497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1138129234314</t>
   </si>
   <si>
     <t xml:space="preserve">5.9896936416626</t>
@@ -179,28 +179,28 @@
     <t xml:space="preserve">6.0177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94965600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375480651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785455703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09779691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18187761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390771865845</t>
+    <t xml:space="preserve">5.94965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375576019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09779739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18187713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390819549561</t>
   </si>
   <si>
     <t xml:space="preserve">6.03373575210571</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">6.10180139541626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01371765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764448165894</t>
+    <t xml:space="preserve">6.01371717453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764495849609</t>
   </si>
   <si>
     <t xml:space="preserve">6.11781597137451</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">6.07377481460571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06977033615112</t>
+    <t xml:space="preserve">6.06977081298828</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342517852783</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">6.2265453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07336616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030550003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998620986938</t>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998525619507</t>
   </si>
   <si>
     <t xml:space="preserve">6.09406566619873</t>
@@ -263,40 +263,37 @@
     <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12718534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13960552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062574386597</t>
+    <t xml:space="preserve">6.1271858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13960599899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062526702881</t>
   </si>
   <si>
     <t xml:space="preserve">6.04438638687134</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89534568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90776634216309</t>
+    <t xml:space="preserve">5.89534521102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90776586532593</t>
   </si>
   <si>
     <t xml:space="preserve">5.81254625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99470520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
+    <t xml:space="preserve">5.99470615386963</t>
   </si>
   <si>
     <t xml:space="preserve">6.04024600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94502592086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96158504486084</t>
+    <t xml:space="preserve">5.94502639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.961585521698</t>
   </si>
   <si>
     <t xml:space="preserve">5.85394668579102</t>
@@ -311,31 +308,31 @@
     <t xml:space="preserve">5.91190624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304639816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10234594345093</t>
+    <t xml:space="preserve">5.86636686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10234546661377</t>
   </si>
   <si>
     <t xml:space="preserve">6.26794576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.156165599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03196573257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1768651008606</t>
+    <t xml:space="preserve">6.15616512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0319652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17686557769775</t>
   </si>
   <si>
     <t xml:space="preserve">6.25138568878174</t>
@@ -350,91 +347,91 @@
     <t xml:space="preserve">6.14374589920044</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07750606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14788627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05266571044922</t>
+    <t xml:space="preserve">6.07750558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1478853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06922578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">5.96986627578735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10648536682129</t>
+    <t xml:space="preserve">6.10648488998413</t>
   </si>
   <si>
     <t xml:space="preserve">5.98642587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92432594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95330619812012</t>
+    <t xml:space="preserve">5.92432689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95330572128296</t>
   </si>
   <si>
     <t xml:space="preserve">6.03610610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95744657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298547744751</t>
+    <t xml:space="preserve">5.95744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298595428467</t>
   </si>
   <si>
     <t xml:space="preserve">5.88706636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9326057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8249659538269</t>
+    <t xml:space="preserve">5.93260669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496643066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.81668615341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84980630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808658599854</t>
+    <t xml:space="preserve">5.8498067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808610916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.75872611999512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90362691879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93674659729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87878608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9201865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06094551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42526578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45010471343994</t>
+    <t xml:space="preserve">5.90362644195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93674612045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87878656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92018604278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06094646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42526531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4501051902771</t>
   </si>
   <si>
     <t xml:space="preserve">6.53290414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5494647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45424509048462</t>
+    <t xml:space="preserve">6.54946422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45424461364746</t>
   </si>
   <si>
     <t xml:space="preserve">6.29278564453125</t>
@@ -443,79 +440,79 @@
     <t xml:space="preserve">6.45838499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38386487960815</t>
+    <t xml:space="preserve">6.38386535644531</t>
   </si>
   <si>
     <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2348256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33832502365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40870475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37558507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34246444702148</t>
+    <t xml:space="preserve">6.23482513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37558460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806474685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3424654006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.49150466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33418464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30520486831665</t>
+    <t xml:space="preserve">6.33418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3714451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30520534515381</t>
   </si>
   <si>
     <t xml:space="preserve">6.39214515686035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18514490127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97400569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01954555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0278263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32590484619141</t>
+    <t xml:space="preserve">6.18514537811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97400617599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01126623153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0195460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32590532302856</t>
   </si>
   <si>
     <t xml:space="preserve">6.36730527877808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28450536727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41284513473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2431058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272567749023</t>
+    <t xml:space="preserve">6.28450489044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24310493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272520065308</t>
   </si>
   <si>
     <t xml:space="preserve">6.69850444793701</t>
@@ -524,91 +521,91 @@
     <t xml:space="preserve">6.68194389343262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72334384918213</t>
+    <t xml:space="preserve">6.6488242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72334432601929</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20358228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874240875244</t>
+    <t xml:space="preserve">7.03798389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20358371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
   </si>
   <si>
     <t xml:space="preserve">7.03384351730347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01314401626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0793833732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02142286300659</t>
+    <t xml:space="preserve">7.01314306259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07938289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02142333984375</t>
   </si>
   <si>
     <t xml:space="preserve">7.05454349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98830318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772361755371</t>
+    <t xml:space="preserve">6.98830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772266387939</t>
   </si>
   <si>
     <t xml:space="preserve">7.60102272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08766412734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370269775391</t>
+    <t xml:space="preserve">7.63414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0876636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370222091675</t>
   </si>
   <si>
     <t xml:space="preserve">7.47682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4892430305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542194366455</t>
+    <t xml:space="preserve">7.48924207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542242050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.27810335159302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17046308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422277450562</t>
+    <t xml:space="preserve">7.1704626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422325134277</t>
   </si>
   <si>
     <t xml:space="preserve">6.94276428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212379455566</t>
+    <t xml:space="preserve">7.0711030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212331771851</t>
   </si>
   <si>
     <t xml:space="preserve">7.00486373901367</t>
@@ -617,70 +614,70 @@
     <t xml:space="preserve">6.83512401580811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">6.88894319534302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91378355026245</t>
+    <t xml:space="preserve">6.91378402709961</t>
   </si>
   <si>
     <t xml:space="preserve">6.95932292938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26982259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50994157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64242124557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0729808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.193039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48698043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49526023864746</t>
+    <t xml:space="preserve">7.22842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26982355117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50994205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64242076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210290908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65898132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9032416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03158187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07297992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19304180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25514125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48697948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49525928497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.3627815246582</t>
@@ -689,22 +686,22 @@
     <t xml:space="preserve">8.39590072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43729877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62773990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63602066040039</t>
+    <t xml:space="preserve">8.43729972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63601875305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52837944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32966136932373</t>
+    <t xml:space="preserve">8.52838134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32966041564941</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986167907715</t>
@@ -713,13 +710,13 @@
     <t xml:space="preserve">7.7666220664978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96120166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51181888580322</t>
+    <t xml:space="preserve">7.96120119094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51181983947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.6028995513916</t>
@@ -731,7 +728,7 @@
     <t xml:space="preserve">8.85957908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37293815612793</t>
+    <t xml:space="preserve">9.37293720245361</t>
   </si>
   <si>
     <t xml:space="preserve">9.4474573135376</t>
@@ -740,19 +737,19 @@
     <t xml:space="preserve">10.0850162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.15953540802</t>
+    <t xml:space="preserve">10.1595373153687</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907350540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6894540786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2920160293579</t>
+    <t xml:space="preserve">10.6894559860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920150756836</t>
   </si>
   <si>
     <t xml:space="preserve">10.3499765396118</t>
@@ -761,13 +758,13 @@
     <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4602603912354</t>
+    <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
     <t xml:space="preserve">9.87489414215088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0615329742432</t>
+    <t xml:space="preserve">10.0615339279175</t>
   </si>
   <si>
     <t xml:space="preserve">10.1209192276001</t>
@@ -776,43 +773,46 @@
     <t xml:space="preserve">10.0530500411987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1718196868896</t>
+    <t xml:space="preserve">10.171820640564</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803045272827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0784997940063</t>
+    <t xml:space="preserve">10.0785007476807</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7062873840332</t>
+    <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638669967651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6129665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7232542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.646900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6299343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4178438186646</t>
+    <t xml:space="preserve">10.6129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3499755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7232522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6469011306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6299333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384172439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4178447723389</t>
   </si>
   <si>
     <t xml:space="preserve">10.3584594726562</t>
@@ -830,25 +830,25 @@
     <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78157520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61190319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43374729156494</t>
+    <t xml:space="preserve">9.83247661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78157424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61190414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43374919891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.1028881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17924022674561</t>
+    <t xml:space="preserve">9.16227531433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17923927307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">9.23862648010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23014163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33194446563721</t>
+    <t xml:space="preserve">9.23014259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.21317481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37436294555664</t>
+    <t xml:space="preserve">9.37436389923096</t>
   </si>
   <si>
     <t xml:space="preserve">9.68825626373291</t>
@@ -875,49 +875,49 @@
     <t xml:space="preserve">10.0954685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90034580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84944438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2227210998535</t>
+    <t xml:space="preserve">10.0360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90034484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2227220535278</t>
   </si>
   <si>
     <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2821083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566556930542</t>
+    <t xml:space="preserve">10.2821073532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566566467285</t>
   </si>
   <si>
     <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3669424057007</t>
+    <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0191164016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9682149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89186191558838</t>
+    <t xml:space="preserve">10.0191173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89186096191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.85792827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764156341553</t>
+    <t xml:space="preserve">9.74764060974121</t>
   </si>
   <si>
     <t xml:space="preserve">9.51010131835938</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">9.35739517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948566436768</t>
+    <t xml:space="preserve">9.56948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39133071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104209899902</t>
+    <t xml:space="preserve">9.50161647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39132976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.38284683227539</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">9.45071506500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51858329772949</t>
+    <t xml:space="preserve">9.51858425140381</t>
   </si>
   <si>
     <t xml:space="preserve">9.27256011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20469188690186</t>
+    <t xml:space="preserve">9.20469093322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.58645439147949</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">9.67977142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583778381348</t>
+    <t xml:space="preserve">9.64583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309322357178</t>
+    <t xml:space="preserve">9.75612354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399368286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309226989746</t>
   </si>
   <si>
     <t xml:space="preserve">9.79854202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69674015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67128849029541</t>
+    <t xml:space="preserve">9.69673919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67128944396973</t>
   </si>
   <si>
     <t xml:space="preserve">9.62887001037598</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">9.47616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13682270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7211275100708</t>
+    <t xml:space="preserve">9.13682460784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72112655639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07637405395508</t>
+    <t xml:space="preserve">8.07637500762939</t>
   </si>
   <si>
     <t xml:space="preserve">8.32663917541504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1230354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6278076171875</t>
+    <t xml:space="preserve">8.10182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62780857086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.33088207244873</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">8.34360694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.195143699646</t>
+    <t xml:space="preserve">8.19514465332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
@@ -1052,43 +1052,43 @@
     <t xml:space="preserve">8.37329959869385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31391429901123</t>
+    <t xml:space="preserve">8.31391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334087371826</t>
+    <t xml:space="preserve">8.09334182739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.03819942474365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85155963897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82610893249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094398498535</t>
+    <t xml:space="preserve">7.85156011581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82610940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094446182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.85580205917358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760536193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02122974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01274681091309</t>
+    <t xml:space="preserve">7.95760440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881269454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0127477645874</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452995300293</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">8.14848518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05092430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061599731445</t>
+    <t xml:space="preserve">8.05092334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">8.17393589019775</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">8.22483730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2884635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42420101165771</t>
+    <t xml:space="preserve">8.28846454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4242000579834</t>
   </si>
   <si>
     <t xml:space="preserve">8.5684232711792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51752185821533</t>
+    <t xml:space="preserve">8.5175199508667</t>
   </si>
   <si>
     <t xml:space="preserve">8.7380952835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55145645141602</t>
+    <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.48358631134033</t>
@@ -1136,34 +1136,34 @@
     <t xml:space="preserve">8.50055313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58538818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45813655853271</t>
+    <t xml:space="preserve">8.65325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4581356048584</t>
   </si>
   <si>
     <t xml:space="preserve">8.40723514556885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3817834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01698970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99153852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518592834473</t>
+    <t xml:space="preserve">8.38178443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20362949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01698875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518545150757</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727642059326</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90776634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75506114959717</t>
+    <t xml:space="preserve">8.90776538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75506019592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.82292938232422</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">8.60235786437988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8398962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94169998168945</t>
+    <t xml:space="preserve">8.83989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94169902801514</t>
   </si>
   <si>
     <t xml:space="preserve">9.36587905883789</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">9.24710941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12833881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11137294769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04350280761719</t>
+    <t xml:space="preserve">9.12833976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11137199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0435037612915</t>
   </si>
   <si>
     <t xml:space="preserve">9.09440422058105</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">10.2142372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5705480575562</t>
+    <t xml:space="preserve">10.5705490112305</t>
   </si>
   <si>
     <t xml:space="preserve">10.6723518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6214504241943</t>
+    <t xml:space="preserve">10.6214513778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.9607934951782</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">11.3680067062378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4698104858398</t>
+    <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.543098449707</t>
@@ -1253,34 +1253,34 @@
     <t xml:space="preserve">11.8729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8362579345703</t>
+    <t xml:space="preserve">11.8362560272217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9567823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4987230300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.700267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6086568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.645302772522</t>
+    <t xml:space="preserve">11.3049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9567813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.498722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6086578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6453018188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.4804000854492</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0040187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">10.004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589866638184</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788534164429</t>
@@ -1304,19 +1304,19 @@
     <t xml:space="preserve">10.0773086547852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2238864898682</t>
+    <t xml:space="preserve">10.2238874435425</t>
   </si>
   <si>
     <t xml:space="preserve">10.2605323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1322746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3154993057251</t>
+    <t xml:space="preserve">10.1322755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3154983520508</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437551498413</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2055635452271</t>
+    <t xml:space="preserve">10.2055644989014</t>
   </si>
   <si>
     <t xml:space="preserve">10.095630645752</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71086025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266864776611</t>
+    <t xml:space="preserve">9.71086120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.67421627044678</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">9.65589332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61924934387207</t>
+    <t xml:space="preserve">9.61924839019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56427955627441</t>
+    <t xml:space="preserve">9.69253826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428050994873</t>
   </si>
   <si>
     <t xml:space="preserve">9.30776786804199</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">9.2528018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3627347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08789920806885</t>
+    <t xml:space="preserve">9.36273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27112293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08790016174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.93215942382812</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293228149414</t>
+    <t xml:space="preserve">9.03293132781982</t>
   </si>
   <si>
     <t xml:space="preserve">8.95964336395264</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">8.63900089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65732288360596</t>
+    <t xml:space="preserve">8.65732383728027</t>
   </si>
   <si>
     <t xml:space="preserve">8.62983989715576</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">9.39937973022461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3810567855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19783401489258</t>
+    <t xml:space="preserve">9.38105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19783306121826</t>
   </si>
   <si>
     <t xml:space="preserve">9.00544834136963</t>
@@ -1445,34 +1445,34 @@
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454509735107</t>
+    <t xml:space="preserve">9.12454414367676</t>
   </si>
   <si>
     <t xml:space="preserve">9.04209327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96880435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628639221191</t>
+    <t xml:space="preserve">8.96880340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628734588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86803150177002</t>
+    <t xml:space="preserve">8.86803245544434</t>
   </si>
   <si>
     <t xml:space="preserve">8.7855806350708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83138561248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84054756164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77642059326172</t>
+    <t xml:space="preserve">8.83138656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84054660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7764196395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.71229076385498</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">8.40997219085693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30919742584229</t>
+    <t xml:space="preserve">8.3091983795166</t>
   </si>
   <si>
     <t xml:space="preserve">8.2450704574585</t>
@@ -1493,31 +1493,31 @@
     <t xml:space="preserve">7.74120426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70455932617188</t>
+    <t xml:space="preserve">7.70455884933472</t>
   </si>
   <si>
     <t xml:space="preserve">7.68623876571655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55798101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59462547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49385261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224075317383</t>
+    <t xml:space="preserve">7.55798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462642669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938530921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224123001099</t>
   </si>
   <si>
     <t xml:space="preserve">7.08159923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10908269882202</t>
+    <t xml:space="preserve">7.10908317565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.38391876220703</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30146789550781</t>
+    <t xml:space="preserve">7.30146741867065</t>
   </si>
   <si>
     <t xml:space="preserve">7.31978940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48469161987305</t>
+    <t xml:space="preserve">7.48469209671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.4205641746521</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">7.80533313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69539976119995</t>
+    <t xml:space="preserve">7.69539880752563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45720815658569</t>
@@ -1553,79 +1553,79 @@
     <t xml:space="preserve">7.58546447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56714200973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817802429199</t>
+    <t xml:space="preserve">7.56714248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817754745483</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327676773071</t>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327724456787</t>
   </si>
   <si>
     <t xml:space="preserve">7.05411577224731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43888568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5396580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53049755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553014755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811283111572</t>
+    <t xml:space="preserve">7.43888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53965759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5304970741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553062438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811235427856</t>
   </si>
   <si>
     <t xml:space="preserve">7.29230642318726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2831449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31062889099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24650001525879</t>
+    <t xml:space="preserve">7.28314542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31062841415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
     <t xml:space="preserve">7.2739839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72288227081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946249008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04352474212646</t>
+    <t xml:space="preserve">7.35643434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72288179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946153640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
     <t xml:space="preserve">8.37332630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39164924621582</t>
+    <t xml:space="preserve">8.3916482925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.49242305755615</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34584331512451</t>
+    <t xml:space="preserve">8.3458423614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13370609283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73977375030518</t>
+    <t xml:space="preserve">9.02377128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.10622119903564</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8588695526123</t>
+    <t xml:space="preserve">8.66648578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85887050628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.01460933685303</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90467548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84970951080322</t>
+    <t xml:space="preserve">8.90467643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84970855712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.8039026260376</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25423145294189</t>
+    <t xml:space="preserve">8.25423049926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.38248729705811</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26339340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23590850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43745517730713</t>
+    <t xml:space="preserve">8.26339244842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2359094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43745422363281</t>
   </si>
   <si>
     <t xml:space="preserve">8.45577716827393</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">8.50158309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42829418182373</t>
+    <t xml:space="preserve">8.42829322814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.46493816375732</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738903045654</t>
+    <t xml:space="preserve">8.54738807678223</t>
   </si>
   <si>
     <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70226860046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40219211578369</t>
+    <t xml:space="preserve">8.70226955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40219116210938</t>
   </si>
   <si>
     <t xml:space="preserve">8.18923091888428</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06339263916016</t>
+    <t xml:space="preserve">8.06339168548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.98595333099365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29571151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
+    <t xml:space="preserve">8.29571056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
   </si>
   <si>
     <t xml:space="preserve">8.03435325622559</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">8.05371189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02467250823975</t>
+    <t xml:space="preserve">8.02467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">7.97627258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96659278869629</t>
+    <t xml:space="preserve">7.96659183502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.16987133026123</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">8.25699043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14083194732666</t>
+    <t xml:space="preserve">8.14083099365234</t>
   </si>
   <si>
     <t xml:space="preserve">7.92787313461304</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">8.07307243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0827522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755340576172</t>
+    <t xml:space="preserve">8.08275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90851402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755388259888</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
+    <t xml:space="preserve">8.11179256439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.13115215301514</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">7.86979389190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87947416305542</t>
+    <t xml:space="preserve">7.87947368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.91819381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44091033935547</t>
+    <t xml:space="preserve">7.95691299438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44091129302979</t>
   </si>
   <si>
     <t xml:space="preserve">8.33442974090576</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">8.28603076934814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.227952003479</t>
+    <t xml:space="preserve">8.22795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5280294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78938770294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14754581451416</t>
+    <t xml:space="preserve">8.52803039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78938865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14754676818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">9.45730495452881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44762516021729</t>
+    <t xml:space="preserve">9.44762420654297</t>
   </si>
   <si>
     <t xml:space="preserve">9.55410385131836</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52506446838379</t>
+    <t xml:space="preserve">9.52506351470947</t>
   </si>
   <si>
     <t xml:space="preserve">10.0284204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3188190460205</t>
+    <t xml:space="preserve">10.3188180923462</t>
   </si>
   <si>
     <t xml:space="preserve">10.0477819442749</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">10.0671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98970031738281</t>
+    <t xml:space="preserve">9.98970127105713</t>
   </si>
   <si>
     <t xml:space="preserve">9.95098209381104</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">9.60250377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61218357086182</t>
+    <t xml:space="preserve">9.6799430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6121826171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.69930267333984</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">9.71866226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50570297241211</t>
+    <t xml:space="preserve">9.50570392608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.58314323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46698379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87354278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40890407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35082530975342</t>
+    <t xml:space="preserve">9.46698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40890502929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3508243560791</t>
   </si>
   <si>
     <t xml:space="preserve">9.43794441223145</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146476745605</t>
+    <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.77674293518066</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">9.19594669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16690731048584</t>
+    <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.0797872543335</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">8.72162818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77002906799316</t>
+    <t xml:space="preserve">8.77002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">8.93458652496338</t>
@@ -2027,31 +2027,31 @@
     <t xml:space="preserve">8.96362686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15722560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05074596405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97330665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32475185394287</t>
+    <t xml:space="preserve">9.1572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05074691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97330760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475090026855</t>
   </si>
   <si>
     <t xml:space="preserve">7.84075498580933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60843515396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53099536895752</t>
+    <t xml:space="preserve">7.79235410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60843563079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
     <t xml:space="preserve">7.61811494827271</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">6.58236169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14004898071289</t>
+    <t xml:space="preserve">6.44684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14004945755005</t>
   </si>
   <si>
     <t xml:space="preserve">5.47884750366211</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">4.53989362716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64637327194214</t>
+    <t xml:space="preserve">4.64637279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.48181343078613</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">4.52053308486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83997106552124</t>
+    <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
     <t xml:space="preserve">5.13037014007568</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">5.51756715774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04028415679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00156450271606</t>
+    <t xml:space="preserve">6.04028463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00156497955322</t>
   </si>
   <si>
     <t xml:space="preserve">5.98220443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88540554046631</t>
+    <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
     <t xml:space="preserve">5.79828596115112</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">6.43716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22420263290405</t>
+    <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">6.5339617729187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54364204406738</t>
+    <t xml:space="preserve">6.54364156723022</t>
   </si>
   <si>
     <t xml:space="preserve">7.28899717330933</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491479873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63747501373291</t>
+    <t xml:space="preserve">7.58907508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71491432189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63747453689575</t>
   </si>
   <si>
     <t xml:space="preserve">7.3954758644104</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">7.43419551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19219779968262</t>
+    <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.40515661239624</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">7.44387626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49227619171143</t>
+    <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555425643921</t>
+    <t xml:space="preserve">7.69555473327637</t>
   </si>
   <si>
     <t xml:space="preserve">7.85043334960938</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">7.31803703308105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30835676193237</t>
+    <t xml:space="preserve">7.30835723876953</t>
   </si>
   <si>
     <t xml:space="preserve">7.23091793060303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52131605148315</t>
+    <t xml:space="preserve">7.521315574646</t>
   </si>
   <si>
     <t xml:space="preserve">7.5406756401062</t>
@@ -2222,28 +2222,28 @@
     <t xml:space="preserve">7.51163625717163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38579607009888</t>
+    <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
     <t xml:space="preserve">7.3373966217041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35675621032715</t>
+    <t xml:space="preserve">7.35675668716431</t>
   </si>
   <si>
     <t xml:space="preserve">7.45355653762817</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
+    <t xml:space="preserve">7.41483592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867649078369</t>
   </si>
   <si>
     <t xml:space="preserve">7.2599573135376</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">7.88915348052979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83107423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74395418167114</t>
+    <t xml:space="preserve">7.83107471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7439546585083</t>
   </si>
   <si>
     <t xml:space="preserve">7.73427391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36643695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26963710784912</t>
+    <t xml:space="preserve">7.36643648147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26963758468628</t>
   </si>
   <si>
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315793991089</t>
+    <t xml:space="preserve">7.16315841674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.12443828582764</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">7.48259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6665153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42451620101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14379835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04699802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
+    <t xml:space="preserve">7.66651487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42451667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04699850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.11475849151611</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">7.20187759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18251800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13411808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15347814559937</t>
+    <t xml:space="preserve">7.18251848220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13411855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15347766876221</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">7.02763891220093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96955919265747</t>
+    <t xml:space="preserve">6.96955871582031</t>
   </si>
   <si>
     <t xml:space="preserve">6.89211940765381</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">7.06635856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0566782951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8727593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94051885604858</t>
+    <t xml:space="preserve">7.05667781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87275981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
     <t xml:space="preserve">6.90179920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82435989379883</t>
+    <t xml:space="preserve">6.82436037063599</t>
   </si>
   <si>
     <t xml:space="preserve">6.80500030517578</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">6.77596044540405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76628017425537</t>
+    <t xml:space="preserve">6.76627969741821</t>
   </si>
   <si>
     <t xml:space="preserve">6.83403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8146800994873</t>
+    <t xml:space="preserve">6.78564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81467962265015</t>
   </si>
   <si>
     <t xml:space="preserve">6.7953200340271</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63076114654541</t>
+    <t xml:space="preserve">6.63076066970825</t>
   </si>
   <si>
     <t xml:space="preserve">6.67916059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93083953857422</t>
+    <t xml:space="preserve">6.93083906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -8035,7 +8035,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8061,7 +8061,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8087,7 +8087,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8113,7 +8113,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8165,7 +8165,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8191,7 +8191,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8217,7 +8217,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8243,7 +8243,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8269,7 +8269,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8295,7 +8295,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8399,7 +8399,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8425,7 +8425,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8477,7 +8477,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8529,7 +8529,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8555,7 +8555,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8581,7 +8581,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8633,7 +8633,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8685,7 +8685,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8711,7 +8711,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8737,7 +8737,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8789,7 +8789,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8815,7 +8815,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8841,7 +8841,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8893,7 +8893,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8945,7 +8945,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9023,7 +9023,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9049,7 +9049,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9075,7 +9075,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9101,7 +9101,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9127,7 +9127,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9179,7 +9179,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9205,7 +9205,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9231,7 +9231,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9257,7 +9257,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9309,7 +9309,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9361,7 +9361,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9387,7 +9387,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9413,7 +9413,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9439,7 +9439,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9465,7 +9465,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9491,7 +9491,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9517,7 +9517,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9543,7 +9543,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9569,7 +9569,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9595,7 +9595,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9621,7 +9621,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9673,7 +9673,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9699,7 +9699,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9725,7 +9725,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9751,7 +9751,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9777,7 +9777,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9803,7 +9803,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9829,7 +9829,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9855,7 +9855,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9881,7 +9881,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9907,7 +9907,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9933,7 +9933,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9959,7 +9959,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9985,7 +9985,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10011,7 +10011,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10037,7 +10037,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10063,7 +10063,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10089,7 +10089,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10141,7 +10141,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10167,7 +10167,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10245,7 +10245,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10271,7 +10271,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10297,7 +10297,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10323,7 +10323,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10349,7 +10349,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10375,7 +10375,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10401,7 +10401,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10427,7 +10427,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10453,7 +10453,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10479,7 +10479,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10505,7 +10505,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10531,7 +10531,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10557,7 +10557,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10583,7 +10583,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10609,7 +10609,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10635,7 +10635,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10661,7 +10661,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10687,7 +10687,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10713,7 +10713,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10739,7 +10739,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10765,7 +10765,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10791,7 +10791,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10817,7 +10817,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10843,7 +10843,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10869,7 +10869,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10895,7 +10895,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10921,7 +10921,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10947,7 +10947,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10973,7 +10973,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10999,7 +10999,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11025,7 +11025,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11051,7 +11051,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11077,7 +11077,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11103,7 +11103,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11129,7 +11129,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11181,7 +11181,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11259,7 +11259,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11285,7 +11285,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11311,7 +11311,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11337,7 +11337,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11363,7 +11363,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11389,7 +11389,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11467,7 +11467,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11493,7 +11493,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11545,7 +11545,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11571,7 +11571,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11649,7 +11649,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11675,7 +11675,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11701,7 +11701,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11727,7 +11727,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11753,7 +11753,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11779,7 +11779,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11805,7 +11805,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11831,7 +11831,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11857,7 +11857,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11883,7 +11883,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11909,7 +11909,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11935,7 +11935,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11961,7 +11961,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11987,7 +11987,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G271" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12013,7 +12013,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12039,7 +12039,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12065,7 +12065,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12091,7 +12091,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12117,7 +12117,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12143,7 +12143,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12169,7 +12169,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12195,7 +12195,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12221,7 +12221,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12247,7 +12247,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12273,7 +12273,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12299,7 +12299,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12325,7 +12325,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12351,7 +12351,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12377,7 +12377,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12403,7 +12403,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12429,7 +12429,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12455,7 +12455,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12481,7 +12481,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12507,7 +12507,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12533,7 +12533,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G292" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12559,7 +12559,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12585,7 +12585,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12611,7 +12611,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12637,7 +12637,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12663,7 +12663,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12689,7 +12689,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12715,7 +12715,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12741,7 +12741,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12767,7 +12767,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12793,7 +12793,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12819,7 +12819,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12845,7 +12845,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12871,7 +12871,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12897,7 +12897,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12923,7 +12923,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12949,7 +12949,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12975,7 +12975,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13001,7 +13001,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13027,7 +13027,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13053,7 +13053,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13079,7 +13079,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13105,7 +13105,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13131,7 +13131,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13157,7 +13157,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13183,7 +13183,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13209,7 +13209,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13235,7 +13235,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13261,7 +13261,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13287,7 +13287,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13313,7 +13313,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13339,7 +13339,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13365,7 +13365,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13391,7 +13391,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13417,7 +13417,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13443,7 +13443,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13469,7 +13469,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13495,7 +13495,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13521,7 +13521,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13547,7 +13547,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13573,7 +13573,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13599,7 +13599,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13625,7 +13625,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13651,7 +13651,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13677,7 +13677,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13703,7 +13703,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13729,7 +13729,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13755,7 +13755,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13781,7 +13781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13807,7 +13807,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13833,7 +13833,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13859,7 +13859,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13885,7 +13885,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13911,7 +13911,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13937,7 +13937,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13963,7 +13963,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13989,7 +13989,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14015,7 +14015,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14041,7 +14041,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14067,7 +14067,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14093,7 +14093,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14119,7 +14119,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14145,7 +14145,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14171,7 +14171,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14197,7 +14197,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14223,7 +14223,7 @@
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14249,7 +14249,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14275,7 +14275,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14301,7 +14301,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14327,7 +14327,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14353,7 +14353,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14379,7 +14379,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14405,7 +14405,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14431,7 +14431,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14457,7 +14457,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14639,7 +14639,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14717,7 +14717,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15393,7 +15393,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15549,7 +15549,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15575,7 +15575,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15809,7 +15809,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16615,7 +16615,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -70963,7 +70963,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6911805556</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>20506</v>
@@ -70984,6 +70984,32 @@
         <v>1487</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6911921296</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>16842</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>30.6000003814697</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>29.9500007629395</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>30.3500003814697</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>30.4500007629395</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="1533">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,55 +44,55 @@
     <t xml:space="preserve">TXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39007520675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980827331543</t>
+    <t xml:space="preserve">6.39007472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39808225631714</t>
   </si>
   <si>
     <t xml:space="preserve">6.22992277145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26996088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379291534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92563390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76548147201538</t>
+    <t xml:space="preserve">6.2699613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09379386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582445144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563343048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356473922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76548099517822</t>
   </si>
   <si>
     <t xml:space="preserve">5.9456524848938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143983840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74145793914795</t>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74145841598511</t>
   </si>
   <si>
     <t xml:space="preserve">5.99770164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88559484481812</t>
+    <t xml:space="preserve">5.88559532165527</t>
   </si>
   <si>
     <t xml:space="preserve">5.91762542724609</t>
@@ -107,76 +107,76 @@
     <t xml:space="preserve">5.84956073760986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7774920463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386960983276</t>
+    <t xml:space="preserve">5.77749252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17387008666992</t>
   </si>
   <si>
     <t xml:space="preserve">6.14984655380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20589923858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29398345947266</t>
+    <t xml:space="preserve">6.20590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29398441314697</t>
   </si>
   <si>
     <t xml:space="preserve">6.22191476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19789171218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40609073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813989639282</t>
+    <t xml:space="preserve">6.19789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990419387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.406090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813941955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.41409778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50218200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49417400360107</t>
+    <t xml:space="preserve">6.48616647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50218105316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49417352676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.23793029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388818740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183950424194</t>
+    <t xml:space="preserve">6.07777786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183902740479</t>
   </si>
   <si>
     <t xml:space="preserve">6.15385055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10980892181396</t>
+    <t xml:space="preserve">6.10980844497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.1138129234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98969411849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01772117614746</t>
+    <t xml:space="preserve">5.98969459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0177206993103</t>
   </si>
   <si>
     <t xml:space="preserve">5.94965600967407</t>
@@ -185,73 +185,73 @@
     <t xml:space="preserve">6.13383102416992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785503387451</t>
+    <t xml:space="preserve">6.05375576019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15785360336304</t>
   </si>
   <si>
     <t xml:space="preserve">6.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12181949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1018009185791</t>
+    <t xml:space="preserve">6.18187665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373670578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10179996490479</t>
   </si>
   <si>
     <t xml:space="preserve">6.01371812820435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95766401290894</t>
+    <t xml:space="preserve">5.95766353607178</t>
   </si>
   <si>
     <t xml:space="preserve">5.93764495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11781549453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07377481460571</t>
+    <t xml:space="preserve">6.11781597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07377433776855</t>
   </si>
   <si>
     <t xml:space="preserve">6.06977033615112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19342517852783</t>
+    <t xml:space="preserve">6.19342565536499</t>
   </si>
   <si>
     <t xml:space="preserve">6.2265453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07336616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16030597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20998573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09406518936157</t>
+    <t xml:space="preserve">6.07336568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16030502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20998525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
     <t xml:space="preserve">6.16858530044556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18928527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20170497894287</t>
+    <t xml:space="preserve">6.18928575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20170545578003</t>
   </si>
   <si>
     <t xml:space="preserve">6.11890554428101</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">6.28864526748657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19756507873535</t>
+    <t xml:space="preserve">6.19756603240967</t>
   </si>
   <si>
     <t xml:space="preserve">6.12718534469604</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">6.13960552215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11062622070312</t>
+    <t xml:space="preserve">6.11062526702881</t>
   </si>
   <si>
     <t xml:space="preserve">6.04438591003418</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">5.90776634216309</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81254625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99470663070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04024600982666</t>
+    <t xml:space="preserve">5.8125467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99470615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0402455329895</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502592086792</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">5.96158599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85394620895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86222553253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01540565490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10234594345093</t>
+    <t xml:space="preserve">5.8539457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78770685195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01540517807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10234498977661</t>
   </si>
   <si>
     <t xml:space="preserve">6.26794576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15616512298584</t>
+    <t xml:space="preserve">6.156165599823</t>
   </si>
   <si>
     <t xml:space="preserve">6.03196573257446</t>
@@ -335,31 +335,31 @@
     <t xml:space="preserve">6.17686557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25138568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13132619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14374589920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07750511169434</t>
+    <t xml:space="preserve">6.25138521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13132572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202569961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14374542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07750606536865</t>
   </si>
   <si>
     <t xml:space="preserve">6.14788579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06922578811646</t>
+    <t xml:space="preserve">6.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">6.05266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96986532211304</t>
+    <t xml:space="preserve">5.96986627578735</t>
   </si>
   <si>
     <t xml:space="preserve">6.10648536682129</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">5.98642587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92432641983032</t>
+    <t xml:space="preserve">5.92432689666748</t>
   </si>
   <si>
     <t xml:space="preserve">5.95330619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03610610961914</t>
+    <t xml:space="preserve">6.03610515594482</t>
   </si>
   <si>
     <t xml:space="preserve">5.95744609832764</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">6.00298595428467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88706684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260622024536</t>
+    <t xml:space="preserve">5.88706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9326057434082</t>
   </si>
   <si>
     <t xml:space="preserve">5.8249659538269</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">5.84980630874634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85808610916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75872611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90362644195557</t>
+    <t xml:space="preserve">5.85808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75872659683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90362596511841</t>
   </si>
   <si>
     <t xml:space="preserve">5.93674612045288</t>
@@ -416,28 +416,28 @@
     <t xml:space="preserve">5.92018604278564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06094598770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42526578903198</t>
+    <t xml:space="preserve">6.06094694137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
     <t xml:space="preserve">6.45010471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53290510177612</t>
+    <t xml:space="preserve">6.53290462493896</t>
   </si>
   <si>
     <t xml:space="preserve">6.54946422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45424461364746</t>
+    <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
     <t xml:space="preserve">6.29278469085693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45838499069214</t>
+    <t xml:space="preserve">6.45838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">6.38386487960815</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">6.2348256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33832550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37972497940063</t>
+    <t xml:space="preserve">6.33832597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37972450256348</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870428085327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50806474685669</t>
+    <t xml:space="preserve">6.3755841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50806522369385</t>
   </si>
   <si>
     <t xml:space="preserve">6.34246492385864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49150466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3341851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3714451789856</t>
+    <t xml:space="preserve">6.49150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33418560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37144565582275</t>
   </si>
   <si>
     <t xml:space="preserve">6.30520486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39214468002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18514490127563</t>
+    <t xml:space="preserve">6.39214515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18514442443848</t>
   </si>
   <si>
     <t xml:space="preserve">5.97400569915771</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0278263092041</t>
+    <t xml:space="preserve">6.02782678604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730575561523</t>
+    <t xml:space="preserve">6.36730480194092</t>
   </si>
   <si>
     <t xml:space="preserve">6.28450536727905</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">6.41284465789795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24310541152954</t>
+    <t xml:space="preserve">6.24310493469238</t>
   </si>
   <si>
     <t xml:space="preserve">6.17272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69850492477417</t>
+    <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194437026978</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334432601929</t>
+    <t xml:space="preserve">6.72334384918213</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990440368652</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">7.03798341751099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384304046631</t>
+    <t xml:space="preserve">7.20358324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17874336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384399414062</t>
   </si>
   <si>
     <t xml:space="preserve">7.01314353942871</t>
@@ -551,88 +551,88 @@
     <t xml:space="preserve">7.02142286300659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05454397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830318450928</t>
+    <t xml:space="preserve">7.05454444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830270767212</t>
   </si>
   <si>
     <t xml:space="preserve">7.20772266387939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6010217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414192199707</t>
+    <t xml:space="preserve">7.60102319717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414239883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.59688282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08766412734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370317459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47682189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27810335159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17046213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10422277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94276428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05868291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04212284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95518350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894319534302</t>
+    <t xml:space="preserve">7.0876636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48924207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10422372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9427638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0711030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05868339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04212379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486278533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894367218018</t>
   </si>
   <si>
     <t xml:space="preserve">6.91378402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932292938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26982259750366</t>
+    <t xml:space="preserve">6.95932340621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2698221206665</t>
   </si>
   <si>
     <t xml:space="preserve">7.54306125640869</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">7.50994157791138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64242172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210195541382</t>
+    <t xml:space="preserve">7.64242124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6921010017395</t>
   </si>
   <si>
     <t xml:space="preserve">7.65898275375366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9032416343689</t>
+    <t xml:space="preserve">7.90324068069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.00674057006836</t>
@@ -659,67 +659,67 @@
     <t xml:space="preserve">8.03158187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0729808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356044769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928115844727</t>
+    <t xml:space="preserve">8.07298183441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356187820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928211212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.19304084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25513935089111</t>
+    <t xml:space="preserve">8.25514125823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.48698043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49525928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36278247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39589977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43729877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62773990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63602161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59461975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5283784866333</t>
+    <t xml:space="preserve">8.49525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36277961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39590072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43729972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63601875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59461879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52837944030762</t>
   </si>
   <si>
     <t xml:space="preserve">8.32966041564941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03985977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76662111282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51181888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60290050506592</t>
+    <t xml:space="preserve">8.03986072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76662158966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96120166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51182079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6028995513916</t>
   </si>
   <si>
     <t xml:space="preserve">8.776780128479</t>
@@ -731,61 +731,61 @@
     <t xml:space="preserve">9.37293720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4474573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.159538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2920160293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3499765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5790319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.460262298584</t>
+    <t xml:space="preserve">9.44745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.085015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1595363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894540786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556924819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3499746322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5790328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
     <t xml:space="preserve">9.87489604949951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0615339279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.053050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1718187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1803035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0784997940063</t>
+    <t xml:space="preserve">10.0615329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0530500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.171820640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1803026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0785026550293</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839101791382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7062864303589</t>
+    <t xml:space="preserve">10.7062854766846</t>
   </si>
   <si>
     <t xml:space="preserve">10.6638679504395</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">10.6129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772310256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7232532501221</t>
+    <t xml:space="preserve">10.4772291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7232542037964</t>
   </si>
   <si>
     <t xml:space="preserve">10.646900177002</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">10.6299343109131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384172439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4178447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3584585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2736234664917</t>
+    <t xml:space="preserve">10.6384181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4178438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3584594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">10.3075571060181</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">10.0445671081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90882873535156</t>
+    <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.83247756958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78157520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61190319061279</t>
+    <t xml:space="preserve">9.78157424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61190414428711</t>
   </si>
   <si>
     <t xml:space="preserve">9.43374824523926</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">9.16227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19620895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23862552642822</t>
+    <t xml:space="preserve">9.17924022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19620800018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23862648010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.23014163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33194446563721</t>
+    <t xml:space="preserve">9.33194637298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.21317481994629</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">9.37436389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360841751099</t>
+    <t xml:space="preserve">9.68825531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360822677612</t>
   </si>
   <si>
     <t xml:space="preserve">9.90034484863281</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">10.2227220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2312049865723</t>
+    <t xml:space="preserve">10.2312059402466</t>
   </si>
   <si>
     <t xml:space="preserve">10.2821063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2566566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2905902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3669424057007</t>
+    <t xml:space="preserve">10.2566576004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2905912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057542800903</t>
@@ -905,79 +905,79 @@
     <t xml:space="preserve">10.0191164016724</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9682149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89186000823975</t>
+    <t xml:space="preserve">9.96821403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89186096191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764156341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51010036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919799804688</t>
+    <t xml:space="preserve">9.74764060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51010131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919895172119</t>
   </si>
   <si>
     <t xml:space="preserve">9.35739517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280460357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161552429199</t>
+    <t xml:space="preserve">9.50161743164062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071506500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27256011962891</t>
+    <t xml:space="preserve">9.28104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51858329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27256202697754</t>
   </si>
   <si>
     <t xml:space="preserve">9.20469284057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58645439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096145629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67977142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583778381348</t>
+    <t xml:space="preserve">9.58645248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096050262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67977333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612449645996</t>
+    <t xml:space="preserve">9.75612354278564</t>
   </si>
   <si>
     <t xml:space="preserve">9.82399368286133</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">9.79854202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69673919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67128753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62887096405029</t>
+    <t xml:space="preserve">9.69674015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67128849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62887001037598</t>
   </si>
   <si>
     <t xml:space="preserve">9.79005813598633</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">9.47616672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13682270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00108432769775</t>
+    <t xml:space="preserve">9.1368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
     <t xml:space="preserve">8.7211275100708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59387302398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07637596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32663917541504</t>
+    <t xml:space="preserve">8.59387397766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07637500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182571411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1230354309082</t>
+    <t xml:space="preserve">8.12303447723389</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278076171875</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">8.34360694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19514465332031</t>
+    <t xml:space="preserve">8.19514560699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.27149677276611</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">8.03819847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85156011581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82610845565796</t>
+    <t xml:space="preserve">7.85155916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82610893249512</t>
   </si>
   <si>
     <t xml:space="preserve">7.80065727233887</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">7.91094446182251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85580158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881317138672</t>
+    <t xml:space="preserve">7.85580205917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9788122177124</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123165130615</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">8.01274681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452995300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16121006011963</t>
+    <t xml:space="preserve">8.25452899932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16121101379395</t>
   </si>
   <si>
     <t xml:space="preserve">8.1484842300415</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">8.05092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2248363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28846549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42420196533203</t>
+    <t xml:space="preserve">8.08061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22483730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28846454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.56842231750488</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">8.51752090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7380952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5514554977417</t>
+    <t xml:space="preserve">8.73809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55145454406738</t>
   </si>
   <si>
     <t xml:space="preserve">8.48358631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50055408477783</t>
+    <t xml:space="preserve">8.50055313110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.65325832366943</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">8.58538913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661853790283</t>
+    <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.45813655853271</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">8.01698875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99153852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518592834473</t>
+    <t xml:space="preserve">7.99153804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518688201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9745717048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3223991394043</t>
+    <t xml:space="preserve">7.97457075119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32239818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.90776634216309</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">8.75506114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77202796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8398962020874</t>
+    <t xml:space="preserve">8.82292938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77202892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61932277679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60235691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83989715576172</t>
   </si>
   <si>
     <t xml:space="preserve">8.94169998168945</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">9.36588001251221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24710750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12833881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11137199401855</t>
+    <t xml:space="preserve">9.24710845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12833976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11137104034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.04350280761719</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">9.41678142547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142381668091</t>
+    <t xml:space="preserve">10.2142372131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6723518371582</t>
+    <t xml:space="preserve">10.6723527908325</t>
   </si>
   <si>
     <t xml:space="preserve">10.6214504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4358739852905</t>
+    <t xml:space="preserve">10.9607944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4358749389648</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680067062378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4698095321655</t>
+    <t xml:space="preserve">11.4698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5430994033813</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">11.8729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8362560272217</t>
+    <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.286584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9567823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
+    <t xml:space="preserve">11.3049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9567813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834943771362</t>
   </si>
   <si>
     <t xml:space="preserve">10.498722076416</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.7002687454224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6086568832397</t>
+    <t xml:space="preserve">10.6086578369141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453008651733</t>
@@ -1283,46 +1283,46 @@
     <t xml:space="preserve">10.4804010391235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1689195632935</t>
+    <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
     <t xml:space="preserve">10.0040187835693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98569583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">9.98569488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589847564697</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0773077011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2238855361938</t>
+    <t xml:space="preserve">10.0773086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2238864898682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2605323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1322755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4071111679077</t>
+    <t xml:space="preserve">10.1322746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4071102142334</t>
   </si>
   <si>
     <t xml:space="preserve">10.3154983520508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.443754196167</t>
+    <t xml:space="preserve">10.4437551498413</t>
   </si>
   <si>
     <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2055644989014</t>
+    <t xml:space="preserve">10.2055654525757</t>
   </si>
   <si>
     <t xml:space="preserve">10.0956296920776</t>
@@ -1331,103 +1331,103 @@
     <t xml:space="preserve">9.78415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8024730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71085929870605</t>
+    <t xml:space="preserve">9.80247211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71086120605469</t>
   </si>
   <si>
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421722412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65589427947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61924839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74750518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69253826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56428050994873</t>
+    <t xml:space="preserve">9.67421531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69253635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428146362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.30776786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2528018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32609176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27112293243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08790016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93215847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8771915435791</t>
+    <t xml:space="preserve">9.25280094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36273384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08789920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93215942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
     <t xml:space="preserve">9.03293132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95964241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94132041931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51990604400635</t>
+    <t xml:space="preserve">8.95964336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94132137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51990699768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.28171539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70312976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63900184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65732288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62984085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35500335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44661521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39938068389893</t>
+    <t xml:space="preserve">8.92299842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63900089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35500431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44661617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39937877655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.3810567855835</t>
@@ -1436,25 +1436,25 @@
     <t xml:space="preserve">9.19783401489258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00544834136963</t>
+    <t xml:space="preserve">9.00544929504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12454509735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04209327697754</t>
+    <t xml:space="preserve">9.12454414367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04209232330322</t>
   </si>
   <si>
     <t xml:space="preserve">8.96880435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99628734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88635349273682</t>
+    <t xml:space="preserve">8.99628829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88635444641113</t>
   </si>
   <si>
     <t xml:space="preserve">8.86803150177002</t>
@@ -1466,19 +1466,16 @@
     <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84054851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7764196395874</t>
+    <t xml:space="preserve">8.84054756164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59319496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60235691070557</t>
+    <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.40997219085693</t>
@@ -1487,43 +1484,43 @@
     <t xml:space="preserve">8.30919742584229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24506950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74120426177979</t>
+    <t xml:space="preserve">8.2450704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74120473861694</t>
   </si>
   <si>
     <t xml:space="preserve">7.70455980300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68623828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55798006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5946249961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49385261535645</t>
+    <t xml:space="preserve">7.68623781204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55798101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59462594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938530921936</t>
   </si>
   <si>
     <t xml:space="preserve">7.39307928085327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40224123001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159875869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10908317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38391876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16405057907104</t>
+    <t xml:space="preserve">7.40224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10908269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38391828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
     <t xml:space="preserve">7.30146789550781</t>
@@ -1532,7 +1529,7 @@
     <t xml:space="preserve">7.31978988647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48469066619873</t>
+    <t xml:space="preserve">7.48469161987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.42056322097778</t>
@@ -1541,7 +1538,7 @@
     <t xml:space="preserve">7.76868772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533313751221</t>
+    <t xml:space="preserve">7.80533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">7.69539833068848</t>
@@ -1550,16 +1547,16 @@
     <t xml:space="preserve">7.45720815658569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58546495437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121750831604</t>
+    <t xml:space="preserve">7.5854640007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217460632324</t>
   </si>
   <si>
     <t xml:space="preserve">7.22817802429199</t>
@@ -1568,25 +1565,25 @@
     <t xml:space="preserve">7.14572763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15488815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06327724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05411577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43888568878174</t>
+    <t xml:space="preserve">7.15488910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06327676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.054114818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43888521194458</t>
   </si>
   <si>
     <t xml:space="preserve">7.53965854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53049802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47553062438965</t>
+    <t xml:space="preserve">7.53049755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47552967071533</t>
   </si>
   <si>
     <t xml:space="preserve">7.33811283111572</t>
@@ -1595,7 +1592,7 @@
     <t xml:space="preserve">7.29230642318726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28314542770386</t>
+    <t xml:space="preserve">7.2831449508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.31062889099121</t>
@@ -1607,13 +1604,13 @@
     <t xml:space="preserve">7.2739839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643434524536</t>
+    <t xml:space="preserve">7.35643482208252</t>
   </si>
   <si>
     <t xml:space="preserve">7.67707681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72288227081299</t>
+    <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
     <t xml:space="preserve">7.86946105957031</t>
@@ -1622,19 +1619,19 @@
     <t xml:space="preserve">8.04352378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37332725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39164924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49242401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40081119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3458423614502</t>
+    <t xml:space="preserve">8.37332820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39165019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49242115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40081024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34584331512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.33668327331543</t>
@@ -1643,7 +1640,7 @@
     <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13370513916016</t>
+    <t xml:space="preserve">9.13370609283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.73977470397949</t>
@@ -1652,55 +1649,55 @@
     <t xml:space="preserve">9.10622119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05125522613525</t>
+    <t xml:space="preserve">9.05125427246094</t>
   </si>
   <si>
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648483276367</t>
+    <t xml:space="preserve">8.6664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01461029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91383743286133</t>
+    <t xml:space="preserve">9.01461124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
     <t xml:space="preserve">8.90467548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84971046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80390167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.813063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58403301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68480587005615</t>
+    <t xml:space="preserve">8.84970951080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8039026260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81306457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58403396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
     <t xml:space="preserve">8.25423240661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248729705811</t>
+    <t xml:space="preserve">8.38248825073242</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255344390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12597465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26339435577393</t>
+    <t xml:space="preserve">8.12597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26339340209961</t>
   </si>
   <si>
     <t xml:space="preserve">8.23590850830078</t>
@@ -1715,7 +1712,7 @@
     <t xml:space="preserve">8.47410011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.50158214569092</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829322814941</t>
@@ -1736,34 +1733,34 @@
     <t xml:space="preserve">8.61151790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54738903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21530532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70226955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40219211578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923187255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89883375167847</t>
+    <t xml:space="preserve">8.54738998413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21530628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70226860046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40219116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89883327484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.06339168548584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98595333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29571056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
+    <t xml:space="preserve">7.98595285415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
   </si>
   <si>
     <t xml:space="preserve">8.03435325622559</t>
@@ -1772,7 +1769,7 @@
     <t xml:space="preserve">8.05371189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02467155456543</t>
+    <t xml:space="preserve">8.02467250823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.10211181640625</t>
@@ -1781,7 +1778,7 @@
     <t xml:space="preserve">8.12147235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15051174163818</t>
+    <t xml:space="preserve">8.1505126953125</t>
   </si>
   <si>
     <t xml:space="preserve">7.97627353668213</t>
@@ -1790,19 +1787,19 @@
     <t xml:space="preserve">7.96659278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16987037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24731159210205</t>
+    <t xml:space="preserve">8.16987133026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24731063842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14083194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9278736114502</t>
+    <t xml:space="preserve">8.14083290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92787313461304</t>
   </si>
   <si>
     <t xml:space="preserve">8.07307243347168</t>
@@ -1814,10 +1811,10 @@
     <t xml:space="preserve">7.90851306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17955112457275</t>
+    <t xml:space="preserve">7.93755340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17955207824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.11179256439209</t>
@@ -1835,19 +1832,19 @@
     <t xml:space="preserve">8.20859050750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99563312530518</t>
+    <t xml:space="preserve">8.16019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99563360214233</t>
   </si>
   <si>
     <t xml:space="preserve">8.00531387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01499271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979389190674</t>
+    <t xml:space="preserve">8.01499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8697943687439</t>
   </si>
   <si>
     <t xml:space="preserve">7.87947416305542</t>
@@ -1856,13 +1853,13 @@
     <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95691299438477</t>
+    <t xml:space="preserve">7.95691347122192</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33442974090576</t>
+    <t xml:space="preserve">8.33443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
@@ -1871,7 +1868,7 @@
     <t xml:space="preserve">8.22795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45059013366699</t>
+    <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.52803039550781</t>
@@ -1880,31 +1877,31 @@
     <t xml:space="preserve">8.78938770294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14754581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13786602020264</t>
+    <t xml:space="preserve">9.14754486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13786506652832</t>
   </si>
   <si>
     <t xml:space="preserve">9.51538372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38954544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48634433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45730495452881</t>
+    <t xml:space="preserve">9.38954448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4863452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45730590820312</t>
   </si>
   <si>
     <t xml:space="preserve">9.44762516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55410385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53474521636963</t>
+    <t xml:space="preserve">9.55410289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53474426269531</t>
   </si>
   <si>
     <t xml:space="preserve">9.52506351470947</t>
@@ -1925,7 +1922,7 @@
     <t xml:space="preserve">9.98970127105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95098209381104</t>
+    <t xml:space="preserve">9.95098114013672</t>
   </si>
   <si>
     <t xml:space="preserve">9.60250377655029</t>
@@ -1946,13 +1943,13 @@
     <t xml:space="preserve">9.50570297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58314228057861</t>
+    <t xml:space="preserve">9.58314323425293</t>
   </si>
   <si>
     <t xml:space="preserve">9.46698379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87354183197021</t>
+    <t xml:space="preserve">9.8735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.40890502929688</t>
@@ -1961,7 +1958,7 @@
     <t xml:space="preserve">9.35082530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43794441223145</t>
+    <t xml:space="preserve">9.43794536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
@@ -1970,7 +1967,7 @@
     <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77674198150635</t>
+    <t xml:space="preserve">9.77674293518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.6412239074707</t>
@@ -1985,28 +1982,28 @@
     <t xml:space="preserve">9.09914684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19594669342041</t>
+    <t xml:space="preserve">9.08946800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
     <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0797872543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10882568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0120267868042</t>
+    <t xml:space="preserve">9.07978630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10882663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94426727294922</t>
+    <t xml:space="preserve">8.9442663192749</t>
   </si>
   <si>
     <t xml:space="preserve">8.85714721679688</t>
@@ -2018,7 +2015,7 @@
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93458652496338</t>
+    <t xml:space="preserve">8.9345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.99266624450684</t>
@@ -2027,7 +2024,7 @@
     <t xml:space="preserve">8.96362686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1572265625</t>
+    <t xml:space="preserve">9.15722560882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.05074691772461</t>
@@ -2039,19 +2036,19 @@
     <t xml:space="preserve">8.79906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32475090026855</t>
+    <t xml:space="preserve">8.32475185394287</t>
   </si>
   <si>
     <t xml:space="preserve">7.84075403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79235410690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60843515396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53099632263184</t>
+    <t xml:space="preserve">7.79235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
     <t xml:space="preserve">7.61811494827271</t>
@@ -2063,7 +2060,7 @@
     <t xml:space="preserve">6.52428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58236122131348</t>
+    <t xml:space="preserve">6.58236169815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.44684219360352</t>
@@ -2075,7 +2072,7 @@
     <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53989362716675</t>
+    <t xml:space="preserve">4.53989315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.64637279510498</t>
@@ -2084,28 +2081,28 @@
     <t xml:space="preserve">4.48181343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52053308486938</t>
+    <t xml:space="preserve">4.52053356170654</t>
   </si>
   <si>
     <t xml:space="preserve">4.83997106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13037014007568</t>
+    <t xml:space="preserve">5.13036918640137</t>
   </si>
   <si>
     <t xml:space="preserve">5.51756715774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04028463363647</t>
+    <t xml:space="preserve">6.04028415679932</t>
   </si>
   <si>
     <t xml:space="preserve">6.00156450271606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9822039604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88540554046631</t>
+    <t xml:space="preserve">5.98220443725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
     <t xml:space="preserve">5.79828596115112</t>
@@ -2126,16 +2123,16 @@
     <t xml:space="preserve">6.46620225906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716239929199</t>
+    <t xml:space="preserve">6.43716192245483</t>
   </si>
   <si>
     <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42748212814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5339617729187</t>
+    <t xml:space="preserve">6.42748165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.54364156723022</t>
@@ -2144,13 +2141,13 @@
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
+    <t xml:space="preserve">7.67619466781616</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
+    <t xml:space="preserve">7.58907604217529</t>
   </si>
   <si>
     <t xml:space="preserve">7.71491432189941</t>
@@ -2168,10 +2165,10 @@
     <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40515661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931690216064</t>
+    <t xml:space="preserve">7.4051570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
     <t xml:space="preserve">7.44387626647949</t>
@@ -2183,277 +2180,280 @@
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555425643921</t>
+    <t xml:space="preserve">7.69555521011353</t>
   </si>
   <si>
     <t xml:space="preserve">7.85043334960938</t>
   </si>
   <si>
+    <t xml:space="preserve">7.32771635055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56003522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59875535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65683507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31803703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30835723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23091745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.521315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54067516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51163625717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38579654693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3373966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35675621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45355606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57939529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41483640670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2599573135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47291564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68587493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88915300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83107423782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74395418167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73427438735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36643695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26963710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21155738830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16315793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12443828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22123765945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48259592056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66651487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42451620101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04699945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11475849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17283773422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25027656555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24059724807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20187759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18251752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13411808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15347814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62779521942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02763891220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07603788375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01795864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96955871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89211893081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97923898696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06635808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0566782951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8727593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94051933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90179967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82435989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80500030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77595996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76628017425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83403968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78563976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81467962265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7953200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75660085678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7372407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63076114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93083906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34717988967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14282083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22067165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28879070281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17201519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43476152420044</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.32771682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56003522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59875535964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65683507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30835676193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23091697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52131605148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5406756401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51163625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38579654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3373966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35675621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45355606079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57939529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41483545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25995779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47291612625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68587446212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88915348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83107471466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74395418167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73427438735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36643695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26963758468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21155738830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16315793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12443828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22123765945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70523452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72459411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48259592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66651487350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42451620101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04699850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11475849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17283773422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25027704238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24059772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20187759399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18251800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13411855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15347766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62779521942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02763891220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07603788375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01795816421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96955871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89211893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97923898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06635808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0566782951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87275981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94051885604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90179967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436037063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80500030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77596044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76628017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81467962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7953200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75660037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7372407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63076066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67916059494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93083906173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34717988967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14282083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22067165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28879117965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17201519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43476152420044</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.49314975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52234363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395635604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70723962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83374786376953</t>
+    <t xml:space="preserve">7.59046411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52234411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70724010467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83374738693237</t>
   </si>
   <si>
     <t xml:space="preserve">8.06729984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03810596466064</t>
+    <t xml:space="preserve">8.03810691833496</t>
   </si>
   <si>
     <t xml:space="preserve">8.08676338195801</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">7.96998643875122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89213514328003</t>
+    <t xml:space="preserve">7.89213562011719</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">7.60019493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5710015296936</t>
+    <t xml:space="preserve">7.57100105285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.72670269012451</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">7.65858316421509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73643398284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69750833511353</t>
+    <t xml:space="preserve">7.73643445968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69750881195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">7.82401657104492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64885187149048</t>
+    <t xml:space="preserve">7.64885139465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">7.63912057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62938928604126</t>
+    <t xml:space="preserve">7.62938976287842</t>
   </si>
   <si>
     <t xml:space="preserve">7.56126928329468</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">7.8434796333313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8045539855957</t>
+    <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.79482221603394</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">8.01864433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079303741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112243652344</t>
+    <t xml:space="preserve">7.94079256057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112148284912</t>
   </si>
   <si>
     <t xml:space="preserve">8.2716588973999</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">8.68037605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81661701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02097511291504</t>
+    <t xml:space="preserve">8.81661605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02097415924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">8.75822734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.806884765625</t>
+    <t xml:space="preserve">8.80688381195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.57333183288574</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">8.51494312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24246406555176</t>
+    <t xml:space="preserve">8.24246501922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.30085277557373</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">8.15488338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23273372650146</t>
+    <t xml:space="preserve">8.23273468017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.17434501647949</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">8.64144992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58306217193604</t>
+    <t xml:space="preserve">8.58306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2684,37 +2684,37 @@
     <t xml:space="preserve">8.84580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01124286651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92599105834961</t>
+    <t xml:space="preserve">9.0112419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92599010467529</t>
   </si>
   <si>
     <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88706493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3152456283569</t>
+    <t xml:space="preserve">9.88706588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3152446746826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3541707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3736343383789</t>
+    <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
     <t xml:space="preserve">9.77028846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50754261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41022872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13775062561035</t>
+    <t xml:space="preserve">9.50754356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41022777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13775157928467</t>
   </si>
   <si>
     <t xml:space="preserve">9.07936191558838</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">9.14748191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32264614105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05989933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08909320831299</t>
+    <t xml:space="preserve">9.32264709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0890941619873</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.11828708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24479484558105</t>
+    <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
     <t xml:space="preserve">8.93339157104492</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.361572265625</t>
+    <t xml:space="preserve">9.19613742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
     <t xml:space="preserve">9.62431812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57566261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53673648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8286771774292</t>
+    <t xml:space="preserve">9.57566165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5367374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82867813110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.86760330200195</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297458648682</t>
+    <t xml:space="preserve">9.67297554016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.61458778381348</t>
@@ -2789,16 +2789,16 @@
     <t xml:space="preserve">9.59512424468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45888519287109</t>
+    <t xml:space="preserve">9.45888614654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.38103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17667675018311</t>
+    <t xml:space="preserve">9.18640613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.21560192108154</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">9.23506355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20587062835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00151252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98204803466797</t>
+    <t xml:space="preserve">9.20586967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0015115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98204898834229</t>
   </si>
   <si>
     <t xml:space="preserve">8.56360054016113</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795864105225</t>
+    <t xml:space="preserve">8.76795959472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.41763019561768</t>
@@ -2849,28 +2849,28 @@
     <t xml:space="preserve">8.79715251922607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95285415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04783821105957</t>
+    <t xml:space="preserve">8.95285511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04783916473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500286102295</t>
+    <t xml:space="preserve">8.87500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969036102295</t>
+    <t xml:space="preserve">9.42969131469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921459197998</t>
+    <t xml:space="preserve">9.80921363830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">9.26425838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37130355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5561990737915</t>
+    <t xml:space="preserve">9.37130260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55619812011719</t>
   </si>
   <si>
     <t xml:space="preserve">9.44915390014648</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136329650879</t>
+    <t xml:space="preserve">9.73136234283447</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595439910889</t>
+    <t xml:space="preserve">10.0038414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1595430374146</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816926956177</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">10.0233039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622291564941</t>
+    <t xml:space="preserve">10.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622301101685</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533226013184</t>
+    <t xml:space="preserve">9.90652942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533130645752</t>
   </si>
   <si>
     <t xml:space="preserve">9.33237743377686</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">9.40049743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48807907104492</t>
+    <t xml:space="preserve">9.48808002471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.63404941558838</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">11.5803232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5997858047485</t>
+    <t xml:space="preserve">11.5997848510742</t>
   </si>
   <si>
     <t xml:space="preserve">11.6776361465454</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">11.6192474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4830083847046</t>
+    <t xml:space="preserve">11.4830093383789</t>
   </si>
   <si>
     <t xml:space="preserve">11.3662338256836</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">11.638710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0668897628784</t>
+    <t xml:space="preserve">12.0668907165527</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">12.4756078720093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1836681365967</t>
+    <t xml:space="preserve">12.1836671829224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970987319946</t>
+    <t xml:space="preserve">11.6970996856689</t>
   </si>
   <si>
     <t xml:space="preserve">11.2299928665161</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159025192261</t>
+    <t xml:space="preserve">11.0159034729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.743426322937</t>
+    <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.9575157165527</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">10.1984691619873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071863174438</t>
+    <t xml:space="preserve">10.6071853637695</t>
   </si>
   <si>
     <t xml:space="preserve">10.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132183074951</t>
+    <t xml:space="preserve">11.1132173538208</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">10.860200881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6266489028931</t>
+    <t xml:space="preserve">10.6266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2105312347412</t>
+    <t xml:space="preserve">11.2105321884155</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219345092773</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695777893066</t>
+    <t xml:space="preserve">11.9695768356323</t>
   </si>
   <si>
     <t xml:space="preserve">11.9306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8528003692627</t>
+    <t xml:space="preserve">11.852801322937</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917264938354</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">12.1058158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5339965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6507720947266</t>
+    <t xml:space="preserve">12.5339956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259372711182</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8648624420166</t>
+    <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
     <t xml:space="preserve">12.5145330429077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3977575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4366817474365</t>
+    <t xml:space="preserve">12.3977565765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4366827011108</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2809801101685</t>
+    <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447410583496</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950714111328</t>
+    <t xml:space="preserve">12.3393688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950723648071</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">12.787013053894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225923538208</t>
+    <t xml:space="preserve">12.2225933074951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762666702271</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">12.9427137374878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1373414993286</t>
+    <t xml:space="preserve">13.1373405456543</t>
   </si>
   <si>
     <t xml:space="preserve">13.0789518356323</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">13.9742383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051042556763</t>
+    <t xml:space="preserve">14.3051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">14.6165084838867</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">14.7527465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1809272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279127120972</t>
+    <t xml:space="preserve">15.1809282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473733901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279117584229</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359172821045</t>
+    <t xml:space="preserve">17.5359191894531</t>
   </si>
   <si>
     <t xml:space="preserve">17.4191417694092</t>
@@ -3257,25 +3257,25 @@
     <t xml:space="preserve">17.7889347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.61376953125</t>
+    <t xml:space="preserve">17.6137676239014</t>
   </si>
   <si>
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500057220459</t>
+    <t xml:space="preserve">17.7500076293945</t>
   </si>
   <si>
     <t xml:space="preserve">18.2949638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2755012512207</t>
+    <t xml:space="preserve">18.2755031585693</t>
   </si>
   <si>
     <t xml:space="preserve">18.2365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8204574584961</t>
+    <t xml:space="preserve">18.8204555511475</t>
   </si>
   <si>
     <t xml:space="preserve">18.7620697021484</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">19.0345458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0419502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0030250549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5479774475098</t>
+    <t xml:space="preserve">18.0419483184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.003023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5479793548584</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">19.7060108184814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8519821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7546653747559</t>
+    <t xml:space="preserve">19.8519802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
     <t xml:space="preserve">19.5113830566406</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036800384521</t>
+    <t xml:space="preserve">19.0734748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036819458008</t>
   </si>
   <si>
     <t xml:space="preserve">18.898307800293</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">19.1902484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9761581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8593807220459</t>
+    <t xml:space="preserve">18.9761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8593826293945</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6452922821045</t>
+    <t xml:space="preserve">18.6452941894531</t>
   </si>
   <si>
     <t xml:space="preserve">18.4701271057129</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">19.0540103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1513252258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9177703857422</t>
+    <t xml:space="preserve">19.1513233184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9177722930908</t>
   </si>
   <si>
     <t xml:space="preserve">18.9956226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.72314453125</t>
+    <t xml:space="preserve">18.7231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -4608,6 +4608,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -23268,7 +23271,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G705" t="s">
-        <v>488</v>
+        <v>391</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23294,7 +23297,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G706" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23346,7 +23349,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G708" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23372,7 +23375,7 @@
         <v>9</v>
       </c>
       <c r="G709" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23398,7 +23401,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G710" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23424,7 +23427,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G711" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23450,7 +23453,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G712" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23476,7 +23479,7 @@
         <v>8.25</v>
       </c>
       <c r="G713" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23502,7 +23505,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23528,7 +23531,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G715" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23554,7 +23557,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G716" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23580,7 +23583,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G717" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23606,7 +23609,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23632,7 +23635,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G719" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23658,7 +23661,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G720" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23684,7 +23687,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G721" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23710,7 +23713,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G722" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23736,7 +23739,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G723" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23762,7 +23765,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23788,7 +23791,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G725" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23814,7 +23817,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G726" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23840,7 +23843,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G727" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23866,7 +23869,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G728" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23892,7 +23895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G729" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23918,7 +23921,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G730" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23944,7 +23947,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G731" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23970,7 +23973,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G732" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23996,7 +23999,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G733" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24022,7 +24025,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G734" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24048,7 +24051,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G735" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24074,7 +24077,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G736" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24100,7 +24103,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G737" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24126,7 +24129,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24152,7 +24155,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G739" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24178,7 +24181,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24204,7 +24207,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G741" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24230,7 +24233,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G742" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24256,7 +24259,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G743" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24282,7 +24285,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G744" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24308,7 +24311,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24334,7 +24337,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G746" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24360,7 +24363,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G747" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24386,7 +24389,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G748" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24412,7 +24415,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G749" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24438,7 +24441,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G750" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24464,7 +24467,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G751" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24490,7 +24493,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G752" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24516,7 +24519,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G753" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24542,7 +24545,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G754" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24568,7 +24571,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G755" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24594,7 +24597,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24620,7 +24623,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24646,7 +24649,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G758" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24672,7 +24675,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24698,7 +24701,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G760" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24724,7 +24727,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G761" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24750,7 +24753,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G762" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24776,7 +24779,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G763" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24802,7 +24805,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G764" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24828,7 +24831,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G765" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24854,7 +24857,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G766" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24880,7 +24883,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G767" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24932,7 +24935,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G769" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24958,7 +24961,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G770" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24984,7 +24987,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G771" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25010,7 +25013,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G772" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25036,7 +25039,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25062,7 +25065,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G774" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25088,7 +25091,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G775" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25114,7 +25117,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G776" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25140,7 +25143,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G777" t="s">
-        <v>488</v>
+        <v>391</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25270,7 +25273,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25296,7 +25299,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G783" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25348,7 +25351,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G785" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25400,7 +25403,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G787" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25426,7 +25429,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G788" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25478,7 +25481,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G790" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25504,7 +25507,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G791" t="s">
-        <v>488</v>
+        <v>391</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25530,7 +25533,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G792" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25582,7 +25585,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G794" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25660,7 +25663,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G797" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25712,7 +25715,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G799" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25816,7 +25819,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G803" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25842,7 +25845,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G804" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25868,7 +25871,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G805" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25894,7 +25897,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G806" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25946,7 +25949,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G808" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26024,7 +26027,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G811" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26050,7 +26053,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G812" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26076,7 +26079,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G813" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26102,7 +26105,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G814" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26128,7 +26131,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G815" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26154,7 +26157,7 @@
         <v>9</v>
       </c>
       <c r="G816" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26180,7 +26183,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G817" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26232,7 +26235,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G819" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26258,7 +26261,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G820" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26284,7 +26287,7 @@
         <v>9</v>
       </c>
       <c r="G821" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26310,7 +26313,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G822" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26336,7 +26339,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G823" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26388,7 +26391,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G825" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26414,7 +26417,7 @@
         <v>9</v>
       </c>
       <c r="G826" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26440,7 +26443,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G827" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26466,7 +26469,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G828" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26492,7 +26495,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26544,7 +26547,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G831" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26570,7 +26573,7 @@
         <v>9.25</v>
       </c>
       <c r="G832" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26596,7 +26599,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G833" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26622,7 +26625,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G834" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26648,7 +26651,7 @@
         <v>9.25</v>
       </c>
       <c r="G835" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26674,7 +26677,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G836" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26700,7 +26703,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G837" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26726,7 +26729,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G838" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26752,7 +26755,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G839" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26778,7 +26781,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G840" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26804,7 +26807,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G841" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26830,7 +26833,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G842" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26882,7 +26885,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G844" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26934,7 +26937,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26960,7 +26963,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26986,7 +26989,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G848" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27012,7 +27015,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G849" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27038,7 +27041,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G850" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27064,7 +27067,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27090,7 +27093,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G852" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27116,7 +27119,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G853" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27142,7 +27145,7 @@
         <v>8.25</v>
       </c>
       <c r="G854" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27168,7 +27171,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G855" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27194,7 +27197,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G856" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27220,7 +27223,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G857" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27246,7 +27249,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G858" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27272,7 +27275,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27298,7 +27301,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G860" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27324,7 +27327,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G861" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27350,7 +27353,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G862" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27376,7 +27379,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G863" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27402,7 +27405,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G864" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27428,7 +27431,7 @@
         <v>8.25</v>
       </c>
       <c r="G865" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27454,7 +27457,7 @@
         <v>8.25</v>
       </c>
       <c r="G866" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27480,7 +27483,7 @@
         <v>8.25</v>
       </c>
       <c r="G867" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27506,7 +27509,7 @@
         <v>8.25</v>
       </c>
       <c r="G868" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27532,7 +27535,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G869" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27558,7 +27561,7 @@
         <v>8.25</v>
       </c>
       <c r="G870" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27584,7 +27587,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G871" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27610,7 +27613,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G872" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27636,7 +27639,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27662,7 +27665,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G874" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27688,7 +27691,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G875" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27714,7 +27717,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G876" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27740,7 +27743,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G877" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27766,7 +27769,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G878" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27792,7 +27795,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G879" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27818,7 +27821,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G880" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27844,7 +27847,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G881" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27870,7 +27873,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G882" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27896,7 +27899,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G883" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27922,7 +27925,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G884" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27948,7 +27951,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G885" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27974,7 +27977,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G886" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28000,7 +28003,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G887" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28026,7 +28029,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G888" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28052,7 +28055,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G889" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28078,7 +28081,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G890" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28104,7 +28107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G891" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28130,7 +28133,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G892" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28156,7 +28159,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G893" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28182,7 +28185,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G894" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28208,7 +28211,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G895" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28234,7 +28237,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G896" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28260,7 +28263,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G897" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28286,7 +28289,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G898" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28312,7 +28315,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G899" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28338,7 +28341,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G900" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28364,7 +28367,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G901" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28390,7 +28393,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G902" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28416,7 +28419,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G903" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28442,7 +28445,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G904" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28468,7 +28471,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G905" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28494,7 +28497,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G906" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28520,7 +28523,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G907" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28546,7 +28549,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G908" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28572,7 +28575,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G909" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28598,7 +28601,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G910" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28624,7 +28627,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G911" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28650,7 +28653,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G912" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -28676,7 +28679,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28702,7 +28705,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G914" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -28728,7 +28731,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G915" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -28754,7 +28757,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G916" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -28780,7 +28783,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G917" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -28806,7 +28809,7 @@
         <v>8.25</v>
       </c>
       <c r="G918" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -28832,7 +28835,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G919" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -28858,7 +28861,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G920" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -28884,7 +28887,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G921" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -28910,7 +28913,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G922" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -28936,7 +28939,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G923" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -28962,7 +28965,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G924" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -28988,7 +28991,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G925" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29014,7 +29017,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G926" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29040,7 +29043,7 @@
         <v>8.25</v>
       </c>
       <c r="G927" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29066,7 +29069,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G928" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29092,7 +29095,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G929" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29118,7 +29121,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29144,7 +29147,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G931" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29170,7 +29173,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G932" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -29196,7 +29199,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G933" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -29222,7 +29225,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G934" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -29248,7 +29251,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G935" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29274,7 +29277,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G936" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29300,7 +29303,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G937" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29326,7 +29329,7 @@
         <v>8.25</v>
       </c>
       <c r="G938" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29352,7 +29355,7 @@
         <v>8.25</v>
       </c>
       <c r="G939" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29378,7 +29381,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29404,7 +29407,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G941" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29430,7 +29433,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G942" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29456,7 +29459,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G943" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29482,7 +29485,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G944" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29508,7 +29511,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G945" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29534,7 +29537,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29560,7 +29563,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29586,7 +29589,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G948" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29612,7 +29615,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29638,7 +29641,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G950" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -29664,7 +29667,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G951" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29690,7 +29693,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G952" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29716,7 +29719,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G953" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29742,7 +29745,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G954" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29768,7 +29771,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G955" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -29794,7 +29797,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G956" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -29820,7 +29823,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G957" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -29846,7 +29849,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G958" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29872,7 +29875,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G959" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -29898,7 +29901,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G960" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29924,7 +29927,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G961" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29950,7 +29953,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G962" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -29976,7 +29979,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30002,7 +30005,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G964" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30028,7 +30031,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G965" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30054,7 +30057,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G966" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30080,7 +30083,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G967" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30106,7 +30109,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G968" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30132,7 +30135,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G969" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30158,7 +30161,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G970" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30184,7 +30187,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G971" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30210,7 +30213,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G972" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30236,7 +30239,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G973" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30262,7 +30265,7 @@
         <v>8.5</v>
       </c>
       <c r="G974" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -30288,7 +30291,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G975" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -30314,7 +30317,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -30340,7 +30343,7 @@
         <v>8.5</v>
       </c>
       <c r="G977" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30366,7 +30369,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G978" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30392,7 +30395,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G979" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30418,7 +30421,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G980" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30444,7 +30447,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30470,7 +30473,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G982" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30496,7 +30499,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G983" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30522,7 +30525,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30548,7 +30551,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G985" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30574,7 +30577,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30600,7 +30603,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G987" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30626,7 +30629,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G988" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -30652,7 +30655,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G989" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -30678,7 +30681,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G990" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -30704,7 +30707,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G991" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -30730,7 +30733,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G992" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -30756,7 +30759,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G993" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -30782,7 +30785,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G994" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -30808,7 +30811,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G995" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -30834,7 +30837,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G996" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -30860,7 +30863,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G997" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -30886,7 +30889,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G998" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -30912,7 +30915,7 @@
         <v>10</v>
       </c>
       <c r="G999" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30938,7 +30941,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1000" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30964,7 +30967,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1001" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30990,7 +30993,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1002" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31016,7 +31019,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1003" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31042,7 +31045,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1004" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31068,7 +31071,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1005" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31094,7 +31097,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1006" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31120,7 +31123,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -31146,7 +31149,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1008" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31172,7 +31175,7 @@
         <v>10</v>
       </c>
       <c r="G1009" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31198,7 +31201,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1010" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -31224,7 +31227,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1011" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -31250,7 +31253,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1012" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31276,7 +31279,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1013" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -31302,7 +31305,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1014" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -31328,7 +31331,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1015" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31354,7 +31357,7 @@
         <v>9.75</v>
       </c>
       <c r="G1016" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -31380,7 +31383,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1017" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31406,7 +31409,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1018" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31432,7 +31435,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1019" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31458,7 +31461,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1020" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31484,7 +31487,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1021" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31510,7 +31513,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31536,7 +31539,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1023" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31562,7 +31565,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1024" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31588,7 +31591,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31614,7 +31617,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1026" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31640,7 +31643,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1027" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31666,7 +31669,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31692,7 +31695,7 @@
         <v>9.5</v>
       </c>
       <c r="G1029" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31718,7 +31721,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1030" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -31744,7 +31747,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1031" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31770,7 +31773,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1032" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31796,7 +31799,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1033" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -31822,7 +31825,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1034" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -31848,7 +31851,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1035" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31874,7 +31877,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1036" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -31900,7 +31903,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1037" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -31926,7 +31929,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1038" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31952,7 +31955,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31978,7 +31981,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1040" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32004,7 +32007,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32030,7 +32033,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1042" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32056,7 +32059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1043" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32082,7 +32085,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32108,7 +32111,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1045" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32134,7 +32137,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1046" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -32160,7 +32163,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -32186,7 +32189,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1048" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -32212,7 +32215,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1049" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -32238,7 +32241,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -32264,7 +32267,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1051" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -32290,7 +32293,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1052" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -32316,7 +32319,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1053" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -32342,7 +32345,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1054" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -32368,7 +32371,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1055" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32394,7 +32397,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1056" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32420,7 +32423,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1057" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32446,7 +32449,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -32472,7 +32475,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1059" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32498,7 +32501,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1060" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -32524,7 +32527,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1061" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -32550,7 +32553,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1062" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -32576,7 +32579,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1063" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32602,7 +32605,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1064" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32628,7 +32631,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1065" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -32654,7 +32657,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1066" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -32680,7 +32683,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1067" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -32706,7 +32709,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1068" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -32732,7 +32735,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1069" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -32758,7 +32761,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1070" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -32784,7 +32787,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1071" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -32810,7 +32813,7 @@
         <v>5</v>
       </c>
       <c r="G1072" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -32836,7 +32839,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1073" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -32862,7 +32865,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1074" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -32888,7 +32891,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1075" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -32914,7 +32917,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1076" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32940,7 +32943,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1077" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32966,7 +32969,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1078" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32992,7 +32995,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1079" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33018,7 +33021,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1080" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33044,7 +33047,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1081" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33070,7 +33073,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1082" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -33096,7 +33099,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1083" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -33122,7 +33125,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1084" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -33148,7 +33151,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1085" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -33174,7 +33177,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1086" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -33200,7 +33203,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1087" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33226,7 +33229,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1088" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -33252,7 +33255,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1089" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -33278,7 +33281,7 @@
         <v>6.75</v>
       </c>
       <c r="G1090" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -33304,7 +33307,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1091" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -33330,7 +33333,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1092" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33356,7 +33359,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1093" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33382,7 +33385,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1094" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33408,7 +33411,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1095" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33434,7 +33437,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1096" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33460,7 +33463,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33486,7 +33489,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33512,7 +33515,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1099" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33538,7 +33541,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1100" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33564,7 +33567,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1101" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33590,7 +33593,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1102" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -33616,7 +33619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1103" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -33642,7 +33645,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1104" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -33668,7 +33671,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1105" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -33694,7 +33697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1106" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -33720,7 +33723,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1107" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -33746,7 +33749,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1108" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -33772,7 +33775,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1109" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -33798,7 +33801,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1110" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -33824,7 +33827,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1111" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -33850,7 +33853,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1112" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -33876,7 +33879,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1113" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33902,7 +33905,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33928,7 +33931,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1115" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33954,7 +33957,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1116" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33980,7 +33983,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1117" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -34006,7 +34009,7 @@
         <v>8.25</v>
       </c>
       <c r="G1118" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -34032,7 +34035,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1119" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -34058,7 +34061,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1120" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -34084,7 +34087,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1121" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -34110,7 +34113,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1122" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -34136,7 +34139,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1123" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -34162,7 +34165,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1124" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -34188,7 +34191,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1125" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -34214,7 +34217,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1126" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -34240,7 +34243,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1127" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -34266,7 +34269,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1128" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -34292,7 +34295,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1129" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -34318,7 +34321,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1130" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -34344,7 +34347,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1131" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34370,7 +34373,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1132" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34396,7 +34399,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1133" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34422,7 +34425,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34448,7 +34451,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1135" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34474,7 +34477,7 @@
         <v>7.75</v>
       </c>
       <c r="G1136" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34500,7 +34503,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34526,7 +34529,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34552,7 +34555,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34578,7 +34581,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1140" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34604,7 +34607,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1141" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -34630,7 +34633,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1142" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -34656,7 +34659,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1143" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -34682,7 +34685,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1144" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -34708,7 +34711,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1145" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -34734,7 +34737,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1146" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -34760,7 +34763,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1147" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -34786,7 +34789,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1148" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -34812,7 +34815,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1149" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -34838,7 +34841,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1150" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -34864,7 +34867,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1151" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34890,7 +34893,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34916,7 +34919,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1153" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34942,7 +34945,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1154" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34968,7 +34971,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1155" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34994,7 +34997,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -35020,7 +35023,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1157" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -35046,7 +35049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -35072,7 +35075,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1159" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -35098,7 +35101,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1160" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -35124,7 +35127,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -35150,7 +35153,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1162" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -35176,7 +35179,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1163" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -35202,7 +35205,7 @@
         <v>7.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -35228,7 +35231,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -35254,7 +35257,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1166" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -35280,7 +35283,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1167" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -35306,7 +35309,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -35332,7 +35335,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1169" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35358,7 +35361,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1170" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35384,7 +35387,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1171" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35410,7 +35413,7 @@
         <v>8.25</v>
       </c>
       <c r="G1172" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35436,7 +35439,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1173" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35462,7 +35465,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1174" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35488,7 +35491,7 @@
         <v>8</v>
       </c>
       <c r="G1175" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35514,7 +35517,7 @@
         <v>8</v>
       </c>
       <c r="G1176" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35540,7 +35543,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1177" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35566,7 +35569,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1178" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35592,7 +35595,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1179" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -35618,7 +35621,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1180" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -35644,7 +35647,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1181" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -35670,7 +35673,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1182" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -35696,7 +35699,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1183" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -35722,7 +35725,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -35748,7 +35751,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1185" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -35774,7 +35777,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1186" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -35800,7 +35803,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1187" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -35826,7 +35829,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1188" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -35852,7 +35855,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -35878,7 +35881,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1190" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35904,7 +35907,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1191" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35930,7 +35933,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1192" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35956,7 +35959,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1193" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35982,7 +35985,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1194" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -36008,7 +36011,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1195" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -36034,7 +36037,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1196" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -36060,7 +36063,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1197" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -36086,7 +36089,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1198" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -36112,7 +36115,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1199" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -36138,7 +36141,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1200" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -36164,7 +36167,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -36190,7 +36193,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -36216,7 +36219,7 @@
         <v>7.5</v>
       </c>
       <c r="G1203" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -36242,7 +36245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1204" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -36268,7 +36271,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1205" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -36294,7 +36297,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1206" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -36320,7 +36323,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1207" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -36346,7 +36349,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1208" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36372,7 +36375,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36398,7 +36401,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1210" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36424,7 +36427,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1211" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36450,7 +36453,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1212" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36476,7 +36479,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1213" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36502,7 +36505,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1214" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36528,7 +36531,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1215" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36554,7 +36557,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1216" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36580,7 +36583,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1217" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36606,7 +36609,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1218" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -36632,7 +36635,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1219" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -36658,7 +36661,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1220" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -36684,7 +36687,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -36710,7 +36713,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36736,7 +36739,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -36762,7 +36765,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1224" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -36788,7 +36791,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1225" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36814,7 +36817,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -36840,7 +36843,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1227" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -36866,7 +36869,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1228" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36892,7 +36895,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1229" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36918,7 +36921,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1230" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36944,7 +36947,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1231" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36970,7 +36973,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1232" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36996,7 +36999,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -37022,7 +37025,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1234" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -37048,7 +37051,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -37074,7 +37077,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1236" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -37100,7 +37103,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1237" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -37126,7 +37129,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1238" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -37152,7 +37155,7 @@
         <v>7.5</v>
       </c>
       <c r="G1239" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -37178,7 +37181,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1240" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -37204,7 +37207,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1241" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -37230,7 +37233,7 @@
         <v>7.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -37256,7 +37259,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1243" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -37282,7 +37285,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1244" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -37308,7 +37311,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1245" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -37334,7 +37337,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1246" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37360,7 +37363,7 @@
         <v>7.5</v>
       </c>
       <c r="G1247" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37386,7 +37389,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1248" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37412,7 +37415,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1249" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37438,7 +37441,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37464,7 +37467,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37490,7 +37493,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1252" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37516,7 +37519,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1253" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37542,7 +37545,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1254" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37568,7 +37571,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1255" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37594,7 +37597,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1256" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -37620,7 +37623,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1257" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -37646,7 +37649,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -37672,7 +37675,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1259" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -37698,7 +37701,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1260" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -37724,7 +37727,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1261" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -37750,7 +37753,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1262" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -37776,7 +37779,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1263" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -37802,7 +37805,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1264" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -37828,7 +37831,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1265" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -37854,7 +37857,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -37880,7 +37883,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1267" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37906,7 +37909,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1268" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37932,7 +37935,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1269" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37958,7 +37961,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1270" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37984,7 +37987,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1271" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -38010,7 +38013,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1272" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -38036,7 +38039,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1273" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -38062,7 +38065,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1274" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -38088,7 +38091,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -38114,7 +38117,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1276" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -38140,7 +38143,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1277" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -38166,7 +38169,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1278" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -38192,7 +38195,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1279" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -38218,7 +38221,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1280" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -38244,7 +38247,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1281" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -38270,7 +38273,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1282" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -38296,7 +38299,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1283" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -38322,7 +38325,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1284" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38348,7 +38351,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1285" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38374,7 +38377,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1286" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38400,7 +38403,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1287" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38426,7 +38429,7 @@
         <v>7.25</v>
       </c>
       <c r="G1288" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38452,7 +38455,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1289" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38478,7 +38481,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1290" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38504,7 +38507,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1291" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38530,7 +38533,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1292" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38556,7 +38559,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38582,7 +38585,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1294" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38608,7 +38611,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1295" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -38634,7 +38637,7 @@
         <v>7.5</v>
       </c>
       <c r="G1296" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -38660,7 +38663,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1297" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -38686,7 +38689,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1298" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -38712,7 +38715,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1299" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38738,7 +38741,7 @@
         <v>7.25</v>
       </c>
       <c r="G1300" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38764,7 +38767,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1301" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38790,7 +38793,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1302" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38816,7 +38819,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1303" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -38842,7 +38845,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1304" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -38868,7 +38871,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1305" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38894,7 +38897,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1306" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38920,7 +38923,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1307" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38946,7 +38949,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1308" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38972,7 +38975,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1309" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38998,7 +39001,7 @@
         <v>7</v>
       </c>
       <c r="G1310" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -39024,7 +39027,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1311" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -39050,7 +39053,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1312" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -39076,7 +39079,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1313" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -39102,7 +39105,7 @@
         <v>7</v>
       </c>
       <c r="G1314" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -39128,7 +39131,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1315" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -39154,7 +39157,7 @@
         <v>7</v>
       </c>
       <c r="G1316" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -39180,7 +39183,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1317" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -39206,7 +39209,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1318" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -39232,7 +39235,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -39258,7 +39261,7 @@
         <v>7</v>
       </c>
       <c r="G1320" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39284,7 +39287,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1321" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39310,7 +39313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1322" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -39336,7 +39339,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39362,7 +39365,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1324" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39388,7 +39391,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1325" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39414,7 +39417,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39440,7 +39443,7 @@
         <v>7</v>
       </c>
       <c r="G1327" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39466,7 +39469,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1328" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39492,7 +39495,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1329" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39518,7 +39521,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1330" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39544,7 +39547,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1331" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39570,7 +39573,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1332" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39596,7 +39599,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -39622,7 +39625,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1334" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -39648,7 +39651,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -39674,7 +39677,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1336" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -39700,7 +39703,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1337" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -39726,7 +39729,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1338" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -39752,7 +39755,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -39778,7 +39781,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1340" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -39804,7 +39807,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1341" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -39830,7 +39833,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1342" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -39856,7 +39859,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1343" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39882,7 +39885,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1344" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39908,7 +39911,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1345" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39934,7 +39937,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1346" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39960,7 +39963,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1347" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39986,7 +39989,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1348" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -40012,7 +40015,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1349" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -40038,7 +40041,7 @@
         <v>7.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -40064,7 +40067,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1351" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -40090,7 +40093,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1352" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -40116,7 +40119,7 @@
         <v>7.5</v>
       </c>
       <c r="G1353" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -40142,7 +40145,7 @@
         <v>7.5</v>
       </c>
       <c r="G1354" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40168,7 +40171,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1355" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40194,7 +40197,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1356" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40220,7 +40223,7 @@
         <v>7.5</v>
       </c>
       <c r="G1357" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40246,7 +40249,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1358" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40272,7 +40275,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1359" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40298,7 +40301,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1360" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40324,7 +40327,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40350,7 +40353,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1362" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40376,7 +40379,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1363" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40402,7 +40405,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1364" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40428,7 +40431,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1365" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40454,7 +40457,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1366" t="s">
-        <v>725</v>
+        <v>804</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -71038,7 +71041,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.6911574074</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>29441</v>
@@ -71059,6 +71062,32 @@
         <v>1482</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6868055556</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>14205</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>30.7000007629395</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>31.1000003814697</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>31.2999992370605</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009378433228</t>
+    <t xml:space="preserve">6.41009426116943</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
@@ -53,55 +53,55 @@
     <t xml:space="preserve">6.22992277145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26996040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09379386901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92563390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85356426239014</t>
+    <t xml:space="preserve">6.26995992660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0937933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582445144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92563343048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85356473922729</t>
   </si>
   <si>
     <t xml:space="preserve">5.76548099517822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94565200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946546554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143983840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7254433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74145841598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559579849243</t>
+    <t xml:space="preserve">5.94565296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559484481812</t>
   </si>
   <si>
     <t xml:space="preserve">5.91762590408325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94164943695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00571012496948</t>
+    <t xml:space="preserve">5.94164848327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00570964813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.84956073760986</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">5.77749252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17387008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14984703063965</t>
+    <t xml:space="preserve">6.17386960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14984607696533</t>
   </si>
   <si>
     <t xml:space="preserve">6.20589971542358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29398345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19789266586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20990371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.406090259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45813941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41409826278687</t>
+    <t xml:space="preserve">6.29398441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22191572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20990324020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40609073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45813894271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41409778594971</t>
   </si>
   <si>
     <t xml:space="preserve">6.48616647720337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50218105316162</t>
+    <t xml:space="preserve">6.50218200683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.49417352676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07777833938599</t>
+    <t xml:space="preserve">6.23793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07777786254883</t>
   </si>
   <si>
     <t xml:space="preserve">6.25394630432129</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">6.19388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14183950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15385055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10980892181396</t>
+    <t xml:space="preserve">6.14183902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10980844497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.1138129234314</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">5.94965600967407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375480651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785503387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09779691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18187665939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21390819549561</t>
+    <t xml:space="preserve">6.13383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375576019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09779596328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18187713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21390771865845</t>
   </si>
   <si>
     <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1018009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01371717453003</t>
+    <t xml:space="preserve">6.10180044174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01371765136719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95766401290894</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">6.11781597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07377433776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06977033615112</t>
+    <t xml:space="preserve">6.07377529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06977081298828</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342517852783</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">6.09406566619873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16858530044556</t>
+    <t xml:space="preserve">6.1685848236084</t>
   </si>
   <si>
     <t xml:space="preserve">6.18928527832031</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">6.20170545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890554428101</t>
+    <t xml:space="preserve">6.11890602111816</t>
   </si>
   <si>
     <t xml:space="preserve">6.28864479064941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19756555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1271858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13960599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438638687134</t>
+    <t xml:space="preserve">6.19756603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12718534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438591003418</t>
   </si>
   <si>
     <t xml:space="preserve">5.89534616470337</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">5.8125467300415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99470615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0402455329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94502639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96158599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85394716262817</t>
+    <t xml:space="preserve">5.99470567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94502592086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.961585521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85394668579102</t>
   </si>
   <si>
     <t xml:space="preserve">5.78770637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86222696304321</t>
+    <t xml:space="preserve">5.8622260093689</t>
   </si>
   <si>
     <t xml:space="preserve">5.91190576553345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86636638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12304544448853</t>
+    <t xml:space="preserve">5.86636590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12304592132568</t>
   </si>
   <si>
     <t xml:space="preserve">6.01540565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10234498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26794481277466</t>
+    <t xml:space="preserve">6.10234546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26794576644897</t>
   </si>
   <si>
     <t xml:space="preserve">6.156165599823</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">6.1768651008606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25138521194458</t>
+    <t xml:space="preserve">6.25138568878174</t>
   </si>
   <si>
     <t xml:space="preserve">6.13132572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15202522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14374542236328</t>
+    <t xml:space="preserve">6.15202569961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14374494552612</t>
   </si>
   <si>
     <t xml:space="preserve">6.07750606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14788579940796</t>
+    <t xml:space="preserve">6.14788627624512</t>
   </si>
   <si>
     <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05266618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96986627578735</t>
+    <t xml:space="preserve">6.05266571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9698657989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.10648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98642635345459</t>
+    <t xml:space="preserve">5.98642587661743</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
@@ -374,31 +374,31 @@
     <t xml:space="preserve">5.95330619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0361065864563</t>
+    <t xml:space="preserve">6.03610563278198</t>
   </si>
   <si>
     <t xml:space="preserve">5.95744657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00298595428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93260622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8498067855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808610916138</t>
+    <t xml:space="preserve">6.00298547744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93260526657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8249659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668615341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84980630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808658599854</t>
   </si>
   <si>
     <t xml:space="preserve">5.75872659683228</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">5.92018604278564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06094598770142</t>
+    <t xml:space="preserve">6.06094551086426</t>
   </si>
   <si>
     <t xml:space="preserve">6.42526531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45010471343994</t>
+    <t xml:space="preserve">6.4501051902771</t>
   </si>
   <si>
     <t xml:space="preserve">6.53290462493896</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29278516769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38386583328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40042543411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2348256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33832550048828</t>
+    <t xml:space="preserve">6.29278564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45838499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38386487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40042495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23482608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33832502365112</t>
   </si>
   <si>
     <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40870523452759</t>
+    <t xml:space="preserve">6.40870428085327</t>
   </si>
   <si>
     <t xml:space="preserve">6.37558460235596</t>
@@ -464,58 +464,58 @@
     <t xml:space="preserve">6.50806474685669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3424654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49150466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3341851234436</t>
+    <t xml:space="preserve">6.34246444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49150514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33418560028076</t>
   </si>
   <si>
     <t xml:space="preserve">6.3714451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30520439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39214563369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18514490127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97400569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01126623153687</t>
+    <t xml:space="preserve">6.30520486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39214468002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18514537811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97400617599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782678604126</t>
+    <t xml:space="preserve">6.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590532302856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28450489044189</t>
+    <t xml:space="preserve">6.36730527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28450584411621</t>
   </si>
   <si>
     <t xml:space="preserve">6.41284513473511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24310493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69850492477417</t>
+    <t xml:space="preserve">6.2431058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194437026978</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">6.6488242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72334480285645</t>
+    <t xml:space="preserve">6.72334384918213</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990440368652</t>
@@ -533,61 +533,61 @@
     <t xml:space="preserve">7.03798389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17874240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384351730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01314353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07938385009766</t>
+    <t xml:space="preserve">7.20358228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384304046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01314401626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07938289642334</t>
   </si>
   <si>
     <t xml:space="preserve">7.02142333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05454397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98830413818359</t>
+    <t xml:space="preserve">7.05454349517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98830366134644</t>
   </si>
   <si>
     <t xml:space="preserve">7.20772314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60102224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0876636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4768214225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48924160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43542242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2781023979187</t>
+    <t xml:space="preserve">7.60102272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414144515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47682189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48924207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43542194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27810287475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.17046356201172</t>
@@ -596,46 +596,46 @@
     <t xml:space="preserve">7.10422325134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94276332855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110404968262</t>
+    <t xml:space="preserve">6.94276428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07110357284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.05868291854858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04212284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00486421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83512449264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894271850586</t>
+    <t xml:space="preserve">7.04212427139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00486373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894367218018</t>
   </si>
   <si>
     <t xml:space="preserve">6.91378402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26982307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306077957153</t>
+    <t xml:space="preserve">6.95932292938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26982259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306125640869</t>
   </si>
   <si>
     <t xml:space="preserve">7.50994157791138</t>
@@ -644,31 +644,31 @@
     <t xml:space="preserve">7.64242219924927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65898180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00674247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03158187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07297992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85356140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25928115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19304084777832</t>
+    <t xml:space="preserve">7.69210243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6589822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00674152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07298183441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85356092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25928020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.193039894104</t>
   </si>
   <si>
     <t xml:space="preserve">8.25514030456543</t>
@@ -689,73 +689,73 @@
     <t xml:space="preserve">8.43729972839355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62773990631104</t>
+    <t xml:space="preserve">8.62773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">8.63601970672607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59462070465088</t>
+    <t xml:space="preserve">8.59461975097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.52837944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03986167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76662111282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96120119094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17648029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51181983947754</t>
+    <t xml:space="preserve">8.32966136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03986072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7666220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96120166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51181888580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.6028995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77678108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85957908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4474573135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.085015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1595363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7556953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2920150756836</t>
+    <t xml:space="preserve">8.77677917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85957813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37293815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0850172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15953540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907341003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894540786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7556924819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920160293579</t>
   </si>
   <si>
     <t xml:space="preserve">10.3499755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5790319442749</t>
+    <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
     <t xml:space="preserve">10.4602613449097</t>
@@ -773,40 +773,40 @@
     <t xml:space="preserve">10.0530500411987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1718196868896</t>
+    <t xml:space="preserve">10.1718215942383</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803045272827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.078501701355</t>
+    <t xml:space="preserve">10.0785007476807</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7062854766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6638689041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6129674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772300720215</t>
+    <t xml:space="preserve">10.7062864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6638669967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6129665374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772291183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.7232532501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6469011306763</t>
+    <t xml:space="preserve">10.646900177002</t>
   </si>
   <si>
     <t xml:space="preserve">10.6299333572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384172439575</t>
+    <t xml:space="preserve">10.6384162902832</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178438186646</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">10.3584594726562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2736225128174</t>
+    <t xml:space="preserve">10.2736234664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.3075580596924</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247661590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78157520294189</t>
+    <t xml:space="preserve">9.83247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78157424926758</t>
   </si>
   <si>
     <t xml:space="preserve">9.61190414428711</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">9.43374919891357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10288715362549</t>
+    <t xml:space="preserve">9.1028881072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.16227436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17924118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19620800018311</t>
+    <t xml:space="preserve">9.17924022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19620704650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.23862648010254</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">9.33194541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317481994629</t>
+    <t xml:space="preserve">9.21317577362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.37436389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954685211182</t>
+    <t xml:space="preserve">9.68825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954675674438</t>
   </si>
   <si>
     <t xml:space="preserve">10.0360822677612</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">10.2227220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2312059402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2821063995361</t>
+    <t xml:space="preserve">10.2312068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2821073532104</t>
   </si>
   <si>
     <t xml:space="preserve">10.2566566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2905912399292</t>
+    <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
     <t xml:space="preserve">10.366943359375</t>
@@ -905,46 +905,46 @@
     <t xml:space="preserve">10.0191164016724</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9682149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89186191558838</t>
+    <t xml:space="preserve">9.96821403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89186096191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.8579273223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74764156341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51010036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56948471069336</t>
+    <t xml:space="preserve">9.74764060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51010227203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522212982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.66280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50161647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39133167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28104305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284778594971</t>
+    <t xml:space="preserve">9.50161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39132976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284587860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.45071601867676</t>
@@ -953,46 +953,46 @@
     <t xml:space="preserve">9.51858329772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469379425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313259124756</t>
+    <t xml:space="preserve">9.27256107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313354492188</t>
   </si>
   <si>
     <t xml:space="preserve">9.84096050262451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67977142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64583683013916</t>
+    <t xml:space="preserve">9.67977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399368286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77309226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79854297637939</t>
+    <t xml:space="preserve">9.75612354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77309322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79854202270508</t>
   </si>
   <si>
     <t xml:space="preserve">9.69673919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67128849029541</t>
+    <t xml:space="preserve">9.67128944396973</t>
   </si>
   <si>
     <t xml:space="preserve">9.62887096405029</t>
@@ -1001,19 +1001,19 @@
     <t xml:space="preserve">9.79005813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73067283630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47616577148438</t>
+    <t xml:space="preserve">9.73067378997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47616672515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.1368236541748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72112655639648</t>
+    <t xml:space="preserve">9.00108528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72112560272217</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">8.07637500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32664012908936</t>
+    <t xml:space="preserve">8.32663917541504</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182476043701</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">8.12303447723389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62780666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33088111877441</t>
+    <t xml:space="preserve">8.6278076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33088207244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.34360694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.195143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2714958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37329959869385</t>
+    <t xml:space="preserve">8.19514560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27149772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37330055236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.31391525268555</t>
@@ -1055,91 +1055,91 @@
     <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09334087371826</t>
+    <t xml:space="preserve">8.09334182739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.03819847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85155916213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82610940933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91094350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85580158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881412506104</t>
+    <t xml:space="preserve">7.85156011581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82610893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065870285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91094446182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85580110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957603931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97881317138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123069763184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.01274681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452995300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.16121006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1484842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05092334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08061599731445</t>
+    <t xml:space="preserve">8.14848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">8.17393589019775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22483730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2884635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42420291900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56842231750488</t>
+    <t xml:space="preserve">8.22483825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28846454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42420101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5684232711792</t>
   </si>
   <si>
     <t xml:space="preserve">8.5175199508667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73809337615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55145454406738</t>
+    <t xml:space="preserve">8.73809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.48358631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50055408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58538913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
+    <t xml:space="preserve">8.50055313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58538818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.4581356048584</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">8.20362949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01698970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99153900146484</t>
+    <t xml:space="preserve">8.01698780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153804779053</t>
   </si>
   <si>
     <t xml:space="preserve">7.91518497467041</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97457122802734</t>
+    <t xml:space="preserve">7.97457075119019</t>
   </si>
   <si>
     <t xml:space="preserve">8.3223991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90776538848877</t>
+    <t xml:space="preserve">8.90776634216309</t>
   </si>
   <si>
     <t xml:space="preserve">8.75506114959717</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">8.77202892303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61932468414307</t>
+    <t xml:space="preserve">8.61932277679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36588096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24710845947266</t>
+    <t xml:space="preserve">9.36587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24710941314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.12833976745605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11137199401855</t>
+    <t xml:space="preserve">9.11137294769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.0435037612915</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">9.26407623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41678142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142391204834</t>
+    <t xml:space="preserve">9.41678047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142372131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.5705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6723508834839</t>
+    <t xml:space="preserve">10.6723518371582</t>
   </si>
   <si>
     <t xml:space="preserve">10.6214504241943</t>
@@ -1235,67 +1235,67 @@
     <t xml:space="preserve">10.9607944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4358730316162</t>
+    <t xml:space="preserve">11.4358749389648</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680057525635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4698085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.543098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8729009628296</t>
+    <t xml:space="preserve">11.4698104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8729019165039</t>
   </si>
   <si>
     <t xml:space="preserve">11.836256980896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4148426055908</t>
+    <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.3049068450928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.286584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9567823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4987239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6086568832397</t>
+    <t xml:space="preserve">11.2865839004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9567813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4987230300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002687454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6086578369141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4804000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689186096191</t>
+    <t xml:space="preserve">10.4804010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689205169678</t>
   </si>
   <si>
     <t xml:space="preserve">10.004017829895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98569583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0589847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788543701172</t>
+    <t xml:space="preserve">9.98569488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058985710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788534164429</t>
   </si>
   <si>
     <t xml:space="preserve">10.0773077011108</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">10.2238874435425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2605314254761</t>
+    <t xml:space="preserve">10.2605323791504</t>
   </si>
   <si>
     <t xml:space="preserve">10.1322755813599</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4071102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3154993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4437561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3338212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2055654525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0956315994263</t>
+    <t xml:space="preserve">10.4071092605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3154973983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4437551498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3338203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2055644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.095630645752</t>
   </si>
   <si>
     <t xml:space="preserve">9.78415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80247211456299</t>
+    <t xml:space="preserve">9.8024730682373</t>
   </si>
   <si>
     <t xml:space="preserve">9.71086120605469</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">9.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67421531677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918319702148</t>
+    <t xml:space="preserve">9.67421627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918224334717</t>
   </si>
   <si>
     <t xml:space="preserve">9.65589332580566</t>
@@ -1355,55 +1355,55 @@
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56428050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30776882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36273574829102</t>
+    <t xml:space="preserve">9.69253730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56428146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30776786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2528018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36273384094238</t>
   </si>
   <si>
     <t xml:space="preserve">9.32609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2711238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06957721710205</t>
+    <t xml:space="preserve">9.27112293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06957626342773</t>
   </si>
   <si>
     <t xml:space="preserve">9.08789920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93215847015381</t>
+    <t xml:space="preserve">8.93215942382812</t>
   </si>
   <si>
     <t xml:space="preserve">8.87719249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03293228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95964241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97796535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94132041931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51990604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28171539306641</t>
+    <t xml:space="preserve">9.03293132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95964336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97796630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94132137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51990699768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.92299747467041</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">8.7031307220459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63900184631348</t>
+    <t xml:space="preserve">8.63900089263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.65732383728027</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">8.44661617279053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39938068389893</t>
+    <t xml:space="preserve">9.39937973022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.3810567855835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19783401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00544929504395</t>
+    <t xml:space="preserve">9.19783306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00545024871826</t>
   </si>
   <si>
     <t xml:space="preserve">9.14286613464355</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">9.12454414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04209327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96880531311035</t>
+    <t xml:space="preserve">9.04209423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96880435943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.99628734588623</t>
@@ -1457,31 +1457,31 @@
     <t xml:space="preserve">8.88635349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86803245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78558158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83138561248779</t>
+    <t xml:space="preserve">8.86803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7855806350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
     <t xml:space="preserve">8.84054660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77641868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71229076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59319496154785</t>
+    <t xml:space="preserve">8.7764196395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.40997123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30919742584229</t>
+    <t xml:space="preserve">8.3091983795166</t>
   </si>
   <si>
     <t xml:space="preserve">8.2450704574585</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">7.74120426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70455980300903</t>
+    <t xml:space="preserve">7.70455932617188</t>
   </si>
   <si>
     <t xml:space="preserve">7.68623828887939</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">7.55798101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59462642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49385213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159923553467</t>
+    <t xml:space="preserve">7.59462594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938530921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159875869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.10908269882202</t>
@@ -1523,40 +1523,40 @@
     <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30146741867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31978940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48469161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42056322097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7686882019043</t>
+    <t xml:space="preserve">7.30146789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31978988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48469209671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42056369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76868867874146</t>
   </si>
   <si>
     <t xml:space="preserve">7.80533361434937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69539833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45720863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56714296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121750831604</t>
+    <t xml:space="preserve">7.69539928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45720815658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5854640007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56714248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51217555999756</t>
   </si>
   <si>
     <t xml:space="preserve">7.22817802429199</t>
@@ -1568,58 +1568,58 @@
     <t xml:space="preserve">7.15488862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06327724456787</t>
+    <t xml:space="preserve">7.06327676773071</t>
   </si>
   <si>
     <t xml:space="preserve">7.05411529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43888568878174</t>
+    <t xml:space="preserve">7.43888521194458</t>
   </si>
   <si>
     <t xml:space="preserve">7.53965759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53049802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47552967071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33811235427856</t>
+    <t xml:space="preserve">7.53049659729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47553062438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33811283111572</t>
   </si>
   <si>
     <t xml:space="preserve">7.29230690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2831449508667</t>
+    <t xml:space="preserve">7.28314542770386</t>
   </si>
   <si>
     <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24650001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27398443222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35643529891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707586288452</t>
+    <t xml:space="preserve">7.24650049209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2739839553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35643482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707681655884</t>
   </si>
   <si>
     <t xml:space="preserve">7.72288274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04352283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37332725524902</t>
+    <t xml:space="preserve">7.86946153640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04352378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37332630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.39164924621582</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.49242305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40081119537354</t>
+    <t xml:space="preserve">8.40081024169922</t>
   </si>
   <si>
     <t xml:space="preserve">8.3458423614502</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377033233643</t>
+    <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.13370513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73977470397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10622215270996</t>
+    <t xml:space="preserve">8.73977375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10622119903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.05125427246094</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648483276367</t>
+    <t xml:space="preserve">8.66648578643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.8588695526123</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">8.91383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90467739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84970760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80390357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81306457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58403491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68480682373047</t>
+    <t xml:space="preserve">8.90467548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84970855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80390167236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.813063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58403396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68480777740479</t>
   </si>
   <si>
     <t xml:space="preserve">8.25423145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248920440674</t>
+    <t xml:space="preserve">8.38248825073242</t>
   </si>
   <si>
     <t xml:space="preserve">8.27255344390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12597370147705</t>
+    <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.26339244842529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23590850830078</t>
+    <t xml:space="preserve">8.2359094619751</t>
   </si>
   <si>
     <t xml:space="preserve">8.43745422363281</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">8.45577716827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47410106658936</t>
+    <t xml:space="preserve">8.47409915924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.50158309936523</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">8.46493816375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51074504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822898864746</t>
+    <t xml:space="preserve">8.51074409484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.62067890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61151790618896</t>
+    <t xml:space="preserve">8.61151885986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.54738903045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21530723571777</t>
+    <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.70226860046387</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">8.18923187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89883279800415</t>
+    <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
     <t xml:space="preserve">8.06339263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29571056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09243202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0537109375</t>
+    <t xml:space="preserve">7.98595380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29571151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09243106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0343542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05371189117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.02467346191406</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">8.15051174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97627305984497</t>
+    <t xml:space="preserve">7.97627258300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.96659183502197</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">7.92787313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">8.073073387146</t>
+    <t xml:space="preserve">8.07307243347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.08275318145752</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">7.90851402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93755292892456</t>
+    <t xml:space="preserve">7.93755388259888</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13115215301514</t>
+    <t xml:space="preserve">8.11179256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13115310668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.04403305053711</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">7.99563360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00531387329102</t>
+    <t xml:space="preserve">8.0053129196167</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87947416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91819286346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95691394805908</t>
+    <t xml:space="preserve">7.86979389190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87947368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91819334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95691251754761</t>
   </si>
   <si>
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33443164825439</t>
+    <t xml:space="preserve">8.33442974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">8.22795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45059013366699</t>
+    <t xml:space="preserve">8.45058917999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.52803039550781</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">8.78938865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14754676818848</t>
+    <t xml:space="preserve">9.14754581451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.13786602020264</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">9.48634433746338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45730400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44762420654297</t>
+    <t xml:space="preserve">9.45730495452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44762516021729</t>
   </si>
   <si>
     <t xml:space="preserve">9.55410385131836</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">10.3188190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0477809906006</t>
+    <t xml:space="preserve">10.0477819442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98970127105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95098114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60250282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6799430847168</t>
+    <t xml:space="preserve">9.98970031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95098209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60250377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67994403839111</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218357086182</t>
@@ -1940,46 +1940,46 @@
     <t xml:space="preserve">9.71866226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50570297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58314323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8735408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40890598297119</t>
+    <t xml:space="preserve">9.50570392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58314418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87354183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40890407562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.3508243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43794345855713</t>
+    <t xml:space="preserve">9.43794441223145</t>
   </si>
   <si>
     <t xml:space="preserve">9.37986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33146476745605</t>
+    <t xml:space="preserve">9.33146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.77674293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6412239074707</t>
+    <t xml:space="preserve">9.64122295379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.66058254241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11850643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09914588928223</t>
+    <t xml:space="preserve">9.11850547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09914684295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.08946704864502</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16690635681152</t>
+    <t xml:space="preserve">9.16690540313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.07978630065918</t>
@@ -2000,25 +2000,25 @@
     <t xml:space="preserve">9.0120267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92490673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94426727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85714817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72162818908691</t>
+    <t xml:space="preserve">8.92490768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9442663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85714721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7216272354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.77002906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9345874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99266624450684</t>
+    <t xml:space="preserve">8.93458652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99266719818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.96362781524658</t>
@@ -2030,40 +2030,40 @@
     <t xml:space="preserve">9.05074691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97330760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32474994659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84075403213501</t>
+    <t xml:space="preserve">8.97330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79906940460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32475185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84075450897217</t>
   </si>
   <si>
     <t xml:space="preserve">7.79235410690308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60843515396118</t>
+    <t xml:space="preserve">7.60843563079834</t>
   </si>
   <si>
     <t xml:space="preserve">7.53099584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61811542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34707641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52428150177002</t>
+    <t xml:space="preserve">7.61811494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52428102493286</t>
   </si>
   <si>
     <t xml:space="preserve">6.58236169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44684171676636</t>
+    <t xml:space="preserve">6.44684219360352</t>
   </si>
   <si>
     <t xml:space="preserve">5.14004945755005</t>
@@ -2081,40 +2081,40 @@
     <t xml:space="preserve">4.48181390762329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52053356170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8399715423584</t>
+    <t xml:space="preserve">4.52053308486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83997201919556</t>
   </si>
   <si>
     <t xml:space="preserve">5.13037014007568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51756763458252</t>
+    <t xml:space="preserve">5.51756715774536</t>
   </si>
   <si>
     <t xml:space="preserve">6.04028415679932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00156402587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98220443725586</t>
+    <t xml:space="preserve">6.00156450271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98220491409302</t>
   </si>
   <si>
     <t xml:space="preserve">5.88540506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79828548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96284484863281</t>
+    <t xml:space="preserve">5.79828596115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96284437179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.99188470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15644407272339</t>
+    <t xml:space="preserve">6.15644454956055</t>
   </si>
   <si>
     <t xml:space="preserve">6.38876247406006</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">6.46620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22420358657837</t>
+    <t xml:space="preserve">6.43716192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.42748212814331</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">6.5339617729187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54364204406738</t>
+    <t xml:space="preserve">6.54364156723022</t>
   </si>
   <si>
     <t xml:space="preserve">7.28899717330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67619514465332</t>
+    <t xml:space="preserve">7.67619466781616</t>
   </si>
   <si>
     <t xml:space="preserve">7.55035543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491432189941</t>
+    <t xml:space="preserve">7.58907508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71491479873657</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3954758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43419599533081</t>
+    <t xml:space="preserve">7.39547634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43419551849365</t>
   </si>
   <si>
     <t xml:space="preserve">7.19219732284546</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44387626647949</t>
+    <t xml:space="preserve">7.44387578964233</t>
   </si>
   <si>
     <t xml:space="preserve">7.49227571487427</t>
@@ -2180,25 +2180,25 @@
     <t xml:space="preserve">7.4632363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69555425643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85043382644653</t>
+    <t xml:space="preserve">7.69555473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85043287277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56003522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5987548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6568341255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50195598602295</t>
+    <t xml:space="preserve">7.56003570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59875535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65683460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50195550918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.31803703308105</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">7.30835723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23091745376587</t>
+    <t xml:space="preserve">7.23091793060303</t>
   </si>
   <si>
     <t xml:space="preserve">7.521315574646</t>
@@ -2228,22 +2228,22 @@
     <t xml:space="preserve">7.35675668716431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64715480804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57939577102661</t>
+    <t xml:space="preserve">7.45355653762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64715528488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
     <t xml:space="preserve">7.41483640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
+    <t xml:space="preserve">7.29867649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995683670044</t>
   </si>
   <si>
     <t xml:space="preserve">7.47291612625122</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">7.88915300369263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83107376098633</t>
+    <t xml:space="preserve">7.83107471466064</t>
   </si>
   <si>
     <t xml:space="preserve">7.74395418167114</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">7.73427391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36643743515015</t>
+    <t xml:space="preserve">7.36643648147583</t>
   </si>
   <si>
     <t xml:space="preserve">7.26963758468628</t>
@@ -2273,37 +2273,37 @@
     <t xml:space="preserve">7.21155738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16315793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12443780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22123718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70523500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7245945930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48259592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6665153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42451620101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14379787445068</t>
+    <t xml:space="preserve">7.16315841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12443828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22123765945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48259544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66651487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42451667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">7.04699897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10507869720459</t>
+    <t xml:space="preserve">7.10507822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.11475801467896</t>
@@ -2312,19 +2312,19 @@
     <t xml:space="preserve">7.17283773422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25027751922607</t>
+    <t xml:space="preserve">7.25027704238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.24059724807739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2018780708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18251752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.134117603302</t>
+    <t xml:space="preserve">7.20187759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18251800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13411808013916</t>
   </si>
   <si>
     <t xml:space="preserve">7.15347814559937</t>
@@ -2333,40 +2333,40 @@
     <t xml:space="preserve">7.62779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02763843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0760383605957</t>
+    <t xml:space="preserve">7.02763891220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07603788375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.01795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96955919265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89211940765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97923898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06635904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05667877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8727593421936</t>
+    <t xml:space="preserve">6.96955871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89211893081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97923946380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06635856628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0566782951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87275981903076</t>
   </si>
   <si>
     <t xml:space="preserve">6.94051933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90179967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82435941696167</t>
+    <t xml:space="preserve">6.90179920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436037063599</t>
   </si>
   <si>
     <t xml:space="preserve">6.80500030517578</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">6.77595996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76628017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83403921127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564023971558</t>
+    <t xml:space="preserve">6.76627969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83403968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">6.81467962265015</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63076114654541</t>
+    <t xml:space="preserve">6.63076066970825</t>
   </si>
   <si>
     <t xml:space="preserve">6.67916107177734</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067165374756</t>
+    <t xml:space="preserve">7.22067213058472</t>
   </si>
   <si>
     <t xml:space="preserve">7.28879117965698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17201471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18174648284912</t>
+    <t xml:space="preserve">7.17201519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18174600601196</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">7.49315023422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59046411514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5223445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46395587921143</t>
+    <t xml:space="preserve">7.59046363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52234363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46395635604858</t>
   </si>
   <si>
     <t xml:space="preserve">7.70724010467529</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00891208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09649467468262</t>
+    <t xml:space="preserve">8.0089111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0964937210083</t>
   </si>
   <si>
     <t xml:space="preserve">8.12568950653076</t>
@@ -2471,16 +2471,16 @@
     <t xml:space="preserve">8.13541889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9699854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89213562011719</t>
+    <t xml:space="preserve">7.96998643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89213514328003</t>
   </si>
   <si>
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019493103027</t>
+    <t xml:space="preserve">7.60019540786743</t>
   </si>
   <si>
     <t xml:space="preserve">7.57100105285645</t>
@@ -2501,46 +2501,46 @@
     <t xml:space="preserve">7.73643398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69750881195068</t>
+    <t xml:space="preserve">7.69750833511353</t>
   </si>
   <si>
     <t xml:space="preserve">7.6683144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82401609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64885187149048</t>
+    <t xml:space="preserve">7.82401657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64885234832764</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60992622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63912010192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62938928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56126976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84347915649414</t>
+    <t xml:space="preserve">7.60992670059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63912057876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6293888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56126928329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8434796333313</t>
   </si>
   <si>
     <t xml:space="preserve">7.80455446243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79482221603394</t>
+    <t xml:space="preserve">7.79482269287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.01864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94079256057739</t>
+    <t xml:space="preserve">7.94079303741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112243652344</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0770320892334</t>
+    <t xml:space="preserve">8.07703304290771</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33977794647217</t>
+    <t xml:space="preserve">8.33977890014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.36897373199463</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">8.5344066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74849510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67064476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68037700653076</t>
+    <t xml:space="preserve">8.74849605560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67064380645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68037605285645</t>
   </si>
   <si>
     <t xml:space="preserve">8.81661605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02097415924072</t>
+    <t xml:space="preserve">9.02097511291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.97231769561768</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">9.04043674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75822734832764</t>
+    <t xml:space="preserve">8.75822830200195</t>
   </si>
   <si>
     <t xml:space="preserve">8.80688381195068</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789890289307</t>
+    <t xml:space="preserve">8.40789794921875</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">8.43709278106689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46628570556641</t>
+    <t xml:space="preserve">8.46628665924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.4565544128418</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">8.48574924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15488243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23273468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17434501647949</t>
+    <t xml:space="preserve">8.15488338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23273372650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17434597015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.14515113830566</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">8.25219631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22300243377686</t>
+    <t xml:space="preserve">8.22300148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.33004760742188</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">8.64145088195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58306217193604</t>
+    <t xml:space="preserve">8.58306121826172</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2672,37 +2672,37 @@
     <t xml:space="preserve">8.60252571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83607769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70956993103027</t>
+    <t xml:space="preserve">8.83607864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70957088470459</t>
   </si>
   <si>
     <t xml:space="preserve">8.84581089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0112419128418</t>
+    <t xml:space="preserve">9.01124286651611</t>
   </si>
   <si>
     <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75082683563232</t>
+    <t xml:space="preserve">9.75082588195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152446746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3541717529297</t>
+    <t xml:space="preserve">10.3152465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3541707992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.3736333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77028942108154</t>
+    <t xml:space="preserve">9.77028846740723</t>
   </si>
   <si>
     <t xml:space="preserve">9.50754261016846</t>
@@ -2723,19 +2723,19 @@
     <t xml:space="preserve">8.85554122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90419769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14748096466064</t>
+    <t xml:space="preserve">8.90419673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14748191833496</t>
   </si>
   <si>
     <t xml:space="preserve">9.32264614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05990028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08909511566162</t>
+    <t xml:space="preserve">9.05989933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08909320831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.34210968017578</t>
@@ -2747,43 +2747,43 @@
     <t xml:space="preserve">9.24479579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93339157104492</t>
+    <t xml:space="preserve">8.93339252471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19613742828369</t>
+    <t xml:space="preserve">9.19613838195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.36157131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62431812286377</t>
+    <t xml:space="preserve">9.62431907653809</t>
   </si>
   <si>
     <t xml:space="preserve">9.57566165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5367374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8286771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86760234832764</t>
+    <t xml:space="preserve">9.53673648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82867813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86760330200195</t>
   </si>
   <si>
     <t xml:space="preserve">9.71190071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67297554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61458778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59512519836426</t>
+    <t xml:space="preserve">9.67297458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61458683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59512424468994</t>
   </si>
   <si>
     <t xml:space="preserve">9.45888519287109</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">9.17667579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21560192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20586967468262</t>
+    <t xml:space="preserve">9.21560096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20587062835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.0015115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98204898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56359958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49548053741455</t>
+    <t xml:space="preserve">8.98204803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56360054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49547958374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795864105225</t>
+    <t xml:space="preserve">8.76795768737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.41762924194336</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">8.37870311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39816570281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47601890563965</t>
+    <t xml:space="preserve">8.71930122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39816665649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47601795196533</t>
   </si>
   <si>
     <t xml:space="preserve">8.79715251922607</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">8.95285415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04783916473389</t>
+    <t xml:space="preserve">8.04783821105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.1646146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87500381469727</t>
+    <t xml:space="preserve">8.87500286102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.03070545196533</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">9.49781131744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80921363830566</t>
+    <t xml:space="preserve">9.80921459197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51727294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47834873199463</t>
+    <t xml:space="preserve">9.98437881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51727390289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47834777832031</t>
   </si>
   <si>
     <t xml:space="preserve">9.26425838470459</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44915390014648</t>
+    <t xml:space="preserve">9.4491548538208</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136329650879</t>
+    <t xml:space="preserve">9.73136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038414001465</t>
+    <t xml:space="preserve">10.0038423538208</t>
   </si>
   <si>
     <t xml:space="preserve">10.1595430374146</t>
@@ -2921,40 +2921,40 @@
     <t xml:space="preserve">10.02330493927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0427675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622301101685</t>
+    <t xml:space="preserve">10.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1400804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90652942657471</t>
+    <t xml:space="preserve">9.90652847290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33237743377686</t>
+    <t xml:space="preserve">9.33237838745117</t>
   </si>
   <si>
     <t xml:space="preserve">9.25452613830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63404941558838</t>
+    <t xml:space="preserve">9.40049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48807907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6340503692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347091674805</t>
+    <t xml:space="preserve">10.3347072601318</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440832138062</t>
+    <t xml:space="preserve">11.4440841674805</t>
   </si>
   <si>
     <t xml:space="preserve">11.4051580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1326789855957</t>
+    <t xml:space="preserve">11.13267993927</t>
   </si>
   <si>
     <t xml:space="preserve">11.2883825302124</t>
@@ -3002,37 +3002,37 @@
     <t xml:space="preserve">11.3662328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6387119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0668916702271</t>
+    <t xml:space="preserve">11.638710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0668907165527</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.572922706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4756078720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1836671829224</t>
+    <t xml:space="preserve">12.5729217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4756088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1836681365967</t>
   </si>
   <si>
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2299938201904</t>
+    <t xml:space="preserve">11.6970996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299928665161</t>
   </si>
   <si>
     <t xml:space="preserve">10.8991279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8407402038574</t>
+    <t xml:space="preserve">10.8407392501831</t>
   </si>
   <si>
     <t xml:space="preserve">10.976978302002</t>
@@ -3050,19 +3050,19 @@
     <t xml:space="preserve">10.7434253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9575157165527</t>
+    <t xml:space="preserve">10.9575147628784</t>
   </si>
   <si>
     <t xml:space="preserve">10.198468208313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4709482192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132164001465</t>
+    <t xml:space="preserve">10.6071863174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">10.9380521774292</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9185905456543</t>
+    <t xml:space="preserve">10.91858959198</t>
   </si>
   <si>
     <t xml:space="preserve">11.2105321884155</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">11.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9306516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.852801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8917264938354</t>
+    <t xml:space="preserve">11.9695777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9306526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8528003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8917274475098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1252784729004</t>
@@ -3110,31 +3110,31 @@
     <t xml:space="preserve">12.6507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843259811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923843383789</t>
+    <t xml:space="preserve">12.8259382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923833847046</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8648633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.514533996582</t>
+    <t xml:space="preserve">12.5145330429077</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977565765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4366827011108</t>
+    <t xml:space="preserve">12.4366817474365</t>
   </si>
   <si>
     <t xml:space="preserve">12.2615184783936</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">12.2809810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447420120239</t>
+    <t xml:space="preserve">12.1447410583496</t>
   </si>
   <si>
     <t xml:space="preserve">12.0474281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3393688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5534582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4950714111328</t>
+    <t xml:space="preserve">12.3393697738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4950704574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">12.7870121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225933074951</t>
+    <t xml:space="preserve">12.2225923538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.1762657165527</t>
@@ -3176,22 +3176,22 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9427146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1373405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0789527893066</t>
+    <t xml:space="preserve">13.0594911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9427137374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1373414993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0789518356323</t>
   </si>
   <si>
     <t xml:space="preserve">13.4487447738647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.468207359314</t>
+    <t xml:space="preserve">13.4682064056396</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">13.9742374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3051052093506</t>
+    <t xml:space="preserve">14.3051042556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.616509437561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7527475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1809282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9473743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9279117584229</t>
+    <t xml:space="preserve">14.7527465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1809272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9473733901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9279127120972</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621215820312</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">16.893648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9909610748291</t>
+    <t xml:space="preserve">16.9909591674805</t>
   </si>
   <si>
     <t xml:space="preserve">17.0298862457275</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4191398620605</t>
+    <t xml:space="preserve">17.5359153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4191417694092</t>
   </si>
   <si>
     <t xml:space="preserve">17.788932800293</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">17.7694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7500076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2949619293213</t>
+    <t xml:space="preserve">17.7500057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2949638366699</t>
   </si>
   <si>
     <t xml:space="preserve">18.2755012512207</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0419483184814</t>
+    <t xml:space="preserve">19.0345478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0419502258301</t>
   </si>
   <si>
     <t xml:space="preserve">18.003023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.547981262207</t>
+    <t xml:space="preserve">18.5479774475098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6842193603516</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">19.9979515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7060127258301</t>
+    <t xml:space="preserve">19.7060108184814</t>
   </si>
   <si>
     <t xml:space="preserve">19.8519821166992</t>
@@ -3308,37 +3308,37 @@
     <t xml:space="preserve">19.7546672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.511381149292</t>
+    <t xml:space="preserve">19.5113830566406</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0734748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7036819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.898307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009948730469</t>
+    <t xml:space="preserve">19.0734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7036800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8983097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009929656982</t>
   </si>
   <si>
     <t xml:space="preserve">18.5090522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8788433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1902503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9761600494385</t>
+    <t xml:space="preserve">18.8788452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1902484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9761581420898</t>
   </si>
   <si>
     <t xml:space="preserve">18.8593826293945</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4701271057129</t>
+    <t xml:space="preserve">18.4701290130615</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486362457275</t>
+    <t xml:space="preserve">19.2486381530762</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">18.9589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8429946899414</t>
+    <t xml:space="preserve">19.84299659729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4815082550049</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">21.4638347625732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.004114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8567657470703</t>
+    <t xml:space="preserve">22.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">21.9549980163574</t>
@@ -3422,10 +3422,10 @@
     <t xml:space="preserve">22.1023464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2988128662109</t>
+    <t xml:space="preserve">22.3479290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2988109588623</t>
   </si>
   <si>
     <t xml:space="preserve">22.4461612701416</t>
@@ -3449,16 +3449,16 @@
     <t xml:space="preserve">21.6111831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3656024932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3832759857178</t>
+    <t xml:space="preserve">21.3656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3832740783691</t>
   </si>
   <si>
     <t xml:space="preserve">20.9235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5306243896484</t>
+    <t xml:space="preserve">20.5306224822998</t>
   </si>
   <si>
     <t xml:space="preserve">20.1376934051514</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">17.8194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748062133789</t>
+    <t xml:space="preserve">18.0748081207275</t>
   </si>
   <si>
     <t xml:space="preserve">18.3302116394043</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">18.4873847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5463237762451</t>
+    <t xml:space="preserve">18.5463218688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.2712726593018</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">17.9962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9569282531738</t>
+    <t xml:space="preserve">17.9569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">18.015869140625</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">17.7997570037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4854125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5836429595947</t>
+    <t xml:space="preserve">17.4854106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5836448669434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5050582885742</t>
@@ -3539,16 +3539,16 @@
     <t xml:space="preserve">17.6229381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.60329246521</t>
+    <t xml:space="preserve">17.6032905578613</t>
   </si>
   <si>
     <t xml:space="preserve">17.0531883239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0335426330566</t>
+    <t xml:space="preserve">16.7388439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.033540725708</t>
   </si>
   <si>
     <t xml:space="preserve">16.7191963195801</t>
@@ -3575,34 +3575,34 @@
     <t xml:space="preserve">16.0512142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2673263549805</t>
+    <t xml:space="preserve">16.2673282623291</t>
   </si>
   <si>
     <t xml:space="preserve">16.1101551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0905055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5423774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3459129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2869739532471</t>
+    <t xml:space="preserve">15.8547487258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0905075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5423793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.345911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2869720458984</t>
   </si>
   <si>
     <t xml:space="preserve">16.1494483947754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6189908981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8154573440552</t>
+    <t xml:space="preserve">15.6189918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8154563903809</t>
   </si>
   <si>
     <t xml:space="preserve">15.5796985626221</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">16.3852062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4794921875</t>
+    <t xml:space="preserve">14.4794931411743</t>
   </si>
   <si>
     <t xml:space="preserve">14.4401998519897</t>
@@ -3623,37 +3623,37 @@
     <t xml:space="preserve">14.7348976135254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9903020858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6563110351562</t>
+    <t xml:space="preserve">14.9903030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6563119888306</t>
   </si>
   <si>
     <t xml:space="preserve">14.636664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580778121948</t>
+    <t xml:space="preserve">14.5580787658691</t>
   </si>
   <si>
     <t xml:space="preserve">14.5384321212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4991397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6956052780151</t>
+    <t xml:space="preserve">14.4991388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6956043243408</t>
   </si>
   <si>
     <t xml:space="preserve">14.9510097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8527765274048</t>
+    <t xml:space="preserve">14.8527774810791</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7958097457886</t>
+    <t xml:space="preserve">15.7958106994629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8743963241577</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">15.5404052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2653541564941</t>
+    <t xml:space="preserve">15.2653532028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.0688886642456</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">16.1298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8567237854004</t>
+    <t xml:space="preserve">16.8567218780518</t>
   </si>
   <si>
     <t xml:space="preserve">16.7977828979492</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">17.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8370742797852</t>
+    <t xml:space="preserve">16.8370761871338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6209659576416</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">16.5816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9549541473389</t>
+    <t xml:space="preserve">16.9549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">17.1907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1514205932617</t>
+    <t xml:space="preserve">17.1514186859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6425838470459</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">17.7801094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5247058868408</t>
+    <t xml:space="preserve">17.5247039794922</t>
   </si>
   <si>
     <t xml:space="preserve">18.2123336791992</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">19.3911247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465301513672</t>
+    <t xml:space="preserve">19.6465282440186</t>
   </si>
   <si>
     <t xml:space="preserve">19.4107723236084</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">19.4304180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697093963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6838493347168</t>
+    <t xml:space="preserve">19.4697113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6838512420654</t>
   </si>
   <si>
     <t xml:space="preserve">18.6052646636963</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">19.7938785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394611358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2359275817871</t>
+    <t xml:space="preserve">20.0394592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3341598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8253211975098</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">21.1200199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779727935791</t>
+    <t xml:space="preserve">20.6779708862305</t>
   </si>
   <si>
     <t xml:space="preserve">20.7270908355713</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">20.579740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2005786895752</t>
+    <t xml:space="preserve">22.2005805969238</t>
   </si>
   <si>
     <t xml:space="preserve">21.5620670318604</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">22.3970432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0532302856445</t>
+    <t xml:space="preserve">22.0532321929932</t>
   </si>
   <si>
     <t xml:space="preserve">21.9058799743652</t>
@@ -71113,7 +71113,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6910185185</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>6790</v>
@@ -71134,6 +71134,32 @@
         <v>1513</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6911574074</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>8156</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>30.7000007629395</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>30.9500007629395</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41009426116943</t>
+    <t xml:space="preserve">6.41009378433228</t>
   </si>
   <si>
     <t xml:space="preserve">TXT.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">6.39007520675659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39808320999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22992277145386</t>
+    <t xml:space="preserve">6.39808225631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2299222946167</t>
   </si>
   <si>
     <t xml:space="preserve">6.26996088027954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09379386901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578634262085</t>
+    <t xml:space="preserve">6.0937933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12582397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578586578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.92563390731812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85356521606445</t>
+    <t xml:space="preserve">5.85356426239014</t>
   </si>
   <si>
     <t xml:space="preserve">5.76548099517822</t>
@@ -77,52 +77,52 @@
     <t xml:space="preserve">5.94565296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72143936157227</t>
+    <t xml:space="preserve">5.74946641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72143983840942</t>
   </si>
   <si>
     <t xml:space="preserve">5.72544288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99770212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88559579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94164896011353</t>
+    <t xml:space="preserve">5.74145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88559532165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94164943695068</t>
   </si>
   <si>
     <t xml:space="preserve">6.00571012496948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84956121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77749300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17386913299561</t>
+    <t xml:space="preserve">5.84956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77749347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17386960983276</t>
   </si>
   <si>
     <t xml:space="preserve">6.14984703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20589923858643</t>
+    <t xml:space="preserve">6.20589971542358</t>
   </si>
   <si>
     <t xml:space="preserve">6.29398393630981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22191572189331</t>
+    <t xml:space="preserve">6.22191476821899</t>
   </si>
   <si>
     <t xml:space="preserve">6.19789266586304</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">6.406090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45813941955566</t>
+    <t xml:space="preserve">6.45813989639282</t>
   </si>
   <si>
     <t xml:space="preserve">6.41409826278687</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">6.23793029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07777786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19388914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14183902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15385007858276</t>
+    <t xml:space="preserve">6.07777833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25394582748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19388866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14183855056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15385055541992</t>
   </si>
   <si>
     <t xml:space="preserve">6.10980844497681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1138129234314</t>
+    <t xml:space="preserve">6.11381244659424</t>
   </si>
   <si>
     <t xml:space="preserve">5.98969459533691</t>
@@ -179,43 +179,43 @@
     <t xml:space="preserve">6.0177206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94965648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05375576019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15785455703735</t>
+    <t xml:space="preserve">5.94965600967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05375480651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578540802002</t>
   </si>
   <si>
     <t xml:space="preserve">6.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18187713623047</t>
+    <t xml:space="preserve">6.18187665939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.12181997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21390724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03373575210571</t>
+    <t xml:space="preserve">6.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03373622894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.1018009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01371669769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95766448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93764448165894</t>
+    <t xml:space="preserve">6.01371717453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95766401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93764495849609</t>
   </si>
   <si>
     <t xml:space="preserve">6.11781597137451</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">6.07377433776855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06977033615112</t>
+    <t xml:space="preserve">6.06977081298828</t>
   </si>
   <si>
     <t xml:space="preserve">6.19342565536499</t>
@@ -239,79 +239,79 @@
     <t xml:space="preserve">6.16030597686768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20998573303223</t>
+    <t xml:space="preserve">6.20998620986938</t>
   </si>
   <si>
     <t xml:space="preserve">6.09406614303589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1685848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18928527832031</t>
+    <t xml:space="preserve">6.16858530044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18928575515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.20170545578003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11890602111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28864479064941</t>
+    <t xml:space="preserve">6.11890506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28864526748657</t>
   </si>
   <si>
     <t xml:space="preserve">6.19756555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1271858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1396050453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11062479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04438638687134</t>
+    <t xml:space="preserve">6.12718534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11062526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04438591003418</t>
   </si>
   <si>
     <t xml:space="preserve">5.89534616470337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90776634216309</t>
+    <t xml:space="preserve">5.90776681900024</t>
   </si>
   <si>
     <t xml:space="preserve">5.8125467300415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99470567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04024505615234</t>
+    <t xml:space="preserve">5.99470615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08578538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04024600982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.94502592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.961585521698</t>
+    <t xml:space="preserve">5.96158599853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.85394620895386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78770589828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8622260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91190624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86636590957642</t>
+    <t xml:space="preserve">5.78770637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91190528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">6.12304592132568</t>
@@ -329,46 +329,46 @@
     <t xml:space="preserve">6.156165599823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0319652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09820556640625</t>
+    <t xml:space="preserve">6.03196477890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09820461273193</t>
   </si>
   <si>
     <t xml:space="preserve">6.1768651008606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25138568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13132572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15202569961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14374589920044</t>
+    <t xml:space="preserve">6.25138521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13132619857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15202522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1437463760376</t>
   </si>
   <si>
     <t xml:space="preserve">6.07750606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14788579940796</t>
+    <t xml:space="preserve">6.1478853225708</t>
   </si>
   <si>
     <t xml:space="preserve">6.06922578811646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05266618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9698657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10648536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98642683029175</t>
+    <t xml:space="preserve">6.0526647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96986627578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10648584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">5.92432641983032</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">6.03610610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95744657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00298595428467</t>
+    <t xml:space="preserve">5.95744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00298547744751</t>
   </si>
   <si>
     <t xml:space="preserve">5.88706636428833</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">5.9326057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82496643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81668567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84980630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85808658599854</t>
+    <t xml:space="preserve">5.8249659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81668615341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8498067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85808610916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.75872611999512</t>
@@ -410,37 +410,37 @@
     <t xml:space="preserve">5.90362596511841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93674659729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87878656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92018604278564</t>
+    <t xml:space="preserve">5.93674612045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9201865196228</t>
   </si>
   <si>
     <t xml:space="preserve">6.06094551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42526483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45010471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53290462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5494647026062</t>
+    <t xml:space="preserve">6.42526578903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45010423660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53290510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54946422576904</t>
   </si>
   <si>
     <t xml:space="preserve">6.45424509048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29278564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45838499069214</t>
+    <t xml:space="preserve">6.29278516769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4583854675293</t>
   </si>
   <si>
     <t xml:space="preserve">6.38386487960815</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">6.40042495727539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2348256111145</t>
+    <t xml:space="preserve">6.23482513427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.33832550048828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37972450256348</t>
+    <t xml:space="preserve">6.37972497940063</t>
   </si>
   <si>
     <t xml:space="preserve">6.40870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37558507919312</t>
+    <t xml:space="preserve">6.37558460235596</t>
   </si>
   <si>
     <t xml:space="preserve">6.50806474685669</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">6.34246492385864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49150419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33418464660645</t>
+    <t xml:space="preserve">6.49150514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3341851234436</t>
   </si>
   <si>
     <t xml:space="preserve">6.3714451789856</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">6.30520486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39214515686035</t>
+    <t xml:space="preserve">6.39214468002319</t>
   </si>
   <si>
     <t xml:space="preserve">6.18514490127563</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">5.97400617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01126575469971</t>
+    <t xml:space="preserve">6.01126623153687</t>
   </si>
   <si>
     <t xml:space="preserve">6.01954555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02782583236694</t>
+    <t xml:space="preserve">6.0278263092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.32590484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36730527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28450489044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41284465789795</t>
+    <t xml:space="preserve">6.36730480194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28450536727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41284513473511</t>
   </si>
   <si>
     <t xml:space="preserve">6.24310493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272520065308</t>
+    <t xml:space="preserve">6.17272567749023</t>
   </si>
   <si>
     <t xml:space="preserve">6.69850444793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194437026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72334432601929</t>
+    <t xml:space="preserve">6.68194389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6488242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72334337234497</t>
   </si>
   <si>
     <t xml:space="preserve">6.73990488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03798294067383</t>
+    <t xml:space="preserve">7.03798389434814</t>
   </si>
   <si>
     <t xml:space="preserve">7.20358276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1787428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03384399414062</t>
+    <t xml:space="preserve">7.17874383926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03384351730347</t>
   </si>
   <si>
     <t xml:space="preserve">7.01314353942871</t>
@@ -551,34 +551,34 @@
     <t xml:space="preserve">7.07938385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02142238616943</t>
+    <t xml:space="preserve">7.02142286300659</t>
   </si>
   <si>
     <t xml:space="preserve">7.05454349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20772314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60102272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63414239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59688138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08766412734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44370174407959</t>
+    <t xml:space="preserve">6.98830270767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20772266387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60102224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63414287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59688234329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08766317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44370222091675</t>
   </si>
   <si>
     <t xml:space="preserve">7.4768214225769</t>
@@ -590,112 +590,112 @@
     <t xml:space="preserve">7.43542242050171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27810192108154</t>
+    <t xml:space="preserve">7.2781023979187</t>
   </si>
   <si>
     <t xml:space="preserve">7.17046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10422277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9427638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07110404968262</t>
+    <t xml:space="preserve">7.10422372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94276428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0711030960083</t>
   </si>
   <si>
     <t xml:space="preserve">7.05868339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04212284088135</t>
+    <t xml:space="preserve">7.04212427139282</t>
   </si>
   <si>
     <t xml:space="preserve">7.00486326217651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83512449264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88894319534302</t>
+    <t xml:space="preserve">6.83512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95518350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88894367218018</t>
   </si>
   <si>
     <t xml:space="preserve">6.91378402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932340621948</t>
+    <t xml:space="preserve">6.95932292938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.22842264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54306221008301</t>
+    <t xml:space="preserve">7.26982307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54306125640869</t>
   </si>
   <si>
     <t xml:space="preserve">7.50994205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64242219924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90324068069458</t>
+    <t xml:space="preserve">7.64242124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6921010017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90324115753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.00674152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03158092498779</t>
+    <t xml:space="preserve">8.03158187866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.0729808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85356140136719</t>
+    <t xml:space="preserve">7.85356092453003</t>
   </si>
   <si>
     <t xml:space="preserve">8.25928115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19304180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25514030456543</t>
+    <t xml:space="preserve">8.19304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25514125823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.48697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49526119232178</t>
+    <t xml:space="preserve">8.49525928497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.3627815246582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39589977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43729972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62773990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63602066040039</t>
+    <t xml:space="preserve">8.39590072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43729877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63602161407471</t>
   </si>
   <si>
     <t xml:space="preserve">8.59461975097656</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">8.52838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3296594619751</t>
+    <t xml:space="preserve">8.32966041564941</t>
   </si>
   <si>
     <t xml:space="preserve">8.03986072540283</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">8.17648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51182079315186</t>
+    <t xml:space="preserve">8.51181983947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.6028995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77677917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85958003997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3729362487793</t>
+    <t xml:space="preserve">8.776780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85957908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37293720245361</t>
   </si>
   <si>
     <t xml:space="preserve">9.4474573135376</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">10.1595363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4907360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894559860229</t>
+    <t xml:space="preserve">10.4907350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894550323486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7556943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2920160293579</t>
+    <t xml:space="preserve">10.2920169830322</t>
   </si>
   <si>
     <t xml:space="preserve">10.3499755859375</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">10.5790328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.460262298584</t>
+    <t xml:space="preserve">10.4602613449097</t>
   </si>
   <si>
     <t xml:space="preserve">9.87489604949951</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">10.0530500411987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1718196868896</t>
+    <t xml:space="preserve">10.1718187332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.1803035736084</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">10.7062864303589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6638689041138</t>
+    <t xml:space="preserve">10.6638679504395</t>
   </si>
   <si>
     <t xml:space="preserve">10.6129665374756</t>
@@ -800,13 +800,10 @@
     <t xml:space="preserve">10.4772291183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3499765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7232551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.646900177002</t>
+    <t xml:space="preserve">10.7232532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6469020843506</t>
   </si>
   <si>
     <t xml:space="preserve">10.6299343109131</t>
@@ -818,28 +815,28 @@
     <t xml:space="preserve">10.4178438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3584585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2736225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04456615448</t>
+    <t xml:space="preserve">10.3584594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2736234664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3075561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0445671081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.90882968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83247661590576</t>
+    <t xml:space="preserve">9.83247756958008</t>
   </si>
   <si>
     <t xml:space="preserve">9.78157520294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61190414428711</t>
+    <t xml:space="preserve">9.61190319061279</t>
   </si>
   <si>
     <t xml:space="preserve">9.43374824523926</t>
@@ -848,10 +845,10 @@
     <t xml:space="preserve">9.1028881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16227245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17924118041992</t>
+    <t xml:space="preserve">9.16227340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17924022674561</t>
   </si>
   <si>
     <t xml:space="preserve">9.19620800018311</t>
@@ -866,22 +863,22 @@
     <t xml:space="preserve">9.33194446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21317577362061</t>
+    <t xml:space="preserve">9.21317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.37436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90034580230713</t>
+    <t xml:space="preserve">9.68825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90034484863281</t>
   </si>
   <si>
     <t xml:space="preserve">9.84944343566895</t>
@@ -890,43 +887,43 @@
     <t xml:space="preserve">10.2227230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2312059402466</t>
+    <t xml:space="preserve">10.2312049865723</t>
   </si>
   <si>
     <t xml:space="preserve">10.2821063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2566566467285</t>
+    <t xml:space="preserve">10.2566556930542</t>
   </si>
   <si>
     <t xml:space="preserve">10.2905902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.366943359375</t>
+    <t xml:space="preserve">10.3669424057007</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.019115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9682149887085</t>
+    <t xml:space="preserve">10.0191164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821594238281</t>
   </si>
   <si>
     <t xml:space="preserve">9.89186191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8579273223877</t>
+    <t xml:space="preserve">9.85792827606201</t>
   </si>
   <si>
     <t xml:space="preserve">9.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51010036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70522308349609</t>
+    <t xml:space="preserve">9.51009941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70522212982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919799804688</t>
@@ -938,7 +935,7 @@
     <t xml:space="preserve">9.56948566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66280555725098</t>
+    <t xml:space="preserve">9.66280651092529</t>
   </si>
   <si>
     <t xml:space="preserve">9.50161647796631</t>
@@ -947,46 +944,46 @@
     <t xml:space="preserve">9.39133071899414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28104305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38284778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45071601867676</t>
+    <t xml:space="preserve">9.28104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38284683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45071697235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.51858329772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27256107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20469284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58645248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49313354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84096145629883</t>
+    <t xml:space="preserve">9.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58645439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84096050262451</t>
   </si>
   <si>
     <t xml:space="preserve">9.67977333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64583778381348</t>
+    <t xml:space="preserve">9.64583683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.63735389709473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75612449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82399368286133</t>
+    <t xml:space="preserve">9.75612545013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82399272918701</t>
   </si>
   <si>
     <t xml:space="preserve">9.77309226989746</t>
@@ -998,19 +995,19 @@
     <t xml:space="preserve">9.69673919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67128944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62887096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79005813598633</t>
+    <t xml:space="preserve">9.67128849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62887001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79005718231201</t>
   </si>
   <si>
     <t xml:space="preserve">9.73067378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47616767883301</t>
+    <t xml:space="preserve">9.47616672515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.13682270050049</t>
@@ -1019,7 +1016,7 @@
     <t xml:space="preserve">9.00108528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72112846374512</t>
+    <t xml:space="preserve">8.7211275100708</t>
   </si>
   <si>
     <t xml:space="preserve">8.59387302398682</t>
@@ -1028,22 +1025,22 @@
     <t xml:space="preserve">8.07637596130371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32663917541504</t>
+    <t xml:space="preserve">8.32664012908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.10182476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12303447723389</t>
+    <t xml:space="preserve">8.12303352355957</t>
   </si>
   <si>
     <t xml:space="preserve">8.62780857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33088111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34360694885254</t>
+    <t xml:space="preserve">8.33088207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34360790252686</t>
   </si>
   <si>
     <t xml:space="preserve">8.19514465332031</t>
@@ -1052,13 +1049,13 @@
     <t xml:space="preserve">8.27149677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37329959869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31391525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29270648956299</t>
+    <t xml:space="preserve">8.37329864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31391429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29270553588867</t>
   </si>
   <si>
     <t xml:space="preserve">8.09334182739258</t>
@@ -1070,10 +1067,10 @@
     <t xml:space="preserve">7.85155916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82610940933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80065727233887</t>
+    <t xml:space="preserve">7.82610845565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80065774917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.91094398498535</t>
@@ -1082,10 +1079,10 @@
     <t xml:space="preserve">7.85580110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97881317138672</t>
+    <t xml:space="preserve">7.95760536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9788122177124</t>
   </si>
   <si>
     <t xml:space="preserve">8.02123069763184</t>
@@ -1094,7 +1091,7 @@
     <t xml:space="preserve">8.0127477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452995300293</t>
+    <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.16121101379395</t>
@@ -1106,46 +1103,46 @@
     <t xml:space="preserve">8.05092430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08061504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17393493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2248363494873</t>
+    <t xml:space="preserve">8.08061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17393589019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22483730316162</t>
   </si>
   <si>
     <t xml:space="preserve">8.2884635925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42420196533203</t>
+    <t xml:space="preserve">8.42420101165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.56842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51752090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7380952835083</t>
+    <t xml:space="preserve">8.51752185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73809432983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.5514554977417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48358631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50055313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
+    <t xml:space="preserve">8.48358535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50055408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.58538913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661758422852</t>
+    <t xml:space="preserve">8.46661853790283</t>
   </si>
   <si>
     <t xml:space="preserve">8.45813655853271</t>
@@ -1154,28 +1151,28 @@
     <t xml:space="preserve">8.40723323822021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3817834854126</t>
+    <t xml:space="preserve">8.38178443908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.20362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01698970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.991539478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91518592834473</t>
+    <t xml:space="preserve">8.01698780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99153757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91518688201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.12727546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97457075119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3223991394043</t>
+    <t xml:space="preserve">7.9745717048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32240009307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.90776634216309</t>
@@ -1187,34 +1184,34 @@
     <t xml:space="preserve">8.82293033599854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77202796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61932468414307</t>
+    <t xml:space="preserve">8.77202892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61932277679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.60235691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83989715576172</t>
+    <t xml:space="preserve">8.8398962020874</t>
   </si>
   <si>
     <t xml:space="preserve">8.94169998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36588001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24710941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12833881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11137199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0435037612915</t>
+    <t xml:space="preserve">9.36587905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24710845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12833976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11137104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04350280761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.09440517425537</t>
@@ -1226,31 +1223,31 @@
     <t xml:space="preserve">9.41678142547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5705480575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6723508834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.621452331543</t>
+    <t xml:space="preserve">10.2142381668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6723518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6214513778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.9607934951782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4358749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680057525635</t>
+    <t xml:space="preserve">11.4358730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680067062378</t>
   </si>
   <si>
     <t xml:space="preserve">11.4698095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.543098449707</t>
+    <t xml:space="preserve">11.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729009628296</t>
@@ -1262,13 +1259,13 @@
     <t xml:space="preserve">11.4148416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3049077987671</t>
+    <t xml:space="preserve">11.3049068450928</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865839004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9567813873291</t>
+    <t xml:space="preserve">10.9567823410034</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834934234619</t>
@@ -1286,19 +1283,19 @@
     <t xml:space="preserve">10.6453018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4804010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1689195632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98569679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058985710144</t>
+    <t xml:space="preserve">10.4804000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1689205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0589866638184</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788534164429</t>
@@ -1310,7 +1307,7 @@
     <t xml:space="preserve">10.2238864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2605314254761</t>
+    <t xml:space="preserve">10.2605323791504</t>
   </si>
   <si>
     <t xml:space="preserve">10.1322746276855</t>
@@ -1325,31 +1322,31 @@
     <t xml:space="preserve">10.4437551498413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3338222503662</t>
+    <t xml:space="preserve">10.3338212966919</t>
   </si>
   <si>
     <t xml:space="preserve">10.2055654525757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0956315994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78414916992188</t>
+    <t xml:space="preserve">10.095630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78415107727051</t>
   </si>
   <si>
     <t xml:space="preserve">9.80247211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71086120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67421531677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72918224334717</t>
+    <t xml:space="preserve">9.71086025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47267055511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67421627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72918319702148</t>
   </si>
   <si>
     <t xml:space="preserve">9.65589332580566</t>
@@ -1361,16 +1358,16 @@
     <t xml:space="preserve">9.74750518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69253826141357</t>
+    <t xml:space="preserve">9.69253730773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.56428050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30776786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25280094146729</t>
+    <t xml:space="preserve">9.30776691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2528018951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.3627347946167</t>
@@ -1385,10 +1382,10 @@
     <t xml:space="preserve">9.06957626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08790016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93215942382812</t>
+    <t xml:space="preserve">9.08789920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93215847015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.8771915435791</t>
@@ -1397,13 +1394,13 @@
     <t xml:space="preserve">9.03293228149414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95964241027832</t>
+    <t xml:space="preserve">8.95964336395264</t>
   </si>
   <si>
     <t xml:space="preserve">8.97796535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94132137298584</t>
+    <t xml:space="preserve">8.94132041931152</t>
   </si>
   <si>
     <t xml:space="preserve">8.51990699768066</t>
@@ -1421,25 +1418,25 @@
     <t xml:space="preserve">8.63900089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65732383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62984085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35500431060791</t>
+    <t xml:space="preserve">8.65732192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35500335693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.44661617279053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39938068389893</t>
+    <t xml:space="preserve">9.39937973022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.3810567855835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19783401489258</t>
+    <t xml:space="preserve">9.19783496856689</t>
   </si>
   <si>
     <t xml:space="preserve">9.00544834136963</t>
@@ -1451,39 +1448,42 @@
     <t xml:space="preserve">9.12454509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04209423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96880435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99628639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86803150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7855806350708</t>
+    <t xml:space="preserve">9.04209327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99628734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88635349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8680305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78557968139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.83138656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84054756164551</t>
+    <t xml:space="preserve">8.84054851531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.77641868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71228981018066</t>
+    <t xml:space="preserve">8.71229076385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.59319591522217</t>
   </si>
   <si>
+    <t xml:space="preserve">8.60235595703125</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.40997219085693</t>
   </si>
   <si>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">8.24506950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74120426177979</t>
+    <t xml:space="preserve">7.74120473861694</t>
   </si>
   <si>
     <t xml:space="preserve">7.70455980300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68623876571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55798101425171</t>
+    <t xml:space="preserve">7.68623828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55798053741455</t>
   </si>
   <si>
     <t xml:space="preserve">7.59462547302246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4938530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08159971237183</t>
+    <t xml:space="preserve">7.49385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39307928085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40224123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08159923553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.10908317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38391828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16404962539673</t>
+    <t xml:space="preserve">7.38391876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16405010223389</t>
   </si>
   <si>
     <t xml:space="preserve">7.30146789550781</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">7.76868724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69539833068848</t>
+    <t xml:space="preserve">7.80533361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69539880752563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45720815658569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58546447753906</t>
+    <t xml:space="preserve">7.5854640007019</t>
   </si>
   <si>
     <t xml:space="preserve">7.56714248657227</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">7.34727382659912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5121750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22817850112915</t>
+    <t xml:space="preserve">7.51217460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22817802429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.14572763442993</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">7.06327676773071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05411577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43888568878174</t>
+    <t xml:space="preserve">7.05411529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43888521194458</t>
   </si>
   <si>
     <t xml:space="preserve">7.53965854644775</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">7.31062889099121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24650001525879</t>
+    <t xml:space="preserve">7.24650049209595</t>
   </si>
   <si>
     <t xml:space="preserve">7.2739839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35643482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67707586288452</t>
+    <t xml:space="preserve">7.35643434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67707681655884</t>
   </si>
   <si>
     <t xml:space="preserve">7.72288227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86946105957031</t>
+    <t xml:space="preserve">7.86946201324463</t>
   </si>
   <si>
     <t xml:space="preserve">8.04352378845215</t>
@@ -1628,22 +1628,22 @@
     <t xml:space="preserve">8.37332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3916482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49242210388184</t>
+    <t xml:space="preserve">8.39164924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49242305755615</t>
   </si>
   <si>
     <t xml:space="preserve">8.40081119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34584331512451</t>
+    <t xml:space="preserve">8.3458423614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.33668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02377128601074</t>
+    <t xml:space="preserve">9.02377223968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.13370609283447</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">8.73977470397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10622119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05125522613525</t>
+    <t xml:space="preserve">9.10622215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05125617980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.7947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66648387908936</t>
+    <t xml:space="preserve">8.66648578643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.8588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01461029052734</t>
+    <t xml:space="preserve">9.01460933685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.91383647918701</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">8.84970951080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8039026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.813063621521</t>
+    <t xml:space="preserve">8.80390071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81306457519531</t>
   </si>
   <si>
     <t xml:space="preserve">8.58403396606445</t>
@@ -1694,43 +1694,43 @@
     <t xml:space="preserve">8.25423240661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38248729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27255439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12597560882568</t>
+    <t xml:space="preserve">8.38248825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27255344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12597465515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.26339340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23590850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43745422363281</t>
+    <t xml:space="preserve">8.2359094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43745517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.45577716827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47410106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50158309936523</t>
+    <t xml:space="preserve">8.47409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50158214569092</t>
   </si>
   <si>
     <t xml:space="preserve">8.42829322814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46493816375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51074409484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822708129883</t>
+    <t xml:space="preserve">8.46493911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51074314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822803497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.62067890167236</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">8.54738998413086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21530723571777</t>
+    <t xml:space="preserve">9.21530628204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.70226860046387</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">8.40219211578369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18923091888428</t>
+    <t xml:space="preserve">8.18923187255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.89883375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06339263916016</t>
+    <t xml:space="preserve">8.06339168548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.98595333099365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29571056365967</t>
+    <t xml:space="preserve">8.29570960998535</t>
   </si>
   <si>
     <t xml:space="preserve">8.09243202209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03435325622559</t>
+    <t xml:space="preserve">8.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.05371189117432</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">8.10211181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15051174163818</t>
+    <t xml:space="preserve">8.12147235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15051078796387</t>
   </si>
   <si>
     <t xml:space="preserve">7.97627258300781</t>
@@ -1793,40 +1793,40 @@
     <t xml:space="preserve">7.96659278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16987228393555</t>
+    <t xml:space="preserve">8.16987133026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.24731159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25699043273926</t>
+    <t xml:space="preserve">8.25699138641357</t>
   </si>
   <si>
     <t xml:space="preserve">8.14083194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92787313461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07307243347168</t>
+    <t xml:space="preserve">7.9278736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.073073387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.0827522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93755340576172</t>
+    <t xml:space="preserve">7.90851402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93755292892456</t>
   </si>
   <si>
     <t xml:space="preserve">8.17955112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11179161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13115119934082</t>
+    <t xml:space="preserve">8.11179256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13115215301514</t>
   </si>
   <si>
     <t xml:space="preserve">8.04403305053711</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">8.20859050750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16019153594971</t>
+    <t xml:space="preserve">8.16019248962402</t>
   </si>
   <si>
     <t xml:space="preserve">7.99563312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0053129196167</t>
+    <t xml:space="preserve">8.00531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">8.01499271392822</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">7.87947416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91819381713867</t>
+    <t xml:space="preserve">7.91819334030151</t>
   </si>
   <si>
     <t xml:space="preserve">7.95691394805908</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">8.44091033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33443069458008</t>
+    <t xml:space="preserve">8.33442974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.28603172302246</t>
@@ -1877,25 +1877,25 @@
     <t xml:space="preserve">8.45059013366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52803039550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78938770294189</t>
+    <t xml:space="preserve">8.52803134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78938865661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.14754676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13786697387695</t>
+    <t xml:space="preserve">9.13786602020264</t>
   </si>
   <si>
     <t xml:space="preserve">9.51538372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3895435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48634433746338</t>
+    <t xml:space="preserve">9.38954448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48634338378906</t>
   </si>
   <si>
     <t xml:space="preserve">9.45730400085449</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">9.44762516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55410385131836</t>
+    <t xml:space="preserve">9.55410289764404</t>
   </si>
   <si>
     <t xml:space="preserve">9.53474426269531</t>
@@ -1913,28 +1913,28 @@
     <t xml:space="preserve">9.52506446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0284204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3188190460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0477819442749</t>
+    <t xml:space="preserve">10.0284194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3188180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.0671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98970031738281</t>
+    <t xml:space="preserve">9.98970127105713</t>
   </si>
   <si>
     <t xml:space="preserve">9.95098209381104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60250377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67994213104248</t>
+    <t xml:space="preserve">9.60250282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6799430847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.61218357086182</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">9.50570297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58314323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46698379516602</t>
+    <t xml:space="preserve">9.58314228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46698474884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.87354183197021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40890502929688</t>
+    <t xml:space="preserve">9.40890598297119</t>
   </si>
   <si>
     <t xml:space="preserve">9.35082530975342</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">9.19594573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16690731048584</t>
+    <t xml:space="preserve">9.16690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.0797872543335</t>
@@ -2009,34 +2009,34 @@
     <t xml:space="preserve">8.92490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9442663192749</t>
+    <t xml:space="preserve">8.94426727294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.85714721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72162914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77002906799316</t>
+    <t xml:space="preserve">8.72162818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">8.93458652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99266624450684</t>
+    <t xml:space="preserve">8.99266719818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.96362686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15722560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05074691772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97330665588379</t>
+    <t xml:space="preserve">9.1572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05074787139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97330760955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.79906845092773</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">7.60843515396118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53099584579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61811494827271</t>
+    <t xml:space="preserve">7.53099632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61811542510986</t>
   </si>
   <si>
     <t xml:space="preserve">7.34707641601562</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">6.58236169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44684171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14004945755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47884702682495</t>
+    <t xml:space="preserve">6.44684219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14004993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47884750366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.53989362716675</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.52053308486938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83997106552124</t>
+    <t xml:space="preserve">4.8399715423584</t>
   </si>
   <si>
     <t xml:space="preserve">5.13037014007568</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">5.51756715774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04028415679932</t>
+    <t xml:space="preserve">6.04028463363647</t>
   </si>
   <si>
     <t xml:space="preserve">6.00156450271606</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">6.22420310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42748212814331</t>
+    <t xml:space="preserve">6.42748260498047</t>
   </si>
   <si>
     <t xml:space="preserve">6.5339617729187</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">7.67619514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55035591125488</t>
+    <t xml:space="preserve">7.55035543441772</t>
   </si>
   <si>
     <t xml:space="preserve">7.58907556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71491432189941</t>
+    <t xml:space="preserve">7.71491384506226</t>
   </si>
   <si>
     <t xml:space="preserve">7.63747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3954758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43419599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19219779968262</t>
+    <t xml:space="preserve">7.39547634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43419551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19219732284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.40515613555908</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">7.44387626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49227619171143</t>
+    <t xml:space="preserve">7.49227571487427</t>
   </si>
   <si>
     <t xml:space="preserve">7.4632363319397</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">7.69555425643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85043382644653</t>
+    <t xml:space="preserve">7.85043334960938</t>
   </si>
   <si>
     <t xml:space="preserve">7.32771682739258</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">7.56003522872925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59875535964966</t>
+    <t xml:space="preserve">7.5987548828125</t>
   </si>
   <si>
     <t xml:space="preserve">7.65683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50195550918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31803703308105</t>
+    <t xml:space="preserve">7.50195598602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3180365562439</t>
   </si>
   <si>
     <t xml:space="preserve">7.30835723876953</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">7.5406756401062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51163625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38579607009888</t>
+    <t xml:space="preserve">7.51163673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38579654693604</t>
   </si>
   <si>
     <t xml:space="preserve">7.3373966217041</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">7.45355606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64715480804443</t>
+    <t xml:space="preserve">7.64715528488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.57939529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41483640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2599573135376</t>
+    <t xml:space="preserve">7.41483592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29867649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25995779037476</t>
   </si>
   <si>
     <t xml:space="preserve">7.47291612625122</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">7.36643695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26963710784912</t>
+    <t xml:space="preserve">7.26963758468628</t>
   </si>
   <si>
     <t xml:space="preserve">7.21155738830566</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">7.24059724807739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20187759399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18251800537109</t>
+    <t xml:space="preserve">7.2018780708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18251752853394</t>
   </si>
   <si>
     <t xml:space="preserve">7.13411808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15347814559937</t>
+    <t xml:space="preserve">7.15347766876221</t>
   </si>
   <si>
     <t xml:space="preserve">7.62779521942139</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">7.02763843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0760383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01795864105225</t>
+    <t xml:space="preserve">7.07603788375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01795816421509</t>
   </si>
   <si>
     <t xml:space="preserve">6.96955871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89211988449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97923851013184</t>
+    <t xml:space="preserve">6.89211940765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97923898696899</t>
   </si>
   <si>
     <t xml:space="preserve">7.06635856628418</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">7.0566782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8727593421936</t>
+    <t xml:space="preserve">6.87275981903076</t>
   </si>
   <si>
     <t xml:space="preserve">6.94051933288574</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">6.80500030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77596044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76628017425537</t>
+    <t xml:space="preserve">6.77595996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76627969741821</t>
   </si>
   <si>
     <t xml:space="preserve">6.83403968811035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564023971558</t>
+    <t xml:space="preserve">6.78564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">6.8146800994873</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">6.7372407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63076114654541</t>
+    <t xml:space="preserve">6.63076066970825</t>
   </si>
   <si>
     <t xml:space="preserve">6.67916059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93083906173706</t>
+    <t xml:space="preserve">6.9308385848999</t>
   </si>
   <si>
     <t xml:space="preserve">7.34717988967896</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">7.14282083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22067213058472</t>
+    <t xml:space="preserve">7.22067165374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.28879117965698</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">7.17201519012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18174600601196</t>
+    <t xml:space="preserve">7.18174648284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.43476152420044</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">7.50288152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49315023422241</t>
+    <t xml:space="preserve">7.49314975738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.59046363830566</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">7.46395635604858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70724010467529</t>
+    <t xml:space="preserve">7.70723962783813</t>
   </si>
   <si>
     <t xml:space="preserve">7.83374786376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06730079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03810691833496</t>
+    <t xml:space="preserve">8.06729984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03810596466064</t>
   </si>
   <si>
     <t xml:space="preserve">8.08676338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0089111328125</t>
+    <t xml:space="preserve">8.00891208648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.0964937210083</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">8.12568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19380760192871</t>
+    <t xml:space="preserve">8.19380855560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.13541889190674</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">7.78509092330933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60019540786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57100105285645</t>
+    <t xml:space="preserve">7.60019493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5710015296936</t>
   </si>
   <si>
     <t xml:space="preserve">7.72670269012451</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">7.82401657104492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64885234832764</t>
+    <t xml:space="preserve">7.64885187149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.54180669784546</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">7.63912057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6293888092041</t>
+    <t xml:space="preserve">7.62938928604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.56126928329468</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">7.8434796333313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80455446243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79482269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01864337921143</t>
+    <t xml:space="preserve">7.8045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79482221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01864433288574</t>
   </si>
   <si>
     <t xml:space="preserve">7.94079303741455</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">8.2716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07703304290771</t>
+    <t xml:space="preserve">8.0770320892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.4468240737915</t>
@@ -2567,22 +2567,22 @@
     <t xml:space="preserve">8.36897373199463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5344066619873</t>
+    <t xml:space="preserve">8.34950923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53440570831299</t>
   </si>
   <si>
     <t xml:space="preserve">8.74849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67064380645752</t>
+    <t xml:space="preserve">8.67064476013184</t>
   </si>
   <si>
     <t xml:space="preserve">8.68037605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81661605834961</t>
+    <t xml:space="preserve">8.81661701202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.02097511291504</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">9.10855674743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04043674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75822830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80688381195068</t>
+    <t xml:space="preserve">9.04043579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75822734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">8.57333183288574</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">8.55386924743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40789794921875</t>
+    <t xml:space="preserve">8.40789890289307</t>
   </si>
   <si>
     <t xml:space="preserve">8.51494312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24246501922607</t>
+    <t xml:space="preserve">8.24246406555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.30085277557373</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">8.32031536102295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43709278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46628665924072</t>
+    <t xml:space="preserve">8.43709182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46628570556641</t>
   </si>
   <si>
     <t xml:space="preserve">8.4565544128418</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">8.23273372650146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17434597015381</t>
+    <t xml:space="preserve">8.17434501647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.14515113830566</t>
@@ -2651,19 +2651,19 @@
     <t xml:space="preserve">8.20353984832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25219631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22300148010254</t>
+    <t xml:space="preserve">8.25219535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22300243377686</t>
   </si>
   <si>
     <t xml:space="preserve">8.33004760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64145088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58306121826172</t>
+    <t xml:space="preserve">8.64144992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58306217193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.61225700378418</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">8.50521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60252571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83607864379883</t>
+    <t xml:space="preserve">8.60252666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83607769012451</t>
   </si>
   <si>
     <t xml:space="preserve">8.70957088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84581089019775</t>
+    <t xml:space="preserve">8.84580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.01124286651611</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">9.92599105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75082588195801</t>
+    <t xml:space="preserve">9.75082683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.88706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3152465820312</t>
+    <t xml:space="preserve">10.3152456283569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3541707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3736333847046</t>
+    <t xml:space="preserve">10.3736343383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.77028846740723</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">9.11828708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24479579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93339252471924</t>
+    <t xml:space="preserve">9.24479484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93339157104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.12801933288574</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">9.19613838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36157131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62431907653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57566165924072</t>
+    <t xml:space="preserve">9.361572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62431812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57566261291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.53673648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82867813110352</t>
+    <t xml:space="preserve">9.8286771774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.86760330200195</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">9.67297458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61458683013916</t>
+    <t xml:space="preserve">9.61458778381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.59512424468994</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">9.1864070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17667579650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21560096740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23506450653076</t>
+    <t xml:space="preserve">9.17667675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21560192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23506355285645</t>
   </si>
   <si>
     <t xml:space="preserve">9.20587062835693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0015115737915</t>
+    <t xml:space="preserve">9.00151252746582</t>
   </si>
   <si>
     <t xml:space="preserve">8.98204803466797</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">8.38843536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76795768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41762924194336</t>
+    <t xml:space="preserve">8.76795864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41763019561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.28139019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37870311737061</t>
+    <t xml:space="preserve">8.37870407104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.71930122375488</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">9.03070545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42969131469727</t>
+    <t xml:space="preserve">9.42969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.49781131744385</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">9.66324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98437881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51727390289307</t>
+    <t xml:space="preserve">9.98437976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.47834777832031</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.5561990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4491548538208</t>
+    <t xml:space="preserve">9.44915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31291484832764</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">9.28372097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73136425018311</t>
+    <t xml:space="preserve">9.73136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">10.1206178665161</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">10.0038423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1595430374146</t>
+    <t xml:space="preserve">10.1595439910889</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816926956177</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">10.1790065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.02330493927</t>
+    <t xml:space="preserve">10.0233039855957</t>
   </si>
   <si>
     <t xml:space="preserve">10.0427665710449</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">9.22533226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33237838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25452613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40049648284912</t>
+    <t xml:space="preserve">9.33237743377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25452709197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40049743652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.48807907104492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6340503692627</t>
+    <t xml:space="preserve">9.63404941558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3347072601318</t>
+    <t xml:space="preserve">10.3347082138062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8018140792847</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">11.191068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2689199447632</t>
+    <t xml:space="preserve">11.2689189910889</t>
   </si>
   <si>
     <t xml:space="preserve">11.5803232192993</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">11.4246206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4440841674805</t>
+    <t xml:space="preserve">11.4440832138062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4051580429077</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">11.6192474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4830093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3662328720093</t>
+    <t xml:space="preserve">11.4830083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3662338256836</t>
   </si>
   <si>
     <t xml:space="preserve">11.638710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0668907165527</t>
+    <t xml:space="preserve">12.0668897628784</t>
   </si>
   <si>
     <t xml:space="preserve">12.3199062347412</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">12.5729217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4756088256836</t>
+    <t xml:space="preserve">12.4756078720093</t>
   </si>
   <si>
     <t xml:space="preserve">12.1836681365967</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">12.3588314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6970996856689</t>
+    <t xml:space="preserve">11.6970987319946</t>
   </si>
   <si>
     <t xml:space="preserve">11.2299928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8991279602051</t>
+    <t xml:space="preserve">10.8991270065308</t>
   </si>
   <si>
     <t xml:space="preserve">10.8407392501831</t>
@@ -3047,19 +3047,19 @@
     <t xml:space="preserve">10.7045001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0159034729004</t>
+    <t xml:space="preserve">11.0159025192261</t>
   </si>
   <si>
     <t xml:space="preserve">10.8796644210815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7434253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9575147628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.198468208313</t>
+    <t xml:space="preserve">10.743426322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9575157165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1984691619873</t>
   </si>
   <si>
     <t xml:space="preserve">10.6071863174438</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">10.9380521774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8602018356323</t>
+    <t xml:space="preserve">10.860200881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.6266489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.91858959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2105321884155</t>
+    <t xml:space="preserve">10.9185905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2105312347412</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219345092773</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">11.8528003692627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1252784729004</t>
+    <t xml:space="preserve">11.8917264938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1252794265747</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058158874512</t>
@@ -3113,31 +3113,31 @@
     <t xml:space="preserve">12.5339965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6507730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8259382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8843240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5923833847046</t>
+    <t xml:space="preserve">12.6507720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8843250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5923843383789</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8648633956909</t>
+    <t xml:space="preserve">12.7091617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8648624420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.5145330429077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3977565765381</t>
+    <t xml:space="preserve">12.3977575302124</t>
   </si>
   <si>
     <t xml:space="preserve">12.4366817474365</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">12.2615184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2809810638428</t>
+    <t xml:space="preserve">12.2809801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447410583496</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">12.5534591674805</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4950704574585</t>
+    <t xml:space="preserve">12.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7870121002197</t>
+    <t xml:space="preserve">12.787013053894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2225923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1762657165527</t>
+    <t xml:space="preserve">13.1762666702271</t>
   </si>
   <si>
     <t xml:space="preserve">12.962176322937</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">12.8453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594911575317</t>
+    <t xml:space="preserve">13.0594902038574</t>
   </si>
   <si>
     <t xml:space="preserve">12.9427137374878</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">13.0789518356323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4487447738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4682064056396</t>
+    <t xml:space="preserve">13.4487438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.468207359314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520887374878</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">13.9353122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9742374420166</t>
+    <t xml:space="preserve">13.9742383956909</t>
   </si>
   <si>
     <t xml:space="preserve">14.3051042556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616509437561</t>
+    <t xml:space="preserve">14.6165084838867</t>
   </si>
   <si>
     <t xml:space="preserve">14.7527465820312</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">15.1809272766113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9473733901978</t>
+    <t xml:space="preserve">14.9473743438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.9279127120972</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">17.2245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5359153747559</t>
+    <t xml:space="preserve">17.5359172821045</t>
   </si>
   <si>
     <t xml:space="preserve">17.4191417694092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.788932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6137676239014</t>
+    <t xml:space="preserve">17.7889347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.61376953125</t>
   </si>
   <si>
     <t xml:space="preserve">17.7694702148438</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">18.6063671112061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0345478057861</t>
+    <t xml:space="preserve">19.0345458984375</t>
   </si>
   <si>
     <t xml:space="preserve">18.0419502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.003023147583</t>
+    <t xml:space="preserve">18.0030250549316</t>
   </si>
   <si>
     <t xml:space="preserve">18.5479774475098</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">19.8519821166992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7546672821045</t>
+    <t xml:space="preserve">19.7546653747559</t>
   </si>
   <si>
     <t xml:space="preserve">19.5113830566406</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">18.7036800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1707859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8009929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5090522766113</t>
+    <t xml:space="preserve">18.898307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1707878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8009948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.50905418396</t>
   </si>
   <si>
     <t xml:space="preserve">18.8788452148438</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">18.9761581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8593826293945</t>
+    <t xml:space="preserve">18.8593807220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.5869064331055</t>
@@ -3356,19 +3356,19 @@
     <t xml:space="preserve">18.6452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4701290130615</t>
+    <t xml:space="preserve">18.4701271057129</t>
   </si>
   <si>
     <t xml:space="preserve">18.3144264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2486381530762</t>
+    <t xml:space="preserve">19.2486362457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.0540103912354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1513233184814</t>
+    <t xml:space="preserve">19.1513252258301</t>
   </si>
   <si>
     <t xml:space="preserve">18.9177703857422</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">18.9956226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7231426239014</t>
+    <t xml:space="preserve">18.72314453125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9392547607422</t>
@@ -14460,7 +14460,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14486,7 +14486,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14512,7 +14512,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14538,7 +14538,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14564,7 +14564,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G370" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14590,7 +14590,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14616,7 +14616,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14668,7 +14668,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14694,7 +14694,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G375" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14746,7 +14746,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14772,7 +14772,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14798,7 +14798,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14824,7 +14824,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14850,7 +14850,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14876,7 +14876,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G382" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14902,7 +14902,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14928,7 +14928,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14954,7 +14954,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14980,7 +14980,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15006,7 +15006,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15032,7 +15032,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15058,7 +15058,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15084,7 +15084,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15110,7 +15110,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15136,7 +15136,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15162,7 +15162,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15188,7 +15188,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15214,7 +15214,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15240,7 +15240,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15266,7 +15266,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15292,7 +15292,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15318,7 +15318,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G399" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15344,7 +15344,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15370,7 +15370,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G401" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15422,7 +15422,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15448,7 +15448,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G404" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15474,7 +15474,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15500,7 +15500,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15526,7 +15526,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G407" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15552,7 +15552,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15604,7 +15604,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15630,7 +15630,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15656,7 +15656,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G412" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15682,7 +15682,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G413" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15708,7 +15708,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15734,7 +15734,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15760,7 +15760,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15786,7 +15786,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15838,7 +15838,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G419" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15864,7 +15864,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15890,7 +15890,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15916,7 +15916,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G422" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15942,7 +15942,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G423" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15968,7 +15968,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15994,7 +15994,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G425" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16020,7 +16020,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G426" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16046,7 +16046,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16072,7 +16072,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G428" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16098,7 +16098,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G429" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16124,7 +16124,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16150,7 +16150,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16176,7 +16176,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G432" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16202,7 +16202,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G433" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16228,7 +16228,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16254,7 +16254,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G435" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16280,7 +16280,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G436" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16306,7 +16306,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G437" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16332,7 +16332,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16358,7 +16358,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16384,7 +16384,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G440" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16410,7 +16410,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16436,7 +16436,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16462,7 +16462,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16488,7 +16488,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16514,7 +16514,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16540,7 +16540,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16566,7 +16566,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G447" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16592,7 +16592,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16644,7 +16644,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16670,7 +16670,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16696,7 +16696,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16722,7 +16722,7 @@
         <v>11.2200002670288